--- a/THESIS/Stats rundown THESIS.xlsx
+++ b/THESIS/Stats rundown THESIS.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\serotonin\THESIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2CB4277-8082-4558-A2D9-DEEE737A854D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E20413-2402-483D-A7E1-3E65794703AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
+    <workbookView xWindow="2760" yWindow="3765" windowWidth="31755" windowHeight="15480" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -221,7 +221,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -605,46 +605,46 @@
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -654,10 +654,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
@@ -673,6 +673,36 @@
   <dxfs count="131">
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -710,884 +740,6 @@
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2045,13 +1197,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2065,6 +1210,861 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3208,94 +3208,94 @@
   <autoFilter ref="A1:U11" xr:uid="{2B1EA398-6077-43CD-8151-400DF211F33C}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{DFDC78A7-E47E-494D-9C61-107C2DD6F0AD}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="86"/>
-    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="83"/>
-    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="80"/>
-    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="79"/>
-    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="78"/>
-    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="77"/>
-    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="76"/>
-    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="75"/>
-    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="74"/>
-    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="73"/>
-    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="72"/>
-    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="130"/>
+    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="129"/>
+    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="128"/>
+    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="127"/>
+    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="126"/>
+    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="125"/>
+    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="124"/>
+    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="123"/>
+    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="122"/>
+    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="121"/>
+    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="120"/>
+    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="119"/>
+    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="118"/>
+    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="117"/>
+    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="116"/>
+    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="115"/>
+    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="114"/>
+    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="113"/>
+    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="112"/>
+    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="111"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="112" headerRowBorderDxfId="113" tableBorderDxfId="114">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="110" headerRowBorderDxfId="109" tableBorderDxfId="108">
   <autoFilter ref="A22:U32" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="111" totalsRowDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="110">
+    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="105">
       <calculatedColumnFormula>(B2-B$17)/B$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="109">
+    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="104">
       <calculatedColumnFormula>(C2-C$17)/C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="108">
+    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="103">
       <calculatedColumnFormula>(D2-D$17)/D$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="107">
+    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="102">
       <calculatedColumnFormula>(E2-E$17)/E$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="106">
+    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="101">
       <calculatedColumnFormula>(F2-F$17)/F$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="105">
+    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="100">
       <calculatedColumnFormula>(G2-G$17)/G$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="104">
+    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="99">
       <calculatedColumnFormula>(H2-H$17)/H$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="103">
+    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="98">
       <calculatedColumnFormula>(I2-I$17)/I$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="102">
+    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="97">
       <calculatedColumnFormula>(J2-J$17)/J$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="101">
+    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="96">
       <calculatedColumnFormula>(K2-K$17)/K$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="100">
+    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="95">
       <calculatedColumnFormula>(L2-L$17)/L$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="99">
+    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="94">
       <calculatedColumnFormula>(M2-M$17)/M$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="98">
+    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="93">
       <calculatedColumnFormula>(N2-N$17)/N$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="97">
+    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="92">
       <calculatedColumnFormula>(O2-O$17)/O$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="96">
+    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="91">
       <calculatedColumnFormula>(P2-P$17)/P$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="95">
+    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="90">
       <calculatedColumnFormula>(Q2-Q$17)/Q$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="94">
+    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="89">
       <calculatedColumnFormula>(R2-R$17)/R$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="93">
+    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="88">
       <calculatedColumnFormula>(S2-S$17)/S$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="92">
+    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="87">
       <calculatedColumnFormula>(T2-T$17)/T$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="30">
+    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="85">
       <calculatedColumnFormula>(U2-U$17)/U$19</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3304,29 +3304,29 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="25" dataDxfId="21" headerRowBorderDxfId="27" tableBorderDxfId="28" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
   <autoFilter ref="A77:C87" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="24" totalsRowDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="23" totalsRowDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="79" totalsRowDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="77" totalsRowDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="75" totalsRowDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="16" tableBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="73" headerRowBorderDxfId="72" tableBorderDxfId="71">
   <autoFilter ref="F77:I87" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="69">
       <calculatedColumnFormula>Table32[[#This Row],[best_pearson_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="12">
+    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="68">
       <calculatedColumnFormula>Table32[[#This Row],[best_difference_vector_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="11">
+    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="67">
       <calculatedColumnFormula>Table33[[#This Row],[best_pearson_r]]+Table33[[#This Row],[best_difference_vector_r]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3335,11 +3335,11 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="70" headerRowBorderDxfId="68" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="66" headerRowBorderDxfId="65" tableBorderDxfId="64">
   <autoFilter ref="A50:L60" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="62">
       <calculatedColumnFormula>D2/B$46</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{19814F94-E875-4959-AFE5-7848DB2FC6EC}" name="seed_b_e">
@@ -3366,8 +3366,8 @@
     <tableColumn id="10" xr3:uid="{40D401B7-4651-43DA-A526-6D0D5CEB229D}" name="seed_r_0_pv">
       <calculatedColumnFormula>L2/J$46</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="66"/>
-    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="61"/>
+    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3378,74 +3378,74 @@
   <autoFilter ref="N50:Y60" xr:uid="{7D09C930-E854-4E6C-82B9-35C9655B8B61}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{016F4276-D961-4FD1-B77D-67CC688C159B}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="59">
       <calculatedColumnFormula>Table23[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="65">
+    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="58">
       <calculatedColumnFormula>Table23[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="64">
+    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="57">
       <calculatedColumnFormula>Table23[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="63">
+    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="56">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="62">
+    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="55">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="61">
+    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="54">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="60">
+    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="53">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="59">
+    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="52">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="58">
+    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="51">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="48" headerRowBorderDxfId="47" tableBorderDxfId="46">
   <autoFilter ref="A63:L73" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="44">
       <calculatedColumnFormula>LOG(B51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="52">
+    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="43">
       <calculatedColumnFormula>LOG(C51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="51">
+    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="42">
       <calculatedColumnFormula>LOG(D51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="50">
+    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="41">
       <calculatedColumnFormula>LOG(E51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="49">
+    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="40">
       <calculatedColumnFormula>LOG(F51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="48">
+    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="39">
       <calculatedColumnFormula>LOG(G51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="47">
+    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="38">
       <calculatedColumnFormula>LOG(H51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="46">
+    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="37">
       <calculatedColumnFormula>LOG(I51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="44">
+    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="36">
       <calculatedColumnFormula>LOG(J51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3456,55 +3456,55 @@
   <autoFilter ref="N63:Y73" xr:uid="{2806A620-3E6B-4861-AE70-E4C12B09B013}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00CF6880-3883-432C-B0EF-EBC8FF079300}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="33">
       <calculatedColumnFormula>Table28[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="43">
+    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="32">
       <calculatedColumnFormula>Table28[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="42">
+    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="31">
       <calculatedColumnFormula>Table28[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="41">
+    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="30">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="40">
+    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="29">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="39">
+    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="28">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="38">
+    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="27">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="37">
+    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="26">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="35">
+    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="25">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{197A1E99-7397-485F-8B54-E30877E39C3B}" name="Table12" displayName="Table12" ref="A1:K11" totalsRowShown="0" headerRowDxfId="115" dataDxfId="116" headerRowBorderDxfId="129" tableBorderDxfId="130" totalsRowBorderDxfId="128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{197A1E99-7397-485F-8B54-E30877E39C3B}" name="Table12" displayName="Table12" ref="A1:K11" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:K11" xr:uid="{197A1E99-7397-485F-8B54-E30877E39C3B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DD6930EE-BF2D-4183-A338-8FDAEDC32845}" name="final_evaluation_seed" dataDxfId="127"/>
-    <tableColumn id="2" xr3:uid="{A8099FF3-60E5-4398-AB58-AB40ED92AE8E}" name="12345" dataDxfId="126"/>
-    <tableColumn id="3" xr3:uid="{1F7752E8-EDC2-4D7F-889D-BA709136B80B}" name="24690" dataDxfId="125"/>
-    <tableColumn id="4" xr3:uid="{2FE03160-264C-4C31-8E1B-28EAED0A37C2}" name="37035" dataDxfId="124"/>
-    <tableColumn id="5" xr3:uid="{4D9BA2DF-D2F3-4C91-8198-EBD06A8DC8B6}" name="49380" dataDxfId="123"/>
-    <tableColumn id="6" xr3:uid="{A7D1C5DF-C43A-42E3-903D-0BCA971A941C}" name="61725" dataDxfId="122"/>
-    <tableColumn id="7" xr3:uid="{59CB4E09-5299-4718-AA8E-6F2BEBF226B3}" name="74070" dataDxfId="121"/>
-    <tableColumn id="8" xr3:uid="{ABA60371-89D5-4C1D-8179-0AA44B054F20}" name="86415" dataDxfId="120"/>
-    <tableColumn id="9" xr3:uid="{1EA815C9-C24B-44FD-B57E-C8395A318CC0}" name="98760" dataDxfId="119"/>
-    <tableColumn id="10" xr3:uid="{D72A3788-A18B-4791-90B3-9E20D3BEB894}" name="111105" dataDxfId="118"/>
-    <tableColumn id="11" xr3:uid="{461AB8F1-9499-4A07-A1F6-DDE3A2953C1F}" name="123450" dataDxfId="117"/>
+    <tableColumn id="1" xr3:uid="{DD6930EE-BF2D-4183-A338-8FDAEDC32845}" name="final_evaluation_seed" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{A8099FF3-60E5-4398-AB58-AB40ED92AE8E}" name="12345" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{1F7752E8-EDC2-4D7F-889D-BA709136B80B}" name="24690" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{2FE03160-264C-4C31-8E1B-28EAED0A37C2}" name="37035" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{4D9BA2DF-D2F3-4C91-8198-EBD06A8DC8B6}" name="49380" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{A7D1C5DF-C43A-42E3-903D-0BCA971A941C}" name="61725" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{59CB4E09-5299-4718-AA8E-6F2BEBF226B3}" name="74070" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{ABA60371-89D5-4C1D-8179-0AA44B054F20}" name="86415" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{1EA815C9-C24B-44FD-B57E-C8395A318CC0}" name="98760" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{D72A3788-A18B-4791-90B3-9E20D3BEB894}" name="111105" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{461AB8F1-9499-4A07-A1F6-DDE3A2953C1F}" name="123450" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3827,6 +3827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E8849C-2D02-46F4-ACC4-400EB6662519}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Y87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5165,83 +5166,83 @@
         <v>21</v>
       </c>
       <c r="B23" s="20">
-        <f>(B2-B$17)/B$19</f>
+        <f t="shared" ref="B23:U23" si="1">(B2-B$17)/B$19</f>
         <v>1</v>
       </c>
       <c r="C23" s="20">
-        <f>(C2-C$17)/C$19</f>
+        <f t="shared" si="1"/>
         <v>0.5319158537587505</v>
       </c>
       <c r="D23" s="20">
-        <f>(D2-D$17)/D$19</f>
+        <f t="shared" si="1"/>
         <v>0.76689850887868849</v>
       </c>
       <c r="E23" s="20">
-        <f>(E2-E$17)/E$19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F23" s="20">
-        <f>(F2-F$17)/F$19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G23" s="20">
-        <f>(G2-G$17)/G$19</f>
+        <f t="shared" si="1"/>
         <v>0.58185987321500265</v>
       </c>
       <c r="H23" s="20">
-        <f>(H2-H$17)/H$19</f>
+        <f t="shared" si="1"/>
         <v>0.23397573684046927</v>
       </c>
       <c r="I23" s="20">
-        <f>(I2-I$17)/I$19</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J23" s="20">
-        <f>(J2-J$17)/J$19</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K23" s="20">
-        <f>(K2-K$17)/K$19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L23" s="20">
-        <f>(L2-L$17)/L$19</f>
+        <f t="shared" si="1"/>
         <v>0.37385160349525931</v>
       </c>
       <c r="M23" s="20">
-        <f>(M2-M$17)/M$19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N23" s="20">
-        <f>(N2-N$17)/N$19</f>
+        <f t="shared" si="1"/>
         <v>0.35918383891264172</v>
       </c>
       <c r="O23" s="20">
-        <f>(O2-O$17)/O$19</f>
+        <f t="shared" si="1"/>
         <v>0.60132763494465202</v>
       </c>
       <c r="P23" s="20">
-        <f>(P2-P$17)/P$19</f>
+        <f t="shared" si="1"/>
         <v>0.12820057331464138</v>
       </c>
       <c r="Q23" s="20">
-        <f>(Q2-Q$17)/Q$19</f>
+        <f t="shared" si="1"/>
         <v>0.1895299463089172</v>
       </c>
       <c r="R23" s="20">
-        <f>(R2-R$17)/R$19</f>
+        <f t="shared" si="1"/>
         <v>3.5851909458570592E-2</v>
       </c>
       <c r="S23" s="20">
-        <f>(S2-S$17)/S$19</f>
+        <f t="shared" si="1"/>
         <v>6.0024332406861535E-4</v>
       </c>
       <c r="T23" s="20">
-        <f>(T2-T$17)/T$19</f>
+        <f t="shared" si="1"/>
         <v>2.507812029450927E-2</v>
       </c>
       <c r="U23" s="20">
-        <f>(U2-U$17)/U$19</f>
+        <f t="shared" si="1"/>
         <v>0.56249203146664295</v>
       </c>
     </row>
@@ -5250,83 +5251,83 @@
         <v>22</v>
       </c>
       <c r="B24" s="20">
-        <f>(B3-B$17)/B$19</f>
+        <f t="shared" ref="B24:U24" si="2">(B3-B$17)/B$19</f>
         <v>0</v>
       </c>
       <c r="C24" s="20">
-        <f>(C3-C$17)/C$19</f>
+        <f t="shared" si="2"/>
         <v>0.44637312509783689</v>
       </c>
       <c r="D24" s="20">
-        <f>(D3-D$17)/D$19</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E24" s="20">
-        <f>(E3-E$17)/E$19</f>
+        <f t="shared" si="2"/>
         <v>1.394163984395156E-4</v>
       </c>
       <c r="F24" s="20">
-        <f>(F3-F$17)/F$19</f>
+        <f t="shared" si="2"/>
         <v>8.6687648579132567E-2</v>
       </c>
       <c r="G24" s="20">
-        <f>(G3-G$17)/G$19</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H24" s="20">
-        <f>(H3-H$17)/H$19</f>
+        <f t="shared" si="2"/>
         <v>0.32898156552826396</v>
       </c>
       <c r="I24" s="20">
-        <f>(I3-I$17)/I$19</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J24" s="20">
-        <f>(J3-J$17)/J$19</f>
+        <f t="shared" si="2"/>
         <v>0.44330352636411174</v>
       </c>
       <c r="K24" s="20">
-        <f>(K3-K$17)/K$19</f>
+        <f t="shared" si="2"/>
         <v>7.0683294185667961E-2</v>
       </c>
       <c r="L24" s="20">
-        <f>(L3-L$17)/L$19</f>
+        <f t="shared" si="2"/>
         <v>0.52008878700836425</v>
       </c>
       <c r="M24" s="20">
-        <f>(M3-M$17)/M$19</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N24" s="20">
-        <f>(N3-N$17)/N$19</f>
+        <f t="shared" si="2"/>
         <v>0.68715919567454697</v>
       </c>
       <c r="O24" s="20">
-        <f>(O3-O$17)/O$19</f>
+        <f t="shared" si="2"/>
         <v>0.45154348916195136</v>
       </c>
       <c r="P24" s="20">
-        <f>(P3-P$17)/P$19</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q24" s="20">
-        <f>(Q3-Q$17)/Q$19</f>
+        <f t="shared" si="2"/>
         <v>0.99837051748094974</v>
       </c>
       <c r="R24" s="20">
-        <f>(R3-R$17)/R$19</f>
+        <f t="shared" si="2"/>
         <v>0.99878318784013453</v>
       </c>
       <c r="S24" s="20">
-        <f>(S3-S$17)/S$19</f>
+        <f t="shared" si="2"/>
         <v>1.9209676044535482E-4</v>
       </c>
       <c r="T24" s="20">
-        <f>(T3-T$17)/T$19</f>
+        <f t="shared" si="2"/>
         <v>9.1884340436242745E-2</v>
       </c>
       <c r="U24" s="20">
-        <f>(U3-U$17)/U$19</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -5335,83 +5336,83 @@
         <v>23</v>
       </c>
       <c r="B25" s="20">
-        <f>(B4-B$17)/B$19</f>
+        <f t="shared" ref="B25:U25" si="3">(B4-B$17)/B$19</f>
         <v>0.45755570134767282</v>
       </c>
       <c r="C25" s="20">
-        <f>(C4-C$17)/C$19</f>
+        <f t="shared" si="3"/>
         <v>0.71821922371682578</v>
       </c>
       <c r="D25" s="20">
-        <f>(D4-D$17)/D$19</f>
+        <f t="shared" si="3"/>
         <v>2.2007300507130068E-2</v>
       </c>
       <c r="E25" s="20">
-        <f>(E4-E$17)/E$19</f>
+        <f t="shared" si="3"/>
         <v>4.6084421998494808E-2</v>
       </c>
       <c r="F25" s="20">
-        <f>(F4-F$17)/F$19</f>
+        <f t="shared" si="3"/>
         <v>0.18018648475919069</v>
       </c>
       <c r="G25" s="20">
-        <f>(G4-G$17)/G$19</f>
+        <f t="shared" si="3"/>
         <v>0.48973188418245789</v>
       </c>
       <c r="H25" s="20">
-        <f>(H4-H$17)/H$19</f>
+        <f t="shared" si="3"/>
         <v>4.0732717629686159E-2</v>
       </c>
       <c r="I25" s="20">
-        <f>(I4-I$17)/I$19</f>
+        <f t="shared" si="3"/>
         <v>0.14015090101193156</v>
       </c>
       <c r="J25" s="20">
-        <f>(J4-J$17)/J$19</f>
+        <f t="shared" si="3"/>
         <v>0.73121346404968113</v>
       </c>
       <c r="K25" s="20">
-        <f>(K4-K$17)/K$19</f>
+        <f t="shared" si="3"/>
         <v>0.71692378208660579</v>
       </c>
       <c r="L25" s="20">
-        <f>(L4-L$17)/L$19</f>
+        <f t="shared" si="3"/>
         <v>0.87284270079521298</v>
       </c>
       <c r="M25" s="20">
-        <f>(M4-M$17)/M$19</f>
+        <f t="shared" si="3"/>
         <v>0.48891203718442572</v>
       </c>
       <c r="N25" s="20">
-        <f>(N4-N$17)/N$19</f>
+        <f t="shared" si="3"/>
         <v>0.38398275029845563</v>
       </c>
       <c r="O25" s="20">
-        <f>(O4-O$17)/O$19</f>
+        <f t="shared" si="3"/>
         <v>0.33688567465498365</v>
       </c>
       <c r="P25" s="20">
-        <f>(P4-P$17)/P$19</f>
+        <f t="shared" si="3"/>
         <v>0.24629971635343259</v>
       </c>
       <c r="Q25" s="20">
-        <f>(Q4-Q$17)/Q$19</f>
+        <f t="shared" si="3"/>
         <v>0.44450172214932904</v>
       </c>
       <c r="R25" s="20">
-        <f>(R4-R$17)/R$19</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S25" s="20">
-        <f>(S4-S$17)/S$19</f>
+        <f t="shared" si="3"/>
         <v>4.7036367088029241E-3</v>
       </c>
       <c r="T25" s="20">
-        <f>(T4-T$17)/T$19</f>
+        <f t="shared" si="3"/>
         <v>0.88761934092650396</v>
       </c>
       <c r="U25" s="20">
-        <f>(U4-U$17)/U$19</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5420,83 +5421,83 @@
         <v>24</v>
       </c>
       <c r="B26" s="20">
-        <f>(B5-B$17)/B$19</f>
+        <f t="shared" ref="B26:U26" si="4">(B5-B$17)/B$19</f>
         <v>0.85032868880228274</v>
       </c>
       <c r="C26" s="20">
-        <f>(C5-C$17)/C$19</f>
+        <f t="shared" si="4"/>
         <v>0.13488560656579915</v>
       </c>
       <c r="D26" s="20">
-        <f>(D5-D$17)/D$19</f>
+        <f t="shared" si="4"/>
         <v>8.0442651895790487E-2</v>
       </c>
       <c r="E26" s="20">
-        <f>(E5-E$17)/E$19</f>
+        <f t="shared" si="4"/>
         <v>4.983231952144538E-2</v>
       </c>
       <c r="F26" s="20">
-        <f>(F5-F$17)/F$19</f>
+        <f t="shared" si="4"/>
         <v>0.70001114464082248</v>
       </c>
       <c r="G26" s="20">
-        <f>(G5-G$17)/G$19</f>
+        <f t="shared" si="4"/>
         <v>0.6549995894115419</v>
       </c>
       <c r="H26" s="20">
-        <f>(H5-H$17)/H$19</f>
+        <f t="shared" si="4"/>
         <v>0.56087132696339814</v>
       </c>
       <c r="I26" s="20">
-        <f>(I5-I$17)/I$19</f>
+        <f t="shared" si="4"/>
         <v>0.51287071023760145</v>
       </c>
       <c r="J26" s="20">
-        <f>(J5-J$17)/J$19</f>
+        <f t="shared" si="4"/>
         <v>0.5216917094416641</v>
       </c>
       <c r="K26" s="20">
-        <f>(K5-K$17)/K$19</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L26" s="20">
-        <f>(L5-L$17)/L$19</f>
+        <f t="shared" si="4"/>
         <v>0.9564454944777675</v>
       </c>
       <c r="M26" s="20">
-        <f>(M5-M$17)/M$19</f>
+        <f t="shared" si="4"/>
         <v>0.61126355886741868</v>
       </c>
       <c r="N26" s="20">
-        <f>(N5-N$17)/N$19</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O26" s="20">
-        <f>(O5-O$17)/O$19</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="P26" s="20">
-        <f>(P5-P$17)/P$19</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="Q26" s="20">
-        <f>(Q5-Q$17)/Q$19</f>
+        <f t="shared" si="4"/>
         <v>0.78214460059334356</v>
       </c>
       <c r="R26" s="20">
-        <f>(R5-R$17)/R$19</f>
+        <f t="shared" si="4"/>
         <v>0.29111295612306348</v>
       </c>
       <c r="S26" s="20">
-        <f>(S5-S$17)/S$19</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="T26" s="20">
-        <f>(T5-T$17)/T$19</f>
+        <f t="shared" si="4"/>
         <v>0.61149587719290754</v>
       </c>
       <c r="U26" s="20">
-        <f>(U5-U$17)/U$19</f>
+        <f t="shared" si="4"/>
         <v>0.5797435979064044</v>
       </c>
     </row>
@@ -5505,83 +5506,83 @@
         <v>25</v>
       </c>
       <c r="B27" s="20">
-        <f>(B6-B$17)/B$19</f>
+        <f t="shared" ref="B27:U27" si="5">(B6-B$17)/B$19</f>
         <v>0.10346292799299334</v>
       </c>
       <c r="C27" s="20">
-        <f>(C6-C$17)/C$19</f>
+        <f t="shared" si="5"/>
         <v>0.74819784356020103</v>
       </c>
       <c r="D27" s="20">
-        <f>(D6-D$17)/D$19</f>
+        <f t="shared" si="5"/>
         <v>8.6921025103273306E-2</v>
       </c>
       <c r="E27" s="20">
-        <f>(E6-E$17)/E$19</f>
+        <f t="shared" si="5"/>
         <v>5.7328074119450963E-2</v>
       </c>
       <c r="F27" s="20">
-        <f>(F6-F$17)/F$19</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G27" s="20">
-        <f>(G6-G$17)/G$19</f>
+        <f t="shared" si="5"/>
         <v>0.46701456394690166</v>
       </c>
       <c r="H27" s="20">
-        <f>(H6-H$17)/H$19</f>
+        <f t="shared" si="5"/>
         <v>0.44285503086999778</v>
       </c>
       <c r="I27" s="20">
-        <f>(I6-I$17)/I$19</f>
+        <f t="shared" si="5"/>
         <v>0.66204703468021198</v>
       </c>
       <c r="J27" s="20">
-        <f>(J6-J$17)/J$19</f>
+        <f t="shared" si="5"/>
         <v>0.79575272746013981</v>
       </c>
       <c r="K27" s="20">
-        <f>(K6-K$17)/K$19</f>
+        <f t="shared" si="5"/>
         <v>0.59924862879399021</v>
       </c>
       <c r="L27" s="20">
-        <f>(L6-L$17)/L$19</f>
+        <f t="shared" si="5"/>
         <v>0.66698734813915894</v>
       </c>
       <c r="M27" s="20">
-        <f>(M6-M$17)/M$19</f>
+        <f t="shared" si="5"/>
         <v>0.46768371242883944</v>
       </c>
       <c r="N27" s="20">
-        <f>(N6-N$17)/N$19</f>
+        <f t="shared" si="5"/>
         <v>3.5264980712116152E-2</v>
       </c>
       <c r="O27" s="20">
-        <f>(O6-O$17)/O$19</f>
+        <f t="shared" si="5"/>
         <v>0.80749622280638889</v>
       </c>
       <c r="P27" s="20">
-        <f>(P6-P$17)/P$19</f>
+        <f t="shared" si="5"/>
         <v>2.6602506275219089E-2</v>
       </c>
       <c r="Q27" s="20">
-        <f>(Q6-Q$17)/Q$19</f>
+        <f t="shared" si="5"/>
         <v>0.99630525362316913</v>
       </c>
       <c r="R27" s="20">
-        <f>(R6-R$17)/R$19</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S27" s="20">
-        <f>(S6-S$17)/S$19</f>
+        <f t="shared" si="5"/>
         <v>3.2588389387961091E-4</v>
       </c>
       <c r="T27" s="20">
-        <f>(T6-T$17)/T$19</f>
+        <f t="shared" si="5"/>
         <v>0.91060519400537188</v>
       </c>
       <c r="U27" s="20">
-        <f>(U6-U$17)/U$19</f>
+        <f t="shared" si="5"/>
         <v>0.55392895656024632</v>
       </c>
     </row>
@@ -5590,83 +5591,83 @@
         <v>26</v>
       </c>
       <c r="B28" s="20">
-        <f>(B7-B$17)/B$19</f>
+        <f t="shared" ref="B28:U28" si="6">(B7-B$17)/B$19</f>
         <v>0.54892097858608468</v>
       </c>
       <c r="C28" s="20">
-        <f>(C7-C$17)/C$19</f>
+        <f t="shared" si="6"/>
         <v>0.34522997991495336</v>
       </c>
       <c r="D28" s="20">
-        <f>(D7-D$17)/D$19</f>
+        <f t="shared" si="6"/>
         <v>0.8589900648809804</v>
       </c>
       <c r="E28" s="20">
-        <f>(E7-E$17)/E$19</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F28" s="20">
-        <f>(F7-F$17)/F$19</f>
+        <f t="shared" si="6"/>
         <v>0.99432750915149848</v>
       </c>
       <c r="G28" s="20">
-        <f>(G7-G$17)/G$19</f>
+        <f t="shared" si="6"/>
         <v>0.72224441252441562</v>
       </c>
       <c r="H28" s="20">
-        <f>(H7-H$17)/H$19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I28" s="20">
-        <f>(I7-I$17)/I$19</f>
+        <f t="shared" si="6"/>
         <v>5.6393647884770068E-2</v>
       </c>
       <c r="J28" s="20">
-        <f>(J7-J$17)/J$19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K28" s="20">
-        <f>(K7-K$17)/K$19</f>
+        <f t="shared" si="6"/>
         <v>0.86324307446340021</v>
       </c>
       <c r="L28" s="20">
-        <f>(L7-L$17)/L$19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M28" s="20">
-        <f>(M7-M$17)/M$19</f>
+        <f t="shared" si="6"/>
         <v>0.73709087524849581</v>
       </c>
       <c r="N28" s="20">
-        <f>(N7-N$17)/N$19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O28" s="20">
-        <f>(O7-O$17)/O$19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P28" s="20">
-        <f>(P7-P$17)/P$19</f>
+        <f t="shared" si="6"/>
         <v>2.8589683977392217E-2</v>
       </c>
       <c r="Q28" s="20">
-        <f>(Q7-Q$17)/Q$19</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="R28" s="20">
-        <f>(R7-R$17)/R$19</f>
+        <f t="shared" si="6"/>
         <v>0.39026101865965351</v>
       </c>
       <c r="S28" s="20">
-        <f>(S7-S$17)/S$19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T28" s="20">
-        <f>(T7-T$17)/T$19</f>
+        <f t="shared" si="6"/>
         <v>0.13322281639933659</v>
       </c>
       <c r="U28" s="20">
-        <f>(U7-U$17)/U$19</f>
+        <f t="shared" si="6"/>
         <v>0.49061744509161626</v>
       </c>
     </row>
@@ -5675,83 +5676,83 @@
         <v>27</v>
       </c>
       <c r="B29" s="20">
-        <f>(B8-B$17)/B$19</f>
+        <f t="shared" ref="B29:U29" si="7">(B8-B$17)/B$19</f>
         <v>0.30538824528130476</v>
       </c>
       <c r="C29" s="20">
-        <f>(C8-C$17)/C$19</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D29" s="20">
-        <f>(D8-D$17)/D$19</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E29" s="20">
-        <f>(E8-E$17)/E$19</f>
+        <f t="shared" si="7"/>
         <v>9.8566177049373878E-3</v>
       </c>
       <c r="F29" s="20">
-        <f>(F8-F$17)/F$19</f>
+        <f t="shared" si="7"/>
         <v>0.6310228758476033</v>
       </c>
       <c r="G29" s="20">
-        <f>(G8-G$17)/G$19</f>
+        <f t="shared" si="7"/>
         <v>0.30977001668136461</v>
       </c>
       <c r="H29" s="20">
-        <f>(H8-H$17)/H$19</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I29" s="20">
-        <f>(I8-I$17)/I$19</f>
+        <f t="shared" si="7"/>
         <v>0.29923397665989621</v>
       </c>
       <c r="J29" s="20">
-        <f>(J8-J$17)/J$19</f>
+        <f t="shared" si="7"/>
         <v>0.81045733427892797</v>
       </c>
       <c r="K29" s="20">
-        <f>(K8-K$17)/K$19</f>
+        <f t="shared" si="7"/>
         <v>0.24234523803226979</v>
       </c>
       <c r="L29" s="20">
-        <f>(L8-L$17)/L$19</f>
+        <f t="shared" si="7"/>
         <v>0.68809342242878913</v>
       </c>
       <c r="M29" s="20">
-        <f>(M8-M$17)/M$19</f>
+        <f t="shared" si="7"/>
         <v>0.32081138053768105</v>
       </c>
       <c r="N29" s="20">
-        <f>(N8-N$17)/N$19</f>
+        <f t="shared" si="7"/>
         <v>0.30226279568701608</v>
       </c>
       <c r="O29" s="20">
-        <f>(O8-O$17)/O$19</f>
+        <f t="shared" si="7"/>
         <v>0.25027054334274274</v>
       </c>
       <c r="P29" s="20">
-        <f>(P8-P$17)/P$19</f>
+        <f t="shared" si="7"/>
         <v>0.11866411107947354</v>
       </c>
       <c r="Q29" s="20">
-        <f>(Q8-Q$17)/Q$19</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R29" s="20">
-        <f>(R8-R$17)/R$19</f>
+        <f t="shared" si="7"/>
         <v>6.4070127793333549E-3</v>
       </c>
       <c r="S29" s="20">
-        <f>(S8-S$17)/S$19</f>
+        <f t="shared" si="7"/>
         <v>2.2587032951653836E-2</v>
       </c>
       <c r="T29" s="20">
-        <f>(T8-T$17)/T$19</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="U29" s="20">
-        <f>(U8-U$17)/U$19</f>
+        <f t="shared" si="7"/>
         <v>3.1267399359640623E-4</v>
       </c>
     </row>
@@ -5760,83 +5761,83 @@
         <v>28</v>
       </c>
       <c r="B30" s="20">
-        <f>(B9-B$17)/B$19</f>
+        <f t="shared" ref="B30:U30" si="8">(B9-B$17)/B$19</f>
         <v>0.73707526175211369</v>
       </c>
       <c r="C30" s="20">
-        <f>(C9-C$17)/C$19</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D30" s="20">
-        <f>(D9-D$17)/D$19</f>
+        <f t="shared" si="8"/>
         <v>0.13818161555164027</v>
       </c>
       <c r="E30" s="20">
-        <f>(E9-E$17)/E$19</f>
+        <f t="shared" si="8"/>
         <v>0.123327643993907</v>
       </c>
       <c r="F30" s="20">
-        <f>(F9-F$17)/F$19</f>
+        <f t="shared" si="8"/>
         <v>0.1981935070938057</v>
       </c>
       <c r="G30" s="20">
-        <f>(G9-G$17)/G$19</f>
+        <f t="shared" si="8"/>
         <v>0.18112001587320958</v>
       </c>
       <c r="H30" s="20">
-        <f>(H9-H$17)/H$19</f>
+        <f t="shared" si="8"/>
         <v>0.17968031014032557</v>
       </c>
       <c r="I30" s="20">
-        <f>(I9-I$17)/I$19</f>
+        <f t="shared" si="8"/>
         <v>0.36218478533119985</v>
       </c>
       <c r="J30" s="20">
-        <f>(J9-J$17)/J$19</f>
+        <f t="shared" si="8"/>
         <v>0.87825737391004077</v>
       </c>
       <c r="K30" s="20">
-        <f>(K9-K$17)/K$19</f>
+        <f t="shared" si="8"/>
         <v>0.93832614931839609</v>
       </c>
       <c r="L30" s="20">
-        <f>(L9-L$17)/L$19</f>
+        <f t="shared" si="8"/>
         <v>0.96905459805275274</v>
       </c>
       <c r="M30" s="20">
-        <f>(M9-M$17)/M$19</f>
+        <f t="shared" si="8"/>
         <v>0.25284459319722946</v>
       </c>
       <c r="N30" s="20">
-        <f>(N9-N$17)/N$19</f>
+        <f t="shared" si="8"/>
         <v>0.28609022987603838</v>
       </c>
       <c r="O30" s="20">
-        <f>(O9-O$17)/O$19</f>
+        <f t="shared" si="8"/>
         <v>0.22312826686145296</v>
       </c>
       <c r="P30" s="20">
-        <f>(P9-P$17)/P$19</f>
+        <f t="shared" si="8"/>
         <v>0.15821824209300192</v>
       </c>
       <c r="Q30" s="20">
-        <f>(Q9-Q$17)/Q$19</f>
+        <f t="shared" si="8"/>
         <v>0.46028826417447366</v>
       </c>
       <c r="R30" s="20">
-        <f>(R9-R$17)/R$19</f>
+        <f t="shared" si="8"/>
         <v>0.63273197114099067</v>
       </c>
       <c r="S30" s="20">
-        <f>(S9-S$17)/S$19</f>
+        <f t="shared" si="8"/>
         <v>5.5047296666863782E-2</v>
       </c>
       <c r="T30" s="20">
-        <f>(T9-T$17)/T$19</f>
+        <f t="shared" si="8"/>
         <v>0.25979385199795729</v>
       </c>
       <c r="U30" s="20">
-        <f>(U9-U$17)/U$19</f>
+        <f t="shared" si="8"/>
         <v>0.19618216926497342</v>
       </c>
     </row>
@@ -5845,83 +5846,83 @@
         <v>29</v>
       </c>
       <c r="B31" s="20">
-        <f>(B10-B$17)/B$19</f>
+        <f t="shared" ref="B31:U31" si="9">(B10-B$17)/B$19</f>
         <v>0.49936834627956128</v>
       </c>
       <c r="C31" s="20">
-        <f>(C10-C$17)/C$19</f>
+        <f t="shared" si="9"/>
         <v>0.52669827183981577</v>
       </c>
       <c r="D31" s="20">
-        <f>(D10-D$17)/D$19</f>
+        <f t="shared" si="9"/>
         <v>0.13369205064261797</v>
       </c>
       <c r="E31" s="20">
-        <f>(E10-E$17)/E$19</f>
+        <f t="shared" si="9"/>
         <v>6.1594711712853037E-2</v>
       </c>
       <c r="F31" s="20">
-        <f>(F10-F$17)/F$19</f>
+        <f t="shared" si="9"/>
         <v>0.86189812980808334</v>
       </c>
       <c r="G31" s="20">
-        <f>(G10-G$17)/G$19</f>
+        <f t="shared" si="9"/>
         <v>0.32831920409850057</v>
       </c>
       <c r="H31" s="20">
-        <f>(H10-H$17)/H$19</f>
+        <f t="shared" si="9"/>
         <v>0.91731288704342184</v>
       </c>
       <c r="I31" s="20">
-        <f>(I10-I$17)/I$19</f>
+        <f t="shared" si="9"/>
         <v>0.15620051444471345</v>
       </c>
       <c r="J31" s="20">
-        <f>(J10-J$17)/J$19</f>
+        <f t="shared" si="9"/>
         <v>0.99965172390531987</v>
       </c>
       <c r="K31" s="20">
-        <f>(K10-K$17)/K$19</f>
+        <f t="shared" si="9"/>
         <v>0.87708795576355514</v>
       </c>
       <c r="L31" s="20">
-        <f>(L10-L$17)/L$19</f>
+        <f t="shared" si="9"/>
         <v>0.90514767366309024</v>
       </c>
       <c r="M31" s="20">
-        <f>(M10-M$17)/M$19</f>
+        <f t="shared" si="9"/>
         <v>0.46345534761614088</v>
       </c>
       <c r="N31" s="20">
-        <f>(N10-N$17)/N$19</f>
+        <f t="shared" si="9"/>
         <v>0.37216312086978548</v>
       </c>
       <c r="O31" s="20">
-        <f>(O10-O$17)/O$19</f>
+        <f t="shared" si="9"/>
         <v>0.46803986637087469</v>
       </c>
       <c r="P31" s="20">
-        <f>(P10-P$17)/P$19</f>
+        <f t="shared" si="9"/>
         <v>0.1012535140496169</v>
       </c>
       <c r="Q31" s="20">
-        <f>(Q10-Q$17)/Q$19</f>
+        <f t="shared" si="9"/>
         <v>0.85413681459583868</v>
       </c>
       <c r="R31" s="20">
-        <f>(R10-R$17)/R$19</f>
+        <f t="shared" si="9"/>
         <v>0.37283574678150694</v>
       </c>
       <c r="S31" s="20">
-        <f>(S10-S$17)/S$19</f>
+        <f t="shared" si="9"/>
         <v>3.6913149653897037E-3</v>
       </c>
       <c r="T31" s="20">
-        <f>(T10-T$17)/T$19</f>
+        <f t="shared" si="9"/>
         <v>6.8439502375498756E-2</v>
       </c>
       <c r="U31" s="20">
-        <f>(U10-U$17)/U$19</f>
+        <f t="shared" si="9"/>
         <v>0.39935301806207207</v>
       </c>
     </row>
@@ -5930,83 +5931,83 @@
         <v>30</v>
       </c>
       <c r="B32" s="20">
-        <f>(B11-B$17)/B$19</f>
+        <f t="shared" ref="B32:U32" si="10">(B11-B$17)/B$19</f>
         <v>0.1765914397890751</v>
       </c>
       <c r="C32" s="20">
-        <f>(C11-C$17)/C$19</f>
+        <f t="shared" si="10"/>
         <v>3.1427819411936495E-2</v>
       </c>
       <c r="D32" s="20">
-        <f>(D11-D$17)/D$19</f>
+        <f t="shared" si="10"/>
         <v>0.12321046242013119</v>
       </c>
       <c r="E32" s="20">
-        <f>(E11-E$17)/E$19</f>
+        <f t="shared" si="10"/>
         <v>9.5600484986369541E-2</v>
       </c>
       <c r="F32" s="20">
-        <f>(F11-F$17)/F$19</f>
+        <f t="shared" si="10"/>
         <v>0.2196243928449117</v>
       </c>
       <c r="G32" s="20">
-        <f>(G11-G$17)/G$19</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H32" s="20">
-        <f>(H11-H$17)/H$19</f>
+        <f t="shared" si="10"/>
         <v>0.51982181240622927</v>
       </c>
       <c r="I32" s="20">
-        <f>(I11-I$17)/I$19</f>
+        <f t="shared" si="10"/>
         <v>0.34018482218002499</v>
       </c>
       <c r="J32" s="20">
-        <f>(J11-J$17)/J$19</f>
+        <f t="shared" si="10"/>
         <v>0.9804273724909961</v>
       </c>
       <c r="K32" s="20">
-        <f>(K11-K$17)/K$19</f>
+        <f t="shared" si="10"/>
         <v>0.98761774612812792</v>
       </c>
       <c r="L32" s="20">
-        <f>(L11-L$17)/L$19</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="M32" s="20">
-        <f>(M11-M$17)/M$19</f>
+        <f t="shared" si="10"/>
         <v>0.51924583837414406</v>
       </c>
       <c r="N32" s="20">
-        <f>(N11-N$17)/N$19</f>
+        <f t="shared" si="10"/>
         <v>0.19630970984472096</v>
       </c>
       <c r="O32" s="20">
-        <f>(O11-O$17)/O$19</f>
+        <f t="shared" si="10"/>
         <v>0.10629533406824947</v>
       </c>
       <c r="P32" s="20">
-        <f>(P11-P$17)/P$19</f>
+        <f t="shared" si="10"/>
         <v>0.18075708301099724</v>
       </c>
       <c r="Q32" s="20">
-        <f>(Q11-Q$17)/Q$19</f>
+        <f t="shared" si="10"/>
         <v>0.477005053481032</v>
       </c>
       <c r="R32" s="20">
-        <f>(R11-R$17)/R$19</f>
+        <f t="shared" si="10"/>
         <v>0.9762266339992931</v>
       </c>
       <c r="S32" s="20">
-        <f>(S11-S$17)/S$19</f>
+        <f t="shared" si="10"/>
         <v>1.6125308328467695E-2</v>
       </c>
       <c r="T32" s="20">
-        <f>(T11-T$17)/T$19</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U32" s="20">
-        <f>(U11-U$17)/U$19</f>
+        <f t="shared" si="10"/>
         <v>0.6642825052295287</v>
       </c>
     </row>
@@ -6424,39 +6425,39 @@
         <v>21</v>
       </c>
       <c r="B51" s="19">
-        <f t="shared" ref="B51" si="1">D2/B$46</f>
+        <f t="shared" ref="B51" si="11">D2/B$46</f>
         <v>5.136353588698177</v>
       </c>
       <c r="C51" s="19">
-        <f t="shared" ref="C51" si="2">E2/C$46</f>
+        <f t="shared" ref="C51" si="12">E2/C$46</f>
         <v>2.1372624292230372E-2</v>
       </c>
       <c r="D51" s="19">
-        <f t="shared" ref="D51" si="3">F2/D$46</f>
+        <f t="shared" ref="D51" si="13">F2/D$46</f>
         <v>3.2476586450870135E-2</v>
       </c>
       <c r="E51" s="19">
-        <f t="shared" ref="E51" si="4">G2/E$46</f>
+        <f t="shared" ref="E51" si="14">G2/E$46</f>
         <v>2.4050276860203788</v>
       </c>
       <c r="F51" s="19">
-        <f t="shared" ref="F51" si="5">H2/F$46</f>
+        <f t="shared" ref="F51" si="15">H2/F$46</f>
         <v>1.1356740435145909</v>
       </c>
       <c r="G51" s="19">
-        <f t="shared" ref="G51" si="6">I2/G$46</f>
+        <f t="shared" ref="G51" si="16">I2/G$46</f>
         <v>2.4242406348355998</v>
       </c>
       <c r="H51" s="19">
-        <f t="shared" ref="H51" si="7">J2/H$46</f>
+        <f t="shared" ref="H51" si="17">J2/H$46</f>
         <v>5.1169784628617572E-6</v>
       </c>
       <c r="I51" s="19">
-        <f t="shared" ref="I51" si="8">K2/I$46</f>
+        <f t="shared" ref="I51" si="18">K2/I$46</f>
         <v>4.9549341788743941</v>
       </c>
       <c r="J51" s="19">
-        <f t="shared" ref="J51" si="9">L2/J$46</f>
+        <f t="shared" ref="J51" si="19">L2/J$46</f>
         <v>2.7454191258149159</v>
       </c>
       <c r="K51" s="19">
@@ -6516,39 +6517,39 @@
         <v>22</v>
       </c>
       <c r="B52" s="19">
-        <f t="shared" ref="B52:B60" si="10">D3/B$46</f>
+        <f t="shared" ref="B52:B60" si="20">D3/B$46</f>
         <v>6.6666654501849774</v>
       </c>
       <c r="C52" s="19">
-        <f t="shared" ref="C52:C60" si="11">E3/C$46</f>
+        <f t="shared" ref="C52:C60" si="21">E3/C$46</f>
         <v>2.2649829213040925E-2</v>
       </c>
       <c r="D52" s="19">
-        <f t="shared" ref="D52:D60" si="12">F3/D$46</f>
+        <f t="shared" ref="D52:D60" si="22">F3/D$46</f>
         <v>0.87213008378552925</v>
       </c>
       <c r="E52" s="19">
-        <f t="shared" ref="E52:E60" si="13">G3/E$46</f>
+        <f t="shared" ref="E52:E60" si="23">G3/E$46</f>
         <v>3.7875008144670077</v>
       </c>
       <c r="F52" s="19">
-        <f t="shared" ref="F52:F60" si="14">H3/F$46</f>
+        <f t="shared" ref="F52:F60" si="24">H3/F$46</f>
         <v>1.4466930831289393</v>
       </c>
       <c r="G52" s="19">
-        <f t="shared" ref="G52:G60" si="15">I3/G$46</f>
+        <f t="shared" ref="G52:G60" si="25">I3/G$46</f>
         <v>0.10488924084422303</v>
       </c>
       <c r="H52" s="19">
-        <f t="shared" ref="H52:H60" si="16">J3/H$46</f>
+        <f t="shared" ref="H52:H60" si="26">J3/H$46</f>
         <v>4.7895685029752118</v>
       </c>
       <c r="I52" s="19">
-        <f t="shared" ref="I52:I60" si="17">K3/I$46</f>
+        <f t="shared" ref="I52:I60" si="27">K3/I$46</f>
         <v>4.6547280582669694</v>
       </c>
       <c r="J52" s="19">
-        <f t="shared" ref="J52:J60" si="18">L3/J$46</f>
+        <f t="shared" ref="J52:J60" si="28">L3/J$46</f>
         <v>2.3268178196794103</v>
       </c>
       <c r="K52" s="19">
@@ -6608,39 +6609,39 @@
         <v>23</v>
       </c>
       <c r="B53" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.24614097699509477</v>
       </c>
       <c r="C53" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.44355574771241485</v>
       </c>
       <c r="D53" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>1.7777565032591365</v>
       </c>
       <c r="E53" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>2.100430109617939</v>
       </c>
       <c r="F53" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>0.50305750748477429</v>
       </c>
       <c r="G53" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0.429948428475394</v>
       </c>
       <c r="H53" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>2.3125222824429605</v>
       </c>
       <c r="I53" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>1.9100151513871</v>
       </c>
       <c r="J53" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>1.3170660895911894</v>
       </c>
       <c r="K53" s="19">
@@ -6700,39 +6701,39 @@
         <v>24</v>
       </c>
       <c r="B54" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.62976920232325329</v>
       </c>
       <c r="C54" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.4778905405530352</v>
       </c>
       <c r="D54" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>6.8127597687125654</v>
       </c>
       <c r="E54" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>2.646845406413235</v>
       </c>
       <c r="F54" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>2.2058268320167196</v>
       </c>
       <c r="G54" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>1.2944166375711514</v>
       </c>
       <c r="H54" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>4.1151522108960599</v>
       </c>
       <c r="I54" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>0.70773370433432425</v>
       </c>
       <c r="J54" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>1.0777545971829789</v>
       </c>
       <c r="K54" s="19">
@@ -6792,39 +6793,39 @@
         <v>25</v>
       </c>
       <c r="B55" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.67229973833509626</v>
       </c>
       <c r="C55" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.54655975568782778</v>
       </c>
       <c r="D55" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>9.7184412088293843</v>
       </c>
       <c r="E55" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>2.0253211144170984</v>
       </c>
       <c r="F55" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>1.8194787986720302</v>
       </c>
       <c r="G55" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>1.6404089536176303</v>
       </c>
       <c r="H55" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>1.7572557994867364</v>
       </c>
       <c r="I55" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>2.4098051182930726</v>
       </c>
       <c r="J55" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>1.9063233320153581</v>
       </c>
       <c r="K55" s="19">
@@ -6884,39 +6885,39 @@
         <v>26</v>
       </c>
       <c r="B56" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>5.7409348799424293</v>
       </c>
       <c r="C56" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>9.1824536384790552</v>
       </c>
       <c r="D56" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>9.6634976631500322</v>
       </c>
       <c r="E56" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>2.8691731741294775</v>
       </c>
       <c r="F56" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>0.36971147079371214</v>
       </c>
       <c r="G56" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0.23568592667802335</v>
       </c>
       <c r="H56" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>8.603550518865454</v>
       </c>
       <c r="I56" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>1.288567783370012</v>
       </c>
       <c r="J56" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>3.8155626130213998</v>
       </c>
       <c r="K56" s="19">
@@ -6976,39 +6977,39 @@
         <v>27</v>
       </c>
       <c r="B57" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.10166299513680295</v>
       </c>
       <c r="C57" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.11166989761302999</v>
       </c>
       <c r="D57" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>6.144541837822306</v>
       </c>
       <c r="E57" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>1.5054323324893637</v>
       </c>
       <c r="F57" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>3.6433952427274319</v>
       </c>
       <c r="G57" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0.79891798173993644</v>
       </c>
       <c r="H57" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>1.6307440471043939</v>
       </c>
       <c r="I57" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>3.9256453689012116</v>
       </c>
       <c r="J57" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>1.8459075741842421</v>
       </c>
       <c r="K57" s="19">
@@ -7068,39 +7069,39 @@
         <v>28</v>
       </c>
       <c r="B58" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>1.0088256404758444</v>
       </c>
       <c r="C58" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>1.1511871622092036</v>
       </c>
       <c r="D58" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>1.9521718845465972</v>
       </c>
       <c r="E58" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>1.0800840874897575</v>
       </c>
       <c r="F58" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>0.95792798623611364</v>
       </c>
       <c r="G58" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0.94492302758460911</v>
       </c>
       <c r="H58" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>1.0474233278883787</v>
       </c>
       <c r="I58" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>0.96967491221594537</v>
       </c>
       <c r="J58" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>1.0416612651118389</v>
       </c>
       <c r="K58" s="19">
@@ -7160,39 +7161,39 @@
         <v>29</v>
       </c>
       <c r="B59" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.9793516358260147</v>
       </c>
       <c r="C59" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.58564676833915918</v>
       </c>
       <c r="D59" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>8.3807913798661691</v>
       </c>
       <c r="E59" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>1.5667604651320757</v>
       </c>
       <c r="F59" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>3.3727037828934314</v>
       </c>
       <c r="G59" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0.46717312176373937</v>
       </c>
       <c r="H59" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>3.0015261714351604E-3</v>
       </c>
       <c r="I59" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>1.2297657969420426</v>
       </c>
       <c r="J59" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>1.2245936861141788</v>
       </c>
       <c r="K59" s="19">
@@ -7252,39 +7253,39 @@
         <v>30</v>
       </c>
       <c r="B60" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.91053998341258502</v>
       </c>
       <c r="C60" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.897176412247913</v>
       </c>
       <c r="D60" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>2.1597506857580457</v>
       </c>
       <c r="E60" s="19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0.48125718968932579</v>
       </c>
       <c r="F60" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="24"/>
         <v>2.0714437023651593</v>
       </c>
       <c r="G60" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0.89389738238217276</v>
       </c>
       <c r="H60" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0.16839910638639849</v>
       </c>
       <c r="I60" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>0.76032361885481514</v>
       </c>
       <c r="J60" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>0.95308060892841995</v>
       </c>
       <c r="K60" s="19">
@@ -7431,35 +7432,35 @@
         <v>2.3607445216001137</v>
       </c>
       <c r="C64" s="19">
-        <f t="shared" ref="C64:J64" si="19">LOG(C51,2)</f>
+        <f t="shared" ref="C64:J64" si="29">LOG(C51,2)</f>
         <v>-5.5480921259072318</v>
       </c>
       <c r="D64" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>-4.9444561880769333</v>
       </c>
       <c r="E64" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>1.266053502001304</v>
       </c>
       <c r="F64" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>0.18354881786721497</v>
       </c>
       <c r="G64" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>1.2775329106315709</v>
       </c>
       <c r="H64" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>-17.576276408203682</v>
       </c>
       <c r="I64" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>2.3088658928421943</v>
       </c>
       <c r="J64" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>1.4570264131928441</v>
       </c>
       <c r="K64" s="19">
@@ -7519,39 +7520,39 @@
         <v>22</v>
       </c>
       <c r="B65" s="19">
-        <f t="shared" ref="B65:J65" si="20">LOG(B52,2)</f>
+        <f t="shared" ref="B65:J65" si="30">LOG(B52,2)</f>
         <v>2.7369653309143671</v>
       </c>
       <c r="C65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>-5.4643560178443993</v>
       </c>
       <c r="D65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>-0.19738475663355029</v>
       </c>
       <c r="E65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>1.9212461988238425</v>
       </c>
       <c r="F65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>0.53275888564756113</v>
       </c>
       <c r="G65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>-3.2530613957782899</v>
       </c>
       <c r="H65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>2.2598956879742653</v>
       </c>
       <c r="I65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>2.218696884121365</v>
       </c>
       <c r="J65" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>1.2183582580427561</v>
       </c>
       <c r="K65" s="19">
@@ -7611,39 +7612,39 @@
         <v>23</v>
       </c>
       <c r="B66" s="19">
-        <f t="shared" ref="B66:J66" si="21">LOG(B53,2)</f>
+        <f t="shared" ref="B66:J66" si="31">LOG(B53,2)</f>
         <v>-2.0224432404781951</v>
       </c>
       <c r="C66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>-1.1728126557638345</v>
       </c>
       <c r="D66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>0.83005773384295534</v>
       </c>
       <c r="E66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1.0706847819276819</v>
       </c>
       <c r="F66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>-0.99120476240971478</v>
       </c>
       <c r="G66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>-1.2177644733163766</v>
       </c>
       <c r="H66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1.2094672668679038</v>
       </c>
       <c r="I66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>0.93358408262978465</v>
       </c>
       <c r="J66" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>0.39732774098789159</v>
       </c>
       <c r="K66" s="19">
@@ -7703,39 +7704,39 @@
         <v>24</v>
       </c>
       <c r="B67" s="19">
-        <f t="shared" ref="B67:J67" si="22">LOG(B54,2)</f>
+        <f t="shared" ref="B67:J67" si="32">LOG(B54,2)</f>
         <v>-0.66710488797281842</v>
       </c>
       <c r="C67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>-1.065247883972352</v>
       </c>
       <c r="D67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2.7682393354027499</v>
       </c>
       <c r="E67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1.4042739341932964</v>
       </c>
       <c r="F67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1.1413195368962794</v>
       </c>
       <c r="G67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>0.37230205644289915</v>
       </c>
       <c r="H67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2.0409457939139006</v>
       </c>
       <c r="I67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>-0.4987214686252387</v>
       </c>
       <c r="J67" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>0.10802871637299623</v>
       </c>
       <c r="K67" s="19">
@@ -7795,39 +7796,39 @@
         <v>25</v>
       </c>
       <c r="B68" s="19">
-        <f t="shared" ref="B68:J68" si="23">LOG(B55,2)</f>
+        <f t="shared" ref="B68:J68" si="33">LOG(B55,2)</f>
         <v>-0.5728235068272447</v>
       </c>
       <c r="C68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>-0.87154885970075868</v>
       </c>
       <c r="D68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3.2807249310496602</v>
       </c>
       <c r="E68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>1.0181506652562498</v>
       </c>
       <c r="F68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>0.86352524039149026</v>
       </c>
       <c r="G68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>0.71405552326234423</v>
       </c>
       <c r="H68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>0.81332421626916596</v>
       </c>
       <c r="I68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>1.2689164799654529</v>
       </c>
       <c r="J68" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>0.93079283589731576</v>
       </c>
       <c r="K68" s="19">
@@ -7887,39 +7888,39 @@
         <v>26</v>
       </c>
       <c r="B69" s="19">
-        <f t="shared" ref="B69:J69" si="24">LOG(B56,2)</f>
+        <f t="shared" ref="B69:J69" si="34">LOG(B56,2)</f>
         <v>2.5212856910530173</v>
       </c>
       <c r="C69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3.1988797069160722</v>
       </c>
       <c r="D69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3.2725454611076854</v>
       </c>
       <c r="E69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>1.5206350471996271</v>
       </c>
       <c r="F69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>-1.435528289121266</v>
       </c>
       <c r="G69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>-2.0850624802025322</v>
       </c>
       <c r="H69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3.1049321550326421</v>
       </c>
       <c r="I69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>0.36576843022015681</v>
       </c>
       <c r="J69" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>1.9318958012724012</v>
       </c>
       <c r="K69" s="19">
@@ -7979,39 +7980,39 @@
         <v>27</v>
       </c>
       <c r="B70" s="19">
-        <f t="shared" ref="B70:J70" si="25">LOG(B57,2)</f>
+        <f t="shared" ref="B70:J70" si="35">LOG(B57,2)</f>
         <v>-3.2981334545091294</v>
       </c>
       <c r="C70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-3.1626877579229191</v>
       </c>
       <c r="D70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>2.6193054413637524</v>
       </c>
       <c r="E70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>0.59017786198087197</v>
       </c>
       <c r="F70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>1.8652835099839846</v>
       </c>
       <c r="G70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-0.32388069362483574</v>
       </c>
       <c r="H70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>0.70553036209248776</v>
       </c>
       <c r="I70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>1.9729298499217129</v>
       </c>
       <c r="J70" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>0.88433031809514107</v>
       </c>
       <c r="K70" s="19">
@@ -8071,39 +8072,39 @@
         <v>28</v>
       </c>
       <c r="B71" s="19">
-        <f t="shared" ref="B71:J71" si="26">LOG(B58,2)</f>
+        <f t="shared" ref="B71:J71" si="36">LOG(B58,2)</f>
         <v>1.2676849015540158E-2</v>
       </c>
       <c r="C71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>0.20312240865680684</v>
       </c>
       <c r="D71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>0.96508008469677264</v>
       </c>
       <c r="E71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>0.11114363450179288</v>
       </c>
       <c r="F71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>-6.2010891749634929E-2</v>
       </c>
       <c r="G71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>-8.1731281156573729E-2</v>
       </c>
       <c r="H71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>6.68446415154242E-2</v>
       </c>
       <c r="I71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>-4.4426936394511819E-2</v>
       </c>
       <c r="J71" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>5.8886207949663268E-2</v>
       </c>
       <c r="K71" s="19">
@@ -8163,39 +8164,39 @@
         <v>29</v>
       </c>
       <c r="B72" s="19">
-        <f t="shared" ref="B72:J72" si="27">LOG(B59,2)</f>
+        <f t="shared" ref="B72:J72" si="37">LOG(B59,2)</f>
         <v>-3.0101142946064852E-2</v>
       </c>
       <c r="C72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>-0.77189732651675569</v>
       </c>
       <c r="D72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>3.0670864809057279</v>
       </c>
       <c r="E72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.647784629598955</v>
       </c>
       <c r="F72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>1.7539056152084656</v>
       </c>
       <c r="G72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>-1.0979708219828659</v>
       </c>
       <c r="H72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>-8.3800880372419684</v>
       </c>
       <c r="I72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.298383587302404</v>
       </c>
       <c r="J72" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>0.29230314982842931</v>
       </c>
       <c r="K72" s="19">
@@ -8255,39 +8256,39 @@
         <v>30</v>
       </c>
       <c r="B73" s="19">
-        <f t="shared" ref="B73:J73" si="28">LOG(B60,2)</f>
+        <f t="shared" ref="B73:J73" si="38">LOG(B60,2)</f>
         <v>-0.13520572501689562</v>
       </c>
       <c r="C73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>-0.15653640399984656</v>
       </c>
       <c r="D73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>1.1108647822127893</v>
       </c>
       <c r="E73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>-1.0551200010461632</v>
       </c>
       <c r="F73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>1.0506366113273589</v>
       </c>
       <c r="G73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>-0.1618188724560726</v>
       </c>
       <c r="H73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>-2.5700436121560464</v>
       </c>
       <c r="I73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>-0.39531448693324878</v>
       </c>
       <c r="J73" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>-6.9329856425569006E-2</v>
       </c>
       <c r="K73" s="19">
@@ -8652,30 +8653,30 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O51:W60">
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="between">
       <formula>0.95</formula>
       <formula>1.05</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="10" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O64:W73">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+      <formula>-0.07</formula>
+      <formula>0.07</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
-      <formula>-0.07</formula>
-      <formula>0.07</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8695,6 +8696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237B445F-8D43-4D1E-9470-CD21867C00BD}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/THESIS/Stats rundown THESIS.xlsx
+++ b/THESIS/Stats rundown THESIS.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E20413-2402-483D-A7E1-3E65794703AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="3765" windowWidth="31755" windowHeight="15480" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
+    <workbookView xWindow="3675" yWindow="4770" windowWidth="28440" windowHeight="13920" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>

--- a/THESIS/Stats rundown THESIS.xlsx
+++ b/THESIS/Stats rundown THESIS.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\serotonin\THESIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380E7169-8A85-4D3F-BC32-7187297CB588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BBEA87-0E74-4712-9819-9ACFD67CD3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
+    <workbookView xWindow="13950" yWindow="1470" windowWidth="16590" windowHeight="8970" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
   </bookViews>
   <sheets>
     <sheet name="Cosine Data" sheetId="2" r:id="rId1"/>
-    <sheet name="Heuristic Analysis" sheetId="4" r:id="rId2"/>
+    <sheet name="Heuristic Analysis" sheetId="7" r:id="rId2"/>
     <sheet name="for RSTUDIO" sheetId="6" r:id="rId3"/>
     <sheet name="neural 12345" sheetId="5" r:id="rId4"/>
-    <sheet name="Old Pearson R" sheetId="3" r:id="rId5"/>
+    <sheet name="OLD Heuristic Analysis" sheetId="4" r:id="rId5"/>
+    <sheet name="Old Pearson R" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="127">
   <si>
     <t>seed_a_e</t>
   </si>
@@ -536,7 +536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -1182,11 +1182,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1304,22 +1315,31 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="306">
+  <dxfs count="322">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1452,11 +1472,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1472,6 +1512,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1582,6 +1642,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1652,6 +1732,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1672,111 +1772,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1821,10 +1821,2265 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2062,13 +4317,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -2094,963 +4342,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <border outline="0">
@@ -4287,794 +5584,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.000"/>
@@ -6358,92 +6867,83 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{96ECA080-13A0-4EAD-9B78-C907FAA1E37A}" name="Table3" displayName="Table3" ref="A1:U11" totalsRowShown="0" dataDxfId="197">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{96ECA080-13A0-4EAD-9B78-C907FAA1E37A}" name="Table3" displayName="Table3" ref="A1:U11" totalsRowShown="0" dataDxfId="321">
   <autoFilter ref="A1:U11" xr:uid="{96ECA080-13A0-4EAD-9B78-C907FAA1E37A}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{90D971B2-8A12-4663-B59E-A64B9E3ACB20}" name="final_evaluation_seed" dataDxfId="196"/>
-    <tableColumn id="2" xr3:uid="{BDA294FC-58D6-46F6-9587-EF102D78D712}" name="best_difference_vector_cosine" dataDxfId="195"/>
-    <tableColumn id="3" xr3:uid="{8DADFB6C-E620-488E-82F0-B00DFE9C72BF}" name="best_pearson_r" dataDxfId="194"/>
-    <tableColumn id="4" xr3:uid="{44E404A7-64C9-48D1-BEA8-37DAC6FF833D}" name="seed_a_e" dataDxfId="193"/>
-    <tableColumn id="5" xr3:uid="{0031A10A-5BB9-4A13-AB85-C453BE259947}" name="seed_b_e" dataDxfId="192"/>
-    <tableColumn id="6" xr3:uid="{A4149257-77E3-4DA3-8D66-E2741B5431E8}" name="seed_d_e" dataDxfId="191"/>
-    <tableColumn id="7" xr3:uid="{DA03BCA9-49D0-4373-AF86-D098B2729C46}" name="seed_c_I_sst" dataDxfId="190"/>
-    <tableColumn id="8" xr3:uid="{B468D88A-1953-4115-BC1A-7553BD6F03F0}" name="seed_c_I_vip" dataDxfId="189"/>
-    <tableColumn id="9" xr3:uid="{BD34FD95-EF0C-4801-B561-1472399ADC58}" name="seed_c_I_pv" dataDxfId="188"/>
-    <tableColumn id="10" xr3:uid="{4CBC17EF-CFF0-4154-B2C4-A4A8888EAB5A}" name="seed_r_0_sst" dataDxfId="187"/>
-    <tableColumn id="11" xr3:uid="{6D288E8E-6667-4469-8AD1-E62747A423DA}" name="seed_r_0_vip" dataDxfId="186"/>
-    <tableColumn id="12" xr3:uid="{9F67D3E9-516C-4278-8CDA-BB0CF64B9740}" name="seed_r_0_pv" dataDxfId="185"/>
-    <tableColumn id="13" xr3:uid="{D5F59086-E128-4CCD-AF15-4E50E57864D1}" name="I_background_e" dataDxfId="184"/>
-    <tableColumn id="14" xr3:uid="{A73EF0CC-855A-45BB-9A63-198EE6689667}" name="I_background_i" dataDxfId="183"/>
-    <tableColumn id="15" xr3:uid="{6960877C-3EFB-49C8-816F-12137BCD97E2}" name="I_background_dend" dataDxfId="182"/>
-    <tableColumn id="16" xr3:uid="{B5C47147-4CF4-474B-92B8-CAB79CF8B07E}" name="mu_ee" dataDxfId="181"/>
-    <tableColumn id="17" xr3:uid="{20F72C98-CEC9-42A5-B3F3-DC5463DB0F1A}" name="mu_ie" dataDxfId="180"/>
-    <tableColumn id="18" xr3:uid="{6849C2FE-7DA3-4843-98B5-75098CE7A33F}" name="e_grad_min" dataDxfId="179"/>
-    <tableColumn id="19" xr3:uid="{982464DB-B2BB-49C3-8939-02D2736F4AA8}" name="balloon_kappa" dataDxfId="178"/>
-    <tableColumn id="20" xr3:uid="{066BD199-F963-4A3B-B6A5-EFAA10564156}" name="balloon_gamma" dataDxfId="177"/>
-    <tableColumn id="21" xr3:uid="{A35DF0CE-40AE-4FAF-84E1-C6D5F0A8913D}" name="balloon_tau" dataDxfId="176"/>
+    <tableColumn id="1" xr3:uid="{90D971B2-8A12-4663-B59E-A64B9E3ACB20}" name="final_evaluation_seed" dataDxfId="320"/>
+    <tableColumn id="2" xr3:uid="{BDA294FC-58D6-46F6-9587-EF102D78D712}" name="best_difference_vector_cosine" dataDxfId="319"/>
+    <tableColumn id="3" xr3:uid="{8DADFB6C-E620-488E-82F0-B00DFE9C72BF}" name="best_pearson_r" dataDxfId="318"/>
+    <tableColumn id="4" xr3:uid="{44E404A7-64C9-48D1-BEA8-37DAC6FF833D}" name="seed_a_e" dataDxfId="317"/>
+    <tableColumn id="5" xr3:uid="{0031A10A-5BB9-4A13-AB85-C453BE259947}" name="seed_b_e" dataDxfId="316"/>
+    <tableColumn id="6" xr3:uid="{A4149257-77E3-4DA3-8D66-E2741B5431E8}" name="seed_d_e" dataDxfId="315"/>
+    <tableColumn id="7" xr3:uid="{DA03BCA9-49D0-4373-AF86-D098B2729C46}" name="seed_c_I_sst" dataDxfId="314"/>
+    <tableColumn id="8" xr3:uid="{B468D88A-1953-4115-BC1A-7553BD6F03F0}" name="seed_c_I_vip" dataDxfId="313"/>
+    <tableColumn id="9" xr3:uid="{BD34FD95-EF0C-4801-B561-1472399ADC58}" name="seed_c_I_pv" dataDxfId="312"/>
+    <tableColumn id="10" xr3:uid="{4CBC17EF-CFF0-4154-B2C4-A4A8888EAB5A}" name="seed_r_0_sst" dataDxfId="311"/>
+    <tableColumn id="11" xr3:uid="{6D288E8E-6667-4469-8AD1-E62747A423DA}" name="seed_r_0_vip" dataDxfId="310"/>
+    <tableColumn id="12" xr3:uid="{9F67D3E9-516C-4278-8CDA-BB0CF64B9740}" name="seed_r_0_pv" dataDxfId="309"/>
+    <tableColumn id="13" xr3:uid="{D5F59086-E128-4CCD-AF15-4E50E57864D1}" name="I_background_e" dataDxfId="308"/>
+    <tableColumn id="14" xr3:uid="{A73EF0CC-855A-45BB-9A63-198EE6689667}" name="I_background_i" dataDxfId="307"/>
+    <tableColumn id="15" xr3:uid="{6960877C-3EFB-49C8-816F-12137BCD97E2}" name="I_background_dend" dataDxfId="306"/>
+    <tableColumn id="16" xr3:uid="{B5C47147-4CF4-474B-92B8-CAB79CF8B07E}" name="mu_ee" dataDxfId="305"/>
+    <tableColumn id="17" xr3:uid="{20F72C98-CEC9-42A5-B3F3-DC5463DB0F1A}" name="mu_ie" dataDxfId="304"/>
+    <tableColumn id="18" xr3:uid="{6849C2FE-7DA3-4843-98B5-75098CE7A33F}" name="e_grad_min" dataDxfId="303"/>
+    <tableColumn id="19" xr3:uid="{982464DB-B2BB-49C3-8939-02D2736F4AA8}" name="balloon_kappa" dataDxfId="302"/>
+    <tableColumn id="20" xr3:uid="{066BD199-F963-4A3B-B6A5-EFAA10564156}" name="balloon_gamma" dataDxfId="301"/>
+    <tableColumn id="21" xr3:uid="{A35DF0CE-40AE-4FAF-84E1-C6D5F0A8913D}" name="balloon_tau" dataDxfId="300"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}" name="Table1" displayName="Table1" ref="C4:M14" totalsRowShown="0" headerRowDxfId="92" dataDxfId="90" headerRowBorderDxfId="91" tableBorderDxfId="89">
-  <autoFilter ref="C4:M14" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{87805D45-55EC-4CC4-8B30-E06DA4E7E751}" name="final_evaluation_seed" dataDxfId="88"/>
-    <tableColumn id="2" xr3:uid="{79824F93-C2A5-45B6-9B69-441998802D80}" name="best_pearson_r" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{7EAF5609-B791-402E-8A39-55B740926D2B}" name="I_background_e" dataDxfId="86"/>
-    <tableColumn id="4" xr3:uid="{5EE101D7-0D41-494A-805A-94CFC73331CF}" name="I_background_i" dataDxfId="85"/>
-    <tableColumn id="5" xr3:uid="{2CCF00EF-4BDB-4EB6-A318-9502957678DF}" name="I_background_dend" dataDxfId="84"/>
-    <tableColumn id="6" xr3:uid="{F5AB52A3-CD6E-43D7-A21D-129262695C38}" name="mu_ee" dataDxfId="83"/>
-    <tableColumn id="7" xr3:uid="{778CC36A-8D50-4F01-8B3E-FCAED3521F9B}" name="mu_ie" dataDxfId="82"/>
-    <tableColumn id="8" xr3:uid="{A7B4CCC7-3054-4367-9B57-4F9D70B71AE8}" name="e_grad_min" dataDxfId="81"/>
-    <tableColumn id="9" xr3:uid="{6C33EE26-7CA7-4527-87D8-E28DD20FFD4E}" name="balloon_kappa" dataDxfId="80"/>
-    <tableColumn id="10" xr3:uid="{DBBC495E-05F7-4608-AD56-F33F1FD9FB2E}" name="balloon_gamma" dataDxfId="79"/>
-    <tableColumn id="11" xr3:uid="{D7DB4319-ACF4-4A69-B4F4-EBD25833DB72}" name="balloon_tau" dataDxfId="78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}" name="Table17" displayName="Table17" ref="A1:N11" totalsRowShown="0" headerRowDxfId="44" dataDxfId="45" headerRowBorderDxfId="60" tableBorderDxfId="61">
+  <autoFilter ref="A1:N11" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{946C78F0-5ED6-4C82-B486-0A2D01401586}" name="final_evaluation_seed" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{F6F73ED1-AC25-4A5B-AA43-B4420270A65B}" name="best_pearson_r" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{9D33DA5E-9FA5-4B81-8347-66FB3F9D278F}" name="I_background_e" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{045CBE2B-CC02-4815-AFDF-FD55F14A5948}" name="I_background_i" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{DD07A8E1-0F8D-4F93-9FFC-80537E7DA893}" name="I_background_dend" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{F002D97C-F001-4AAB-86C7-02AFD658391E}" name="mu_ee" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{6A9A90F5-365B-424C-8DFB-AC07BB4F58AB}" name="mu_ie" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{3C77AB83-9D42-417E-973A-786B92AD8D39}" name="e_grad_min" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{202C73E4-ED7F-44C3-8FE0-67B8DEC3AF51}" name="balloon_kappa" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{39BA6440-2759-406C-962E-1F482C31D9D8}" name="balloon_gamma" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{71495690-5E12-40F8-8FB8-D35062B95476}" name="balloon_tau" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{D2BEB5FD-80DF-4E80-AD46-55385CB1B6FF}" name="Stim" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{7A8508B0-FDAF-4D41-8BA2-B789691A3BE1}" name="Auto" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{42D86400-C902-4CEB-A96A-D8CE8C7A5EE0}" name="BOLD" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}" name="Table1411" displayName="Table1411" ref="T21:V31" totalsRowShown="0">
-  <autoFilter ref="T21:V31" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2EE0C1C9-847E-49D1-B328-3A3EED7F56C1}" name="Stim" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{865FC042-E96D-4C4D-B1EA-4B7C3183DA79}" name="Auto" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{D9EC8ABD-24A2-4068-9CAB-09D34D97FE88}" name="BOLD" dataDxfId="75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0AA8468E-35CF-47CB-BBB1-E82D79B508B4}" name="Table112" displayName="Table112" ref="A1:O11" totalsRowShown="0" headerRowDxfId="188" dataDxfId="186" headerRowBorderDxfId="187" tableBorderDxfId="185">
+  <autoFilter ref="A1:O11" xr:uid="{0AA8468E-35CF-47CB-BBB1-E82D79B508B4}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{5A2518A5-0C39-4BE0-8539-9F65123ED022}" name="seed" dataDxfId="184"/>
+    <tableColumn id="2" xr3:uid="{DECF84D9-CAF5-47BD-A6E4-D268671B8AF0}" name="r" dataDxfId="183"/>
+    <tableColumn id="3" xr3:uid="{DFB8AAA2-2333-48A2-BBEC-5BC4763C536A}" name="I_background_e" dataDxfId="182"/>
+    <tableColumn id="4" xr3:uid="{A0403004-5B3F-4971-82E7-C3DD9CC768BC}" name="I_background_i" dataDxfId="181"/>
+    <tableColumn id="5" xr3:uid="{55645ADB-2DE6-4470-8D97-7BD3E8A2072B}" name="I_background_dend" dataDxfId="180"/>
+    <tableColumn id="6" xr3:uid="{DE4F9698-73B0-45AE-98CB-18EC17C1E5C7}" name="mu_ee" dataDxfId="179"/>
+    <tableColumn id="7" xr3:uid="{2D122CFB-25EF-479D-9614-B53C87A158B9}" name="mu_ie" dataDxfId="178"/>
+    <tableColumn id="8" xr3:uid="{57738AAA-F1FC-4531-8EF7-1E8364CA800A}" name="e_grad_min" dataDxfId="177"/>
+    <tableColumn id="9" xr3:uid="{6825AB37-C2BD-44BF-B0E4-270EE0FB0A7E}" name="balloon_kappa" dataDxfId="176"/>
+    <tableColumn id="10" xr3:uid="{C1515A5A-0566-48B8-B6A6-70B8E1EAD853}" name="balloon_gamma" dataDxfId="175"/>
+    <tableColumn id="11" xr3:uid="{B90DC991-DB68-4B30-A5C5-B61FEB53097C}" name="balloon_tau" dataDxfId="174"/>
+    <tableColumn id="12" xr3:uid="{0D0F6034-D566-4618-AEC8-3275BFF2F760}" name="Stim" dataDxfId="173"/>
+    <tableColumn id="13" xr3:uid="{C91D58C0-382F-4FF3-8460-220BACFC2671}" name="Auto" dataDxfId="172"/>
+    <tableColumn id="14" xr3:uid="{E8779799-2FBC-4C3A-A217-D9C280212DC4}" name="BOLD" dataDxfId="171"/>
+    <tableColumn id="15" xr3:uid="{7671ADD5-87B4-43C4-A4D2-AEFEA0DFC960}" name="cosine" dataDxfId="170"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0AA8468E-35CF-47CB-BBB1-E82D79B508B4}" name="Table112" displayName="Table112" ref="A1:O11" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71">
-  <autoFilter ref="A1:O11" xr:uid="{0AA8468E-35CF-47CB-BBB1-E82D79B508B4}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5A2518A5-0C39-4BE0-8539-9F65123ED022}" name="seed" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{DECF84D9-CAF5-47BD-A6E4-D268671B8AF0}" name="r" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{DFB8AAA2-2333-48A2-BBEC-5BC4763C536A}" name="I_background_e" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{A0403004-5B3F-4971-82E7-C3DD9CC768BC}" name="I_background_i" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{55645ADB-2DE6-4470-8D97-7BD3E8A2072B}" name="I_background_dend" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{DE4F9698-73B0-45AE-98CB-18EC17C1E5C7}" name="mu_ee" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{2D122CFB-25EF-479D-9614-B53C87A158B9}" name="mu_ie" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{57738AAA-F1FC-4531-8EF7-1E8364CA800A}" name="e_grad_min" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{6825AB37-C2BD-44BF-B0E4-270EE0FB0A7E}" name="balloon_kappa" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{C1515A5A-0566-48B8-B6A6-70B8E1EAD853}" name="balloon_gamma" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{B90DC991-DB68-4B30-A5C5-B61FEB53097C}" name="balloon_tau" dataDxfId="60"/>
-    <tableColumn id="12" xr3:uid="{0D0F6034-D566-4618-AEC8-3275BFF2F760}" name="Stim" dataDxfId="59"/>
-    <tableColumn id="13" xr3:uid="{C91D58C0-382F-4FF3-8460-220BACFC2671}" name="Auto" dataDxfId="58"/>
-    <tableColumn id="14" xr3:uid="{E8779799-2FBC-4C3A-A217-D9C280212DC4}" name="BOLD" dataDxfId="57"/>
-    <tableColumn id="15" xr3:uid="{7671ADD5-87B4-43C4-A4D2-AEFEA0DFC960}" name="cosine" dataDxfId="56"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F965AD62-A08E-4EEF-9030-458864B7316B}" name="Table2" displayName="Table2" ref="A1:D41" totalsRowShown="0">
   <autoFilter ref="A1:D41" xr:uid="{F965AD62-A08E-4EEF-9030-458864B7316B}"/>
   <tableColumns count="4">
@@ -6456,99 +6956,131 @@
 </table>
 </file>
 
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}" name="Table1" displayName="Table1" ref="C4:M14" totalsRowShown="0" headerRowDxfId="206" dataDxfId="204" headerRowBorderDxfId="205" tableBorderDxfId="203">
+  <autoFilter ref="C4:M14" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{87805D45-55EC-4CC4-8B30-E06DA4E7E751}" name="final_evaluation_seed" dataDxfId="202"/>
+    <tableColumn id="2" xr3:uid="{79824F93-C2A5-45B6-9B69-441998802D80}" name="best_pearson_r" dataDxfId="201"/>
+    <tableColumn id="3" xr3:uid="{7EAF5609-B791-402E-8A39-55B740926D2B}" name="I_background_e" dataDxfId="200"/>
+    <tableColumn id="4" xr3:uid="{5EE101D7-0D41-494A-805A-94CFC73331CF}" name="I_background_i" dataDxfId="199"/>
+    <tableColumn id="5" xr3:uid="{2CCF00EF-4BDB-4EB6-A318-9502957678DF}" name="I_background_dend" dataDxfId="198"/>
+    <tableColumn id="6" xr3:uid="{F5AB52A3-CD6E-43D7-A21D-129262695C38}" name="mu_ee" dataDxfId="197"/>
+    <tableColumn id="7" xr3:uid="{778CC36A-8D50-4F01-8B3E-FCAED3521F9B}" name="mu_ie" dataDxfId="196"/>
+    <tableColumn id="8" xr3:uid="{A7B4CCC7-3054-4367-9B57-4F9D70B71AE8}" name="e_grad_min" dataDxfId="195"/>
+    <tableColumn id="9" xr3:uid="{6C33EE26-7CA7-4527-87D8-E28DD20FFD4E}" name="balloon_kappa" dataDxfId="194"/>
+    <tableColumn id="10" xr3:uid="{DBBC495E-05F7-4608-AD56-F33F1FD9FB2E}" name="balloon_gamma" dataDxfId="193"/>
+    <tableColumn id="11" xr3:uid="{D7DB4319-ACF4-4A69-B4F4-EBD25833DB72}" name="balloon_tau" dataDxfId="192"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}" name="Table1411" displayName="Table1411" ref="T21:V31" totalsRowShown="0">
+  <autoFilter ref="T21:V31" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{2EE0C1C9-847E-49D1-B328-3A3EED7F56C1}" name="Stim" dataDxfId="191"/>
+    <tableColumn id="2" xr3:uid="{865FC042-E96D-4C4D-B1EA-4B7C3183DA79}" name="Auto" dataDxfId="190"/>
+    <tableColumn id="3" xr3:uid="{D9EC8ABD-24A2-4068-9CAB-09D34D97FE88}" name="BOLD" dataDxfId="189"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{2B1EA398-6077-43CD-8151-400DF211F33C}" name="Table1820" displayName="Table1820" ref="A1:U11" totalsRowShown="0">
   <autoFilter ref="A1:U11" xr:uid="{2B1EA398-6077-43CD-8151-400DF211F33C}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{DFDC78A7-E47E-494D-9C61-107C2DD6F0AD}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="305"/>
-    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="304"/>
-    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="303"/>
-    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="302"/>
-    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="301"/>
-    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="300"/>
-    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="299"/>
-    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="298"/>
-    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="297"/>
-    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="296"/>
-    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="295"/>
-    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="294"/>
-    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="293"/>
-    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="292"/>
-    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="291"/>
-    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="290"/>
-    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="289"/>
-    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="288"/>
-    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="287"/>
-    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="286"/>
+    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="169"/>
+    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="168"/>
+    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="167"/>
+    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="166"/>
+    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="165"/>
+    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="164"/>
+    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="163"/>
+    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="162"/>
+    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="161"/>
+    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="160"/>
+    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="159"/>
+    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="158"/>
+    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="157"/>
+    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="156"/>
+    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="155"/>
+    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="154"/>
+    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="153"/>
+    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="152"/>
+    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="151"/>
+    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="285" headerRowBorderDxfId="284" tableBorderDxfId="283">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="149" headerRowBorderDxfId="148" tableBorderDxfId="147">
   <autoFilter ref="A22:U32" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="282" totalsRowDxfId="281"/>
-    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="280">
+    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="146" totalsRowDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="144">
       <calculatedColumnFormula>(B2-B$17)/B$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="279">
+    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="143">
       <calculatedColumnFormula>(C2-C$17)/C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="278">
+    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="142">
       <calculatedColumnFormula>(D2-D$17)/D$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="277">
+    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="141">
       <calculatedColumnFormula>(E2-E$17)/E$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="276">
+    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="140">
       <calculatedColumnFormula>(F2-F$17)/F$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="275">
+    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="139">
       <calculatedColumnFormula>(G2-G$17)/G$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="274">
+    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="138">
       <calculatedColumnFormula>(H2-H$17)/H$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="273">
+    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="137">
       <calculatedColumnFormula>(I2-I$17)/I$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="272">
+    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="136">
       <calculatedColumnFormula>(J2-J$17)/J$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="271">
+    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="135">
       <calculatedColumnFormula>(K2-K$17)/K$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="270">
+    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="134">
       <calculatedColumnFormula>(L2-L$17)/L$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="269">
+    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="133">
       <calculatedColumnFormula>(M2-M$17)/M$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="268">
+    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="132">
       <calculatedColumnFormula>(N2-N$17)/N$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="267">
+    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="131">
       <calculatedColumnFormula>(O2-O$17)/O$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="266">
+    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="130">
       <calculatedColumnFormula>(P2-P$17)/P$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="265">
+    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="129">
       <calculatedColumnFormula>(Q2-Q$17)/Q$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="264">
+    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="128">
       <calculatedColumnFormula>(R2-R$17)/R$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="263">
+    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="127">
       <calculatedColumnFormula>(S2-S$17)/S$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="262">
+    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="126">
       <calculatedColumnFormula>(T2-T$17)/T$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="261" totalsRowDxfId="260">
+    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="124">
       <calculatedColumnFormula>(U2-U$17)/U$19</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6556,30 +7088,30 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="259" dataDxfId="257" headerRowBorderDxfId="258" tableBorderDxfId="256" totalsRowBorderDxfId="255">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="123" dataDxfId="121" headerRowBorderDxfId="122" tableBorderDxfId="120" totalsRowBorderDxfId="119">
   <autoFilter ref="A77:C87" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="254" totalsRowDxfId="253"/>
-    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="252" totalsRowDxfId="251"/>
-    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="250" totalsRowDxfId="249"/>
+    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="118" totalsRowDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="116" totalsRowDxfId="115"/>
+    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="114" totalsRowDxfId="113"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="248" headerRowBorderDxfId="247" tableBorderDxfId="246">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="112" headerRowBorderDxfId="111" tableBorderDxfId="110">
   <autoFilter ref="F77:I87" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="245"/>
-    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="244">
+    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="108">
       <calculatedColumnFormula>Table32[[#This Row],[best_pearson_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="243">
+    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="107">
       <calculatedColumnFormula>Table32[[#This Row],[best_difference_vector_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="242">
+    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="106">
       <calculatedColumnFormula>Table33[[#This Row],[best_pearson_r]]+Table33[[#This Row],[best_difference_vector_r]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6587,12 +7119,12 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="241" headerRowBorderDxfId="240" tableBorderDxfId="239">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="105" headerRowBorderDxfId="104" tableBorderDxfId="103">
   <autoFilter ref="A50:L60" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="238"/>
-    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="237">
+    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="101">
       <calculatedColumnFormula>D2/B$46</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{19814F94-E875-4959-AFE5-7848DB2FC6EC}" name="seed_b_e">
@@ -6619,115 +7151,76 @@
     <tableColumn id="10" xr3:uid="{40D401B7-4651-43DA-A526-6D0D5CEB229D}" name="seed_r_0_pv">
       <calculatedColumnFormula>L2/J$46</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="236"/>
-    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="235"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{7D09C930-E854-4E6C-82B9-35C9655B8B61}" name="Table26" displayName="Table26" ref="N50:Y60" totalsRowShown="0">
-  <autoFilter ref="N50:Y60" xr:uid="{7D09C930-E854-4E6C-82B9-35C9655B8B61}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{016F4276-D961-4FD1-B77D-67CC688C159B}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="234">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_a_e]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="233">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_b_e]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="232">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_d_e]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="231">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="230">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="229">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="228">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="227">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="226">
-      <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="225"/>
-    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="224"/>
+    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="100"/>
+    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="99"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DFD61772-D69C-4F23-9385-16963B13A2DF}" name="Table4" displayName="Table4" ref="A22:U32" totalsRowShown="0" headerRowDxfId="175" headerRowBorderDxfId="174" tableBorderDxfId="173">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DFD61772-D69C-4F23-9385-16963B13A2DF}" name="Table4" displayName="Table4" ref="A22:U32" totalsRowShown="0" headerRowDxfId="299" headerRowBorderDxfId="298" tableBorderDxfId="297">
   <autoFilter ref="A22:U32" xr:uid="{DFD61772-D69C-4F23-9385-16963B13A2DF}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{1AEB5A3A-F66E-487F-8B57-78476E3E17F7}" name="final_evaluation_seed" dataDxfId="172"/>
-    <tableColumn id="2" xr3:uid="{87B559BD-A209-4B7E-8D6E-BB923AB7A8E8}" name="best_difference_vector_cosine" dataDxfId="171">
+    <tableColumn id="1" xr3:uid="{1AEB5A3A-F66E-487F-8B57-78476E3E17F7}" name="final_evaluation_seed" dataDxfId="296"/>
+    <tableColumn id="2" xr3:uid="{87B559BD-A209-4B7E-8D6E-BB923AB7A8E8}" name="best_difference_vector_cosine" dataDxfId="295">
       <calculatedColumnFormula>(B2-B$17)/B$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{385CEE55-6660-4848-AF20-71847F4B542D}" name="best_pearson_r" dataDxfId="170">
+    <tableColumn id="3" xr3:uid="{385CEE55-6660-4848-AF20-71847F4B542D}" name="best_pearson_r" dataDxfId="294">
       <calculatedColumnFormula>(C2-C$17)/C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9FD6AB42-5FFB-4D20-B3F4-CE63A83B6D12}" name="seed_a_e" dataDxfId="169">
+    <tableColumn id="4" xr3:uid="{9FD6AB42-5FFB-4D20-B3F4-CE63A83B6D12}" name="seed_a_e" dataDxfId="293">
       <calculatedColumnFormula>(D2-D$17)/D$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12425BD5-667B-4BD9-A2D5-E3413A89F26B}" name="seed_b_e" dataDxfId="168">
+    <tableColumn id="5" xr3:uid="{12425BD5-667B-4BD9-A2D5-E3413A89F26B}" name="seed_b_e" dataDxfId="292">
       <calculatedColumnFormula>(E2-E$17)/E$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{48A1E88D-847D-44D6-8AA1-FDFD1F597332}" name="seed_d_e" dataDxfId="167">
+    <tableColumn id="6" xr3:uid="{48A1E88D-847D-44D6-8AA1-FDFD1F597332}" name="seed_d_e" dataDxfId="291">
       <calculatedColumnFormula>(F2-F$17)/F$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8BADB531-31CB-4F1E-A33D-A4903B0CCA47}" name="seed_c_I_sst" dataDxfId="166">
+    <tableColumn id="7" xr3:uid="{8BADB531-31CB-4F1E-A33D-A4903B0CCA47}" name="seed_c_I_sst" dataDxfId="290">
       <calculatedColumnFormula>(G2-G$17)/G$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F7C9E813-1F15-4645-A977-D3F082CB992C}" name="seed_c_I_vip" dataDxfId="165">
+    <tableColumn id="8" xr3:uid="{F7C9E813-1F15-4645-A977-D3F082CB992C}" name="seed_c_I_vip" dataDxfId="289">
       <calculatedColumnFormula>(H2-H$17)/H$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5D08ABDD-556E-4A7C-A59D-5F82AF9D6DCC}" name="seed_c_I_pv" dataDxfId="164">
+    <tableColumn id="9" xr3:uid="{5D08ABDD-556E-4A7C-A59D-5F82AF9D6DCC}" name="seed_c_I_pv" dataDxfId="288">
       <calculatedColumnFormula>(I2-I$17)/I$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E98DCCCB-DE18-497E-B8B5-617FC5273627}" name="seed_r_0_sst" dataDxfId="163">
+    <tableColumn id="10" xr3:uid="{E98DCCCB-DE18-497E-B8B5-617FC5273627}" name="seed_r_0_sst" dataDxfId="287">
       <calculatedColumnFormula>(J2-J$17)/J$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4A41846B-5748-4141-B926-2D1720DDC295}" name="seed_r_0_vip" dataDxfId="162">
+    <tableColumn id="11" xr3:uid="{4A41846B-5748-4141-B926-2D1720DDC295}" name="seed_r_0_vip" dataDxfId="286">
       <calculatedColumnFormula>(K2-K$17)/K$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00345844-80B6-4710-BBB6-182F979E75C0}" name="seed_r_0_pv" dataDxfId="161">
+    <tableColumn id="12" xr3:uid="{00345844-80B6-4710-BBB6-182F979E75C0}" name="seed_r_0_pv" dataDxfId="285">
       <calculatedColumnFormula>(L2-L$17)/L$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{8C4D71B1-F32C-4B68-8E32-C87B2962B441}" name="I_background_e" dataDxfId="160">
+    <tableColumn id="13" xr3:uid="{8C4D71B1-F32C-4B68-8E32-C87B2962B441}" name="I_background_e" dataDxfId="284">
       <calculatedColumnFormula>(M2-M$17)/M$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6C6EEF91-A2EB-4237-810F-E03C26A20E2E}" name="I_background_i" dataDxfId="159">
+    <tableColumn id="14" xr3:uid="{6C6EEF91-A2EB-4237-810F-E03C26A20E2E}" name="I_background_i" dataDxfId="283">
       <calculatedColumnFormula>(N2-N$17)/N$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F6C5A251-ECD9-431A-B5BC-50BF7B66898F}" name="I_background_dend" dataDxfId="158">
+    <tableColumn id="15" xr3:uid="{F6C5A251-ECD9-431A-B5BC-50BF7B66898F}" name="I_background_dend" dataDxfId="282">
       <calculatedColumnFormula>(O2-O$17)/O$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{290A288B-4107-4FA2-8DAA-9AC2562ABE78}" name="mu_ee" dataDxfId="157">
+    <tableColumn id="16" xr3:uid="{290A288B-4107-4FA2-8DAA-9AC2562ABE78}" name="mu_ee" dataDxfId="281">
       <calculatedColumnFormula>(P2-P$17)/P$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C8FEE778-D4A0-49C9-812A-38E859DD0CF6}" name="mu_ie" dataDxfId="156">
+    <tableColumn id="17" xr3:uid="{C8FEE778-D4A0-49C9-812A-38E859DD0CF6}" name="mu_ie" dataDxfId="280">
       <calculatedColumnFormula>(Q2-Q$17)/Q$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00DD43C9-F907-4912-A951-59897BDE04D8}" name="e_grad_min" dataDxfId="155">
+    <tableColumn id="18" xr3:uid="{00DD43C9-F907-4912-A951-59897BDE04D8}" name="e_grad_min" dataDxfId="279">
       <calculatedColumnFormula>(R2-R$17)/R$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{3172B8BE-C05C-4B6C-B46C-82BFCBC9F5B6}" name="balloon_kappa" dataDxfId="154">
+    <tableColumn id="19" xr3:uid="{3172B8BE-C05C-4B6C-B46C-82BFCBC9F5B6}" name="balloon_kappa" dataDxfId="278">
       <calculatedColumnFormula>(S2-S$17)/S$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F109293C-9D49-45E3-8FB2-18F0FB9F9C49}" name="balloon_gamma" dataDxfId="153">
+    <tableColumn id="20" xr3:uid="{F109293C-9D49-45E3-8FB2-18F0FB9F9C49}" name="balloon_gamma" dataDxfId="277">
       <calculatedColumnFormula>(T2-T$17)/T$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{9DB8825C-87FA-4083-9DE6-33B59F795E4F}" name="balloon_tau" dataDxfId="152">
+    <tableColumn id="21" xr3:uid="{9DB8825C-87FA-4083-9DE6-33B59F795E4F}" name="balloon_tau" dataDxfId="276">
       <calculatedColumnFormula>(U2-U$17)/U$19</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6736,78 +7229,117 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="223" headerRowBorderDxfId="222" tableBorderDxfId="221">
-  <autoFilter ref="A63:L73" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{7D09C930-E854-4E6C-82B9-35C9655B8B61}" name="Table26" displayName="Table26" ref="N50:Y60" totalsRowShown="0">
+  <autoFilter ref="N50:Y60" xr:uid="{7D09C930-E854-4E6C-82B9-35C9655B8B61}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="219">
-      <calculatedColumnFormula>LOG(B51,2)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{016F4276-D961-4FD1-B77D-67CC688C159B}" name="final_evaluation_seed"/>
+    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="98">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="218">
-      <calculatedColumnFormula>LOG(C51,2)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="97">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="217">
-      <calculatedColumnFormula>LOG(D51,2)</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="96">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="216">
-      <calculatedColumnFormula>LOG(E51,2)</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="95">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="215">
-      <calculatedColumnFormula>LOG(F51,2)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="94">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="214">
-      <calculatedColumnFormula>LOG(G51,2)</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="93">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="213">
-      <calculatedColumnFormula>LOG(H51,2)</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="92">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="212">
-      <calculatedColumnFormula>LOG(I51,2)</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="91">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="211">
-      <calculatedColumnFormula>LOG(J51,2)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="90">
+      <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="210"/>
-    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="209"/>
+    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="89"/>
+    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="87" headerRowBorderDxfId="86" tableBorderDxfId="85">
+  <autoFilter ref="A63:L73" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="83">
+      <calculatedColumnFormula>LOG(B51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="82">
+      <calculatedColumnFormula>LOG(C51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="81">
+      <calculatedColumnFormula>LOG(D51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="80">
+      <calculatedColumnFormula>LOG(E51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="79">
+      <calculatedColumnFormula>LOG(F51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="78">
+      <calculatedColumnFormula>LOG(G51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="77">
+      <calculatedColumnFormula>LOG(H51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="76">
+      <calculatedColumnFormula>LOG(I51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="75">
+      <calculatedColumnFormula>LOG(J51,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="74"/>
+    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="73"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{2806A620-3E6B-4861-AE70-E4C12B09B013}" name="Table31" displayName="Table31" ref="N63:Y73" totalsRowShown="0">
   <autoFilter ref="N63:Y73" xr:uid="{2806A620-3E6B-4861-AE70-E4C12B09B013}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00CF6880-3883-432C-B0EF-EBC8FF079300}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="208">
+    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="72">
       <calculatedColumnFormula>Table28[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="207">
+    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="71">
       <calculatedColumnFormula>Table28[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="206">
+    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="70">
       <calculatedColumnFormula>Table28[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="205">
+    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="69">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="204">
+    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="68">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="203">
+    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="67">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="202">
+    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="66">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="201">
+    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="65">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="200">
+    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="64">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="199"/>
-    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="198"/>
+    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="63"/>
+    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6818,31 +7350,31 @@
   <autoFilter ref="A48:J58" xr:uid="{97EFFDD9-6247-402C-AB46-14867C9F85D4}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F4FBFAE2-9088-497A-9057-916DC5DB15D4}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{C4B1F04F-8E5A-439A-932B-B7B90B770F92}" name="seed_a_e" dataDxfId="151">
+    <tableColumn id="2" xr3:uid="{C4B1F04F-8E5A-439A-932B-B7B90B770F92}" name="seed_a_e" dataDxfId="275">
       <calculatedColumnFormula>D2/B$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB9D53EB-8B03-4520-98A3-50420B8DDFEA}" name="seed_b_e" dataDxfId="150">
+    <tableColumn id="3" xr3:uid="{DB9D53EB-8B03-4520-98A3-50420B8DDFEA}" name="seed_b_e" dataDxfId="274">
       <calculatedColumnFormula>E2/C$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{635855CC-4D50-4F2E-AD09-A74DD01A1ADD}" name="seed_d_e" dataDxfId="149">
+    <tableColumn id="4" xr3:uid="{635855CC-4D50-4F2E-AD09-A74DD01A1ADD}" name="seed_d_e" dataDxfId="273">
       <calculatedColumnFormula>F2/D$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F3709610-A526-40FE-B7D2-70F6B421C5CC}" name="seed_c_I_sst" dataDxfId="148">
+    <tableColumn id="5" xr3:uid="{F3709610-A526-40FE-B7D2-70F6B421C5CC}" name="seed_c_I_sst" dataDxfId="272">
       <calculatedColumnFormula>G2/E$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F5B39384-6EB0-4288-80D9-908F2B12B79D}" name="seed_c_I_vip" dataDxfId="147">
+    <tableColumn id="6" xr3:uid="{F5B39384-6EB0-4288-80D9-908F2B12B79D}" name="seed_c_I_vip" dataDxfId="271">
       <calculatedColumnFormula>H2/F$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{66CDCA44-9C31-41A1-8C31-0B27E71C85A1}" name="seed_c_I_pv" dataDxfId="146">
+    <tableColumn id="7" xr3:uid="{66CDCA44-9C31-41A1-8C31-0B27E71C85A1}" name="seed_c_I_pv" dataDxfId="270">
       <calculatedColumnFormula>I2/G$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{23822275-B279-4D54-B818-6046B8F37F2F}" name="seed_r_0_sst" dataDxfId="145">
+    <tableColumn id="8" xr3:uid="{23822275-B279-4D54-B818-6046B8F37F2F}" name="seed_r_0_sst" dataDxfId="269">
       <calculatedColumnFormula>J2/H$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{9BA3CF7B-6BE4-4514-9ED5-A9F04AE8D4D2}" name="seed_r_0_vip" dataDxfId="144">
+    <tableColumn id="9" xr3:uid="{9BA3CF7B-6BE4-4514-9ED5-A9F04AE8D4D2}" name="seed_r_0_vip" dataDxfId="268">
       <calculatedColumnFormula>K2/I$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{9684379E-C620-49D0-9297-A073F778E9B6}" name="seed_r_0_pv" dataDxfId="143">
+    <tableColumn id="10" xr3:uid="{9684379E-C620-49D0-9297-A073F778E9B6}" name="seed_r_0_pv" dataDxfId="267">
       <calculatedColumnFormula>L2/J$44</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6851,35 +7383,35 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4DD75104-6774-4C8F-8B0B-A5E15769D0D0}" name="Table8" displayName="Table8" ref="A66:J76" totalsRowShown="0" headerRowDxfId="142" headerRowBorderDxfId="141" tableBorderDxfId="140">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4DD75104-6774-4C8F-8B0B-A5E15769D0D0}" name="Table8" displayName="Table8" ref="A66:J76" totalsRowShown="0" headerRowDxfId="266" headerRowBorderDxfId="265" tableBorderDxfId="264">
   <autoFilter ref="A66:J76" xr:uid="{4DD75104-6774-4C8F-8B0B-A5E15769D0D0}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{22FE01C1-7C04-4B98-B6C0-92DBAFAFCA56}" name="final_evaluation_seed" dataDxfId="139"/>
-    <tableColumn id="2" xr3:uid="{1F95DED3-D749-4644-83B5-6B330DC0DC38}" name="seed_a_e" dataDxfId="138">
+    <tableColumn id="1" xr3:uid="{22FE01C1-7C04-4B98-B6C0-92DBAFAFCA56}" name="final_evaluation_seed" dataDxfId="263"/>
+    <tableColumn id="2" xr3:uid="{1F95DED3-D749-4644-83B5-6B330DC0DC38}" name="seed_a_e" dataDxfId="262">
       <calculatedColumnFormula>LOG(B49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{02366814-CBD1-45A2-A259-363B4B6E520F}" name="seed_b_e" dataDxfId="137">
+    <tableColumn id="3" xr3:uid="{02366814-CBD1-45A2-A259-363B4B6E520F}" name="seed_b_e" dataDxfId="261">
       <calculatedColumnFormula>LOG(C49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E4CDF7FB-1C5B-46B8-9DD8-2D3797D90AC7}" name="seed_d_e" dataDxfId="136">
+    <tableColumn id="4" xr3:uid="{E4CDF7FB-1C5B-46B8-9DD8-2D3797D90AC7}" name="seed_d_e" dataDxfId="260">
       <calculatedColumnFormula>LOG(D49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{453B0FFC-FD7C-44AA-9A50-64AD33D3319E}" name="seed_c_I_sst" dataDxfId="135">
+    <tableColumn id="5" xr3:uid="{453B0FFC-FD7C-44AA-9A50-64AD33D3319E}" name="seed_c_I_sst" dataDxfId="259">
       <calculatedColumnFormula>LOG(E49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2263A195-7621-4E69-A20A-AD1DCB8039BA}" name="seed_c_I_vip" dataDxfId="134">
+    <tableColumn id="6" xr3:uid="{2263A195-7621-4E69-A20A-AD1DCB8039BA}" name="seed_c_I_vip" dataDxfId="258">
       <calculatedColumnFormula>LOG(F49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5DD607AE-E111-47EF-827E-9F92EE37D88A}" name="seed_c_I_pv" dataDxfId="133">
+    <tableColumn id="7" xr3:uid="{5DD607AE-E111-47EF-827E-9F92EE37D88A}" name="seed_c_I_pv" dataDxfId="257">
       <calculatedColumnFormula>LOG(G49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A1C02190-5F07-4816-9DB5-5A2CB3631EBA}" name="seed_r_0_sst" dataDxfId="132">
+    <tableColumn id="8" xr3:uid="{A1C02190-5F07-4816-9DB5-5A2CB3631EBA}" name="seed_r_0_sst" dataDxfId="256">
       <calculatedColumnFormula>LOG(H49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{81E30CEB-7912-4939-A4D4-2DF9452B08E1}" name="seed_r_0_vip" dataDxfId="131">
+    <tableColumn id="9" xr3:uid="{81E30CEB-7912-4939-A4D4-2DF9452B08E1}" name="seed_r_0_vip" dataDxfId="255">
       <calculatedColumnFormula>LOG(I49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{CEDE804F-029D-4EC6-AF1F-7014BC8A9A11}" name="seed_r_0_pv" dataDxfId="130">
+    <tableColumn id="10" xr3:uid="{CEDE804F-029D-4EC6-AF1F-7014BC8A9A11}" name="seed_r_0_pv" dataDxfId="254">
       <calculatedColumnFormula>LOG(J49,2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6892,54 +7424,54 @@
   <autoFilter ref="L48:V58" xr:uid="{6F7FBBF5-4735-475C-ACA0-5A23C14BF699}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{3F02BD34-270A-4822-956C-2DDCC5712605}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{09E7F0DA-CA50-436D-BDB6-D809D0C3F061}" name="seed_a_e" dataDxfId="129"/>
-    <tableColumn id="3" xr3:uid="{9BDD528B-BC4E-40FD-826B-CDC2F2A66851}" name="seed_b_e" dataDxfId="128"/>
-    <tableColumn id="4" xr3:uid="{CFB644C0-8E98-46D0-A16E-A3B30D7558B4}" name="seed_d_e" dataDxfId="127"/>
-    <tableColumn id="5" xr3:uid="{27BE3A49-7EE0-4BF5-A5EB-DAE368609638}" name="seed_c_I_sst" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{C8DB1166-7992-4A7A-B711-AE1433816777}" name="seed_c_I_vip" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{05B823EE-3D09-41A6-B630-4DA1158655E9}" name="seed_c_I_pv" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{4442F8FB-038E-4A4D-A10D-AEBF4520DEAD}" name="seed_r_0_sst" dataDxfId="123"/>
-    <tableColumn id="9" xr3:uid="{74B2E56A-A200-4799-BC74-E266EEFF9D93}" name="seed_r_0_vip" dataDxfId="122"/>
-    <tableColumn id="10" xr3:uid="{6B158E59-D908-4B50-AB3A-F978257DD29D}" name="seed_r_0_pv" dataDxfId="121"/>
-    <tableColumn id="11" xr3:uid="{DB51154D-A98B-4303-AAD5-5ACAD0949DF1}" name="best_difference_vector_cosine" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{09E7F0DA-CA50-436D-BDB6-D809D0C3F061}" name="seed_a_e" dataDxfId="253"/>
+    <tableColumn id="3" xr3:uid="{9BDD528B-BC4E-40FD-826B-CDC2F2A66851}" name="seed_b_e" dataDxfId="252"/>
+    <tableColumn id="4" xr3:uid="{CFB644C0-8E98-46D0-A16E-A3B30D7558B4}" name="seed_d_e" dataDxfId="251"/>
+    <tableColumn id="5" xr3:uid="{27BE3A49-7EE0-4BF5-A5EB-DAE368609638}" name="seed_c_I_sst" dataDxfId="250"/>
+    <tableColumn id="6" xr3:uid="{C8DB1166-7992-4A7A-B711-AE1433816777}" name="seed_c_I_vip" dataDxfId="249"/>
+    <tableColumn id="7" xr3:uid="{05B823EE-3D09-41A6-B630-4DA1158655E9}" name="seed_c_I_pv" dataDxfId="248"/>
+    <tableColumn id="8" xr3:uid="{4442F8FB-038E-4A4D-A10D-AEBF4520DEAD}" name="seed_r_0_sst" dataDxfId="247"/>
+    <tableColumn id="9" xr3:uid="{74B2E56A-A200-4799-BC74-E266EEFF9D93}" name="seed_r_0_vip" dataDxfId="246"/>
+    <tableColumn id="10" xr3:uid="{6B158E59-D908-4B50-AB3A-F978257DD29D}" name="seed_r_0_pv" dataDxfId="245"/>
+    <tableColumn id="11" xr3:uid="{DB51154D-A98B-4303-AAD5-5ACAD0949DF1}" name="best_difference_vector_cosine" dataDxfId="244"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E28C8B6A-1FB1-4F51-B313-972AE5E332CA}" name="Table814" displayName="Table814" ref="L66:V76" totalsRowShown="0" headerRowDxfId="119" headerRowBorderDxfId="118" tableBorderDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E28C8B6A-1FB1-4F51-B313-972AE5E332CA}" name="Table814" displayName="Table814" ref="L66:V76" totalsRowShown="0" headerRowDxfId="243" headerRowBorderDxfId="242" tableBorderDxfId="241">
   <autoFilter ref="L66:V76" xr:uid="{E28C8B6A-1FB1-4F51-B313-972AE5E332CA}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{015AC9AA-0FB9-4151-943F-AE82B49C07F8}" name="final_evaluation_seed" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{4D0C05EB-6A2A-402F-B9D2-AE471D304861}" name="seed_a_e" dataDxfId="115">
+    <tableColumn id="1" xr3:uid="{015AC9AA-0FB9-4151-943F-AE82B49C07F8}" name="final_evaluation_seed" dataDxfId="240"/>
+    <tableColumn id="2" xr3:uid="{4D0C05EB-6A2A-402F-B9D2-AE471D304861}" name="seed_a_e" dataDxfId="239">
       <calculatedColumnFormula>LOG(M49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F818FC1A-0CB6-49D2-8323-1F1D5C351685}" name="seed_b_e" dataDxfId="114">
+    <tableColumn id="3" xr3:uid="{F818FC1A-0CB6-49D2-8323-1F1D5C351685}" name="seed_b_e" dataDxfId="238">
       <calculatedColumnFormula>LOG(N49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B0B1392D-8E4E-4B92-ADDA-58CB1F8768B7}" name="seed_d_e" dataDxfId="113">
+    <tableColumn id="4" xr3:uid="{B0B1392D-8E4E-4B92-ADDA-58CB1F8768B7}" name="seed_d_e" dataDxfId="237">
       <calculatedColumnFormula>LOG(O49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{18A2346B-DA04-4C32-96E8-691120F0AEE1}" name="seed_c_I_sst" dataDxfId="112">
+    <tableColumn id="5" xr3:uid="{18A2346B-DA04-4C32-96E8-691120F0AEE1}" name="seed_c_I_sst" dataDxfId="236">
       <calculatedColumnFormula>LOG(P49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{827A23AF-D7EF-418C-AE96-E3529E1D74E4}" name="seed_c_I_vip" dataDxfId="111">
+    <tableColumn id="6" xr3:uid="{827A23AF-D7EF-418C-AE96-E3529E1D74E4}" name="seed_c_I_vip" dataDxfId="235">
       <calculatedColumnFormula>LOG(Q49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BB03EA5B-E58C-4978-B947-C4DA9B31F4E8}" name="seed_c_I_pv" dataDxfId="110">
+    <tableColumn id="7" xr3:uid="{BB03EA5B-E58C-4978-B947-C4DA9B31F4E8}" name="seed_c_I_pv" dataDxfId="234">
       <calculatedColumnFormula>LOG(R49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{325C3F8D-426F-49E2-B239-2A986C13BAB3}" name="seed_r_0_sst" dataDxfId="109">
+    <tableColumn id="8" xr3:uid="{325C3F8D-426F-49E2-B239-2A986C13BAB3}" name="seed_r_0_sst" dataDxfId="233">
       <calculatedColumnFormula>LOG(S49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1C9D470D-52B6-46AE-908F-9C78B731AE73}" name="seed_r_0_vip" dataDxfId="108">
+    <tableColumn id="9" xr3:uid="{1C9D470D-52B6-46AE-908F-9C78B731AE73}" name="seed_r_0_vip" dataDxfId="232">
       <calculatedColumnFormula>LOG(T49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{DE930B3E-6CEC-41DC-B7DA-9D377C1E0493}" name="seed_r_0_pv" dataDxfId="107">
+    <tableColumn id="10" xr3:uid="{DE930B3E-6CEC-41DC-B7DA-9D377C1E0493}" name="seed_r_0_pv" dataDxfId="231">
       <calculatedColumnFormula>LOG(U49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D022E080-9A73-4747-BE95-197C6EEE0D66}" name="best_difference_vector_cosine" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{D022E080-9A73-4747-BE95-197C6EEE0D66}" name="best_difference_vector_cosine" dataDxfId="230"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6949,9 +7481,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{FCD4B681-E473-42B6-B040-F1403AF7C04D}" name="Table14" displayName="Table14" ref="Y48:AA58" totalsRowShown="0">
   <autoFilter ref="Y48:AA58" xr:uid="{FCD4B681-E473-42B6-B040-F1403AF7C04D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B6D16439-85A8-46E4-881D-A7A8D9208144}" name="Stim" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{83CB5D98-7946-4391-84D7-7BB717F5267A}" name="Auto" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{500C6F3D-55AA-463E-B538-D91D98F88DB6}" name="BOLD" dataDxfId="103"/>
+    <tableColumn id="1" xr3:uid="{B6D16439-85A8-46E4-881D-A7A8D9208144}" name="Stim" dataDxfId="229"/>
+    <tableColumn id="2" xr3:uid="{83CB5D98-7946-4391-84D7-7BB717F5267A}" name="Auto" dataDxfId="228"/>
+    <tableColumn id="3" xr3:uid="{500C6F3D-55AA-463E-B538-D91D98F88DB6}" name="BOLD" dataDxfId="227"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6965,34 +7497,34 @@
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{45778312-C73E-4142-8D98-09B51AD29C97}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{8543C9FA-310D-4D2C-86DA-D352F099E3F2}" name="seed_a_e" dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{A7FD3580-474A-4405-9EAD-B93EA4A32AE6}" name="seed_b_e" dataDxfId="101"/>
-    <tableColumn id="4" xr3:uid="{EA684B5D-99C1-4A32-A3EC-30564128701B}" name="seed_d_e" dataDxfId="100"/>
-    <tableColumn id="5" xr3:uid="{32AD5A85-3748-4639-BC0B-99FFC16F408E}" name="seed_c_I_sst" dataDxfId="99"/>
-    <tableColumn id="6" xr3:uid="{19BA603B-63D9-46B3-90DF-7402BEFDD3A8}" name="seed_c_I_vip" dataDxfId="98"/>
-    <tableColumn id="7" xr3:uid="{33433CFB-03AD-4FC5-88CB-005F669B11B5}" name="seed_c_I_pv" dataDxfId="97"/>
-    <tableColumn id="8" xr3:uid="{862DAC63-1554-4142-A5BA-F391ED3DF0AE}" name="seed_r_0_sst" dataDxfId="96"/>
-    <tableColumn id="9" xr3:uid="{832CB555-1A44-4984-BE42-8B801C12E557}" name="seed_r_0_vip" dataDxfId="95"/>
-    <tableColumn id="10" xr3:uid="{2CBB8CD2-430A-496B-BE9B-986ADFAF0244}" name="seed_r_0_pv" dataDxfId="94"/>
-    <tableColumn id="11" xr3:uid="{E6F34906-FD08-40A7-A514-2C610EBB0315}" name="best_difference_vector_cosine" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{8543C9FA-310D-4D2C-86DA-D352F099E3F2}" name="seed_a_e" dataDxfId="226"/>
+    <tableColumn id="3" xr3:uid="{A7FD3580-474A-4405-9EAD-B93EA4A32AE6}" name="seed_b_e" dataDxfId="225"/>
+    <tableColumn id="4" xr3:uid="{EA684B5D-99C1-4A32-A3EC-30564128701B}" name="seed_d_e" dataDxfId="224"/>
+    <tableColumn id="5" xr3:uid="{32AD5A85-3748-4639-BC0B-99FFC16F408E}" name="seed_c_I_sst" dataDxfId="223"/>
+    <tableColumn id="6" xr3:uid="{19BA603B-63D9-46B3-90DF-7402BEFDD3A8}" name="seed_c_I_vip" dataDxfId="222"/>
+    <tableColumn id="7" xr3:uid="{33433CFB-03AD-4FC5-88CB-005F669B11B5}" name="seed_c_I_pv" dataDxfId="221"/>
+    <tableColumn id="8" xr3:uid="{862DAC63-1554-4142-A5BA-F391ED3DF0AE}" name="seed_r_0_sst" dataDxfId="220"/>
+    <tableColumn id="9" xr3:uid="{832CB555-1A44-4984-BE42-8B801C12E557}" name="seed_r_0_vip" dataDxfId="219"/>
+    <tableColumn id="10" xr3:uid="{2CBB8CD2-430A-496B-BE9B-986ADFAF0244}" name="seed_r_0_pv" dataDxfId="218"/>
+    <tableColumn id="11" xr3:uid="{E6F34906-FD08-40A7-A514-2C610EBB0315}" name="best_difference_vector_cosine" dataDxfId="217"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{47408CFF-1559-4407-86A0-0A65C58408F0}" name="Table6" displayName="Table6" ref="A92:F102" totalsRowShown="0" headerRowDxfId="46" dataDxfId="47" headerRowBorderDxfId="54" tableBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{47408CFF-1559-4407-86A0-0A65C58408F0}" name="Table6" displayName="Table6" ref="A92:F102" totalsRowShown="0" headerRowDxfId="216" dataDxfId="214" headerRowBorderDxfId="215" tableBorderDxfId="213">
   <autoFilter ref="A92:F102" xr:uid="{47408CFF-1559-4407-86A0-0A65C58408F0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A93:F102">
     <sortCondition descending="1" ref="B92:B102"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2A379670-8DD1-40F7-88F4-838C6A0F14A8}" name="final_evaluation_seed" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{94C026B0-B434-4C68-B386-9A2D7873AFB7}" name="best_pearson_r" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{47BF99FD-8002-4CE1-AF82-352FCFBC3B21}" name="best_difference_vector_cosine" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{8584DC60-8470-4406-BC16-AFFFE16FF642}" name="stimulus" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{3F2FA6AF-7F1A-4150-B794-704F2B1ED811}" name="Auto" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{A60217A7-8F2D-4DD0-96DC-08129C1F48E5}" name="BOLD" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{2A379670-8DD1-40F7-88F4-838C6A0F14A8}" name="final_evaluation_seed" dataDxfId="212"/>
+    <tableColumn id="2" xr3:uid="{94C026B0-B434-4C68-B386-9A2D7873AFB7}" name="best_pearson_r" dataDxfId="211"/>
+    <tableColumn id="3" xr3:uid="{47BF99FD-8002-4CE1-AF82-352FCFBC3B21}" name="best_difference_vector_cosine" dataDxfId="210"/>
+    <tableColumn id="4" xr3:uid="{8584DC60-8470-4406-BC16-AFFFE16FF642}" name="stimulus" dataDxfId="209"/>
+    <tableColumn id="5" xr3:uid="{3F2FA6AF-7F1A-4150-B794-704F2B1ED811}" name="Auto" dataDxfId="208"/>
+    <tableColumn id="6" xr3:uid="{A60217A7-8F2D-4DD0-96DC-08129C1F48E5}" name="BOLD" dataDxfId="207"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11921,7 +12453,7 @@
     </row>
     <row r="90" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="91" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="123" t="s">
+      <c r="A91" s="115" t="s">
         <v>124</v>
       </c>
     </row>
@@ -11949,19 +12481,19 @@
       <c r="A93" s="52">
         <v>12345</v>
       </c>
-      <c r="B93" s="115">
+      <c r="B93" s="79">
         <v>0.712406808509643</v>
       </c>
-      <c r="C93" s="119">
+      <c r="C93" s="23">
         <v>0.60391527521822497</v>
       </c>
-      <c r="D93" s="121" t="s">
+      <c r="D93" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E93" s="121" t="s">
+      <c r="E93" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="F93" s="121" t="s">
+      <c r="F93" s="97" t="s">
         <v>70</v>
       </c>
       <c r="T93" s="94" t="s">
@@ -11975,19 +12507,19 @@
       <c r="A94" s="53">
         <v>49380</v>
       </c>
-      <c r="B94" s="116">
+      <c r="B94" s="80">
         <v>0.67887988874580396</v>
       </c>
-      <c r="C94" s="120">
+      <c r="C94" s="24">
         <v>0.52520044160502999</v>
       </c>
-      <c r="D94" s="122" t="s">
+      <c r="D94" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E94" s="122" t="s">
+      <c r="E94" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="F94" s="122" t="s">
+      <c r="F94" s="62" t="s">
         <v>71</v>
       </c>
       <c r="T94" s="96">
@@ -11998,22 +12530,22 @@
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="125">
+      <c r="A95" s="53">
         <v>98760</v>
       </c>
-      <c r="B95" s="116">
+      <c r="B95" s="80">
         <v>0.65351070789674404</v>
       </c>
-      <c r="C95" s="124">
+      <c r="C95" s="24">
         <v>0.59117161347732095</v>
       </c>
-      <c r="D95" s="121" t="s">
+      <c r="D95" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E95" s="121" t="s">
+      <c r="E95" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="F95" s="121" t="s">
+      <c r="F95" s="97" t="s">
         <v>71</v>
       </c>
       <c r="T95" s="63">
@@ -12027,19 +12559,19 @@
       <c r="A96" s="53">
         <v>74070</v>
       </c>
-      <c r="B96" s="116">
+      <c r="B96" s="80">
         <v>0.61136346201208103</v>
       </c>
-      <c r="C96" s="120">
+      <c r="C96" s="24">
         <v>0.54313186736951702</v>
       </c>
-      <c r="D96" s="122" t="s">
+      <c r="D96" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E96" s="122" t="s">
+      <c r="E96" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="F96" s="122" t="s">
+      <c r="F96" s="62" t="s">
         <v>71</v>
       </c>
       <c r="T96" s="96">
@@ -12053,19 +12585,19 @@
       <c r="A97" s="52">
         <v>111105</v>
       </c>
-      <c r="B97" s="117">
+      <c r="B97" s="81">
         <v>0.60026349158933801</v>
       </c>
-      <c r="C97" s="119">
+      <c r="C97" s="23">
         <v>0.50762810253022606</v>
       </c>
-      <c r="D97" s="121" t="s">
+      <c r="D97" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E97" s="121" t="s">
+      <c r="E97" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="F97" s="121" t="s">
+      <c r="F97" s="97" t="s">
         <v>70</v>
       </c>
       <c r="T97" s="63">
@@ -12079,19 +12611,19 @@
       <c r="A98" s="52">
         <v>37035</v>
       </c>
-      <c r="B98" s="117">
+      <c r="B98" s="81">
         <v>0.59089730657681105</v>
       </c>
-      <c r="C98" s="119">
+      <c r="C98" s="23">
         <v>0.66176179774459298</v>
       </c>
-      <c r="D98" s="121" t="s">
+      <c r="D98" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E98" s="121" t="s">
+      <c r="E98" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="F98" s="121" t="s">
+      <c r="F98" s="97" t="s">
         <v>71</v>
       </c>
       <c r="T98" s="96">
@@ -12105,19 +12637,19 @@
       <c r="A99" s="52">
         <v>86415</v>
       </c>
-      <c r="B99" s="117">
+      <c r="B99" s="81">
         <v>0.55681124125554704</v>
       </c>
-      <c r="C99" s="119">
+      <c r="C99" s="23">
         <v>0.689942458078181</v>
       </c>
-      <c r="D99" s="121" t="s">
+      <c r="D99" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E99" s="121" t="s">
+      <c r="E99" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="F99" s="121" t="s">
+      <c r="F99" s="97" t="s">
         <v>71</v>
       </c>
       <c r="T99" s="63">
@@ -12128,22 +12660,22 @@
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A100" s="125">
+      <c r="A100" s="53">
         <v>123450</v>
       </c>
-      <c r="B100" s="116">
+      <c r="B100" s="80">
         <v>0.52796028692755004</v>
       </c>
-      <c r="C100" s="124">
+      <c r="C100" s="24">
         <v>0.53793669261472898</v>
       </c>
-      <c r="D100" s="121" t="s">
+      <c r="D100" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E100" s="121" t="s">
+      <c r="E100" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="F100" s="121" t="s">
+      <c r="F100" s="97" t="s">
         <v>71</v>
       </c>
       <c r="T100" s="96">
@@ -12157,19 +12689,19 @@
       <c r="A101" s="52">
         <v>61725</v>
       </c>
-      <c r="B101" s="117">
+      <c r="B101" s="81">
         <v>0.51157923348573597</v>
       </c>
-      <c r="C101" s="119">
+      <c r="C101" s="23">
         <v>0.65013584412540804</v>
       </c>
-      <c r="D101" s="121" t="s">
+      <c r="D101" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="E101" s="121" t="s">
+      <c r="E101" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="F101" s="121" t="s">
+      <c r="F101" s="97" t="s">
         <v>71</v>
       </c>
       <c r="T101" s="63">
@@ -12183,19 +12715,19 @@
       <c r="A102" s="53">
         <v>24690</v>
       </c>
-      <c r="B102" s="118">
+      <c r="B102" s="82">
         <v>0.48840316014479601</v>
       </c>
-      <c r="C102" s="120">
+      <c r="C102" s="24">
         <v>0.48624727790761502</v>
       </c>
-      <c r="D102" s="122" t="s">
+      <c r="D102" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E102" s="122" t="s">
+      <c r="E102" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="F102" s="122" t="s">
+      <c r="F102" s="62" t="s">
         <v>71</v>
       </c>
       <c r="T102" s="96">
@@ -13386,135 +13918,135 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="K132:O141">
-    <cfRule type="cellIs" dxfId="43" priority="52" operator="between">
+  <conditionalFormatting sqref="B110:J119">
+    <cfRule type="cellIs" dxfId="43" priority="3" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="53" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="4" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="5" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D93:F102">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K132:O141">
+    <cfRule type="cellIs" dxfId="38" priority="52" operator="between">
+      <formula>0.975</formula>
+      <formula>1.025</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="53" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="54" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K154:S155">
-    <cfRule type="cellIs" dxfId="40" priority="10" operator="between">
+    <cfRule type="cellIs" dxfId="35" priority="10" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="11" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="12" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49:U58">
-    <cfRule type="cellIs" dxfId="37" priority="93" operator="between">
+    <cfRule type="cellIs" dxfId="32" priority="93" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="96" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="96" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="97" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="97" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67:U76">
-    <cfRule type="cellIs" dxfId="34" priority="94" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="94" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="95" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="95" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B110:J119">
-    <cfRule type="cellIs" dxfId="32" priority="3" operator="between">
+  <conditionalFormatting sqref="Q132:R141">
+    <cfRule type="cellIs" dxfId="27" priority="61" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="62" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q132:R141">
-    <cfRule type="cellIs" dxfId="29" priority="61" operator="between">
-      <formula>0.975</formula>
-      <formula>1.025</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="62" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T94:U103">
-    <cfRule type="cellIs" dxfId="26" priority="79" operator="between">
+    <cfRule type="cellIs" dxfId="24" priority="79" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="80" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="80" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="81" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="81" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T106:U115">
-    <cfRule type="cellIs" dxfId="23" priority="76" operator="between">
+    <cfRule type="cellIs" dxfId="21" priority="76" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="77" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="77" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="78" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="78" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T118:U127">
-    <cfRule type="cellIs" dxfId="20" priority="73" operator="between">
+    <cfRule type="cellIs" dxfId="18" priority="73" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="74" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="74" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="75" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="75" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T132:U141">
-    <cfRule type="cellIs" dxfId="17" priority="55" operator="between">
+    <cfRule type="cellIs" dxfId="15" priority="55" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="56" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="56" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="57" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="57" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y49:AA58">
-    <cfRule type="cellIs" dxfId="14" priority="91" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="91" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="92" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D93:F102">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
-      <formula>"Pass"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="92" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13535,921 +14067,456 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D838E4-5041-4172-BF4F-6C64A37B593C}">
-  <dimension ref="C4:V31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B9B394B-2F94-478A-9EA6-A5E96B91D71F}">
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="8" t="s">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>2</v>
-      </c>
-      <c r="Q4">
-        <v>3</v>
-      </c>
-      <c r="R4">
-        <v>12</v>
-      </c>
-      <c r="S4">
-        <v>13</v>
-      </c>
-      <c r="T4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C5" s="52">
+      <c r="L1" s="134" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="32">
         <v>12345</v>
       </c>
-      <c r="D5" s="79">
+      <c r="B2" s="116">
         <v>0.712406808509643</v>
       </c>
-      <c r="E5" s="83">
+      <c r="C2" s="122">
         <v>249.944372693215</v>
       </c>
-      <c r="F5" s="84">
+      <c r="D2" s="123">
         <v>282.06339872878402</v>
       </c>
-      <c r="G5" s="84">
+      <c r="E2" s="123">
         <v>39.279403191200601</v>
       </c>
-      <c r="H5" s="84">
+      <c r="F2" s="123">
         <v>1.21732841562099</v>
       </c>
-      <c r="I5" s="84">
+      <c r="G2" s="123">
         <v>3.4961092224547201</v>
       </c>
-      <c r="J5" s="84">
+      <c r="H2" s="123">
         <v>0.11255193689562699</v>
       </c>
-      <c r="K5" s="84">
+      <c r="I2" s="123">
         <v>0.101294616086198</v>
       </c>
-      <c r="L5" s="84">
+      <c r="J2" s="123">
         <v>0.116619630354845</v>
       </c>
-      <c r="M5" s="85">
+      <c r="K2" s="124">
         <v>1.5778363102433</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <f>O5+P5</f>
-        <v>2</v>
-      </c>
-      <c r="S5">
-        <f>P5+Q5</f>
-        <v>2</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T14" si="0">SUM(O5:Q5)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C6" s="53">
+      <c r="L2" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="120"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="33">
         <v>24690</v>
       </c>
-      <c r="D6" s="80">
+      <c r="B3" s="117">
         <v>0.48840316014479601</v>
       </c>
-      <c r="E6" s="86">
+      <c r="C3" s="125">
         <v>418.25670506356499</v>
       </c>
-      <c r="F6" s="24">
+      <c r="D3" s="126">
         <v>330.038709874456</v>
       </c>
-      <c r="G6" s="24">
+      <c r="E3" s="126">
         <v>32.478360119580003</v>
       </c>
-      <c r="H6" s="24">
+      <c r="F3" s="126">
         <v>0.51822808473398296</v>
       </c>
-      <c r="I6" s="24">
+      <c r="G3" s="126">
         <v>5.9949632502605397</v>
       </c>
-      <c r="J6" s="24">
+      <c r="H3" s="126">
         <v>0.44945725927744501</v>
       </c>
-      <c r="K6" s="24">
+      <c r="I3" s="126">
         <v>0.100567648699738</v>
       </c>
-      <c r="L6" s="24">
+      <c r="J3" s="126">
         <v>0.21097341589110599</v>
       </c>
-      <c r="M6" s="87">
+      <c r="K3" s="127">
         <v>2.4971317426222299</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" ref="R6:R14" si="1">O6+P6</f>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f t="shared" ref="S6:S14" si="2">P6+Q6</f>
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C7" s="52">
+      <c r="L3" s="121" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="32">
         <v>37035</v>
       </c>
-      <c r="D7" s="81">
+      <c r="B4" s="118">
         <v>0.59089730657681105</v>
       </c>
-      <c r="E7" s="88">
+      <c r="C4" s="128">
         <v>332.23429799566497</v>
       </c>
-      <c r="F7" s="23">
+      <c r="D4" s="129">
         <v>285.69091361756898</v>
       </c>
-      <c r="G7" s="23">
+      <c r="E4" s="129">
         <v>27.272250147894098</v>
       </c>
-      <c r="H7" s="23">
+      <c r="F4" s="129">
         <v>1.8613438661077599</v>
       </c>
-      <c r="I7" s="23">
+      <c r="G4" s="129">
         <v>4.2838259514911803</v>
       </c>
-      <c r="J7" s="23">
+      <c r="H4" s="129">
         <v>0.10000825970358</v>
       </c>
-      <c r="K7" s="23">
+      <c r="I4" s="129">
         <v>0.108603346406101</v>
       </c>
-      <c r="L7" s="23">
+      <c r="J4" s="129">
         <v>1.33482998823821</v>
       </c>
-      <c r="M7" s="89">
+      <c r="K4" s="130">
         <v>0.39592331101205303</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C8" s="53">
+      <c r="L4" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="33">
         <v>49380</v>
       </c>
-      <c r="D8" s="80">
+      <c r="B5" s="117">
         <v>0.67887988874580396</v>
       </c>
-      <c r="E8" s="86">
+      <c r="C5" s="125">
         <v>352.82756797919097</v>
       </c>
-      <c r="F8" s="24">
+      <c r="D5" s="126">
         <v>375.80018132998202</v>
       </c>
-      <c r="G8" s="24">
+      <c r="E5" s="126">
         <v>57.3813719412165</v>
       </c>
-      <c r="H8" s="24">
+      <c r="F5" s="126">
         <v>5.9714044068960703</v>
       </c>
-      <c r="I8" s="24">
+      <c r="G5" s="126">
         <v>5.3269490301681097</v>
       </c>
-      <c r="J8" s="24">
+      <c r="H5" s="126">
         <v>0.20186132703462301</v>
       </c>
-      <c r="K8" s="24">
+      <c r="I5" s="126">
         <v>1.8813684765391401</v>
       </c>
-      <c r="L8" s="24">
+      <c r="J5" s="126">
         <v>0.94484692942459003</v>
       </c>
-      <c r="M8" s="87">
+      <c r="K5" s="127">
         <v>1.6140854471050099</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C9" s="52">
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="32">
         <v>61725</v>
       </c>
-      <c r="D9" s="81">
+      <c r="B6" s="118">
         <v>0.51157923348573597</v>
       </c>
-      <c r="E9" s="88">
+      <c r="C6" s="128">
         <v>328.66130914373701</v>
       </c>
-      <c r="F9" s="23">
+      <c r="D6" s="129">
         <v>234.68146076384599</v>
       </c>
-      <c r="G9" s="23">
+      <c r="E6" s="129">
         <v>48.640617215127101</v>
       </c>
-      <c r="H9" s="23">
+      <c r="F6" s="129">
         <v>0.66329624206417603</v>
       </c>
-      <c r="I9" s="23">
+      <c r="G6" s="129">
         <v>5.9885827680080004</v>
       </c>
-      <c r="J9" s="23">
+      <c r="H6" s="129">
         <v>0.44988299110504398</v>
       </c>
-      <c r="K9" s="23">
+      <c r="I6" s="129">
         <v>0.10080594271322001</v>
       </c>
-      <c r="L9" s="23">
+      <c r="J6" s="129">
         <v>1.3672940648941001</v>
       </c>
-      <c r="M9" s="89">
+      <c r="K6" s="130">
         <v>1.5598435050494699</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C10" s="53">
+      <c r="L6" s="120"/>
+      <c r="M6" s="120"/>
+      <c r="N6" s="120"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="33">
         <v>74070</v>
       </c>
-      <c r="D10" s="80">
+      <c r="B7" s="117">
         <v>0.61136346201208103</v>
       </c>
-      <c r="E10" s="86">
+      <c r="C7" s="125">
         <v>374.00585707519201</v>
       </c>
-      <c r="F10" s="24">
+      <c r="D7" s="126">
         <v>229.52299874123099</v>
       </c>
-      <c r="G10" s="24">
+      <c r="E7" s="126">
         <v>11.975744823062</v>
       </c>
-      <c r="H10" s="24">
+      <c r="F7" s="126">
         <v>0.67413267245759501</v>
       </c>
-      <c r="I10" s="24">
+      <c r="G7" s="126">
         <v>5.9999974178098601</v>
       </c>
-      <c r="J10" s="24">
+      <c r="H7" s="126">
         <v>0.23655072878358799</v>
       </c>
-      <c r="K10" s="24">
+      <c r="I7" s="126">
         <v>0.10022549690346</v>
       </c>
-      <c r="L10" s="24">
+      <c r="J7" s="126">
         <v>0.26935782511441803</v>
       </c>
-      <c r="M10" s="87">
+      <c r="K7" s="127">
         <v>1.4268128233335999</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C11" s="52">
+      <c r="L7" s="121"/>
+      <c r="M7" s="121"/>
+      <c r="N7" s="121"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="32">
         <v>86415</v>
       </c>
-      <c r="D11" s="81">
+      <c r="B8" s="118">
         <v>0.55681124125554704</v>
       </c>
-      <c r="E11" s="88">
+      <c r="C8" s="128">
         <v>303.94088440246401</v>
       </c>
-      <c r="F11" s="23">
+      <c r="D8" s="129">
         <v>273.73714889572699</v>
       </c>
-      <c r="G11" s="23">
+      <c r="E8" s="129">
         <v>23.339435792740499</v>
       </c>
-      <c r="H11" s="23">
+      <c r="F8" s="129">
         <v>1.1653244055629799</v>
       </c>
-      <c r="I11" s="23">
+      <c r="G8" s="129">
         <v>2.9105702589015099</v>
       </c>
-      <c r="J11" s="23">
+      <c r="H8" s="129">
         <v>0.10224991157883501</v>
       </c>
-      <c r="K11" s="23">
+      <c r="I8" s="129">
         <v>0.140456232076098</v>
       </c>
-      <c r="L11" s="23">
+      <c r="J8" s="129">
         <v>1.4935508465976299</v>
       </c>
-      <c r="M11" s="89">
+      <c r="K8" s="130">
         <v>0.39658030424374302</v>
       </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C12" s="53">
+      <c r="L8" s="120"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="120"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="33">
         <v>98760</v>
       </c>
-      <c r="D12" s="80">
+      <c r="B9" s="117">
         <v>0.65351070789674404</v>
       </c>
-      <c r="E12" s="86">
+      <c r="C9" s="125">
         <v>292.50123590147302</v>
       </c>
-      <c r="F12" s="24">
+      <c r="D9" s="126">
         <v>271.37147153366601</v>
       </c>
-      <c r="G12" s="24">
+      <c r="E9" s="126">
         <v>22.107023707693202</v>
       </c>
-      <c r="H12" s="24">
+      <c r="F9" s="126">
         <v>1.38102005624965</v>
       </c>
-      <c r="I12" s="24">
+      <c r="G9" s="126">
         <v>4.3325973231689101</v>
       </c>
-      <c r="J12" s="24">
+      <c r="H9" s="126">
         <v>0.32138518815565298</v>
       </c>
-      <c r="K12" s="24">
+      <c r="I9" s="126">
         <v>0.198272602909567</v>
       </c>
-      <c r="L12" s="24">
+      <c r="J9" s="126">
         <v>0.448120466117577</v>
       </c>
-      <c r="M12" s="87">
+      <c r="K9" s="127">
         <v>0.80814293920319002</v>
       </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C13" s="52">
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="32">
         <v>111105</v>
       </c>
-      <c r="D13" s="81">
+      <c r="B10" s="118">
         <v>0.60026349158933801</v>
       </c>
-      <c r="E13" s="88">
+      <c r="C10" s="128">
         <v>327.949623199999</v>
       </c>
-      <c r="F13" s="23">
+      <c r="D10" s="129">
         <v>283.96197152550002</v>
       </c>
-      <c r="G13" s="23">
+      <c r="E10" s="129">
         <v>33.227388471928798</v>
       </c>
-      <c r="H13" s="23">
+      <c r="F10" s="129">
         <v>1.0703813500850601</v>
       </c>
-      <c r="I13" s="23">
+      <c r="G10" s="129">
         <v>5.5493637313373601</v>
       </c>
-      <c r="J13" s="23">
+      <c r="H10" s="129">
         <v>0.230454066465624</v>
       </c>
-      <c r="K13" s="23">
+      <c r="I10" s="129">
         <v>0.10680025663968799</v>
       </c>
-      <c r="L13" s="23">
+      <c r="J10" s="129">
         <v>0.17786109165508901</v>
       </c>
-      <c r="M13" s="89">
+      <c r="K10" s="130">
         <v>1.2350472397530501</v>
       </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="53">
+      <c r="L10" s="120"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="120"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="33">
         <v>123450</v>
       </c>
-      <c r="D14" s="82">
+      <c r="B11" s="119">
         <v>0.52796028692755004</v>
       </c>
-      <c r="E14" s="90">
+      <c r="C11" s="131">
         <v>337.33985082356497</v>
       </c>
-      <c r="F14" s="91">
+      <c r="D11" s="132">
         <v>258.23863001213198</v>
       </c>
-      <c r="G14" s="91">
+      <c r="E11" s="132">
         <v>16.802151126164599</v>
       </c>
-      <c r="H14" s="91">
+      <c r="F11" s="132">
         <v>1.50392832987264</v>
       </c>
-      <c r="I14" s="91">
+      <c r="G11" s="132">
         <v>4.3842426260623402</v>
       </c>
-      <c r="J14" s="91">
+      <c r="H11" s="132">
         <v>0.44156529106103798</v>
       </c>
-      <c r="K14" s="91">
+      <c r="I11" s="132">
         <v>0.128946976627171</v>
       </c>
-      <c r="L14" s="91">
+      <c r="J11" s="132">
         <v>8.1200539454317905E-2</v>
       </c>
-      <c r="M14" s="92">
+      <c r="K11" s="133">
         <v>1.7917193119714701</v>
       </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="12">
-        <f>AVERAGE(Table3[best_pearson_r])</f>
-        <v>0.593207558714405</v>
-      </c>
-      <c r="E17" s="12">
-        <f>AVERAGE(Table3[I_background_e])</f>
-        <v>331.76617042780663</v>
-      </c>
-      <c r="F17" s="12">
-        <f>AVERAGE(Table3[I_background_i])</f>
-        <v>282.51068850228933</v>
-      </c>
-      <c r="G17" s="12">
-        <f>AVERAGE(Table3[I_background_dend])</f>
-        <v>31.250374653660735</v>
-      </c>
-      <c r="H17" s="12">
-        <f>AVERAGE(Table3[mu_ee])</f>
-        <v>1.6026387829650908</v>
-      </c>
-      <c r="I17" s="12">
-        <f>AVERAGE(Table3[mu_ie])</f>
-        <v>4.8267201579662524</v>
-      </c>
-      <c r="J17" s="12">
-        <f>AVERAGE(Table3[e_grad_min])</f>
-        <v>0.26459669600610575</v>
-      </c>
-      <c r="K17" s="12">
-        <f>AVERAGE(Table3[balloon_kappa])</f>
-        <v>0.29673415956003812</v>
-      </c>
-      <c r="L17" s="12">
-        <f>AVERAGE(Table3[balloon_gamma])</f>
-        <v>0.64446547977418822</v>
-      </c>
-      <c r="M17" s="12">
-        <f>AVERAGE(Table3[balloon_tau])</f>
-        <v>1.3303122934537115</v>
-      </c>
-      <c r="O17">
-        <f>CORREL($D$5:$D$14,O5:O14)</f>
-        <v>3.0493728569702346E-3</v>
-      </c>
-      <c r="P17">
-        <f t="shared" ref="P17:T17" si="3">CORREL($D$5:$D$14,P5:P14)</f>
-        <v>-0.17335784029891846</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="3"/>
-        <v>0.45184144269452314</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="3"/>
-        <v>-9.2811391260808951E-2</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="3"/>
-        <v>0.12803006374638529</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="3"/>
-        <v>8.69439801662652E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="12">
-        <f>_xlfn.STDEV.P(Table3[best_pearson_r])</f>
-        <v>6.985591113403529E-2</v>
-      </c>
-      <c r="E18" s="12">
-        <f>_xlfn.STDEV.P(Table3[I_background_e])</f>
-        <v>43.329742255920529</v>
-      </c>
-      <c r="F18" s="12">
-        <f>_xlfn.STDEV.P(Table3[I_background_i])</f>
-        <v>41.060665700231496</v>
-      </c>
-      <c r="G18" s="12">
-        <f>_xlfn.STDEV.P(Table3[I_background_dend])</f>
-        <v>13.406726668954178</v>
-      </c>
-      <c r="H18" s="12">
-        <f>_xlfn.STDEV.P(Table3[mu_ee])</f>
-        <v>1.5084873382969142</v>
-      </c>
-      <c r="I18" s="12">
-        <f>_xlfn.STDEV.P(Table3[mu_ie])</f>
-        <v>1.0507412903951312</v>
-      </c>
-      <c r="J18" s="12">
-        <f>_xlfn.STDEV.P(Table3[e_grad_min])</f>
-        <v>0.13619791407416829</v>
-      </c>
-      <c r="K18" s="12">
-        <f>_xlfn.STDEV.P(Table3[balloon_kappa])</f>
-        <v>0.52900713153886858</v>
-      </c>
-      <c r="L18" s="12">
-        <f>_xlfn.STDEV.P(Table3[balloon_gamma])</f>
-        <v>0.54690401979118364</v>
-      </c>
-      <c r="M18" s="12">
-        <f>_xlfn.STDEV.P(Table3[balloon_tau])</f>
-        <v>0.61683310529164304</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="12">
-        <f t="shared" ref="D19" si="4">D18/D17</f>
-        <v>0.117759644340046</v>
-      </c>
-      <c r="E19" s="12">
-        <f t="shared" ref="E19:M19" si="5">E18/E17</f>
-        <v>0.13060325650456642</v>
-      </c>
-      <c r="F19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.1453419901311053</v>
-      </c>
-      <c r="G19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.42901011003987072</v>
-      </c>
-      <c r="H19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.94125223620634957</v>
-      </c>
-      <c r="I19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.21769260616050776</v>
-      </c>
-      <c r="J19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.51473777310894853</v>
-      </c>
-      <c r="K19" s="12">
-        <f t="shared" si="5"/>
-        <v>1.7827645200108306</v>
-      </c>
-      <c r="L19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.84861646892679377</v>
-      </c>
-      <c r="M19" s="12">
-        <f t="shared" si="5"/>
-        <v>0.46367541540959673</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="P21">
-        <f>Q17^2</f>
-        <v>0.20416068933626805</v>
-      </c>
-      <c r="T21" t="s">
-        <v>67</v>
-      </c>
-      <c r="U21" t="s">
-        <v>68</v>
-      </c>
-      <c r="V21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T22" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="U22" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="V22" s="54" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T23" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="U23" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="V23" s="54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T24" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="U24" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="V24" s="54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T25" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="U25" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="V25" s="54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T26" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="U26" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="V26" s="54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T27" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="U27" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="V27" s="54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T28" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="U28" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="V28" s="54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T29" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="U29" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="V29" s="54" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T30" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="U30" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="V30" s="54" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="T31" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="U31" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="V31" s="54" t="s">
-        <v>71</v>
-      </c>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="T22:V31">
+  <conditionalFormatting sqref="L2:N11">
     <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14458,9 +14525,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15013,7 +15079,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" customWidth="1"/>
   </cols>
@@ -15601,6 +15667,937 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D838E4-5041-4172-BF4F-6C64A37B593C}">
+  <dimension ref="C4:V31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="17.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>12</v>
+      </c>
+      <c r="S4">
+        <v>13</v>
+      </c>
+      <c r="T4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C5" s="52">
+        <v>12345</v>
+      </c>
+      <c r="D5" s="79">
+        <v>0.712406808509643</v>
+      </c>
+      <c r="E5" s="83">
+        <v>249.944372693215</v>
+      </c>
+      <c r="F5" s="84">
+        <v>282.06339872878402</v>
+      </c>
+      <c r="G5" s="84">
+        <v>39.279403191200601</v>
+      </c>
+      <c r="H5" s="84">
+        <v>1.21732841562099</v>
+      </c>
+      <c r="I5" s="84">
+        <v>3.4961092224547201</v>
+      </c>
+      <c r="J5" s="84">
+        <v>0.11255193689562699</v>
+      </c>
+      <c r="K5" s="84">
+        <v>0.101294616086198</v>
+      </c>
+      <c r="L5" s="84">
+        <v>0.116619630354845</v>
+      </c>
+      <c r="M5" s="85">
+        <v>1.5778363102433</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <f>O5+P5</f>
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <f>P5+Q5</f>
+        <v>2</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T14" si="0">SUM(O5:Q5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C6" s="53">
+        <v>24690</v>
+      </c>
+      <c r="D6" s="80">
+        <v>0.48840316014479601</v>
+      </c>
+      <c r="E6" s="86">
+        <v>418.25670506356499</v>
+      </c>
+      <c r="F6" s="24">
+        <v>330.038709874456</v>
+      </c>
+      <c r="G6" s="24">
+        <v>32.478360119580003</v>
+      </c>
+      <c r="H6" s="24">
+        <v>0.51822808473398296</v>
+      </c>
+      <c r="I6" s="24">
+        <v>5.9949632502605397</v>
+      </c>
+      <c r="J6" s="24">
+        <v>0.44945725927744501</v>
+      </c>
+      <c r="K6" s="24">
+        <v>0.100567648699738</v>
+      </c>
+      <c r="L6" s="24">
+        <v>0.21097341589110599</v>
+      </c>
+      <c r="M6" s="87">
+        <v>2.4971317426222299</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f t="shared" ref="R6:R14" si="1">O6+P6</f>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" ref="S6:S14" si="2">P6+Q6</f>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C7" s="52">
+        <v>37035</v>
+      </c>
+      <c r="D7" s="81">
+        <v>0.59089730657681105</v>
+      </c>
+      <c r="E7" s="88">
+        <v>332.23429799566497</v>
+      </c>
+      <c r="F7" s="23">
+        <v>285.69091361756898</v>
+      </c>
+      <c r="G7" s="23">
+        <v>27.272250147894098</v>
+      </c>
+      <c r="H7" s="23">
+        <v>1.8613438661077599</v>
+      </c>
+      <c r="I7" s="23">
+        <v>4.2838259514911803</v>
+      </c>
+      <c r="J7" s="23">
+        <v>0.10000825970358</v>
+      </c>
+      <c r="K7" s="23">
+        <v>0.108603346406101</v>
+      </c>
+      <c r="L7" s="23">
+        <v>1.33482998823821</v>
+      </c>
+      <c r="M7" s="89">
+        <v>0.39592331101205303</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C8" s="53">
+        <v>49380</v>
+      </c>
+      <c r="D8" s="80">
+        <v>0.67887988874580396</v>
+      </c>
+      <c r="E8" s="86">
+        <v>352.82756797919097</v>
+      </c>
+      <c r="F8" s="24">
+        <v>375.80018132998202</v>
+      </c>
+      <c r="G8" s="24">
+        <v>57.3813719412165</v>
+      </c>
+      <c r="H8" s="24">
+        <v>5.9714044068960703</v>
+      </c>
+      <c r="I8" s="24">
+        <v>5.3269490301681097</v>
+      </c>
+      <c r="J8" s="24">
+        <v>0.20186132703462301</v>
+      </c>
+      <c r="K8" s="24">
+        <v>1.8813684765391401</v>
+      </c>
+      <c r="L8" s="24">
+        <v>0.94484692942459003</v>
+      </c>
+      <c r="M8" s="87">
+        <v>1.6140854471050099</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C9" s="52">
+        <v>61725</v>
+      </c>
+      <c r="D9" s="81">
+        <v>0.51157923348573597</v>
+      </c>
+      <c r="E9" s="88">
+        <v>328.66130914373701</v>
+      </c>
+      <c r="F9" s="23">
+        <v>234.68146076384599</v>
+      </c>
+      <c r="G9" s="23">
+        <v>48.640617215127101</v>
+      </c>
+      <c r="H9" s="23">
+        <v>0.66329624206417603</v>
+      </c>
+      <c r="I9" s="23">
+        <v>5.9885827680080004</v>
+      </c>
+      <c r="J9" s="23">
+        <v>0.44988299110504398</v>
+      </c>
+      <c r="K9" s="23">
+        <v>0.10080594271322001</v>
+      </c>
+      <c r="L9" s="23">
+        <v>1.3672940648941001</v>
+      </c>
+      <c r="M9" s="89">
+        <v>1.5598435050494699</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C10" s="53">
+        <v>74070</v>
+      </c>
+      <c r="D10" s="80">
+        <v>0.61136346201208103</v>
+      </c>
+      <c r="E10" s="86">
+        <v>374.00585707519201</v>
+      </c>
+      <c r="F10" s="24">
+        <v>229.52299874123099</v>
+      </c>
+      <c r="G10" s="24">
+        <v>11.975744823062</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.67413267245759501</v>
+      </c>
+      <c r="I10" s="24">
+        <v>5.9999974178098601</v>
+      </c>
+      <c r="J10" s="24">
+        <v>0.23655072878358799</v>
+      </c>
+      <c r="K10" s="24">
+        <v>0.10022549690346</v>
+      </c>
+      <c r="L10" s="24">
+        <v>0.26935782511441803</v>
+      </c>
+      <c r="M10" s="87">
+        <v>1.4268128233335999</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C11" s="52">
+        <v>86415</v>
+      </c>
+      <c r="D11" s="81">
+        <v>0.55681124125554704</v>
+      </c>
+      <c r="E11" s="88">
+        <v>303.94088440246401</v>
+      </c>
+      <c r="F11" s="23">
+        <v>273.73714889572699</v>
+      </c>
+      <c r="G11" s="23">
+        <v>23.339435792740499</v>
+      </c>
+      <c r="H11" s="23">
+        <v>1.1653244055629799</v>
+      </c>
+      <c r="I11" s="23">
+        <v>2.9105702589015099</v>
+      </c>
+      <c r="J11" s="23">
+        <v>0.10224991157883501</v>
+      </c>
+      <c r="K11" s="23">
+        <v>0.140456232076098</v>
+      </c>
+      <c r="L11" s="23">
+        <v>1.4935508465976299</v>
+      </c>
+      <c r="M11" s="89">
+        <v>0.39658030424374302</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C12" s="53">
+        <v>98760</v>
+      </c>
+      <c r="D12" s="80">
+        <v>0.65351070789674404</v>
+      </c>
+      <c r="E12" s="86">
+        <v>292.50123590147302</v>
+      </c>
+      <c r="F12" s="24">
+        <v>271.37147153366601</v>
+      </c>
+      <c r="G12" s="24">
+        <v>22.107023707693202</v>
+      </c>
+      <c r="H12" s="24">
+        <v>1.38102005624965</v>
+      </c>
+      <c r="I12" s="24">
+        <v>4.3325973231689101</v>
+      </c>
+      <c r="J12" s="24">
+        <v>0.32138518815565298</v>
+      </c>
+      <c r="K12" s="24">
+        <v>0.198272602909567</v>
+      </c>
+      <c r="L12" s="24">
+        <v>0.448120466117577</v>
+      </c>
+      <c r="M12" s="87">
+        <v>0.80814293920319002</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C13" s="52">
+        <v>111105</v>
+      </c>
+      <c r="D13" s="81">
+        <v>0.60026349158933801</v>
+      </c>
+      <c r="E13" s="88">
+        <v>327.949623199999</v>
+      </c>
+      <c r="F13" s="23">
+        <v>283.96197152550002</v>
+      </c>
+      <c r="G13" s="23">
+        <v>33.227388471928798</v>
+      </c>
+      <c r="H13" s="23">
+        <v>1.0703813500850601</v>
+      </c>
+      <c r="I13" s="23">
+        <v>5.5493637313373601</v>
+      </c>
+      <c r="J13" s="23">
+        <v>0.230454066465624</v>
+      </c>
+      <c r="K13" s="23">
+        <v>0.10680025663968799</v>
+      </c>
+      <c r="L13" s="23">
+        <v>0.17786109165508901</v>
+      </c>
+      <c r="M13" s="89">
+        <v>1.2350472397530501</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="53">
+        <v>123450</v>
+      </c>
+      <c r="D14" s="82">
+        <v>0.52796028692755004</v>
+      </c>
+      <c r="E14" s="90">
+        <v>337.33985082356497</v>
+      </c>
+      <c r="F14" s="91">
+        <v>258.23863001213198</v>
+      </c>
+      <c r="G14" s="91">
+        <v>16.802151126164599</v>
+      </c>
+      <c r="H14" s="91">
+        <v>1.50392832987264</v>
+      </c>
+      <c r="I14" s="91">
+        <v>4.3842426260623402</v>
+      </c>
+      <c r="J14" s="91">
+        <v>0.44156529106103798</v>
+      </c>
+      <c r="K14" s="91">
+        <v>0.128946976627171</v>
+      </c>
+      <c r="L14" s="91">
+        <v>8.1200539454317905E-2</v>
+      </c>
+      <c r="M14" s="92">
+        <v>1.7917193119714701</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="12">
+        <f>AVERAGE(Table3[best_pearson_r])</f>
+        <v>0.593207558714405</v>
+      </c>
+      <c r="E17" s="12">
+        <f>AVERAGE(Table3[I_background_e])</f>
+        <v>331.76617042780663</v>
+      </c>
+      <c r="F17" s="12">
+        <f>AVERAGE(Table3[I_background_i])</f>
+        <v>282.51068850228933</v>
+      </c>
+      <c r="G17" s="12">
+        <f>AVERAGE(Table3[I_background_dend])</f>
+        <v>31.250374653660735</v>
+      </c>
+      <c r="H17" s="12">
+        <f>AVERAGE(Table3[mu_ee])</f>
+        <v>1.6026387829650908</v>
+      </c>
+      <c r="I17" s="12">
+        <f>AVERAGE(Table3[mu_ie])</f>
+        <v>4.8267201579662524</v>
+      </c>
+      <c r="J17" s="12">
+        <f>AVERAGE(Table3[e_grad_min])</f>
+        <v>0.26459669600610575</v>
+      </c>
+      <c r="K17" s="12">
+        <f>AVERAGE(Table3[balloon_kappa])</f>
+        <v>0.29673415956003812</v>
+      </c>
+      <c r="L17" s="12">
+        <f>AVERAGE(Table3[balloon_gamma])</f>
+        <v>0.64446547977418822</v>
+      </c>
+      <c r="M17" s="12">
+        <f>AVERAGE(Table3[balloon_tau])</f>
+        <v>1.3303122934537115</v>
+      </c>
+      <c r="O17">
+        <f>CORREL($D$5:$D$14,O5:O14)</f>
+        <v>3.0493728569702346E-3</v>
+      </c>
+      <c r="P17">
+        <f t="shared" ref="P17:T17" si="3">CORREL($D$5:$D$14,P5:P14)</f>
+        <v>-0.17335784029891846</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="3"/>
+        <v>0.45184144269452314</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="3"/>
+        <v>-9.2811391260808951E-2</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="3"/>
+        <v>0.12803006374638529</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="3"/>
+        <v>8.69439801662652E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="12">
+        <f>_xlfn.STDEV.P(Table3[best_pearson_r])</f>
+        <v>6.985591113403529E-2</v>
+      </c>
+      <c r="E18" s="12">
+        <f>_xlfn.STDEV.P(Table3[I_background_e])</f>
+        <v>43.329742255920529</v>
+      </c>
+      <c r="F18" s="12">
+        <f>_xlfn.STDEV.P(Table3[I_background_i])</f>
+        <v>41.060665700231496</v>
+      </c>
+      <c r="G18" s="12">
+        <f>_xlfn.STDEV.P(Table3[I_background_dend])</f>
+        <v>13.406726668954178</v>
+      </c>
+      <c r="H18" s="12">
+        <f>_xlfn.STDEV.P(Table3[mu_ee])</f>
+        <v>1.5084873382969142</v>
+      </c>
+      <c r="I18" s="12">
+        <f>_xlfn.STDEV.P(Table3[mu_ie])</f>
+        <v>1.0507412903951312</v>
+      </c>
+      <c r="J18" s="12">
+        <f>_xlfn.STDEV.P(Table3[e_grad_min])</f>
+        <v>0.13619791407416829</v>
+      </c>
+      <c r="K18" s="12">
+        <f>_xlfn.STDEV.P(Table3[balloon_kappa])</f>
+        <v>0.52900713153886858</v>
+      </c>
+      <c r="L18" s="12">
+        <f>_xlfn.STDEV.P(Table3[balloon_gamma])</f>
+        <v>0.54690401979118364</v>
+      </c>
+      <c r="M18" s="12">
+        <f>_xlfn.STDEV.P(Table3[balloon_tau])</f>
+        <v>0.61683310529164304</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="12">
+        <f t="shared" ref="D19" si="4">D18/D17</f>
+        <v>0.117759644340046</v>
+      </c>
+      <c r="E19" s="12">
+        <f t="shared" ref="E19:M19" si="5">E18/E17</f>
+        <v>0.13060325650456642</v>
+      </c>
+      <c r="F19" s="12">
+        <f t="shared" si="5"/>
+        <v>0.1453419901311053</v>
+      </c>
+      <c r="G19" s="12">
+        <f t="shared" si="5"/>
+        <v>0.42901011003987072</v>
+      </c>
+      <c r="H19" s="12">
+        <f t="shared" si="5"/>
+        <v>0.94125223620634957</v>
+      </c>
+      <c r="I19" s="12">
+        <f t="shared" si="5"/>
+        <v>0.21769260616050776</v>
+      </c>
+      <c r="J19" s="12">
+        <f t="shared" si="5"/>
+        <v>0.51473777310894853</v>
+      </c>
+      <c r="K19" s="12">
+        <f t="shared" si="5"/>
+        <v>1.7827645200108306</v>
+      </c>
+      <c r="L19" s="12">
+        <f t="shared" si="5"/>
+        <v>0.84861646892679377</v>
+      </c>
+      <c r="M19" s="12">
+        <f t="shared" si="5"/>
+        <v>0.46367541540959673</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="P21">
+        <f>Q17^2</f>
+        <v>0.20416068933626805</v>
+      </c>
+      <c r="T21" t="s">
+        <v>67</v>
+      </c>
+      <c r="U21" t="s">
+        <v>68</v>
+      </c>
+      <c r="V21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T22" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="U22" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="V22" s="54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T23" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="U23" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="V23" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T24" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="U24" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="V24" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T25" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="U25" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="V25" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T26" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="U26" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="V26" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T27" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="U27" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="V27" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T28" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="U28" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="V28" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T29" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="U29" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="V29" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T30" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="U30" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="V30" s="54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="T31" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="U31" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="V31" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="T22:V31">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E8849C-2D02-46F4-ACC4-400EB6662519}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Y87"/>

--- a/THESIS/Stats rundown THESIS.xlsx
+++ b/THESIS/Stats rundown THESIS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\serotonin\THESIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GlenA\Documents\GitHub\serotonin\THESIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BBEA87-0E74-4712-9819-9ACFD67CD3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE506CE-765B-4ACD-9434-A9D0BCB99E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="1470" windowWidth="16590" windowHeight="8970" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
   </bookViews>
   <sheets>
     <sheet name="Cosine Data" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="138">
   <si>
     <t>seed_a_e</t>
   </si>
@@ -422,6 +422,39 @@
   </si>
   <si>
     <t>cosine</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower </t>
+  </si>
+  <si>
+    <t>upper</t>
+  </si>
+  <si>
+    <t>optimised range</t>
+  </si>
+  <si>
+    <t>boundary range</t>
+  </si>
+  <si>
+    <t>exploration %</t>
+  </si>
+  <si>
+    <t>whole</t>
+  </si>
+  <si>
+    <t>above</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>below</t>
+  </si>
+  <si>
+    <t>correlations</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1316,25 +1349,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1779,515 +1797,6 @@
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.000"/>
@@ -3078,6 +2587,105 @@
       <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3221,9 +2829,7 @@
       <numFmt numFmtId="164" formatCode="0.000"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
@@ -3315,6 +2921,74 @@
       </font>
       <numFmt numFmtId="164" formatCode="0.000"/>
       <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -3326,6 +3000,65 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3470,6 +3203,256 @@
       </font>
       <numFmt numFmtId="164" formatCode="0.000"/>
       <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -3610,6 +3593,22 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3623,15 +3622,27 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3645,15 +3656,27 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3667,12 +3690,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4010,7 +4029,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -5614,7 +5632,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>102</xdr:row>
-      <xdr:rowOff>106017</xdr:rowOff>
+      <xdr:rowOff>94587</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5660,9 +5678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>618110</xdr:colOff>
+      <xdr:colOff>629540</xdr:colOff>
       <xdr:row>123</xdr:row>
-      <xdr:rowOff>121487</xdr:rowOff>
+      <xdr:rowOff>131012</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5704,7 +5722,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>315830</xdr:colOff>
+      <xdr:colOff>321545</xdr:colOff>
       <xdr:row>151</xdr:row>
       <xdr:rowOff>172728</xdr:rowOff>
     </xdr:to>
@@ -6897,23 +6915,23 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}" name="Table17" displayName="Table17" ref="A1:N11" totalsRowShown="0" headerRowDxfId="44" dataDxfId="45" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}" name="Table17" displayName="Table17" ref="A1:N11" totalsRowShown="0" headerRowDxfId="206" dataDxfId="204" headerRowBorderDxfId="205" tableBorderDxfId="203">
   <autoFilter ref="A1:N11" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{946C78F0-5ED6-4C82-B486-0A2D01401586}" name="final_evaluation_seed" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{F6F73ED1-AC25-4A5B-AA43-B4420270A65B}" name="best_pearson_r" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{9D33DA5E-9FA5-4B81-8347-66FB3F9D278F}" name="I_background_e" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{045CBE2B-CC02-4815-AFDF-FD55F14A5948}" name="I_background_i" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{DD07A8E1-0F8D-4F93-9FFC-80537E7DA893}" name="I_background_dend" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{F002D97C-F001-4AAB-86C7-02AFD658391E}" name="mu_ee" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{6A9A90F5-365B-424C-8DFB-AC07BB4F58AB}" name="mu_ie" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{3C77AB83-9D42-417E-973A-786B92AD8D39}" name="e_grad_min" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{202C73E4-ED7F-44C3-8FE0-67B8DEC3AF51}" name="balloon_kappa" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{39BA6440-2759-406C-962E-1F482C31D9D8}" name="balloon_gamma" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{71495690-5E12-40F8-8FB8-D35062B95476}" name="balloon_tau" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{D2BEB5FD-80DF-4E80-AD46-55385CB1B6FF}" name="Stim" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{7A8508B0-FDAF-4D41-8BA2-B789691A3BE1}" name="Auto" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{42D86400-C902-4CEB-A96A-D8CE8C7A5EE0}" name="BOLD" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{946C78F0-5ED6-4C82-B486-0A2D01401586}" name="final_evaluation_seed" dataDxfId="202"/>
+    <tableColumn id="2" xr3:uid="{F6F73ED1-AC25-4A5B-AA43-B4420270A65B}" name="best_pearson_r" dataDxfId="201"/>
+    <tableColumn id="3" xr3:uid="{9D33DA5E-9FA5-4B81-8347-66FB3F9D278F}" name="I_background_e" dataDxfId="200"/>
+    <tableColumn id="4" xr3:uid="{045CBE2B-CC02-4815-AFDF-FD55F14A5948}" name="I_background_i" dataDxfId="199"/>
+    <tableColumn id="5" xr3:uid="{DD07A8E1-0F8D-4F93-9FFC-80537E7DA893}" name="I_background_dend" dataDxfId="198"/>
+    <tableColumn id="6" xr3:uid="{F002D97C-F001-4AAB-86C7-02AFD658391E}" name="mu_ee" dataDxfId="197"/>
+    <tableColumn id="7" xr3:uid="{6A9A90F5-365B-424C-8DFB-AC07BB4F58AB}" name="mu_ie" dataDxfId="196"/>
+    <tableColumn id="8" xr3:uid="{3C77AB83-9D42-417E-973A-786B92AD8D39}" name="e_grad_min" dataDxfId="195"/>
+    <tableColumn id="9" xr3:uid="{202C73E4-ED7F-44C3-8FE0-67B8DEC3AF51}" name="balloon_kappa" dataDxfId="194"/>
+    <tableColumn id="10" xr3:uid="{39BA6440-2759-406C-962E-1F482C31D9D8}" name="balloon_gamma" dataDxfId="193"/>
+    <tableColumn id="11" xr3:uid="{71495690-5E12-40F8-8FB8-D35062B95476}" name="balloon_tau" dataDxfId="192"/>
+    <tableColumn id="12" xr3:uid="{D2BEB5FD-80DF-4E80-AD46-55385CB1B6FF}" name="Stim" dataDxfId="191"/>
+    <tableColumn id="13" xr3:uid="{7A8508B0-FDAF-4D41-8BA2-B789691A3BE1}" name="Auto" dataDxfId="190"/>
+    <tableColumn id="14" xr3:uid="{42D86400-C902-4CEB-A96A-D8CE8C7A5EE0}" name="BOLD" dataDxfId="189"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6957,20 +6975,20 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}" name="Table1" displayName="Table1" ref="C4:M14" totalsRowShown="0" headerRowDxfId="206" dataDxfId="204" headerRowBorderDxfId="205" tableBorderDxfId="203">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}" name="Table1" displayName="Table1" ref="C4:M14" totalsRowShown="0" headerRowDxfId="169" dataDxfId="167" headerRowBorderDxfId="168" tableBorderDxfId="166">
   <autoFilter ref="C4:M14" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{87805D45-55EC-4CC4-8B30-E06DA4E7E751}" name="final_evaluation_seed" dataDxfId="202"/>
-    <tableColumn id="2" xr3:uid="{79824F93-C2A5-45B6-9B69-441998802D80}" name="best_pearson_r" dataDxfId="201"/>
-    <tableColumn id="3" xr3:uid="{7EAF5609-B791-402E-8A39-55B740926D2B}" name="I_background_e" dataDxfId="200"/>
-    <tableColumn id="4" xr3:uid="{5EE101D7-0D41-494A-805A-94CFC73331CF}" name="I_background_i" dataDxfId="199"/>
-    <tableColumn id="5" xr3:uid="{2CCF00EF-4BDB-4EB6-A318-9502957678DF}" name="I_background_dend" dataDxfId="198"/>
-    <tableColumn id="6" xr3:uid="{F5AB52A3-CD6E-43D7-A21D-129262695C38}" name="mu_ee" dataDxfId="197"/>
-    <tableColumn id="7" xr3:uid="{778CC36A-8D50-4F01-8B3E-FCAED3521F9B}" name="mu_ie" dataDxfId="196"/>
-    <tableColumn id="8" xr3:uid="{A7B4CCC7-3054-4367-9B57-4F9D70B71AE8}" name="e_grad_min" dataDxfId="195"/>
-    <tableColumn id="9" xr3:uid="{6C33EE26-7CA7-4527-87D8-E28DD20FFD4E}" name="balloon_kappa" dataDxfId="194"/>
-    <tableColumn id="10" xr3:uid="{DBBC495E-05F7-4608-AD56-F33F1FD9FB2E}" name="balloon_gamma" dataDxfId="193"/>
-    <tableColumn id="11" xr3:uid="{D7DB4319-ACF4-4A69-B4F4-EBD25833DB72}" name="balloon_tau" dataDxfId="192"/>
+    <tableColumn id="1" xr3:uid="{87805D45-55EC-4CC4-8B30-E06DA4E7E751}" name="final_evaluation_seed" dataDxfId="165"/>
+    <tableColumn id="2" xr3:uid="{79824F93-C2A5-45B6-9B69-441998802D80}" name="best_pearson_r" dataDxfId="164"/>
+    <tableColumn id="3" xr3:uid="{7EAF5609-B791-402E-8A39-55B740926D2B}" name="I_background_e" dataDxfId="163"/>
+    <tableColumn id="4" xr3:uid="{5EE101D7-0D41-494A-805A-94CFC73331CF}" name="I_background_i" dataDxfId="162"/>
+    <tableColumn id="5" xr3:uid="{2CCF00EF-4BDB-4EB6-A318-9502957678DF}" name="I_background_dend" dataDxfId="161"/>
+    <tableColumn id="6" xr3:uid="{F5AB52A3-CD6E-43D7-A21D-129262695C38}" name="mu_ee" dataDxfId="160"/>
+    <tableColumn id="7" xr3:uid="{778CC36A-8D50-4F01-8B3E-FCAED3521F9B}" name="mu_ie" dataDxfId="159"/>
+    <tableColumn id="8" xr3:uid="{A7B4CCC7-3054-4367-9B57-4F9D70B71AE8}" name="e_grad_min" dataDxfId="158"/>
+    <tableColumn id="9" xr3:uid="{6C33EE26-7CA7-4527-87D8-E28DD20FFD4E}" name="balloon_kappa" dataDxfId="157"/>
+    <tableColumn id="10" xr3:uid="{DBBC495E-05F7-4608-AD56-F33F1FD9FB2E}" name="balloon_gamma" dataDxfId="156"/>
+    <tableColumn id="11" xr3:uid="{D7DB4319-ACF4-4A69-B4F4-EBD25833DB72}" name="balloon_tau" dataDxfId="155"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6980,9 +6998,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}" name="Table1411" displayName="Table1411" ref="T21:V31" totalsRowShown="0">
   <autoFilter ref="T21:V31" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2EE0C1C9-847E-49D1-B328-3A3EED7F56C1}" name="Stim" dataDxfId="191"/>
-    <tableColumn id="2" xr3:uid="{865FC042-E96D-4C4D-B1EA-4B7C3183DA79}" name="Auto" dataDxfId="190"/>
-    <tableColumn id="3" xr3:uid="{D9EC8ABD-24A2-4068-9CAB-09D34D97FE88}" name="BOLD" dataDxfId="189"/>
+    <tableColumn id="1" xr3:uid="{2EE0C1C9-847E-49D1-B328-3A3EED7F56C1}" name="Stim" dataDxfId="154"/>
+    <tableColumn id="2" xr3:uid="{865FC042-E96D-4C4D-B1EA-4B7C3183DA79}" name="Auto" dataDxfId="153"/>
+    <tableColumn id="3" xr3:uid="{D9EC8ABD-24A2-4068-9CAB-09D34D97FE88}" name="BOLD" dataDxfId="152"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6993,94 +7011,94 @@
   <autoFilter ref="A1:U11" xr:uid="{2B1EA398-6077-43CD-8151-400DF211F33C}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{DFDC78A7-E47E-494D-9C61-107C2DD6F0AD}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="169"/>
-    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="168"/>
-    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="167"/>
-    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="166"/>
-    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="165"/>
-    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="164"/>
-    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="163"/>
-    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="162"/>
-    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="161"/>
-    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="160"/>
-    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="159"/>
-    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="158"/>
-    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="157"/>
-    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="156"/>
-    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="155"/>
-    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="154"/>
-    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="153"/>
-    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="152"/>
-    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="151"/>
-    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="150"/>
+    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="151"/>
+    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="150"/>
+    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="149"/>
+    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="148"/>
+    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="147"/>
+    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="146"/>
+    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="145"/>
+    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="144"/>
+    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="143"/>
+    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="142"/>
+    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="141"/>
+    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="140"/>
+    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="139"/>
+    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="138"/>
+    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="137"/>
+    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="136"/>
+    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="135"/>
+    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="134"/>
+    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="133"/>
+    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="149" headerRowBorderDxfId="148" tableBorderDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="131" headerRowBorderDxfId="130" tableBorderDxfId="129">
   <autoFilter ref="A22:U32" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="146" totalsRowDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="144">
+    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="128" totalsRowDxfId="127"/>
+    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="126">
       <calculatedColumnFormula>(B2-B$17)/B$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="143">
+    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="125">
       <calculatedColumnFormula>(C2-C$17)/C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="142">
+    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="124">
       <calculatedColumnFormula>(D2-D$17)/D$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="141">
+    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="123">
       <calculatedColumnFormula>(E2-E$17)/E$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="140">
+    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="122">
       <calculatedColumnFormula>(F2-F$17)/F$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="139">
+    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="121">
       <calculatedColumnFormula>(G2-G$17)/G$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="138">
+    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="120">
       <calculatedColumnFormula>(H2-H$17)/H$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="137">
+    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="119">
       <calculatedColumnFormula>(I2-I$17)/I$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="136">
+    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="118">
       <calculatedColumnFormula>(J2-J$17)/J$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="135">
+    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="117">
       <calculatedColumnFormula>(K2-K$17)/K$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="134">
+    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="116">
       <calculatedColumnFormula>(L2-L$17)/L$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="133">
+    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="115">
       <calculatedColumnFormula>(M2-M$17)/M$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="132">
+    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="114">
       <calculatedColumnFormula>(N2-N$17)/N$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="131">
+    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="113">
       <calculatedColumnFormula>(O2-O$17)/O$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="130">
+    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="112">
       <calculatedColumnFormula>(P2-P$17)/P$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="129">
+    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="111">
       <calculatedColumnFormula>(Q2-Q$17)/Q$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="128">
+    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="110">
       <calculatedColumnFormula>(R2-R$17)/R$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="127">
+    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="109">
       <calculatedColumnFormula>(S2-S$17)/S$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="126">
+    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="108">
       <calculatedColumnFormula>(T2-T$17)/T$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="124">
+    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="107" totalsRowDxfId="106">
       <calculatedColumnFormula>(U2-U$17)/U$19</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7089,29 +7107,29 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="123" dataDxfId="121" headerRowBorderDxfId="122" tableBorderDxfId="120" totalsRowBorderDxfId="119">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="105" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102" totalsRowBorderDxfId="101">
   <autoFilter ref="A77:C87" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="118" totalsRowDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="116" totalsRowDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="114" totalsRowDxfId="113"/>
+    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="96" totalsRowDxfId="95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="112" headerRowBorderDxfId="111" tableBorderDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="94" headerRowBorderDxfId="93" tableBorderDxfId="92">
   <autoFilter ref="F77:I87" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="108">
+    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="90">
       <calculatedColumnFormula>Table32[[#This Row],[best_pearson_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="107">
+    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="89">
       <calculatedColumnFormula>Table32[[#This Row],[best_difference_vector_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="106">
+    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="88">
       <calculatedColumnFormula>Table33[[#This Row],[best_pearson_r]]+Table33[[#This Row],[best_difference_vector_r]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7120,11 +7138,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="105" headerRowBorderDxfId="104" tableBorderDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="87" headerRowBorderDxfId="86" tableBorderDxfId="85">
   <autoFilter ref="A50:L60" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="102"/>
-    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="101">
+    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="83">
       <calculatedColumnFormula>D2/B$46</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{19814F94-E875-4959-AFE5-7848DB2FC6EC}" name="seed_b_e">
@@ -7151,8 +7169,8 @@
     <tableColumn id="10" xr3:uid="{40D401B7-4651-43DA-A526-6D0D5CEB229D}" name="seed_r_0_pv">
       <calculatedColumnFormula>L2/J$46</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="100"/>
-    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="99"/>
+    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="82"/>
+    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7233,74 +7251,74 @@
   <autoFilter ref="N50:Y60" xr:uid="{7D09C930-E854-4E6C-82B9-35C9655B8B61}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{016F4276-D961-4FD1-B77D-67CC688C159B}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="98">
+    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="80">
       <calculatedColumnFormula>Table23[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="97">
+    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="79">
       <calculatedColumnFormula>Table23[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="96">
+    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="78">
       <calculatedColumnFormula>Table23[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="95">
+    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="77">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="94">
+    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="76">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="93">
+    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="75">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="92">
+    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="74">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="91">
+    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="73">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="90">
+    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="72">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="89"/>
-    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="88"/>
+    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="87" headerRowBorderDxfId="86" tableBorderDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="69" headerRowBorderDxfId="68" tableBorderDxfId="67">
   <autoFilter ref="A63:L73" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="83">
+    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="65">
       <calculatedColumnFormula>LOG(B51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="82">
+    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="64">
       <calculatedColumnFormula>LOG(C51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="81">
+    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="63">
       <calculatedColumnFormula>LOG(D51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="80">
+    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="62">
       <calculatedColumnFormula>LOG(E51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="79">
+    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="61">
       <calculatedColumnFormula>LOG(F51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="78">
+    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="60">
       <calculatedColumnFormula>LOG(G51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="77">
+    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="59">
       <calculatedColumnFormula>LOG(H51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="76">
+    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="58">
       <calculatedColumnFormula>LOG(I51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="75">
+    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="57">
       <calculatedColumnFormula>LOG(J51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="74"/>
-    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="56"/>
+    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7311,35 +7329,35 @@
   <autoFilter ref="N63:Y73" xr:uid="{2806A620-3E6B-4861-AE70-E4C12B09B013}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00CF6880-3883-432C-B0EF-EBC8FF079300}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="72">
+    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="54">
       <calculatedColumnFormula>Table28[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="71">
+    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="53">
       <calculatedColumnFormula>Table28[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="70">
+    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="52">
       <calculatedColumnFormula>Table28[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="69">
+    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="51">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="68">
+    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="50">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="67">
+    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="49">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="66">
+    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="48">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="65">
+    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="47">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="64">
+    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="46">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="63"/>
-    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="62"/>
+    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7848,35 +7866,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237B445F-8D43-4D1E-9470-CD21867C00BD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AA155"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI155"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="23" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="20" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.7109375" customWidth="1"/>
-    <col min="24" max="24" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.6640625" customWidth="1"/>
+    <col min="24" max="24" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -7940,8 +7966,44 @@
       <c r="U1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X1" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="94" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z1" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA1" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB1" s="94" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC1" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" s="94" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF1" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG1" s="94" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH1" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI1" s="95" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="35">
         <v>12345</v>
       </c>
@@ -8005,8 +8067,44 @@
       <c r="U2" s="46">
         <v>1.5778363102433</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X2" s="118">
+        <v>12345</v>
+      </c>
+      <c r="Y2" s="23">
+        <v>0.60391527521822497</v>
+      </c>
+      <c r="Z2" s="79">
+        <v>0.712406808509643</v>
+      </c>
+      <c r="AA2" s="83">
+        <v>249.944372693215</v>
+      </c>
+      <c r="AB2" s="84">
+        <v>282.06339872878402</v>
+      </c>
+      <c r="AC2" s="84">
+        <v>39.279403191200601</v>
+      </c>
+      <c r="AD2" s="84">
+        <v>1.21732841562099</v>
+      </c>
+      <c r="AE2" s="84">
+        <v>3.4961092224547201</v>
+      </c>
+      <c r="AF2" s="84">
+        <v>0.11255193689562699</v>
+      </c>
+      <c r="AG2" s="84">
+        <v>0.101294616086198</v>
+      </c>
+      <c r="AH2" s="84">
+        <v>0.116619630354845</v>
+      </c>
+      <c r="AI2" s="85">
+        <v>1.5778363102433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="35">
         <v>24690</v>
       </c>
@@ -8070,8 +8168,44 @@
       <c r="U3" s="48">
         <v>2.4971317426222299</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X3" s="119">
+        <v>24690</v>
+      </c>
+      <c r="Y3" s="24">
+        <v>0.48624727790761502</v>
+      </c>
+      <c r="Z3" s="80">
+        <v>0.48840316014479601</v>
+      </c>
+      <c r="AA3" s="86">
+        <v>418.25670506356499</v>
+      </c>
+      <c r="AB3" s="24">
+        <v>330.038709874456</v>
+      </c>
+      <c r="AC3" s="24">
+        <v>32.478360119580003</v>
+      </c>
+      <c r="AD3" s="24">
+        <v>0.51822808473398296</v>
+      </c>
+      <c r="AE3" s="24">
+        <v>5.9949632502605397</v>
+      </c>
+      <c r="AF3" s="24">
+        <v>0.44945725927744501</v>
+      </c>
+      <c r="AG3" s="24">
+        <v>0.100567648699738</v>
+      </c>
+      <c r="AH3" s="24">
+        <v>0.21097341589110599</v>
+      </c>
+      <c r="AI3" s="87">
+        <v>2.4971317426222299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="35">
         <v>37035</v>
       </c>
@@ -8135,8 +8269,44 @@
       <c r="U4" s="48">
         <v>0.39592331101205303</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X4" s="118">
+        <v>37035</v>
+      </c>
+      <c r="Y4" s="23">
+        <v>0.66176179774459298</v>
+      </c>
+      <c r="Z4" s="81">
+        <v>0.59089730657681105</v>
+      </c>
+      <c r="AA4" s="88">
+        <v>332.23429799566497</v>
+      </c>
+      <c r="AB4" s="23">
+        <v>285.69091361756898</v>
+      </c>
+      <c r="AC4" s="23">
+        <v>27.272250147894098</v>
+      </c>
+      <c r="AD4" s="23">
+        <v>1.8613438661077599</v>
+      </c>
+      <c r="AE4" s="23">
+        <v>4.2838259514911803</v>
+      </c>
+      <c r="AF4" s="23">
+        <v>0.10000825970358</v>
+      </c>
+      <c r="AG4" s="23">
+        <v>0.108603346406101</v>
+      </c>
+      <c r="AH4" s="23">
+        <v>1.33482998823821</v>
+      </c>
+      <c r="AI4" s="89">
+        <v>0.39592331101205303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>49380</v>
       </c>
@@ -8200,8 +8370,44 @@
       <c r="U5" s="48">
         <v>1.6140854471050099</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X5" s="119">
+        <v>49380</v>
+      </c>
+      <c r="Y5" s="24">
+        <v>0.52520044160502999</v>
+      </c>
+      <c r="Z5" s="80">
+        <v>0.67887988874580396</v>
+      </c>
+      <c r="AA5" s="86">
+        <v>352.82756797919097</v>
+      </c>
+      <c r="AB5" s="24">
+        <v>375.80018132998202</v>
+      </c>
+      <c r="AC5" s="24">
+        <v>57.3813719412165</v>
+      </c>
+      <c r="AD5" s="24">
+        <v>5.9714044068960703</v>
+      </c>
+      <c r="AE5" s="24">
+        <v>5.3269490301681097</v>
+      </c>
+      <c r="AF5" s="24">
+        <v>0.20186132703462301</v>
+      </c>
+      <c r="AG5" s="24">
+        <v>1.8813684765391401</v>
+      </c>
+      <c r="AH5" s="24">
+        <v>0.94484692942459003</v>
+      </c>
+      <c r="AI5" s="87">
+        <v>1.6140854471050099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>61725</v>
       </c>
@@ -8265,8 +8471,44 @@
       <c r="U6" s="48">
         <v>1.5598435050494699</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X6" s="118">
+        <v>61725</v>
+      </c>
+      <c r="Y6" s="23">
+        <v>0.65013584412540804</v>
+      </c>
+      <c r="Z6" s="81">
+        <v>0.51157923348573597</v>
+      </c>
+      <c r="AA6" s="88">
+        <v>328.66130914373701</v>
+      </c>
+      <c r="AB6" s="23">
+        <v>234.68146076384599</v>
+      </c>
+      <c r="AC6" s="23">
+        <v>48.640617215127101</v>
+      </c>
+      <c r="AD6" s="23">
+        <v>0.66329624206417603</v>
+      </c>
+      <c r="AE6" s="23">
+        <v>5.9885827680080004</v>
+      </c>
+      <c r="AF6" s="23">
+        <v>0.44988299110504398</v>
+      </c>
+      <c r="AG6" s="23">
+        <v>0.10080594271322001</v>
+      </c>
+      <c r="AH6" s="23">
+        <v>1.3672940648941001</v>
+      </c>
+      <c r="AI6" s="89">
+        <v>1.5598435050494699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>74070</v>
       </c>
@@ -8330,8 +8572,44 @@
       <c r="U7" s="48">
         <v>1.4268128233335999</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X7" s="119">
+        <v>74070</v>
+      </c>
+      <c r="Y7" s="24">
+        <v>0.54313186736951702</v>
+      </c>
+      <c r="Z7" s="80">
+        <v>0.61136346201208103</v>
+      </c>
+      <c r="AA7" s="86">
+        <v>374.00585707519201</v>
+      </c>
+      <c r="AB7" s="24">
+        <v>229.52299874123099</v>
+      </c>
+      <c r="AC7" s="24">
+        <v>11.975744823062</v>
+      </c>
+      <c r="AD7" s="24">
+        <v>0.67413267245759501</v>
+      </c>
+      <c r="AE7" s="24">
+        <v>5.9999974178098601</v>
+      </c>
+      <c r="AF7" s="24">
+        <v>0.23655072878358799</v>
+      </c>
+      <c r="AG7" s="24">
+        <v>0.10022549690346</v>
+      </c>
+      <c r="AH7" s="24">
+        <v>0.26935782511441803</v>
+      </c>
+      <c r="AI7" s="87">
+        <v>1.4268128233335999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>86415</v>
       </c>
@@ -8395,8 +8673,44 @@
       <c r="U8" s="48">
         <v>0.39658030424374302</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X8" s="118">
+        <v>86415</v>
+      </c>
+      <c r="Y8" s="23">
+        <v>0.689942458078181</v>
+      </c>
+      <c r="Z8" s="81">
+        <v>0.55681124125554704</v>
+      </c>
+      <c r="AA8" s="88">
+        <v>303.94088440246401</v>
+      </c>
+      <c r="AB8" s="23">
+        <v>273.73714889572699</v>
+      </c>
+      <c r="AC8" s="23">
+        <v>23.339435792740499</v>
+      </c>
+      <c r="AD8" s="23">
+        <v>1.1653244055629799</v>
+      </c>
+      <c r="AE8" s="23">
+        <v>2.9105702589015099</v>
+      </c>
+      <c r="AF8" s="23">
+        <v>0.10224991157883501</v>
+      </c>
+      <c r="AG8" s="23">
+        <v>0.140456232076098</v>
+      </c>
+      <c r="AH8" s="23">
+        <v>1.4935508465976299</v>
+      </c>
+      <c r="AI8" s="89">
+        <v>0.39658030424374302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>98760</v>
       </c>
@@ -8460,8 +8774,44 @@
       <c r="U9" s="48">
         <v>0.80814293920319002</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X9" s="119">
+        <v>98760</v>
+      </c>
+      <c r="Y9" s="24">
+        <v>0.59117161347732095</v>
+      </c>
+      <c r="Z9" s="80">
+        <v>0.65351070789674404</v>
+      </c>
+      <c r="AA9" s="86">
+        <v>292.50123590147302</v>
+      </c>
+      <c r="AB9" s="24">
+        <v>271.37147153366601</v>
+      </c>
+      <c r="AC9" s="24">
+        <v>22.107023707693202</v>
+      </c>
+      <c r="AD9" s="24">
+        <v>1.38102005624965</v>
+      </c>
+      <c r="AE9" s="24">
+        <v>4.3325973231689101</v>
+      </c>
+      <c r="AF9" s="24">
+        <v>0.32138518815565298</v>
+      </c>
+      <c r="AG9" s="24">
+        <v>0.198272602909567</v>
+      </c>
+      <c r="AH9" s="24">
+        <v>0.448120466117577</v>
+      </c>
+      <c r="AI9" s="87">
+        <v>0.80814293920319002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>111105</v>
       </c>
@@ -8525,8 +8875,44 @@
       <c r="U10" s="48">
         <v>1.2350472397530501</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X10" s="118">
+        <v>111105</v>
+      </c>
+      <c r="Y10" s="23">
+        <v>0.50762810253022606</v>
+      </c>
+      <c r="Z10" s="81">
+        <v>0.60026349158933801</v>
+      </c>
+      <c r="AA10" s="88">
+        <v>327.949623199999</v>
+      </c>
+      <c r="AB10" s="23">
+        <v>283.96197152550002</v>
+      </c>
+      <c r="AC10" s="23">
+        <v>33.227388471928798</v>
+      </c>
+      <c r="AD10" s="23">
+        <v>1.0703813500850601</v>
+      </c>
+      <c r="AE10" s="23">
+        <v>5.5493637313373601</v>
+      </c>
+      <c r="AF10" s="23">
+        <v>0.230454066465624</v>
+      </c>
+      <c r="AG10" s="23">
+        <v>0.10680025663968799</v>
+      </c>
+      <c r="AH10" s="23">
+        <v>0.17786109165508901</v>
+      </c>
+      <c r="AI10" s="89">
+        <v>1.2350472397530501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="35">
         <v>123450</v>
       </c>
@@ -8590,9 +8976,45 @@
       <c r="U11" s="51">
         <v>1.7917193119714701</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="X11" s="119">
+        <v>123450</v>
+      </c>
+      <c r="Y11" s="24">
+        <v>0.53793669261472898</v>
+      </c>
+      <c r="Z11" s="82">
+        <v>0.52796028692755004</v>
+      </c>
+      <c r="AA11" s="90">
+        <v>337.33985082356497</v>
+      </c>
+      <c r="AB11" s="91">
+        <v>258.23863001213198</v>
+      </c>
+      <c r="AC11" s="91">
+        <v>16.802151126164599</v>
+      </c>
+      <c r="AD11" s="91">
+        <v>1.50392832987264</v>
+      </c>
+      <c r="AE11" s="91">
+        <v>4.3842426260623402</v>
+      </c>
+      <c r="AF11" s="91">
+        <v>0.44156529106103798</v>
+      </c>
+      <c r="AG11" s="91">
+        <v>0.128946976627171</v>
+      </c>
+      <c r="AH11" s="91">
+        <v>8.1200539454317905E-2</v>
+      </c>
+      <c r="AI11" s="92">
+        <v>1.7917193119714701</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -8676,8 +9098,38 @@
         <f>AVERAGE(Table3[balloon_tau])</f>
         <v>1.3303122934537115</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA13">
+        <v>100</v>
+      </c>
+      <c r="AB13">
+        <v>100</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0.5</v>
+      </c>
+      <c r="AE13">
+        <v>0.5</v>
+      </c>
+      <c r="AF13">
+        <v>0.1</v>
+      </c>
+      <c r="AG13">
+        <v>0.1</v>
+      </c>
+      <c r="AH13">
+        <v>0.05</v>
+      </c>
+      <c r="AI13">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -8761,8 +9213,38 @@
         <f>_xlfn.STDEV.P(Table3[balloon_tau])</f>
         <v>0.61683310529164304</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Z14" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA14">
+        <v>310</v>
+      </c>
+      <c r="AB14">
+        <v>300</v>
+      </c>
+      <c r="AC14">
+        <v>30</v>
+      </c>
+      <c r="AD14">
+        <v>1.45</v>
+      </c>
+      <c r="AE14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AF14">
+        <v>0.45</v>
+      </c>
+      <c r="AG14">
+        <v>0.65</v>
+      </c>
+      <c r="AH14">
+        <v>0.41</v>
+      </c>
+      <c r="AI14">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>60</v>
       </c>
@@ -8846,9 +9328,39 @@
         <f t="shared" si="0"/>
         <v>0.46367541540959673</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z15" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA15">
+        <v>600</v>
+      </c>
+      <c r="AB15">
+        <v>600</v>
+      </c>
+      <c r="AC15">
+        <v>80</v>
+      </c>
+      <c r="AD15">
+        <v>6</v>
+      </c>
+      <c r="AE15">
+        <v>6</v>
+      </c>
+      <c r="AF15">
+        <v>0.45</v>
+      </c>
+      <c r="AG15">
+        <v>2</v>
+      </c>
+      <c r="AH15">
+        <v>1.5</v>
+      </c>
+      <c r="AI15">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
         <v>32</v>
       </c>
@@ -8932,8 +9444,47 @@
         <f>MIN(Table3[balloon_tau])</f>
         <v>0.39592331101205303</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA17" s="10">
+        <f>M17</f>
+        <v>249.944372693215</v>
+      </c>
+      <c r="AB17" s="10">
+        <f t="shared" ref="AB17:AI18" si="1">N17</f>
+        <v>229.52299874123099</v>
+      </c>
+      <c r="AC17" s="10">
+        <f t="shared" si="1"/>
+        <v>11.975744823062</v>
+      </c>
+      <c r="AD17" s="10">
+        <f t="shared" si="1"/>
+        <v>0.51822808473398296</v>
+      </c>
+      <c r="AE17" s="10">
+        <f t="shared" si="1"/>
+        <v>2.9105702589015099</v>
+      </c>
+      <c r="AF17" s="10">
+        <f t="shared" si="1"/>
+        <v>0.10000825970358</v>
+      </c>
+      <c r="AG17" s="10">
+        <f t="shared" si="1"/>
+        <v>0.10022549690346</v>
+      </c>
+      <c r="AH17" s="10">
+        <f t="shared" si="1"/>
+        <v>8.1200539454317905E-2</v>
+      </c>
+      <c r="AI17" s="10">
+        <f t="shared" si="1"/>
+        <v>0.39592331101205303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
         <v>33</v>
       </c>
@@ -9017,8 +9568,47 @@
         <f>MAX(Table3[balloon_tau])</f>
         <v>2.4971317426222299</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Z18" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA18" s="10">
+        <f>M18</f>
+        <v>418.25670506356499</v>
+      </c>
+      <c r="AB18" s="10">
+        <f t="shared" si="1"/>
+        <v>375.80018132998202</v>
+      </c>
+      <c r="AC18" s="10">
+        <f t="shared" si="1"/>
+        <v>57.3813719412165</v>
+      </c>
+      <c r="AD18" s="10">
+        <f t="shared" si="1"/>
+        <v>5.9714044068960703</v>
+      </c>
+      <c r="AE18" s="10">
+        <f t="shared" si="1"/>
+        <v>5.9999974178098601</v>
+      </c>
+      <c r="AF18" s="10">
+        <f t="shared" si="1"/>
+        <v>0.44988299110504398</v>
+      </c>
+      <c r="AG18" s="10">
+        <f t="shared" si="1"/>
+        <v>1.8813684765391401</v>
+      </c>
+      <c r="AH18" s="10">
+        <f t="shared" si="1"/>
+        <v>1.4935508465976299</v>
+      </c>
+      <c r="AI18" s="10">
+        <f t="shared" si="1"/>
+        <v>2.4971317426222299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="40" t="s">
         <v>34</v>
       </c>
@@ -9027,89 +9617,171 @@
         <v>0.20369518017056598</v>
       </c>
       <c r="C19" s="36">
-        <f t="shared" ref="C19:U19" si="1">C18-C17</f>
+        <f t="shared" ref="C19:U19" si="2">C18-C17</f>
         <v>0.22400364836484699</v>
       </c>
       <c r="D19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.40085449774015708</v>
       </c>
       <c r="E19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>154.7319169775615</v>
       </c>
       <c r="F19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.62894195754683202</v>
       </c>
       <c r="G19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>268.15319009514803</v>
       </c>
       <c r="H19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>384.52823316390391</v>
       </c>
       <c r="I19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>611.34565397616893</v>
       </c>
       <c r="J19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>120.6962745800837</v>
       </c>
       <c r="K19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>107.87381856279991</v>
       </c>
       <c r="L19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>344.28748239901245</v>
       </c>
       <c r="M19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>168.31233237034999</v>
       </c>
       <c r="N19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>146.27718258875103</v>
       </c>
       <c r="O19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>45.405627118154499</v>
       </c>
       <c r="P19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.4531763221620873</v>
       </c>
       <c r="Q19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0894271589083502</v>
       </c>
       <c r="R19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.34987473140146397</v>
       </c>
       <c r="S19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7811429796356801</v>
       </c>
       <c r="T19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4123503071433121</v>
       </c>
       <c r="U19" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.1012084316101767</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Y20" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA20" s="10">
+        <f t="shared" ref="AA20:AI20" si="3">AA18-AA17</f>
+        <v>168.31233237034999</v>
+      </c>
+      <c r="AB20" s="10">
+        <f t="shared" si="3"/>
+        <v>146.27718258875103</v>
+      </c>
+      <c r="AC20" s="10">
+        <f t="shared" si="3"/>
+        <v>45.405627118154499</v>
+      </c>
+      <c r="AD20" s="10">
+        <f t="shared" si="3"/>
+        <v>5.4531763221620873</v>
+      </c>
+      <c r="AE20" s="10">
+        <f t="shared" si="3"/>
+        <v>3.0894271589083502</v>
+      </c>
+      <c r="AF20" s="10">
+        <f t="shared" si="3"/>
+        <v>0.34987473140146397</v>
+      </c>
+      <c r="AG20" s="10">
+        <f t="shared" si="3"/>
+        <v>1.7811429796356801</v>
+      </c>
+      <c r="AH20" s="10">
+        <f t="shared" si="3"/>
+        <v>1.4123503071433121</v>
+      </c>
+      <c r="AI20" s="10">
+        <f t="shared" si="3"/>
+        <v>2.1012084316101767</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="30" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Z21" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA21">
+        <f>AA15-AA13</f>
+        <v>500</v>
+      </c>
+      <c r="AB21">
+        <f t="shared" ref="AB21:AI21" si="4">AB15-AB13</f>
+        <v>500</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="4"/>
+        <v>80</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="4"/>
+        <v>5.5</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="4"/>
+        <v>5.5</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="4"/>
+        <v>0.35</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="4"/>
+        <v>1.9</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="4"/>
+        <v>1.45</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="4"/>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>18</v>
       </c>
@@ -9173,859 +9845,1184 @@
       <c r="U22" s="59" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z22" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA22">
+        <f>100*(AA20/AA21)</f>
+        <v>33.662466474069994</v>
+      </c>
+      <c r="AB22">
+        <f t="shared" ref="AB22:AI22" si="5">100*(AB20/AB21)</f>
+        <v>29.255436517750205</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="5"/>
+        <v>56.75703389769312</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="5"/>
+        <v>99.148660402947044</v>
+      </c>
+      <c r="AE22">
+        <f t="shared" si="5"/>
+        <v>56.171402889242728</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="5"/>
+        <v>99.964208971846858</v>
+      </c>
+      <c r="AG22">
+        <f t="shared" si="5"/>
+        <v>93.744367349246332</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="5"/>
+        <v>97.403469458159464</v>
+      </c>
+      <c r="AI22">
+        <f t="shared" si="5"/>
+        <v>95.509474164098933</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="52">
         <v>12345</v>
       </c>
       <c r="B23" s="10">
-        <f t="shared" ref="B23:U23" si="2">(B2-B$17)/B$19</f>
+        <f t="shared" ref="B23:U23" si="6">(B2-B$17)/B$19</f>
         <v>0.57766706709544924</v>
       </c>
       <c r="C23" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>8.167303710477474E-5</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.99944249137628272</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.77323923366167602</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.99654487983911755</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M23" s="44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N23" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.35918383891264172</v>
       </c>
       <c r="O23" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.60132763494465202</v>
       </c>
       <c r="P23" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.12820057331464138</v>
       </c>
       <c r="Q23" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.1895299463089172</v>
       </c>
       <c r="R23" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>3.5851909458570592E-2</v>
       </c>
       <c r="S23" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>6.0024332406861535E-4</v>
       </c>
       <c r="T23" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>2.507812029450927E-2</v>
       </c>
       <c r="U23" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.56249203146664295</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>24690</v>
       </c>
       <c r="B24" s="10">
-        <f t="shared" ref="B24:U24" si="3">(B3-B$17)/B$19</f>
+        <f t="shared" ref="B24:U24" si="7">(B3-B$17)/B$19</f>
         <v>0</v>
       </c>
       <c r="C24" s="42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.56508481544955691</v>
       </c>
       <c r="F24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.9286710882143472E-3</v>
       </c>
       <c r="G24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.60911136657423781</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.14794889133597769</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.24712050034375901</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.94656675329455409</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.47869394211020772</v>
       </c>
       <c r="M24" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.68715919567454697</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.45154348916195136</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.99837051748094974</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.99878318784013453</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9209676044535482E-4</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>9.1884340436242745E-2</v>
       </c>
       <c r="U24" s="48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Y24" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA24" s="10">
+        <f>AA18-AA14</f>
+        <v>108.25670506356499</v>
+      </c>
+      <c r="AB24" s="10">
+        <f t="shared" ref="AB24:AI24" si="8">AB18-AB14</f>
+        <v>75.800181329982024</v>
+      </c>
+      <c r="AC24" s="10">
+        <f t="shared" si="8"/>
+        <v>27.3813719412165</v>
+      </c>
+      <c r="AD24" s="10">
+        <f t="shared" si="8"/>
+        <v>4.5214044068960701</v>
+      </c>
+      <c r="AE24" s="10">
+        <f t="shared" si="8"/>
+        <v>3.7599974178098599</v>
+      </c>
+      <c r="AF24" s="10">
+        <f t="shared" si="8"/>
+        <v>-1.1700889495602773E-4</v>
+      </c>
+      <c r="AG24" s="10">
+        <f t="shared" si="8"/>
+        <v>1.2313684765391399</v>
+      </c>
+      <c r="AH24" s="10">
+        <f t="shared" si="8"/>
+        <v>1.08355084659763</v>
+      </c>
+      <c r="AI24" s="10">
+        <f t="shared" si="8"/>
+        <v>1.5171317426222299</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="52">
         <v>37035</v>
       </c>
       <c r="B25" s="10">
-        <f t="shared" ref="B25:U25" si="4">(B4-B$17)/B$19</f>
+        <f t="shared" ref="B25:U25" si="9">(B4-B$17)/B$19</f>
         <v>0.86165278770960274</v>
       </c>
       <c r="C25" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.45755570134767282</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9.4827643583014987E-2</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.33538046387795506</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.32574078567631715</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.15308288688363339</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.5181468057039214E-2</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.24954063501167509</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.87277989064627981</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.85148944051055686</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.82696912207264206</v>
       </c>
       <c r="M25" s="47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.48891203718442572</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.38398275029845563</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.33688567465498365</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.24629971635343259</v>
       </c>
       <c r="Q25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.44450172214932904</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4.7036367088029241E-3</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.88761934092650396</v>
       </c>
       <c r="U25" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z25" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA25">
+        <f>AA15-AA14</f>
+        <v>290</v>
+      </c>
+      <c r="AB25">
+        <f t="shared" ref="AB25:AI25" si="10">AB15-AB14</f>
+        <v>300</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="10"/>
+        <v>50</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="10"/>
+        <v>4.55</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="10"/>
+        <v>3.76</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <f t="shared" si="10"/>
+        <v>1.35</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" si="10"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="10"/>
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="53">
         <v>49380</v>
       </c>
       <c r="B26" s="10">
-        <f t="shared" ref="B26:U26" si="5">(B5-B$17)/B$19</f>
+        <f t="shared" ref="B26:U26" si="11">(B5-B$17)/B$19</f>
         <v>0.19123262349554462</v>
       </c>
       <c r="C26" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.85032868880228274</v>
       </c>
       <c r="D26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9.0804202698139436E-2</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.2218636057516413</v>
       </c>
       <c r="F26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.34829824361674816</v>
       </c>
       <c r="G26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>4.5604990573167449E-2</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.14894321566829535</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.23227376767740676</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.88670172654256996</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.90073231548714205</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.82776850118646195</v>
       </c>
       <c r="M26" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.61126355886741868</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.78214460059334356</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.29111295612306348</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.61149587719290754</v>
       </c>
       <c r="U26" s="48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.5797435979064044</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z26" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA26">
+        <f>100*(AA24/AA25)</f>
+        <v>37.329898297781035</v>
+      </c>
+      <c r="AB26">
+        <f t="shared" ref="AB26:AI26" si="12">100*(AB24/AB25)</f>
+        <v>25.266727109994008</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="12"/>
+        <v>54.762743882432993</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="12"/>
+        <v>99.371525426287249</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="12"/>
+        <v>99.999931324730312</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="12"/>
+        <v>91.212479743639989</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="12"/>
+        <v>99.408334550241278</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="12"/>
+        <v>99.811298856725656</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="52">
         <v>61725</v>
       </c>
       <c r="B27" s="10">
-        <f t="shared" ref="B27:U27" si="6">(B6-B$17)/B$19</f>
+        <f t="shared" ref="B27:U27" si="13">(B6-B$17)/B$19</f>
         <v>0.8045775362998745</v>
       </c>
       <c r="C27" s="42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.10346292799299334</v>
       </c>
       <c r="D27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.61058118210595025</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>1.7743989746884278E-2</v>
       </c>
       <c r="F27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.59484483579861691</v>
       </c>
       <c r="G27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.37593068239866895</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.38746695639955925</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.93295670310037293</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.8261214756545211</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.14009667987759186</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.9612411237119729</v>
       </c>
       <c r="M27" s="47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.46768371242883944</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>3.5264980712116152E-2</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.80749622280638889</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>2.6602506275219089E-2</v>
       </c>
       <c r="Q27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.99630525362316913</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>3.2588389387961091E-4</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.91060519400537188</v>
       </c>
       <c r="U27" s="48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.55392895656024632</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="53">
         <v>74070</v>
       </c>
       <c r="B28" s="10">
-        <f t="shared" ref="B28:U28" si="7">(B7-B$17)/B$19</f>
+        <f t="shared" ref="B28:U28" si="14">(B7-B$17)/B$19</f>
         <v>0.27926330615319017</v>
       </c>
       <c r="C28" s="42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.54892097858608468</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.35203962433682878</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.1236640144294518</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>2.2118450633736193E-2</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.6987449561894632</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.26794961875472201</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.86947135247003071</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.50380247166595882</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M28" s="47">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.73709087524849581</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>2.8589683977392217E-2</v>
       </c>
       <c r="Q28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.39026101865965351</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.13322281639933659</v>
       </c>
       <c r="U28" s="48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.49061744509161626</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Y28" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA28" s="10">
+        <f>AA14-AA17</f>
+        <v>60.055627306784999</v>
+      </c>
+      <c r="AB28" s="10">
+        <f t="shared" ref="AB28:AI28" si="15">AB14-AB17</f>
+        <v>70.477001258769008</v>
+      </c>
+      <c r="AC28" s="10">
+        <f t="shared" si="15"/>
+        <v>18.024255176937999</v>
+      </c>
+      <c r="AD28" s="10">
+        <f t="shared" si="15"/>
+        <v>0.93177191526601699</v>
+      </c>
+      <c r="AE28" s="10">
+        <f t="shared" si="15"/>
+        <v>-0.67057025890150967</v>
+      </c>
+      <c r="AF28" s="10">
+        <f t="shared" si="15"/>
+        <v>0.34999174029642</v>
+      </c>
+      <c r="AG28" s="10">
+        <f t="shared" si="15"/>
+        <v>0.54977450309653997</v>
+      </c>
+      <c r="AH28" s="10">
+        <f t="shared" si="15"/>
+        <v>0.3287994605456821</v>
+      </c>
+      <c r="AI28" s="10">
+        <f t="shared" si="15"/>
+        <v>0.58407668898794696</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="52">
         <v>86415</v>
       </c>
       <c r="B29" s="10">
-        <f t="shared" ref="B29:U29" si="8">(B8-B$17)/B$19</f>
+        <f t="shared" ref="B29:U29" si="16">(B8-B$17)/B$19</f>
         <v>1</v>
       </c>
       <c r="C29" s="42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.30538824528130476</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>4.2910378710609015E-2</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.22660563530226732</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>5.1668125491660004E-4</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>3.5292514696789491E-2</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>2.4213556171417258E-3</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.15409767555634624</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.90313772698387296</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.94024815391234073</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.71308600863609339</v>
       </c>
       <c r="M29" s="47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.32081138053768105</v>
       </c>
       <c r="N29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.30226279568701608</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.25027054334274274</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.11866411107947354</v>
       </c>
       <c r="Q29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>6.4070127793333549E-3</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>2.2587032951653836E-2</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="U29" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>3.1267399359640623E-4</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z29" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA29">
+        <f>AA14-AA13</f>
+        <v>210</v>
+      </c>
+      <c r="AB29">
+        <f t="shared" ref="AB29:AI29" si="17">AB14-AB13</f>
+        <v>200</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="17"/>
+        <v>30</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="17"/>
+        <v>0.95</v>
+      </c>
+      <c r="AE29">
+        <f t="shared" si="17"/>
+        <v>1.7400000000000002</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="17"/>
+        <v>0.35</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" si="17"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="17"/>
+        <v>0.36</v>
+      </c>
+      <c r="AI29">
+        <f t="shared" si="17"/>
+        <v>0.67999999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>98760</v>
       </c>
       <c r="B30" s="10">
-        <f t="shared" ref="B30:U30" si="9">(B9-B$17)/B$19</f>
+        <f t="shared" ref="B30:U30" si="18">(B9-B$17)/B$19</f>
         <v>0.5151046553082238</v>
       </c>
       <c r="C30" s="42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.73707526175211369</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.45796048121650085</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.72049162551017998</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.11468813287025763</v>
       </c>
       <c r="G30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.13112773022749816</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>1.3186320912202353E-2</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>2.009274811181443E-2</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.45829502674836275</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.98219836676943839</v>
       </c>
       <c r="M30" s="47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.25284459319722946</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.28609022987603838</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.22312826686145296</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.15821824209300192</v>
       </c>
       <c r="Q30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.46028826417447366</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.63273197114099067</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>5.5047296666863782E-2</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.25979385199795729</v>
       </c>
       <c r="U30" s="48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v>0.19618216926497342</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Z30" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA30">
+        <f>100*(AA28/AA29)</f>
+        <v>28.597917765135715</v>
+      </c>
+      <c r="AB30">
+        <f t="shared" ref="AB30:AI30" si="19">100*(AB28/AB29)</f>
+        <v>35.238500629384504</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="19"/>
+        <v>60.080850589793336</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="19"/>
+        <v>98.081254238528103</v>
+      </c>
+      <c r="AE30">
+        <f t="shared" si="19"/>
+        <v>-38.538520626523542</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="19"/>
+        <v>99.997640084691426</v>
+      </c>
+      <c r="AG30">
+        <f t="shared" si="19"/>
+        <v>99.959000563007265</v>
+      </c>
+      <c r="AH30">
+        <f t="shared" si="19"/>
+        <v>91.3331834849117</v>
+      </c>
+      <c r="AI30">
+        <f t="shared" si="19"/>
+        <v>85.893630733521618</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="52">
         <v>111105</v>
       </c>
       <c r="B31" s="10">
-        <f t="shared" ref="B31:U31" si="10">(B10-B$17)/B$19</f>
+        <f t="shared" ref="B31:U31" si="20">(B10-B$17)/B$19</f>
         <v>0.10496480380491877</v>
       </c>
       <c r="C31" s="42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.49936834627956128</v>
       </c>
       <c r="D31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>2.7885162002687234E-2</v>
       </c>
       <c r="E31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="G31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.72047243528274851</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.41702301033121214</v>
       </c>
       <c r="L31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.26692585966159904</v>
       </c>
       <c r="M31" s="47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.46345534761614088</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.37216312086978548</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.46803986637087469</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.1012535140496169</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.85413681459583868</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.37283574678150694</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>3.6913149653897037E-3</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>6.8439502375498756E-2</v>
       </c>
       <c r="U31" s="48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0.39935301806207207</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="53">
         <v>123450</v>
       </c>
       <c r="B32" s="10">
-        <f t="shared" ref="B32:U32" si="11">(B11-B$17)/B$19</f>
+        <f t="shared" ref="B32:U32" si="21">(B11-B$17)/B$19</f>
         <v>0.25375865380727897</v>
       </c>
       <c r="C32" s="43">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.1765914397890751</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.94932709028905304</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="F32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="G32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.87041102180181451</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>8.6803403438864384E-3</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.19378615422520684</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.48565427920201104</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.72646094987826793</v>
       </c>
       <c r="M32" s="49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.51924583837414406</v>
       </c>
       <c r="N32" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.19630970984472096</v>
       </c>
       <c r="O32" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.10629533406824947</v>
       </c>
       <c r="P32" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.18075708301099724</v>
       </c>
       <c r="Q32" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.477005053481032</v>
       </c>
       <c r="R32" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.9762266339992931</v>
       </c>
       <c r="S32" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>1.6125308328467695E-2</v>
       </c>
       <c r="T32" s="50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="U32" s="51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0.6642825052295287</v>
       </c>
-    </row>
-    <row r="33" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="X32" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y32">
+        <f t="shared" ref="Y32:AI32" si="22">CORREL($Z$2:$Z$11,Y2:Y11)</f>
+        <v>6.5264090807847022E-3</v>
+      </c>
+      <c r="Z32">
+        <f t="shared" si="22"/>
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="AA32">
+        <f t="shared" si="22"/>
+        <v>-0.58608019031096492</v>
+      </c>
+      <c r="AB32">
+        <f t="shared" si="22"/>
+        <v>0.2487237895049676</v>
+      </c>
+      <c r="AC32">
+        <f t="shared" si="22"/>
+        <v>0.21354987946022019</v>
+      </c>
+      <c r="AD32">
+        <f t="shared" si="22"/>
+        <v>0.4806215384089379</v>
+      </c>
+      <c r="AE32">
+        <f t="shared" si="22"/>
+        <v>-0.32228779529157164</v>
+      </c>
+      <c r="AF32">
+        <f t="shared" si="22"/>
+        <v>-0.63673419378023133</v>
+      </c>
+      <c r="AG32">
+        <f t="shared" si="22"/>
+        <v>0.42008726573173627</v>
+      </c>
+      <c r="AH32">
+        <f t="shared" si="22"/>
+        <v>-0.17915655715374673</v>
+      </c>
+      <c r="AI32">
+        <f t="shared" si="22"/>
+        <v>-0.25894728122590877</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="55" t="s">
         <v>36</v>
       </c>
@@ -10110,7 +11107,7 @@
         <v>0.44469123975750807</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="56" t="s">
         <v>37</v>
       </c>
@@ -10195,7 +11192,7 @@
         <v>0.29356112226284808</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="57" t="s">
         <v>60</v>
       </c>
@@ -10204,89 +11201,89 @@
         <v>0.71413399453986959</v>
       </c>
       <c r="C36" s="61">
-        <f t="shared" ref="C36:U36" si="12">C35/C34</f>
+        <f t="shared" ref="C36:U36" si="23">C35/C34</f>
         <v>0.66653606229740459</v>
       </c>
       <c r="D36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.99904342662783296</v>
       </c>
       <c r="E36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>1.0024674841354415</v>
       </c>
       <c r="F36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>1.1090015875037971</v>
       </c>
       <c r="G36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.79111569303556184</v>
       </c>
       <c r="H36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>1.3535157653488339</v>
       </c>
       <c r="I36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.77568261386300108</v>
       </c>
       <c r="J36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.692158639040653</v>
       </c>
       <c r="K36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.56081597510253234</v>
       </c>
       <c r="L36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.46455658602958216</v>
       </c>
       <c r="M36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.52956233492291305</v>
       </c>
       <c r="N36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.77490952871109742</v>
       </c>
       <c r="O36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.69556337977867688</v>
       </c>
       <c r="P36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>1.3910664481248312</v>
       </c>
       <c r="Q36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.54836069501033702</v>
       </c>
       <c r="R36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.82750597267858184</v>
       </c>
       <c r="S36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>2.692029574611531</v>
       </c>
       <c r="T36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.97095341932804236</v>
       </c>
       <c r="U36" s="61">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>0.66014595300534396</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="30" t="s">
         <v>50</v>
       </c>
@@ -10318,7 +11315,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="31" t="s">
         <v>51</v>
       </c>
@@ -10350,8 +11347,8 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:27" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:27" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="30" t="s">
         <v>62</v>
       </c>
@@ -10362,7 +11359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -10439,7 +11436,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>12345</v>
       </c>
@@ -10448,35 +11445,35 @@
         <v>3.7015741310872814</v>
       </c>
       <c r="C49" s="10">
-        <f t="shared" ref="C49:J57" si="13">E2/C$44</f>
+        <f t="shared" ref="C49:J57" si="24">E2/C$44</f>
         <v>0.37083115765629815</v>
       </c>
       <c r="D49" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.3662280335415846</v>
       </c>
       <c r="E49" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.4693932221661439</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.56653283755186434</v>
       </c>
       <c r="G49" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.4136252561621121</v>
       </c>
       <c r="H49" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>4.2323150644463636</v>
       </c>
       <c r="I49" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>3.9022623769436366</v>
       </c>
       <c r="J49" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>4.0071833665052106</v>
       </c>
       <c r="L49">
@@ -10525,44 +11522,44 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>24690</v>
       </c>
       <c r="B50" s="10">
-        <f t="shared" ref="B50:B57" si="14">D3/B$44</f>
+        <f t="shared" ref="B50:B57" si="25">D3/B$44</f>
         <v>0.73228155523426586</v>
       </c>
       <c r="C50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.9897944784678703</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.33541157594627274</v>
       </c>
       <c r="E50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.1359734407797122</v>
       </c>
       <c r="F50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.99752166924869701</v>
       </c>
       <c r="G50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.56746349470196666</v>
       </c>
       <c r="H50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>3.3284810109961214</v>
       </c>
       <c r="I50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.80802691626256673</v>
       </c>
       <c r="J50" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.272358817360137</v>
       </c>
       <c r="L50">
@@ -10611,44 +11608,44 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>37035</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>1.013852573310948</v>
       </c>
       <c r="C51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.3315982811204317</v>
       </c>
       <c r="D51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.99051611930270134</v>
       </c>
       <c r="E51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.2095682013609546</v>
       </c>
       <c r="F51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.6690197144616038</v>
       </c>
       <c r="G51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.0297531392620909</v>
       </c>
       <c r="H51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.0401550241609454</v>
       </c>
       <c r="I51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.1188254856170972</v>
       </c>
       <c r="J51" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.0101821342935104</v>
       </c>
       <c r="L51">
@@ -10697,44 +11694,44 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>49380</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>1.0019058001621037</v>
       </c>
       <c r="C52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.0063264095064612</v>
       </c>
       <c r="D52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.036578884738854</v>
       </c>
       <c r="E52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.99123077135817428</v>
       </c>
       <c r="F52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.0004182281782272</v>
       </c>
       <c r="G52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.99776518683000603</v>
       </c>
       <c r="H52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.98923642634283937</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.95785527468573939</v>
       </c>
       <c r="J52" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.0072851214242537</v>
       </c>
       <c r="L52">
@@ -10783,44 +11780,44 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>61725</v>
       </c>
       <c r="B53" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>2.5452757262170222</v>
       </c>
       <c r="C53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.42144086363350186</v>
       </c>
       <c r="D53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.540031794847182</v>
       </c>
       <c r="E53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.6622753776717727</v>
       </c>
       <c r="F53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.6952599902315453</v>
       </c>
       <c r="G53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.2958241789090819</v>
       </c>
       <c r="H53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.2108064443826665</v>
       </c>
       <c r="I53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>3.4442998367507274</v>
       </c>
       <c r="J53" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.52356982480844416</v>
       </c>
       <c r="L53">
@@ -10869,44 +11866,44 @@
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>74070</v>
       </c>
       <c r="B54" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>1.7775901981836961</v>
       </c>
       <c r="C54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.72494472410469257</v>
       </c>
       <c r="D54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.37051343827471106</v>
       </c>
       <c r="E54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.3180608119539698</v>
       </c>
       <c r="F54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.3470949093450075</v>
       </c>
       <c r="G54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.1782135934575275</v>
       </c>
       <c r="H54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.3896762324972909</v>
       </c>
       <c r="I54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.63335878413151825</v>
       </c>
       <c r="J54" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.38310460441034316</v>
       </c>
       <c r="L54">
@@ -10955,44 +11952,44 @@
         <v>71</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>86415</v>
       </c>
       <c r="B55" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>0.8596950241667185</v>
       </c>
       <c r="C55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.0199142488163242</v>
       </c>
       <c r="D55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.3264022073669513</v>
       </c>
       <c r="E55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.97028135238825008</v>
       </c>
       <c r="F55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.57358647086490222</v>
       </c>
       <c r="G55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.85293908330560908</v>
       </c>
       <c r="H55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.92912236506217571</v>
       </c>
       <c r="I55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.82868180848462425</v>
       </c>
       <c r="J55" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.4229035070601472</v>
       </c>
       <c r="L55">
@@ -11041,44 +12038,44 @@
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>98760</v>
       </c>
       <c r="B56" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>2.092100212144496</v>
       </c>
       <c r="C56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.435098064246537</v>
       </c>
       <c r="D56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.55954251994784743</v>
       </c>
       <c r="E56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.9300494561210075</v>
       </c>
       <c r="F56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.94852006803044697</v>
       </c>
       <c r="G56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.59189197949472416</v>
       </c>
       <c r="H56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>4.1588265843502423</v>
       </c>
       <c r="I56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.4041401174379877</v>
       </c>
       <c r="J56" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.44761912533182319</v>
       </c>
       <c r="L56">
@@ -11127,44 +12124,44 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>111105</v>
       </c>
       <c r="B57" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>0.8150807597453037</v>
       </c>
       <c r="C57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.37059713125636112</v>
       </c>
       <c r="D57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.32534713425040906</v>
       </c>
       <c r="E57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.89858589479412887</v>
       </c>
       <c r="F57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>3.4796255130359848</v>
       </c>
       <c r="G57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1.9021837738526788</v>
       </c>
       <c r="H57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>0.57485219838322121</v>
       </c>
       <c r="I57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>2.5390543601866122</v>
       </c>
       <c r="J57" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>3.0398230274516944</v>
       </c>
       <c r="L57">
@@ -11213,7 +12210,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>123450</v>
       </c>
@@ -11222,35 +12219,35 @@
         <v>3.5511114364856962</v>
       </c>
       <c r="C58" s="10">
-        <f t="shared" ref="C58:J58" si="15">E11/C$44</f>
+        <f t="shared" ref="C58:J58" si="26">E11/C$44</f>
         <v>3.2360030012112038</v>
       </c>
       <c r="D58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>2.3673664769349285</v>
       </c>
       <c r="E58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>2.6667941689618107</v>
       </c>
       <c r="F58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>0.59181947342834929</v>
       </c>
       <c r="G58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>2.4200260825085391</v>
       </c>
       <c r="H58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>3.5235494014104844</v>
       </c>
       <c r="I58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>2.314705358795603</v>
       </c>
       <c r="J58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>1.3744316665601157</v>
       </c>
       <c r="L58">
@@ -11299,8 +12296,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="55" t="s">
         <v>36</v>
       </c>
@@ -11341,7 +12338,7 @@
         <v>1.5488461195205676</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="56" t="s">
         <v>37</v>
       </c>
@@ -11382,7 +12379,7 @@
         <v>1.1420367587685476</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="57" t="s">
         <v>60</v>
       </c>
@@ -11391,40 +12388,40 @@
         <v>0.5946420049593516</v>
       </c>
       <c r="C62" s="61">
-        <f t="shared" ref="C62:J62" si="16">C61/C60</f>
+        <f t="shared" ref="C62:J62" si="27">C61/C60</f>
         <v>0.71462013453018336</v>
       </c>
       <c r="D62" s="61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>0.75588681832478644</v>
       </c>
       <c r="E62" s="61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>0.40163666674346216</v>
       </c>
       <c r="F62" s="61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>0.70747535898113467</v>
       </c>
       <c r="G62" s="61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>0.48703957326216935</v>
       </c>
       <c r="H62" s="61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>0.61696712325832948</v>
       </c>
       <c r="I62" s="61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>0.59396572124289382</v>
       </c>
       <c r="J62" s="61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>0.73734681862524576</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:22" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="65" spans="1:22" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="30" t="s">
         <v>63</v>
       </c>
@@ -11432,7 +12429,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
         <v>18</v>
       </c>
@@ -11497,7 +12494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="32">
         <v>12345</v>
       </c>
@@ -11506,35 +12503,35 @@
         <v>1.8881389215967568</v>
       </c>
       <c r="C67" s="10">
-        <f t="shared" ref="C67:J67" si="17">LOG(C49,2)</f>
+        <f t="shared" ref="C67:J67" si="28">LOG(C49,2)</f>
         <v>-1.4311656289504635</v>
       </c>
       <c r="D67" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="28"/>
         <v>1.2425891129875246</v>
       </c>
       <c r="E67" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="28"/>
         <v>1.304156587188968</v>
       </c>
       <c r="F67" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="28"/>
         <v>-0.81976851448105381</v>
       </c>
       <c r="G67" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="28"/>
         <v>1.2712016980296328</v>
       </c>
       <c r="H67" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="28"/>
         <v>2.08144702938844</v>
       </c>
       <c r="I67" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="28"/>
         <v>1.9643107838899196</v>
       </c>
       <c r="J67" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="28"/>
         <v>2.002588528210187</v>
       </c>
       <c r="L67" s="32">
@@ -11545,790 +12542,790 @@
         <v>1.8881389215967568</v>
       </c>
       <c r="N67" s="65">
-        <f t="shared" ref="N67:U67" si="18">LOG(N49,2)</f>
+        <f t="shared" ref="N67:U67" si="29">LOG(N49,2)</f>
         <v>-1.4311656289504635</v>
       </c>
       <c r="O67" s="66">
-        <f t="shared" si="18"/>
+        <f t="shared" si="29"/>
         <v>1.2425891129875246</v>
       </c>
       <c r="P67" s="63">
-        <f t="shared" si="18"/>
+        <f t="shared" si="29"/>
         <v>1.304156587188968</v>
       </c>
       <c r="Q67" s="62">
-        <f t="shared" si="18"/>
+        <f t="shared" si="29"/>
         <v>-0.81976851448105381</v>
       </c>
       <c r="R67" s="62">
-        <f t="shared" si="18"/>
+        <f t="shared" si="29"/>
         <v>1.2712016980296328</v>
       </c>
       <c r="S67" s="62">
-        <f t="shared" si="18"/>
+        <f t="shared" si="29"/>
         <v>2.08144702938844</v>
       </c>
       <c r="T67" s="62">
-        <f t="shared" si="18"/>
+        <f t="shared" si="29"/>
         <v>1.9643107838899196</v>
       </c>
       <c r="U67" s="62">
-        <f t="shared" si="18"/>
+        <f t="shared" si="29"/>
         <v>2.002588528210187</v>
       </c>
       <c r="V67" s="62">
         <v>0.60391527521822497</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="33">
         <v>24690</v>
       </c>
       <c r="B68" s="10">
-        <f t="shared" ref="B68:J68" si="19">LOG(B50,2)</f>
+        <f t="shared" ref="B68:J68" si="30">LOG(B50,2)</f>
         <v>-0.4495296373062978</v>
       </c>
       <c r="C68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>0.99261942563960548</v>
       </c>
       <c r="D68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>-1.575995613879893</v>
       </c>
       <c r="E68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>1.094893708311226</v>
       </c>
       <c r="F68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>-3.5799134239802434E-3</v>
       </c>
       <c r="G68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>-0.81740050901494998</v>
       </c>
       <c r="H68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>1.7348639376958066</v>
       </c>
       <c r="I68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>-0.30752474335614682</v>
       </c>
       <c r="J68" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>1.1841906619345723</v>
       </c>
       <c r="L68" s="33">
         <v>24690</v>
       </c>
       <c r="M68" s="67">
-        <f t="shared" ref="M68:U68" si="20">LOG(M50,2)</f>
+        <f t="shared" ref="M68:U68" si="31">LOG(M50,2)</f>
         <v>-0.4495296373062978</v>
       </c>
       <c r="N68" s="62">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>0.99261942563960548</v>
       </c>
       <c r="O68" s="68">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>-1.575995613879893</v>
       </c>
       <c r="P68" s="63">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>1.094893708311226</v>
       </c>
       <c r="Q68" s="62">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>-3.5799134239802434E-3</v>
       </c>
       <c r="R68" s="62">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>-0.81740050901494998</v>
       </c>
       <c r="S68" s="62">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>1.7348639376958066</v>
       </c>
       <c r="T68" s="62">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>-0.30752474335614682</v>
       </c>
       <c r="U68" s="62">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>1.1841906619345723</v>
       </c>
       <c r="V68" s="62">
         <v>0.48624727790761502</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="32">
         <v>37035</v>
       </c>
       <c r="B69" s="10">
-        <f t="shared" ref="B69:J69" si="21">LOG(B51,2)</f>
+        <f t="shared" ref="B69:J69" si="32">LOG(B51,2)</f>
         <v>1.9847881910834628E-2</v>
       </c>
       <c r="C69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>0.4131589133043691</v>
       </c>
       <c r="D69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>-1.3747641681893808E-2</v>
       </c>
       <c r="E69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>0.27449211780168947</v>
       </c>
       <c r="F69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>-0.57987937051251526</v>
       </c>
       <c r="G69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>4.2298524352270384E-2</v>
       </c>
       <c r="H69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>5.6798562905649636E-2</v>
       </c>
       <c r="I69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>0.16198502231128811</v>
       </c>
       <c r="J69" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="32"/>
         <v>1.4615432138064233E-2</v>
       </c>
       <c r="L69" s="32">
         <v>37035</v>
       </c>
       <c r="M69" s="67">
-        <f t="shared" ref="M69:U69" si="22">LOG(M51,2)</f>
+        <f t="shared" ref="M69:U69" si="33">LOG(M51,2)</f>
         <v>1.9847881910834628E-2</v>
       </c>
       <c r="N69" s="62">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>0.4131589133043691</v>
       </c>
       <c r="O69" s="68">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>-1.3747641681893808E-2</v>
       </c>
       <c r="P69" s="63">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>0.27449211780168947</v>
       </c>
       <c r="Q69" s="62">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>-0.57987937051251526</v>
       </c>
       <c r="R69" s="62">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>4.2298524352270384E-2</v>
       </c>
       <c r="S69" s="62">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>5.6798562905649636E-2</v>
       </c>
       <c r="T69" s="62">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>0.16198502231128811</v>
       </c>
       <c r="U69" s="62">
-        <f t="shared" si="22"/>
+        <f t="shared" si="33"/>
         <v>1.4615432138064233E-2</v>
       </c>
       <c r="V69" s="62">
         <v>0.66176179774459298</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="33">
         <v>49380</v>
       </c>
       <c r="B70" s="10">
-        <f t="shared" ref="B70:J70" si="23">LOG(B52,2)</f>
+        <f t="shared" ref="B70:J70" si="34">LOG(B52,2)</f>
         <v>2.746871779063762E-3</v>
       </c>
       <c r="C70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>9.098329990876293E-3</v>
       </c>
       <c r="D70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>5.1829911228837573E-2</v>
       </c>
       <c r="E70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>-1.2707120285398787E-2</v>
       </c>
       <c r="F70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>6.0324957949339699E-4</v>
       </c>
       <c r="G70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>-3.2277619450108447E-3</v>
       </c>
       <c r="H70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>-1.5612730274144221E-2</v>
       </c>
       <c r="I70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>-6.2120403713050019E-2</v>
       </c>
       <c r="J70" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="34"/>
         <v>1.0472109404339571E-2</v>
       </c>
       <c r="L70" s="33">
         <v>49380</v>
       </c>
       <c r="M70" s="67">
-        <f t="shared" ref="M70:U70" si="24">LOG(M52,2)</f>
+        <f t="shared" ref="M70:U70" si="35">LOG(M52,2)</f>
         <v>2.746871779063762E-3</v>
       </c>
       <c r="N70" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>9.098329990876293E-3</v>
       </c>
       <c r="O70" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>5.1829911228837573E-2</v>
       </c>
       <c r="P70" s="63">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>-1.2707120285398787E-2</v>
       </c>
       <c r="Q70" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>6.0324957949339699E-4</v>
       </c>
       <c r="R70" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>-3.2277619450108447E-3</v>
       </c>
       <c r="S70" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>-1.5612730274144221E-2</v>
       </c>
       <c r="T70" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>-6.2120403713050019E-2</v>
       </c>
       <c r="U70" s="62">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>1.0472109404339571E-2</v>
       </c>
       <c r="V70" s="62">
         <v>0.52520044160502999</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="32">
         <v>61725</v>
       </c>
       <c r="B71" s="10">
-        <f t="shared" ref="B71:J71" si="25">LOG(B53,2)</f>
+        <f t="shared" ref="B71:J71" si="36">LOG(B53,2)</f>
         <v>1.3478219499352353</v>
       </c>
       <c r="C71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>-1.246597887748792</v>
       </c>
       <c r="D71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>0.62296013650124349</v>
       </c>
       <c r="E71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>0.73315940322246198</v>
       </c>
       <c r="F71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>0.76150654643185345</v>
       </c>
       <c r="G71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>1.1990121603373902</v>
       </c>
       <c r="H71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>0.2759682588824352</v>
       </c>
       <c r="I71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>1.7842107391820301</v>
       </c>
       <c r="J71" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>-0.93354614285571635</v>
       </c>
       <c r="L71" s="32">
         <v>61725</v>
       </c>
       <c r="M71" s="67">
-        <f t="shared" ref="M71:U71" si="26">LOG(M53,2)</f>
+        <f t="shared" ref="M71:U71" si="37">LOG(M53,2)</f>
         <v>1.3478219499352353</v>
       </c>
       <c r="N71" s="62">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>-1.246597887748792</v>
       </c>
       <c r="O71" s="68">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0.62296013650124349</v>
       </c>
       <c r="P71" s="63">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0.73315940322246198</v>
       </c>
       <c r="Q71" s="62">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0.76150654643185345</v>
       </c>
       <c r="R71" s="62">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>1.1990121603373902</v>
       </c>
       <c r="S71" s="62">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0.2759682588824352</v>
       </c>
       <c r="T71" s="62">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>1.7842107391820301</v>
       </c>
       <c r="U71" s="62">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>-0.93354614285571635</v>
       </c>
       <c r="V71" s="62">
         <v>0.65013584412540804</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="33">
         <v>74070</v>
       </c>
       <c r="B72" s="10">
-        <f t="shared" ref="B72:J72" si="27">LOG(B54,2)</f>
+        <f t="shared" ref="B72:J72" si="38">LOG(B54,2)</f>
         <v>0.82992276669182485</v>
       </c>
       <c r="C72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>-0.46405709879458601</v>
       </c>
       <c r="D72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>-1.432402225822659</v>
       </c>
       <c r="E72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>1.2129184144693266</v>
       </c>
       <c r="F72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>0.42985149921724702</v>
       </c>
       <c r="G72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>1.1231454302315853</v>
       </c>
       <c r="H72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>1.2568151665693217</v>
       </c>
       <c r="I72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>-0.65890510795032053</v>
       </c>
       <c r="J72" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>-1.3841897297362467</v>
       </c>
       <c r="L72" s="33">
         <v>74070</v>
       </c>
       <c r="M72" s="67">
-        <f t="shared" ref="M72:U72" si="28">LOG(M54,2)</f>
+        <f t="shared" ref="M72:U72" si="39">LOG(M54,2)</f>
         <v>0.82992276669182485</v>
       </c>
       <c r="N72" s="62">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>-0.46405709879458601</v>
       </c>
       <c r="O72" s="68">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>-1.432402225822659</v>
       </c>
       <c r="P72" s="63">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>1.2129184144693266</v>
       </c>
       <c r="Q72" s="62">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>0.42985149921724702</v>
       </c>
       <c r="R72" s="62">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>1.1231454302315853</v>
       </c>
       <c r="S72" s="62">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>1.2568151665693217</v>
       </c>
       <c r="T72" s="62">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>-0.65890510795032053</v>
       </c>
       <c r="U72" s="62">
-        <f t="shared" si="28"/>
+        <f t="shared" si="39"/>
         <v>-1.3841897297362467</v>
       </c>
       <c r="V72" s="62">
         <v>0.54313186736951702</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" s="32">
         <v>86415</v>
       </c>
       <c r="B73" s="10">
-        <f t="shared" ref="B73:J73" si="29">LOG(B55,2)</f>
+        <f t="shared" ref="B73:J73" si="40">LOG(B55,2)</f>
         <v>-0.21810313874181891</v>
       </c>
       <c r="C73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>2.8447860032079077E-2</v>
       </c>
       <c r="D73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>-1.615277281001404</v>
       </c>
       <c r="E73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>-4.3524948784128645E-2</v>
       </c>
       <c r="F73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>-0.80191709917094234</v>
       </c>
       <c r="G73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>-0.22948538658080106</v>
       </c>
       <c r="H73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>-0.1060594833784206</v>
       </c>
       <c r="I73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>-0.2711098429155151</v>
       </c>
       <c r="J73" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="40"/>
         <v>0.50883783009637207</v>
       </c>
       <c r="L73" s="32">
         <v>86415</v>
       </c>
       <c r="M73" s="67">
-        <f t="shared" ref="M73:U73" si="30">LOG(M55,2)</f>
+        <f t="shared" ref="M73:U73" si="41">LOG(M55,2)</f>
         <v>-0.21810313874181891</v>
       </c>
       <c r="N73" s="62">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>2.8447860032079077E-2</v>
       </c>
       <c r="O73" s="68">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>-1.615277281001404</v>
       </c>
       <c r="P73" s="63">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>-4.3524948784128645E-2</v>
       </c>
       <c r="Q73" s="62">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>-0.80191709917094234</v>
       </c>
       <c r="R73" s="62">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>-0.22948538658080106</v>
       </c>
       <c r="S73" s="62">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>-0.1060594833784206</v>
       </c>
       <c r="T73" s="62">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>-0.2711098429155151</v>
       </c>
       <c r="U73" s="62">
-        <f t="shared" si="30"/>
+        <f t="shared" si="41"/>
         <v>0.50883783009637207</v>
       </c>
       <c r="V73" s="62">
         <v>0.689942458078181</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="33">
         <v>98760</v>
       </c>
       <c r="B74" s="10">
-        <f t="shared" ref="B74:J74" si="31">LOG(B56,2)</f>
+        <f t="shared" ref="B74:J74" si="42">LOG(B56,2)</f>
         <v>1.0649519587078191</v>
       </c>
       <c r="C74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>1.2839798724938232</v>
       </c>
       <c r="D74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>-0.83768032832004014</v>
       </c>
       <c r="E74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>1.550925016012151</v>
       </c>
       <c r="F74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>-7.6249797537662589E-2</v>
       </c>
       <c r="G74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>-0.75659418738938511</v>
       </c>
       <c r="H74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>2.0561765284288476</v>
       </c>
       <c r="I74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>1.2655209812579513</v>
       </c>
       <c r="J74" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>-1.1596564155169586</v>
       </c>
       <c r="L74" s="33">
         <v>98760</v>
       </c>
       <c r="M74" s="67">
-        <f t="shared" ref="M74:U74" si="32">LOG(M56,2)</f>
+        <f t="shared" ref="M74:U74" si="43">LOG(M56,2)</f>
         <v>1.0649519587078191</v>
       </c>
       <c r="N74" s="62">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>1.2839798724938232</v>
       </c>
       <c r="O74" s="68">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>-0.83768032832004014</v>
       </c>
       <c r="P74" s="63">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>1.550925016012151</v>
       </c>
       <c r="Q74" s="62">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>-7.6249797537662589E-2</v>
       </c>
       <c r="R74" s="62">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>-0.75659418738938511</v>
       </c>
       <c r="S74" s="62">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>2.0561765284288476</v>
       </c>
       <c r="T74" s="62">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>1.2655209812579513</v>
       </c>
       <c r="U74" s="62">
-        <f t="shared" si="32"/>
+        <f t="shared" si="43"/>
         <v>-1.1596564155169586</v>
       </c>
       <c r="V74" s="62">
         <v>0.59117161347732095</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="32">
         <v>111105</v>
       </c>
       <c r="B75" s="10">
-        <f t="shared" ref="B75:J75" si="33">LOG(B57,2)</f>
+        <f t="shared" ref="B75:J75" si="44">LOG(B57,2)</f>
         <v>-0.29498508350467378</v>
       </c>
       <c r="C75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>-1.4320763811914767</v>
       </c>
       <c r="D75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>-1.6199482487660752</v>
       </c>
       <c r="E75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>-0.15427167899782776</v>
       </c>
       <c r="F75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>1.7989320475804622</v>
       </c>
       <c r="G75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>0.92765663464123949</v>
       </c>
       <c r="H75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>-0.79873702590789963</v>
       </c>
       <c r="I75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>1.3442912828673073</v>
       </c>
       <c r="J75" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="44"/>
         <v>1.6039873352314564</v>
       </c>
       <c r="L75" s="32">
         <v>111105</v>
       </c>
       <c r="M75" s="67">
-        <f t="shared" ref="M75:U75" si="34">LOG(M57,2)</f>
+        <f t="shared" ref="M75:U75" si="45">LOG(M57,2)</f>
         <v>-0.29498508350467378</v>
       </c>
       <c r="N75" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>-1.4320763811914767</v>
       </c>
       <c r="O75" s="68">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>-1.6199482487660752</v>
       </c>
       <c r="P75" s="63">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>-0.15427167899782776</v>
       </c>
       <c r="Q75" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>1.7989320475804622</v>
       </c>
       <c r="R75" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>0.92765663464123949</v>
       </c>
       <c r="S75" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>-0.79873702590789963</v>
       </c>
       <c r="T75" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>1.3442912828673073</v>
       </c>
       <c r="U75" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="45"/>
         <v>1.6039873352314564</v>
       </c>
       <c r="V75" s="62">
         <v>0.50762810253022606</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="33">
         <v>123450</v>
       </c>
       <c r="B76" s="10">
-        <f t="shared" ref="B76:J76" si="35">LOG(B58,2)</f>
+        <f t="shared" ref="B76:J76" si="46">LOG(B58,2)</f>
         <v>1.8282706338995041</v>
       </c>
       <c r="C76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>1.6942129457872086</v>
       </c>
       <c r="D76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>1.2432830577966723</v>
       </c>
       <c r="E76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>1.415106477728151</v>
       </c>
       <c r="F76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>-0.75677092664837575</v>
       </c>
       <c r="G76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>1.2750225966333175</v>
       </c>
       <c r="H76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>1.8170294413084713</v>
       </c>
       <c r="I76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>1.2108285630502869</v>
       </c>
       <c r="J76" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="46"/>
         <v>0.4588351813030343</v>
       </c>
       <c r="L76" s="33">
         <v>123450</v>
       </c>
       <c r="M76" s="69">
-        <f t="shared" ref="M76:U76" si="36">LOG(M58,2)</f>
+        <f t="shared" ref="M76:U76" si="47">LOG(M58,2)</f>
         <v>1.8282706338995041</v>
       </c>
       <c r="N76" s="70">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>1.6942129457872086</v>
       </c>
       <c r="O76" s="71">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>1.2432830577966723</v>
       </c>
       <c r="P76" s="63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>1.415106477728151</v>
       </c>
       <c r="Q76" s="62">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>-0.75677092664837575</v>
       </c>
       <c r="R76" s="62">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>1.2750225966333175</v>
       </c>
       <c r="S76" s="62">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>1.8170294413084713</v>
       </c>
       <c r="T76" s="62">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>1.2108285630502869</v>
       </c>
       <c r="U76" s="62">
-        <f t="shared" si="36"/>
+        <f t="shared" si="47"/>
         <v>0.4588351813030343</v>
       </c>
       <c r="V76" s="62">
         <v>0.53793669261472898</v>
       </c>
     </row>
-    <row r="77" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="55" t="s">
         <v>36</v>
       </c>
@@ -12369,7 +13366,7 @@
         <v>0.23061347902091037</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="56" t="s">
         <v>37</v>
       </c>
@@ -12410,7 +13407,7 @@
         <v>1.0979835831797293</v>
       </c>
     </row>
-    <row r="80" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="57" t="s">
         <v>60</v>
       </c>
@@ -12419,45 +13416,45 @@
         <v>1.4157171370497528</v>
       </c>
       <c r="C80" s="61">
-        <f t="shared" ref="C80:J80" si="37">C79/C78</f>
+        <f t="shared" ref="C80:J80" si="48">C79/C78</f>
         <v>-70.503842465480119</v>
       </c>
       <c r="D80" s="61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="48"/>
         <v>-2.830694116111784</v>
       </c>
       <c r="E80" s="61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="48"/>
         <v>0.85520164444135305</v>
       </c>
       <c r="F80" s="61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="48"/>
         <v>-166.97604227869769</v>
       </c>
       <c r="G80" s="61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="48"/>
         <v>1.9952715076083474</v>
       </c>
       <c r="H80" s="61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="48"/>
         <v>1.2078675506387606</v>
       </c>
       <c r="I80" s="61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="48"/>
         <v>1.426113608114659</v>
       </c>
       <c r="J80" s="61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="48"/>
         <v>4.7611422707870954</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="115" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
         <v>18</v>
       </c>
@@ -12477,7 +13474,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" s="52">
         <v>12345</v>
       </c>
@@ -12503,7 +13500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" s="53">
         <v>49380</v>
       </c>
@@ -12529,7 +13526,7 @@
         <v>4.2323150644463636</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" s="53">
         <v>98760</v>
       </c>
@@ -12555,7 +13552,7 @@
         <v>3.3284810109961214</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" s="53">
         <v>74070</v>
       </c>
@@ -12581,7 +13578,7 @@
         <v>1.0401550241609454</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="52">
         <v>111105</v>
       </c>
@@ -12607,7 +13604,7 @@
         <v>0.98923642634283937</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="52">
         <v>37035</v>
       </c>
@@ -12633,7 +13630,7 @@
         <v>1.2108064443826665</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="52">
         <v>86415</v>
       </c>
@@ -12659,7 +13656,7 @@
         <v>2.3896762324972909</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="53">
         <v>123450</v>
       </c>
@@ -12685,7 +13682,7 @@
         <v>0.92912236506217571</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="52">
         <v>61725</v>
       </c>
@@ -12711,7 +13708,7 @@
         <v>4.1588265843502423</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="53">
         <v>24690</v>
       </c>
@@ -12737,7 +13734,7 @@
         <v>0.57485219838322121</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T103" s="63">
         <v>2.6667941689618107</v>
       </c>
@@ -12745,7 +13742,7 @@
         <v>3.5235494014104844</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T105" s="94" t="s">
         <v>4</v>
       </c>
@@ -12753,7 +13750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T106" s="97">
         <v>0.56653283755186434</v>
       </c>
@@ -12761,7 +13758,7 @@
         <v>3.9022623769436366</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T107" s="62">
         <v>0.99752166924869701</v>
       </c>
@@ -12769,7 +13766,7 @@
         <v>0.80802691626256673</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E108" s="113"/>
       <c r="F108" s="105"/>
       <c r="G108" s="114"/>
@@ -12783,7 +13780,7 @@
         <v>1.1188254856170972</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12824,7 +13821,7 @@
         <v>0.95785527468573939</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>86415</v>
       </c>
@@ -12865,7 +13862,7 @@
         <v>3.4442998367507274</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>37035</v>
       </c>
@@ -12906,7 +13903,7 @@
         <v>0.63335878413151825</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>61725</v>
       </c>
@@ -12947,7 +13944,7 @@
         <v>0.82868180848462425</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>12345</v>
       </c>
@@ -12988,7 +13985,7 @@
         <v>2.4041401174379877</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>98760</v>
       </c>
@@ -13029,7 +14026,7 @@
         <v>2.5390543601866122</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>74070</v>
       </c>
@@ -13070,7 +14067,7 @@
         <v>2.314705358795603</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>123450</v>
       </c>
@@ -13105,7 +14102,7 @@
         <v>0.53793669261472898</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>49380</v>
       </c>
@@ -13146,7 +14143,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>111105</v>
       </c>
@@ -13187,7 +14184,7 @@
         <v>4.0071833665052106</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>24690</v>
       </c>
@@ -13228,7 +14225,7 @@
         <v>2.272358817360137</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T120" s="97">
         <v>1.0297531392620909</v>
       </c>
@@ -13236,7 +14233,7 @@
         <v>1.0101821342935104</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T121" s="62">
         <v>0.99776518683000603</v>
       </c>
@@ -13244,7 +14241,7 @@
         <v>1.0072851214242537</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T122" s="97">
         <v>2.2958241789090819</v>
       </c>
@@ -13252,7 +14249,7 @@
         <v>0.52356982480844416</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T123" s="62">
         <v>2.1782135934575275</v>
       </c>
@@ -13260,7 +14257,7 @@
         <v>0.38310460441034316</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T124" s="97">
         <v>0.85293908330560908</v>
       </c>
@@ -13268,7 +14265,7 @@
         <v>1.4229035070601472</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T125" s="62">
         <v>0.59189197949472416</v>
       </c>
@@ -13276,7 +14273,7 @@
         <v>0.44761912533182319</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T126" s="97">
         <v>1.9021837738526788</v>
       </c>
@@ -13284,7 +14281,7 @@
         <v>3.0398230274516944</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="T127" s="62">
         <v>2.4200260825085391</v>
       </c>
@@ -13292,8 +14289,8 @@
         <v>1.3744316665601157</v>
       </c>
     </row>
-    <row r="129" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="130" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="130" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K130" s="108" t="s">
         <v>117</v>
       </c>
@@ -13307,7 +14304,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="131" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I131" s="95" t="s">
         <v>59</v>
       </c>
@@ -13342,7 +14339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="132" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H132" s="113"/>
       <c r="I132" s="111">
         <v>0.60391527521822497</v>
@@ -13390,7 +14387,7 @@
         <v>1.660234270533365</v>
       </c>
     </row>
-    <row r="133" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="133" spans="8:22" x14ac:dyDescent="0.3">
       <c r="I133" s="112">
         <v>0.48624727790761502</v>
       </c>
@@ -13413,7 +14410,7 @@
         <v>3.3284810109961214</v>
       </c>
       <c r="P133">
-        <f t="shared" ref="P133:P141" si="38">O133/N133</f>
+        <f t="shared" ref="P133:P141" si="49">O133/N133</f>
         <v>1.5582970028789769</v>
       </c>
       <c r="Q133" s="67">
@@ -13423,7 +14420,7 @@
         <v>0.80802691626256673</v>
       </c>
       <c r="S133">
-        <f t="shared" ref="S133:S141" si="39">R133/Q133</f>
+        <f t="shared" ref="S133:S141" si="50">R133/Q133</f>
         <v>0.81003444954849757</v>
       </c>
       <c r="T133" s="67">
@@ -13433,11 +14430,11 @@
         <v>2.272358817360137</v>
       </c>
       <c r="V133">
-        <f t="shared" ref="V133:V141" si="40">U133/T133</f>
+        <f t="shared" ref="V133:V141" si="51">U133/T133</f>
         <v>4.0044140963703505</v>
       </c>
     </row>
-    <row r="134" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="134" spans="8:22" x14ac:dyDescent="0.3">
       <c r="I134" s="111">
         <v>0.66176179774459298</v>
       </c>
@@ -13460,7 +14457,7 @@
         <v>1.0401550241609454</v>
       </c>
       <c r="P134">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>0.85993912785621129</v>
       </c>
       <c r="Q134" s="100">
@@ -13470,7 +14467,7 @@
         <v>1.1188254856170972</v>
       </c>
       <c r="S134">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>1.6723356000315721</v>
       </c>
       <c r="T134" s="100">
@@ -13480,11 +14477,11 @@
         <v>1.0101821342935104</v>
       </c>
       <c r="V134">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>0.98099446923501998</v>
       </c>
     </row>
-    <row r="135" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="135" spans="8:22" x14ac:dyDescent="0.3">
       <c r="I135" s="112">
         <v>0.52520044160502999</v>
       </c>
@@ -13507,7 +14504,7 @@
         <v>0.98923642634283937</v>
       </c>
       <c r="P135">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>0.99798801139657689</v>
       </c>
       <c r="Q135" s="67">
@@ -13517,7 +14514,7 @@
         <v>0.95785527468573939</v>
       </c>
       <c r="S135">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>0.95745484009223281</v>
       </c>
       <c r="T135" s="67">
@@ -13527,11 +14524,11 @@
         <v>1.0072851214242537</v>
       </c>
       <c r="V135">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>1.0095412575222167</v>
       </c>
     </row>
-    <row r="136" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="136" spans="8:22" x14ac:dyDescent="0.3">
       <c r="I136" s="111">
         <v>0.65013584412540804</v>
       </c>
@@ -13554,7 +14551,7 @@
         <v>1.2108064443826665</v>
       </c>
       <c r="P136">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>0.7284030435911012</v>
       </c>
       <c r="Q136" s="100">
@@ -13564,7 +14561,7 @@
         <v>3.4442998367507274</v>
       </c>
       <c r="S136">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>2.0317236627995281</v>
       </c>
       <c r="T136" s="100">
@@ -13574,11 +14571,11 @@
         <v>0.52356982480844416</v>
       </c>
       <c r="V136">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>0.22805310163482617</v>
       </c>
     </row>
-    <row r="137" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="137" spans="8:22" x14ac:dyDescent="0.3">
       <c r="I137" s="112">
         <v>0.54313186736951702</v>
       </c>
@@ -13601,7 +14598,7 @@
         <v>2.3896762324972909</v>
       </c>
       <c r="P137">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>1.0308945391656719</v>
       </c>
       <c r="Q137" s="67">
@@ -13611,7 +14608,7 @@
         <v>0.63335878413151825</v>
       </c>
       <c r="S137">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>0.47016641495547906</v>
       </c>
       <c r="T137" s="67">
@@ -13621,11 +14618,11 @@
         <v>0.38310460441034316</v>
       </c>
       <c r="V137">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>0.1758801825317014</v>
       </c>
     </row>
-    <row r="138" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="138" spans="8:22" x14ac:dyDescent="0.3">
       <c r="I138" s="111">
         <v>0.689942458078181</v>
       </c>
@@ -13648,7 +14645,7 @@
         <v>0.92912236506217571</v>
       </c>
       <c r="P138">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>0.95758035829013344</v>
       </c>
       <c r="Q138" s="100">
@@ -13658,7 +14655,7 @@
         <v>0.82868180848462425</v>
       </c>
       <c r="S138">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>1.4447373684303741</v>
       </c>
       <c r="T138" s="100">
@@ -13668,11 +14665,11 @@
         <v>1.4229035070601472</v>
       </c>
       <c r="V138">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>1.6682357918757948</v>
       </c>
     </row>
-    <row r="139" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="139" spans="8:22" x14ac:dyDescent="0.3">
       <c r="I139" s="112">
         <v>0.59117161347732095</v>
       </c>
@@ -13695,7 +14692,7 @@
         <v>4.1588265843502423</v>
       </c>
       <c r="P139">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>1.4193707808113147</v>
       </c>
       <c r="Q139" s="67">
@@ -13705,7 +14702,7 @@
         <v>2.4041401174379877</v>
       </c>
       <c r="S139">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>2.5346223010653435</v>
       </c>
       <c r="T139" s="67">
@@ -13715,11 +14712,11 @@
         <v>0.44761912533182319</v>
       </c>
       <c r="V139">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>0.75625137835781919</v>
       </c>
     </row>
-    <row r="140" spans="8:22" x14ac:dyDescent="0.25">
+    <row r="140" spans="8:22" x14ac:dyDescent="0.3">
       <c r="H140" s="113"/>
       <c r="I140" s="111">
         <v>0.50762810253022606</v>
@@ -13743,7 +14740,7 @@
         <v>0.57485219838322121</v>
       </c>
       <c r="P140">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>0.63972982628992092</v>
       </c>
       <c r="Q140" s="100">
@@ -13753,7 +14750,7 @@
         <v>2.5390543601866122</v>
       </c>
       <c r="S140">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>0.72969184490525218</v>
       </c>
       <c r="T140" s="100">
@@ -13763,11 +14760,11 @@
         <v>3.0398230274516944</v>
       </c>
       <c r="V140">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>1.5980701072298833</v>
       </c>
     </row>
-    <row r="141" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I141" s="112">
         <v>0.53793669261472898</v>
       </c>
@@ -13790,7 +14787,7 @@
         <v>3.5235494014104844</v>
       </c>
       <c r="P141">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>1.3212678512726053</v>
       </c>
       <c r="Q141" s="69">
@@ -13800,7 +14797,7 @@
         <v>2.314705358795603</v>
       </c>
       <c r="S141">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>3.9111679536105042</v>
       </c>
       <c r="T141" s="69">
@@ -13810,12 +14807,12 @@
         <v>1.3744316665601157</v>
       </c>
       <c r="V141">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>0.56794084844549031</v>
       </c>
     </row>
-    <row r="145" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="146" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="146" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L146" s="106" t="s">
         <v>108</v>
       </c>
@@ -13832,7 +14829,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L147" s="108" t="s">
         <v>109</v>
       </c>
@@ -13849,7 +14846,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="148" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L148" s="107" t="s">
         <v>110</v>
       </c>
@@ -13857,8 +14854,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="153" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="154" spans="11:19" x14ac:dyDescent="0.25">
+    <row r="153" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="154" spans="11:19" x14ac:dyDescent="0.3">
       <c r="K154" s="102">
         <v>3.7015741310872814</v>
       </c>
@@ -13887,7 +14884,7 @@
         <v>4.0071833665052106</v>
       </c>
     </row>
-    <row r="155" spans="11:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="11:19" x14ac:dyDescent="0.3">
       <c r="K155" s="100">
         <v>0.8150807597453037</v>
       </c>
@@ -14069,21 +15066,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B9B394B-2F94-478A-9EA6-A5E96B91D71F}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -14117,7 +15114,7 @@
       <c r="K1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="134" t="s">
+      <c r="L1" s="117" t="s">
         <v>67</v>
       </c>
       <c r="M1" s="8" t="s">
@@ -14127,393 +15124,393 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="32">
         <v>12345</v>
       </c>
-      <c r="B2" s="116">
+      <c r="B2" s="79">
         <v>0.712406808509643</v>
       </c>
-      <c r="C2" s="122">
+      <c r="C2" s="83">
         <v>249.944372693215</v>
       </c>
-      <c r="D2" s="123">
+      <c r="D2" s="84">
         <v>282.06339872878402</v>
       </c>
-      <c r="E2" s="123">
+      <c r="E2" s="84">
         <v>39.279403191200601</v>
       </c>
-      <c r="F2" s="123">
+      <c r="F2" s="84">
         <v>1.21732841562099</v>
       </c>
-      <c r="G2" s="123">
+      <c r="G2" s="84">
         <v>3.4961092224547201</v>
       </c>
-      <c r="H2" s="123">
+      <c r="H2" s="84">
         <v>0.11255193689562699</v>
       </c>
-      <c r="I2" s="123">
+      <c r="I2" s="84">
         <v>0.101294616086198</v>
       </c>
-      <c r="J2" s="123">
+      <c r="J2" s="84">
         <v>0.116619630354845</v>
       </c>
-      <c r="K2" s="124">
+      <c r="K2" s="85">
         <v>1.5778363102433</v>
       </c>
-      <c r="L2" s="120" t="s">
+      <c r="L2" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="120" t="s">
+      <c r="M2" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="N2" s="120"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N2" s="116"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="33">
         <v>24690</v>
       </c>
-      <c r="B3" s="117">
+      <c r="B3" s="80">
         <v>0.48840316014479601</v>
       </c>
-      <c r="C3" s="125">
+      <c r="C3" s="86">
         <v>418.25670506356499</v>
       </c>
-      <c r="D3" s="126">
+      <c r="D3" s="24">
         <v>330.038709874456</v>
       </c>
-      <c r="E3" s="126">
+      <c r="E3" s="24">
         <v>32.478360119580003</v>
       </c>
-      <c r="F3" s="126">
+      <c r="F3" s="24">
         <v>0.51822808473398296</v>
       </c>
-      <c r="G3" s="126">
+      <c r="G3" s="24">
         <v>5.9949632502605397</v>
       </c>
-      <c r="H3" s="126">
+      <c r="H3" s="24">
         <v>0.44945725927744501</v>
       </c>
-      <c r="I3" s="126">
+      <c r="I3" s="24">
         <v>0.100567648699738</v>
       </c>
-      <c r="J3" s="126">
+      <c r="J3" s="24">
         <v>0.21097341589110599</v>
       </c>
-      <c r="K3" s="127">
+      <c r="K3" s="87">
         <v>2.4971317426222299</v>
       </c>
-      <c r="L3" s="121" t="s">
+      <c r="L3" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="32">
         <v>37035</v>
       </c>
-      <c r="B4" s="118">
+      <c r="B4" s="81">
         <v>0.59089730657681105</v>
       </c>
-      <c r="C4" s="128">
+      <c r="C4" s="88">
         <v>332.23429799566497</v>
       </c>
-      <c r="D4" s="129">
+      <c r="D4" s="23">
         <v>285.69091361756898</v>
       </c>
-      <c r="E4" s="129">
+      <c r="E4" s="23">
         <v>27.272250147894098</v>
       </c>
-      <c r="F4" s="129">
+      <c r="F4" s="23">
         <v>1.8613438661077599</v>
       </c>
-      <c r="G4" s="129">
+      <c r="G4" s="23">
         <v>4.2838259514911803</v>
       </c>
-      <c r="H4" s="129">
+      <c r="H4" s="23">
         <v>0.10000825970358</v>
       </c>
-      <c r="I4" s="129">
+      <c r="I4" s="23">
         <v>0.108603346406101</v>
       </c>
-      <c r="J4" s="129">
+      <c r="J4" s="23">
         <v>1.33482998823821</v>
       </c>
-      <c r="K4" s="130">
+      <c r="K4" s="89">
         <v>0.39592331101205303</v>
       </c>
-      <c r="L4" s="120" t="s">
+      <c r="L4" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>49380</v>
       </c>
-      <c r="B5" s="117">
+      <c r="B5" s="80">
         <v>0.67887988874580396</v>
       </c>
-      <c r="C5" s="125">
+      <c r="C5" s="86">
         <v>352.82756797919097</v>
       </c>
-      <c r="D5" s="126">
+      <c r="D5" s="24">
         <v>375.80018132998202</v>
       </c>
-      <c r="E5" s="126">
+      <c r="E5" s="24">
         <v>57.3813719412165</v>
       </c>
-      <c r="F5" s="126">
+      <c r="F5" s="24">
         <v>5.9714044068960703</v>
       </c>
-      <c r="G5" s="126">
+      <c r="G5" s="24">
         <v>5.3269490301681097</v>
       </c>
-      <c r="H5" s="126">
+      <c r="H5" s="24">
         <v>0.20186132703462301</v>
       </c>
-      <c r="I5" s="126">
+      <c r="I5" s="24">
         <v>1.8813684765391401</v>
       </c>
-      <c r="J5" s="126">
+      <c r="J5" s="24">
         <v>0.94484692942459003</v>
       </c>
-      <c r="K5" s="127">
+      <c r="K5" s="87">
         <v>1.6140854471050099</v>
       </c>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="32">
         <v>61725</v>
       </c>
-      <c r="B6" s="118">
+      <c r="B6" s="81">
         <v>0.51157923348573597</v>
       </c>
-      <c r="C6" s="128">
+      <c r="C6" s="88">
         <v>328.66130914373701</v>
       </c>
-      <c r="D6" s="129">
+      <c r="D6" s="23">
         <v>234.68146076384599</v>
       </c>
-      <c r="E6" s="129">
+      <c r="E6" s="23">
         <v>48.640617215127101</v>
       </c>
-      <c r="F6" s="129">
+      <c r="F6" s="23">
         <v>0.66329624206417603</v>
       </c>
-      <c r="G6" s="129">
+      <c r="G6" s="23">
         <v>5.9885827680080004</v>
       </c>
-      <c r="H6" s="129">
+      <c r="H6" s="23">
         <v>0.44988299110504398</v>
       </c>
-      <c r="I6" s="129">
+      <c r="I6" s="23">
         <v>0.10080594271322001</v>
       </c>
-      <c r="J6" s="129">
+      <c r="J6" s="23">
         <v>1.3672940648941001</v>
       </c>
-      <c r="K6" s="130">
+      <c r="K6" s="89">
         <v>1.5598435050494699</v>
       </c>
-      <c r="L6" s="120"/>
-      <c r="M6" s="120"/>
-      <c r="N6" s="120"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L6" s="116"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="116"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>74070</v>
       </c>
-      <c r="B7" s="117">
+      <c r="B7" s="80">
         <v>0.61136346201208103</v>
       </c>
-      <c r="C7" s="125">
+      <c r="C7" s="86">
         <v>374.00585707519201</v>
       </c>
-      <c r="D7" s="126">
+      <c r="D7" s="24">
         <v>229.52299874123099</v>
       </c>
-      <c r="E7" s="126">
+      <c r="E7" s="24">
         <v>11.975744823062</v>
       </c>
-      <c r="F7" s="126">
+      <c r="F7" s="24">
         <v>0.67413267245759501</v>
       </c>
-      <c r="G7" s="126">
+      <c r="G7" s="24">
         <v>5.9999974178098601</v>
       </c>
-      <c r="H7" s="126">
+      <c r="H7" s="24">
         <v>0.23655072878358799</v>
       </c>
-      <c r="I7" s="126">
+      <c r="I7" s="24">
         <v>0.10022549690346</v>
       </c>
-      <c r="J7" s="126">
+      <c r="J7" s="24">
         <v>0.26935782511441803</v>
       </c>
-      <c r="K7" s="127">
+      <c r="K7" s="87">
         <v>1.4268128233335999</v>
       </c>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="121"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="32">
         <v>86415</v>
       </c>
-      <c r="B8" s="118">
+      <c r="B8" s="81">
         <v>0.55681124125554704</v>
       </c>
-      <c r="C8" s="128">
+      <c r="C8" s="88">
         <v>303.94088440246401</v>
       </c>
-      <c r="D8" s="129">
+      <c r="D8" s="23">
         <v>273.73714889572699</v>
       </c>
-      <c r="E8" s="129">
+      <c r="E8" s="23">
         <v>23.339435792740499</v>
       </c>
-      <c r="F8" s="129">
+      <c r="F8" s="23">
         <v>1.1653244055629799</v>
       </c>
-      <c r="G8" s="129">
+      <c r="G8" s="23">
         <v>2.9105702589015099</v>
       </c>
-      <c r="H8" s="129">
+      <c r="H8" s="23">
         <v>0.10224991157883501</v>
       </c>
-      <c r="I8" s="129">
+      <c r="I8" s="23">
         <v>0.140456232076098</v>
       </c>
-      <c r="J8" s="129">
+      <c r="J8" s="23">
         <v>1.4935508465976299</v>
       </c>
-      <c r="K8" s="130">
+      <c r="K8" s="89">
         <v>0.39658030424374302</v>
       </c>
-      <c r="L8" s="120"/>
-      <c r="M8" s="120"/>
-      <c r="N8" s="120"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L8" s="116"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="116"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>98760</v>
       </c>
-      <c r="B9" s="117">
+      <c r="B9" s="80">
         <v>0.65351070789674404</v>
       </c>
-      <c r="C9" s="125">
+      <c r="C9" s="86">
         <v>292.50123590147302</v>
       </c>
-      <c r="D9" s="126">
+      <c r="D9" s="24">
         <v>271.37147153366601</v>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="24">
         <v>22.107023707693202</v>
       </c>
-      <c r="F9" s="126">
+      <c r="F9" s="24">
         <v>1.38102005624965</v>
       </c>
-      <c r="G9" s="126">
+      <c r="G9" s="24">
         <v>4.3325973231689101</v>
       </c>
-      <c r="H9" s="126">
+      <c r="H9" s="24">
         <v>0.32138518815565298</v>
       </c>
-      <c r="I9" s="126">
+      <c r="I9" s="24">
         <v>0.198272602909567</v>
       </c>
-      <c r="J9" s="126">
+      <c r="J9" s="24">
         <v>0.448120466117577</v>
       </c>
-      <c r="K9" s="127">
+      <c r="K9" s="87">
         <v>0.80814293920319002</v>
       </c>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="32">
         <v>111105</v>
       </c>
-      <c r="B10" s="118">
+      <c r="B10" s="81">
         <v>0.60026349158933801</v>
       </c>
-      <c r="C10" s="128">
+      <c r="C10" s="88">
         <v>327.949623199999</v>
       </c>
-      <c r="D10" s="129">
+      <c r="D10" s="23">
         <v>283.96197152550002</v>
       </c>
-      <c r="E10" s="129">
+      <c r="E10" s="23">
         <v>33.227388471928798</v>
       </c>
-      <c r="F10" s="129">
+      <c r="F10" s="23">
         <v>1.0703813500850601</v>
       </c>
-      <c r="G10" s="129">
+      <c r="G10" s="23">
         <v>5.5493637313373601</v>
       </c>
-      <c r="H10" s="129">
+      <c r="H10" s="23">
         <v>0.230454066465624</v>
       </c>
-      <c r="I10" s="129">
+      <c r="I10" s="23">
         <v>0.10680025663968799</v>
       </c>
-      <c r="J10" s="129">
+      <c r="J10" s="23">
         <v>0.17786109165508901</v>
       </c>
-      <c r="K10" s="130">
+      <c r="K10" s="89">
         <v>1.2350472397530501</v>
       </c>
-      <c r="L10" s="120"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="120"/>
-    </row>
-    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="116"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33">
         <v>123450</v>
       </c>
-      <c r="B11" s="119">
+      <c r="B11" s="82">
         <v>0.52796028692755004</v>
       </c>
-      <c r="C11" s="131">
+      <c r="C11" s="90">
         <v>337.33985082356497</v>
       </c>
-      <c r="D11" s="132">
+      <c r="D11" s="91">
         <v>258.23863001213198</v>
       </c>
-      <c r="E11" s="132">
+      <c r="E11" s="91">
         <v>16.802151126164599</v>
       </c>
-      <c r="F11" s="132">
+      <c r="F11" s="91">
         <v>1.50392832987264</v>
       </c>
-      <c r="G11" s="132">
+      <c r="G11" s="91">
         <v>4.3842426260623402</v>
       </c>
-      <c r="H11" s="132">
+      <c r="H11" s="91">
         <v>0.44156529106103798</v>
       </c>
-      <c r="I11" s="132">
+      <c r="I11" s="91">
         <v>0.128946976627171</v>
       </c>
-      <c r="J11" s="132">
+      <c r="J11" s="91">
         <v>8.1200539454317905E-2</v>
       </c>
-      <c r="K11" s="133">
+      <c r="K11" s="92">
         <v>1.7917193119714701</v>
       </c>
-      <c r="L11" s="121"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:N11">
@@ -14534,20 +15531,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FCF11C-DDE7-4784-B0AC-FF45FB494109}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>107</v>
       </c>
@@ -14594,7 +15591,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="52">
         <v>12345</v>
       </c>
@@ -14641,7 +15638,7 @@
         <v>0.60391527521822497</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="53">
         <v>24690</v>
       </c>
@@ -14688,7 +15685,7 @@
         <v>0.48624727790761502</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="52">
         <v>37035</v>
       </c>
@@ -14735,7 +15732,7 @@
         <v>0.66176179774459298</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="53">
         <v>49380</v>
       </c>
@@ -14782,7 +15779,7 @@
         <v>0.52520044160502999</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>61725</v>
       </c>
@@ -14829,7 +15826,7 @@
         <v>0.65013584412540804</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="53">
         <v>74070</v>
       </c>
@@ -14876,7 +15873,7 @@
         <v>0.54313186736951702</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="52">
         <v>86415</v>
       </c>
@@ -14923,7 +15920,7 @@
         <v>0.689942458078181</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="53">
         <v>98760</v>
       </c>
@@ -14970,7 +15967,7 @@
         <v>0.59117161347732095</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="52">
         <v>111105</v>
       </c>
@@ -15017,7 +16014,7 @@
         <v>0.50762810253022606</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="53">
         <v>123450</v>
       </c>
@@ -15076,15 +16073,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74838A9-EA36-440F-BC03-31688569CF0D}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>72</v>
       </c>
@@ -15098,7 +16095,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -15112,7 +16109,7 @@
         <v>-0.45965949888373803</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -15126,7 +16123,7 @@
         <v>0.19376473419892001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -15140,7 +16137,7 @@
         <v>-0.28405184904618402</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -15154,7 +16151,7 @@
         <v>7.2200220231434506E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -15168,7 +16165,7 @@
         <v>-9.6022789968516306E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -15182,7 +16179,7 @@
         <v>-0.47201309660431301</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -15196,7 +16193,7 @@
         <v>-0.13640339554943001</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -15210,7 +16207,7 @@
         <v>6.3205573209875798E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -15224,7 +16221,7 @@
         <v>5.8121653149551603E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -15238,7 +16235,7 @@
         <v>0.44130801936368202</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -15252,7 +16249,7 @@
         <v>0.23885655891296401</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>5</v>
       </c>
@@ -15266,7 +16263,7 @@
         <v>-2.2231198244722101E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -15280,7 +16277,7 @@
         <v>1.49421743525793E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -15294,7 +16291,7 @@
         <v>-2.5767946213576299E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -15308,7 +16305,7 @@
         <v>-0.208721184212809</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -15322,7 +16319,7 @@
         <v>0.14536670100049301</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -15336,7 +16333,7 @@
         <v>-2.0865512606801799E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>10</v>
       </c>
@@ -15350,7 +16347,7 @@
         <v>0.96646564267355795</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>88</v>
       </c>
@@ -15364,7 +16361,7 @@
         <v>-5.090744290343E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -15378,7 +16375,7 @@
         <v>-3.3134686314884303E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -15392,7 +16389,7 @@
         <v>0.77286824351740502</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>91</v>
       </c>
@@ -15406,7 +16403,7 @@
         <v>0.11083096187591999</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -15420,7 +16417,7 @@
         <v>-0.35513067931786702</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -15434,7 +16431,7 @@
         <v>0.41934943267650499</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -15448,7 +16445,7 @@
         <v>0.27430664460676102</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>95</v>
       </c>
@@ -15462,7 +16459,7 @@
         <v>-0.232398016499614</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
@@ -15476,7 +16473,7 @@
         <v>0.46601541381699302</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>96</v>
       </c>
@@ -15490,7 +16487,7 @@
         <v>0.121100210187723</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>32</v>
       </c>
@@ -15504,7 +16501,7 @@
         <v>1.1877979999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -15518,7 +16515,7 @@
         <v>-0.24863147470347399</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>9</v>
       </c>
@@ -15532,7 +16529,7 @@
         <v>0.76242033842198298</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>98</v>
       </c>
@@ -15546,7 +16543,7 @@
         <v>0.276280659692554</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -15560,7 +16557,7 @@
         <v>0.80364542202849298</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>100</v>
       </c>
@@ -15574,7 +16571,7 @@
         <v>-0.53736354954134202</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -15588,7 +16585,7 @@
         <v>-0.29963637906952301</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>102</v>
       </c>
@@ -15602,7 +16599,7 @@
         <v>0.94816817278999399</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>103</v>
       </c>
@@ -15616,7 +16613,7 @@
         <v>8.5007066231793701E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>104</v>
       </c>
@@ -15630,7 +16627,7 @@
         <v>0.17337086753551201</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>105</v>
       </c>
@@ -15644,7 +16641,7 @@
         <v>0.91885899999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>106</v>
       </c>
@@ -15669,20 +16666,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D838E4-5041-4172-BF4F-6C64A37B593C}">
   <dimension ref="C4:V31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C4" s="8" t="s">
         <v>18</v>
       </c>
@@ -15735,7 +16732,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C5" s="52">
         <v>12345</v>
       </c>
@@ -15791,7 +16788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C6" s="53">
         <v>24690</v>
       </c>
@@ -15847,7 +16844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C7" s="52">
         <v>37035</v>
       </c>
@@ -15903,7 +16900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C8" s="53">
         <v>49380</v>
       </c>
@@ -15959,7 +16956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C9" s="52">
         <v>61725</v>
       </c>
@@ -16015,7 +17012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C10" s="53">
         <v>74070</v>
       </c>
@@ -16071,7 +17068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C11" s="52">
         <v>86415</v>
       </c>
@@ -16127,7 +17124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C12" s="53">
         <v>98760</v>
       </c>
@@ -16183,7 +17180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C13" s="52">
         <v>111105</v>
       </c>
@@ -16239,7 +17236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="53">
         <v>123450</v>
       </c>
@@ -16295,8 +17292,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>36</v>
       </c>
@@ -16365,7 +17362,7 @@
         <v>8.69439801662652E-2</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
@@ -16410,7 +17407,7 @@
         <v>0.61683310529164304</v>
       </c>
     </row>
-    <row r="19" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="4" t="s">
         <v>60</v>
       </c>
@@ -16455,7 +17452,7 @@
         <v>0.46367541540959673</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
       <c r="P21">
         <f>Q17^2</f>
         <v>0.20416068933626805</v>
@@ -16470,7 +17467,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T22" s="54" t="s">
         <v>70</v>
       </c>
@@ -16481,7 +17478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T23" s="54" t="s">
         <v>71</v>
       </c>
@@ -16492,7 +17489,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T24" s="54" t="s">
         <v>70</v>
       </c>
@@ -16503,7 +17500,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T25" s="54" t="s">
         <v>71</v>
       </c>
@@ -16514,7 +17511,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T26" s="54" t="s">
         <v>70</v>
       </c>
@@ -16525,7 +17522,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T27" s="54" t="s">
         <v>71</v>
       </c>
@@ -16536,7 +17533,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T28" s="54" t="s">
         <v>70</v>
       </c>
@@ -16547,7 +17544,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T29" s="54" t="s">
         <v>70</v>
       </c>
@@ -16558,7 +17555,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T30" s="54" t="s">
         <v>70</v>
       </c>
@@ -16569,7 +17566,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
       <c r="T31" s="54" t="s">
         <v>70</v>
       </c>
@@ -16601,34 +17598,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E8849C-2D02-46F4-ACC4-400EB6662519}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Y87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="25.5703125" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="25.5546875" customWidth="1"/>
+    <col min="9" max="10" width="14.5546875" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" customWidth="1"/>
-    <col min="13" max="13" width="21.140625" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
+    <col min="13" max="13" width="21.109375" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
-    <col min="15" max="15" width="20.42578125" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" customWidth="1"/>
+    <col min="15" max="15" width="20.44140625" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" customWidth="1"/>
     <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" customWidth="1"/>
-    <col min="21" max="21" width="13.7109375" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="20" max="20" width="17.109375" customWidth="1"/>
+    <col min="21" max="21" width="13.6640625" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" customWidth="1"/>
     <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="25" max="25" width="27.85546875" customWidth="1"/>
+    <col min="25" max="25" width="27.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -16693,7 +17690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -16758,7 +17755,7 @@
         <v>1.5778363102433</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -16826,7 +17823,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -16895,7 +17892,7 @@
         <v>0.15529912764928527</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -16960,7 +17957,7 @@
         <v>1.6140854471050099</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -17025,7 +18022,7 @@
         <v>1.5598435050494699</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -17090,7 +18087,7 @@
         <v>1.4268128233335999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -17155,7 +18152,7 @@
         <v>0.39658030424374302</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -17220,7 +18217,7 @@
         <v>0.80814293920319002</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -17285,7 +18282,7 @@
         <v>1.2350472397530501</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -17350,8 +18347,8 @@
         <v>1.7917193119714701</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -17436,7 +18433,7 @@
         <v>1.3303122934537115</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -17521,7 +18518,7 @@
         <v>0.61683310529164304</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
@@ -17606,8 +18603,8 @@
         <v>0.4227589775374791</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>32</v>
       </c>
@@ -17692,7 +18689,7 @@
         <v>0.39592331101205303</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>33</v>
       </c>
@@ -17777,7 +18774,7 @@
         <v>2.4971317426222299</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="18" t="s">
         <v>34</v>
       </c>
@@ -17862,13 +18859,13 @@
         <v>2.1012084316101767</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>18</v>
       </c>
@@ -17933,7 +18930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -18018,7 +19015,7 @@
         <v>0.56249203146664295</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
@@ -18103,7 +19100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -18188,7 +19185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
@@ -18273,7 +19270,7 @@
         <v>0.5797435979064044</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -18358,7 +19355,7 @@
         <v>0.55392895656024632</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
@@ -18443,7 +19440,7 @@
         <v>0.49061744509161626</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -18528,7 +19525,7 @@
         <v>3.1267399359640623E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
@@ -18613,7 +19610,7 @@
         <v>0.19618216926497342</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -18698,7 +19695,7 @@
         <v>0.39935301806207207</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
@@ -18783,8 +19780,8 @@
         <v>0.6642825052295287</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>36</v>
       </c>
@@ -18869,7 +19866,7 @@
         <v>0.44469123975750807</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
@@ -18954,7 +19951,7 @@
         <v>0.29356112226284808</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>38</v>
       </c>
@@ -19039,13 +20036,13 @@
         <v>9.57534805602476E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="30" t="s">
         <v>50</v>
       </c>
@@ -19077,7 +20074,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="31" t="s">
         <v>51</v>
       </c>
@@ -19109,8 +20106,8 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
         <v>57</v>
       </c>
@@ -19118,7 +20115,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>31</v>
       </c>
@@ -19192,7 +20189,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>21</v>
       </c>
@@ -19284,7 +20281,7 @@
         <v>0.52304667728695398</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>22</v>
       </c>
@@ -19376,7 +20373,7 @@
         <v>0.495336580378823</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>23</v>
       </c>
@@ -19468,7 +20465,7 @@
         <v>0.58339645238371796</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>24</v>
       </c>
@@ -19560,7 +20557,7 @@
         <v>0.39443555162616101</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>25</v>
       </c>
@@ -19652,7 +20649,7 @@
         <v>0.59310751110297899</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>26</v>
       </c>
@@ -19744,7 +20741,7 @@
         <v>0.46257299662969398</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>27</v>
       </c>
@@ -19836,7 +20833,7 @@
         <v>0.35074167737220402</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>28</v>
       </c>
@@ -19928,7 +20925,7 @@
         <v>0.67467449249167699</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>29</v>
       </c>
@@ -20020,7 +21017,7 @@
         <v>0.52135653128783699</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>30</v>
       </c>
@@ -20112,8 +21109,8 @@
         <v>0.36092217938737903</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="14" t="s">
         <v>57</v>
       </c>
@@ -20121,7 +21118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>18</v>
       </c>
@@ -20195,7 +21192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>21</v>
       </c>
@@ -20287,7 +21284,7 @@
         <v>0.52304667728695398</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>22</v>
       </c>
@@ -20379,7 +21376,7 @@
         <v>0.495336580378823</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>23</v>
       </c>
@@ -20471,7 +21468,7 @@
         <v>0.58339645238371796</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>24</v>
       </c>
@@ -20563,7 +21560,7 @@
         <v>0.39443555162616101</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>25</v>
       </c>
@@ -20655,7 +21652,7 @@
         <v>0.59310751110297899</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>26</v>
       </c>
@@ -20747,7 +21744,7 @@
         <v>0.46257299662969398</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>27</v>
       </c>
@@ -20839,7 +21836,7 @@
         <v>0.35074167737220402</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>28</v>
       </c>
@@ -20931,7 +21928,7 @@
         <v>0.67467449249167699</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>29</v>
       </c>
@@ -21023,7 +22020,7 @@
         <v>0.52135653128783699</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>30</v>
       </c>
@@ -21115,8 +22112,8 @@
         <v>0.36092217938737903</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="14" t="s">
         <v>53</v>
       </c>
@@ -21124,7 +22121,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>18</v>
       </c>
@@ -21150,7 +22147,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>21</v>
       </c>
@@ -21176,7 +22173,7 @@
         <v>0.78110128743181817</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>22</v>
       </c>
@@ -21202,7 +22199,7 @@
         <v>0.48389597470080942</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>23</v>
       </c>
@@ -21228,7 +22225,7 @@
         <v>0.68951104757363746</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>24</v>
       </c>
@@ -21254,7 +22251,7 @@
         <v>0.61645730773014906</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>25</v>
       </c>
@@ -21280,7 +22277,7 @@
         <v>0.61348983186062345</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>26</v>
       </c>
@@ -21306,7 +22303,7 @@
         <v>0.58773905989437214</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>27</v>
       </c>
@@ -21332,7 +22329,7 @@
         <v>0.43305848263441027</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>28</v>
       </c>
@@ -21358,7 +22355,7 @@
         <v>0.88226191615460547</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>29</v>
       </c>
@@ -21384,7 +22381,7 @@
         <v>0.63212889205150868</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="25" t="s">
         <v>30</v>
       </c>

--- a/THESIS/Stats rundown THESIS.xlsx
+++ b/THESIS/Stats rundown THESIS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GlenA\Documents\GitHub\serotonin\THESIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\serotonin\THESIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE506CE-765B-4ACD-9434-A9D0BCB99E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DEB5B-FA2D-42E5-9D1C-95990FA14404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2C90E502-06BA-4582-B789-DE830060AC34}"/>
   </bookViews>
   <sheets>
     <sheet name="Cosine Data" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="172">
   <si>
     <t>seed_a_e</t>
   </si>
@@ -456,6 +456,108 @@
   <si>
     <t>correlations</t>
   </si>
+  <si>
+    <t>poor ordering</t>
+  </si>
+  <si>
+    <t>good ordering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decent ordering </t>
+  </si>
+  <si>
+    <t>decent spread</t>
+  </si>
+  <si>
+    <t>not steep</t>
+  </si>
+  <si>
+    <t>good spread</t>
+  </si>
+  <si>
+    <t>steep</t>
+  </si>
+  <si>
+    <t>weak ordering</t>
+  </si>
+  <si>
+    <t>unclear</t>
+  </si>
+  <si>
+    <t>weak spread</t>
+  </si>
+  <si>
+    <t>not correct</t>
+  </si>
+  <si>
+    <t>no spread</t>
+  </si>
+  <si>
+    <t>AUTOCORRELATION</t>
+  </si>
+  <si>
+    <t>Slightly Slow</t>
+  </si>
+  <si>
+    <t>rebound</t>
+  </si>
+  <si>
+    <t>sparse</t>
+  </si>
+  <si>
+    <t>Fast</t>
+  </si>
+  <si>
+    <t>slight fast</t>
+  </si>
+  <si>
+    <t>no underswing</t>
+  </si>
+  <si>
+    <t>fast</t>
+  </si>
+  <si>
+    <t>On time</t>
+  </si>
+  <si>
+    <t>limited  rebound</t>
+  </si>
+  <si>
+    <t>on time</t>
+  </si>
+  <si>
+    <t>slow</t>
+  </si>
+  <si>
+    <t>best_pearson_r2</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
 </sst>
 </file>
 
@@ -569,7 +671,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1215,22 +1317,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1349,15 +1440,14 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="322">
+  <dxfs count="319">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1425,26 +1515,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3609,18 +3679,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <left/>
+        <right/>
         <top style="thin">
-          <color indexed="64"/>
+          <color theme="4" tint="0.39997558519241921"/>
         </top>
         <bottom style="thin">
-          <color indexed="64"/>
+          <color theme="4" tint="0.39997558519241921"/>
         </bottom>
         <vertical/>
         <horizontal/>
@@ -3643,52 +3710,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <left/>
+        <right/>
         <top style="thin">
-          <color indexed="64"/>
+          <color theme="4" tint="0.39997558519241921"/>
         </top>
         <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
+          <color theme="4" tint="0.39997558519241921"/>
         </bottom>
         <vertical/>
         <horizontal/>
@@ -5761,6 +5791,748 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>737909</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>211664</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{381F8E5B-E1F3-50F6-8920-0DCD3F7D94A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9063880" y="7631206"/>
+          <a:ext cx="7239431" cy="2857500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>739589</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>164167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>246530</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>110721</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{131842B1-FC53-6B8A-5C12-DAD979A810E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9065560" y="10473579"/>
+          <a:ext cx="7272617" cy="4518554"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>454401</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>44825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>123267</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>67727</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{429D4740-1E3A-94AA-257B-1573287BCC80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="24042783" y="7496737"/>
+          <a:ext cx="6325160" cy="2499402"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>566460</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>78444</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>313768</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>60999</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54FC133D-7499-3239-66D6-D8F565115085}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="24154842" y="10006856"/>
+          <a:ext cx="6403602" cy="3983055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1299883</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>22413</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>582706</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>8077</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7079C451-B2C7-AC3D-E9B0-49260B6885CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1299883" y="10522325"/>
+          <a:ext cx="6723529" cy="4176664"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1299881</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>21656</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>593911</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B39DF241-F9CB-D671-F8DF-769FD596F9F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1299881" y="7854568"/>
+          <a:ext cx="6734736" cy="2656550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>122145</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>21291</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>431428</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>173691</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3C59DCC-CCF9-4764-B075-FA182E7020A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25525880" y="6330203"/>
+          <a:ext cx="914401" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3600"/>
+            <a:t>9</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1126191</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>39220</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>908797</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08A6281C-5F8E-430B-A078-4E2223C825C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3759573" y="6348132"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3600"/>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>326091</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>146797</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>41462</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>108697</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0039770-7DFA-4430-A9E3-3F8351FD2D6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13078385" y="6265209"/>
+          <a:ext cx="914401" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3600"/>
+            <a:t>6</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>5602</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>151279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>268942</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48EA3B4B-6C94-4FD1-8F38-69BD0666470A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19358161" y="6650691"/>
+          <a:ext cx="868457" cy="834838"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3600"/>
+            <a:t>8</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="3600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>28580</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>134472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>38861</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>100851</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CD3DD40-D445-5CC9-DB14-DBA62FF233AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16938256" y="10443884"/>
+          <a:ext cx="6083870" cy="3776379"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>600077</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>228981</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>139611</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73EA4752-B8EF-F67A-B250-8CACDCDEB2EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16691724" y="7877735"/>
+          <a:ext cx="6520522" cy="2571288"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6885,77 +7657,76 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{96ECA080-13A0-4EAD-9B78-C907FAA1E37A}" name="Table3" displayName="Table3" ref="A1:U11" totalsRowShown="0" dataDxfId="321">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{96ECA080-13A0-4EAD-9B78-C907FAA1E37A}" name="Table3" displayName="Table3" ref="A1:U11" totalsRowShown="0" dataDxfId="318">
   <autoFilter ref="A1:U11" xr:uid="{96ECA080-13A0-4EAD-9B78-C907FAA1E37A}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{90D971B2-8A12-4663-B59E-A64B9E3ACB20}" name="final_evaluation_seed" dataDxfId="320"/>
-    <tableColumn id="2" xr3:uid="{BDA294FC-58D6-46F6-9587-EF102D78D712}" name="best_difference_vector_cosine" dataDxfId="319"/>
-    <tableColumn id="3" xr3:uid="{8DADFB6C-E620-488E-82F0-B00DFE9C72BF}" name="best_pearson_r" dataDxfId="318"/>
-    <tableColumn id="4" xr3:uid="{44E404A7-64C9-48D1-BEA8-37DAC6FF833D}" name="seed_a_e" dataDxfId="317"/>
-    <tableColumn id="5" xr3:uid="{0031A10A-5BB9-4A13-AB85-C453BE259947}" name="seed_b_e" dataDxfId="316"/>
-    <tableColumn id="6" xr3:uid="{A4149257-77E3-4DA3-8D66-E2741B5431E8}" name="seed_d_e" dataDxfId="315"/>
-    <tableColumn id="7" xr3:uid="{DA03BCA9-49D0-4373-AF86-D098B2729C46}" name="seed_c_I_sst" dataDxfId="314"/>
-    <tableColumn id="8" xr3:uid="{B468D88A-1953-4115-BC1A-7553BD6F03F0}" name="seed_c_I_vip" dataDxfId="313"/>
-    <tableColumn id="9" xr3:uid="{BD34FD95-EF0C-4801-B561-1472399ADC58}" name="seed_c_I_pv" dataDxfId="312"/>
-    <tableColumn id="10" xr3:uid="{4CBC17EF-CFF0-4154-B2C4-A4A8888EAB5A}" name="seed_r_0_sst" dataDxfId="311"/>
-    <tableColumn id="11" xr3:uid="{6D288E8E-6667-4469-8AD1-E62747A423DA}" name="seed_r_0_vip" dataDxfId="310"/>
-    <tableColumn id="12" xr3:uid="{9F67D3E9-516C-4278-8CDA-BB0CF64B9740}" name="seed_r_0_pv" dataDxfId="309"/>
-    <tableColumn id="13" xr3:uid="{D5F59086-E128-4CCD-AF15-4E50E57864D1}" name="I_background_e" dataDxfId="308"/>
-    <tableColumn id="14" xr3:uid="{A73EF0CC-855A-45BB-9A63-198EE6689667}" name="I_background_i" dataDxfId="307"/>
-    <tableColumn id="15" xr3:uid="{6960877C-3EFB-49C8-816F-12137BCD97E2}" name="I_background_dend" dataDxfId="306"/>
-    <tableColumn id="16" xr3:uid="{B5C47147-4CF4-474B-92B8-CAB79CF8B07E}" name="mu_ee" dataDxfId="305"/>
-    <tableColumn id="17" xr3:uid="{20F72C98-CEC9-42A5-B3F3-DC5463DB0F1A}" name="mu_ie" dataDxfId="304"/>
-    <tableColumn id="18" xr3:uid="{6849C2FE-7DA3-4843-98B5-75098CE7A33F}" name="e_grad_min" dataDxfId="303"/>
-    <tableColumn id="19" xr3:uid="{982464DB-B2BB-49C3-8939-02D2736F4AA8}" name="balloon_kappa" dataDxfId="302"/>
-    <tableColumn id="20" xr3:uid="{066BD199-F963-4A3B-B6A5-EFAA10564156}" name="balloon_gamma" dataDxfId="301"/>
-    <tableColumn id="21" xr3:uid="{A35DF0CE-40AE-4FAF-84E1-C6D5F0A8913D}" name="balloon_tau" dataDxfId="300"/>
+    <tableColumn id="1" xr3:uid="{90D971B2-8A12-4663-B59E-A64B9E3ACB20}" name="final_evaluation_seed" dataDxfId="317"/>
+    <tableColumn id="2" xr3:uid="{BDA294FC-58D6-46F6-9587-EF102D78D712}" name="best_difference_vector_cosine" dataDxfId="316"/>
+    <tableColumn id="3" xr3:uid="{8DADFB6C-E620-488E-82F0-B00DFE9C72BF}" name="best_pearson_r" dataDxfId="315"/>
+    <tableColumn id="4" xr3:uid="{44E404A7-64C9-48D1-BEA8-37DAC6FF833D}" name="seed_a_e" dataDxfId="314"/>
+    <tableColumn id="5" xr3:uid="{0031A10A-5BB9-4A13-AB85-C453BE259947}" name="seed_b_e" dataDxfId="313"/>
+    <tableColumn id="6" xr3:uid="{A4149257-77E3-4DA3-8D66-E2741B5431E8}" name="seed_d_e" dataDxfId="312"/>
+    <tableColumn id="7" xr3:uid="{DA03BCA9-49D0-4373-AF86-D098B2729C46}" name="seed_c_I_sst" dataDxfId="311"/>
+    <tableColumn id="8" xr3:uid="{B468D88A-1953-4115-BC1A-7553BD6F03F0}" name="seed_c_I_vip" dataDxfId="310"/>
+    <tableColumn id="9" xr3:uid="{BD34FD95-EF0C-4801-B561-1472399ADC58}" name="seed_c_I_pv" dataDxfId="309"/>
+    <tableColumn id="10" xr3:uid="{4CBC17EF-CFF0-4154-B2C4-A4A8888EAB5A}" name="seed_r_0_sst" dataDxfId="308"/>
+    <tableColumn id="11" xr3:uid="{6D288E8E-6667-4469-8AD1-E62747A423DA}" name="seed_r_0_vip" dataDxfId="307"/>
+    <tableColumn id="12" xr3:uid="{9F67D3E9-516C-4278-8CDA-BB0CF64B9740}" name="seed_r_0_pv" dataDxfId="306"/>
+    <tableColumn id="13" xr3:uid="{D5F59086-E128-4CCD-AF15-4E50E57864D1}" name="I_background_e" dataDxfId="305"/>
+    <tableColumn id="14" xr3:uid="{A73EF0CC-855A-45BB-9A63-198EE6689667}" name="I_background_i" dataDxfId="304"/>
+    <tableColumn id="15" xr3:uid="{6960877C-3EFB-49C8-816F-12137BCD97E2}" name="I_background_dend" dataDxfId="303"/>
+    <tableColumn id="16" xr3:uid="{B5C47147-4CF4-474B-92B8-CAB79CF8B07E}" name="mu_ee" dataDxfId="302"/>
+    <tableColumn id="17" xr3:uid="{20F72C98-CEC9-42A5-B3F3-DC5463DB0F1A}" name="mu_ie" dataDxfId="301"/>
+    <tableColumn id="18" xr3:uid="{6849C2FE-7DA3-4843-98B5-75098CE7A33F}" name="e_grad_min" dataDxfId="300"/>
+    <tableColumn id="19" xr3:uid="{982464DB-B2BB-49C3-8939-02D2736F4AA8}" name="balloon_kappa" dataDxfId="299"/>
+    <tableColumn id="20" xr3:uid="{066BD199-F963-4A3B-B6A5-EFAA10564156}" name="balloon_gamma" dataDxfId="298"/>
+    <tableColumn id="21" xr3:uid="{A35DF0CE-40AE-4FAF-84E1-C6D5F0A8913D}" name="balloon_tau" dataDxfId="297"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}" name="Table17" displayName="Table17" ref="A1:N11" totalsRowShown="0" headerRowDxfId="206" dataDxfId="204" headerRowBorderDxfId="205" tableBorderDxfId="203">
-  <autoFilter ref="A1:N11" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{946C78F0-5ED6-4C82-B486-0A2D01401586}" name="final_evaluation_seed" dataDxfId="202"/>
-    <tableColumn id="2" xr3:uid="{F6F73ED1-AC25-4A5B-AA43-B4420270A65B}" name="best_pearson_r" dataDxfId="201"/>
-    <tableColumn id="3" xr3:uid="{9D33DA5E-9FA5-4B81-8347-66FB3F9D278F}" name="I_background_e" dataDxfId="200"/>
-    <tableColumn id="4" xr3:uid="{045CBE2B-CC02-4815-AFDF-FD55F14A5948}" name="I_background_i" dataDxfId="199"/>
-    <tableColumn id="5" xr3:uid="{DD07A8E1-0F8D-4F93-9FFC-80537E7DA893}" name="I_background_dend" dataDxfId="198"/>
-    <tableColumn id="6" xr3:uid="{F002D97C-F001-4AAB-86C7-02AFD658391E}" name="mu_ee" dataDxfId="197"/>
-    <tableColumn id="7" xr3:uid="{6A9A90F5-365B-424C-8DFB-AC07BB4F58AB}" name="mu_ie" dataDxfId="196"/>
-    <tableColumn id="8" xr3:uid="{3C77AB83-9D42-417E-973A-786B92AD8D39}" name="e_grad_min" dataDxfId="195"/>
-    <tableColumn id="9" xr3:uid="{202C73E4-ED7F-44C3-8FE0-67B8DEC3AF51}" name="balloon_kappa" dataDxfId="194"/>
-    <tableColumn id="10" xr3:uid="{39BA6440-2759-406C-962E-1F482C31D9D8}" name="balloon_gamma" dataDxfId="193"/>
-    <tableColumn id="11" xr3:uid="{71495690-5E12-40F8-8FB8-D35062B95476}" name="balloon_tau" dataDxfId="192"/>
-    <tableColumn id="12" xr3:uid="{D2BEB5FD-80DF-4E80-AD46-55385CB1B6FF}" name="Stim" dataDxfId="191"/>
-    <tableColumn id="13" xr3:uid="{7A8508B0-FDAF-4D41-8BA2-B789691A3BE1}" name="Auto" dataDxfId="190"/>
-    <tableColumn id="14" xr3:uid="{42D86400-C902-4CEB-A96A-D8CE8C7A5EE0}" name="BOLD" dataDxfId="189"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}" name="Table17" displayName="Table17" ref="A1:M11" totalsRowShown="0" headerRowDxfId="203" dataDxfId="201" headerRowBorderDxfId="202" tableBorderDxfId="200">
+  <autoFilter ref="A1:M11" xr:uid="{07160D78-02CC-4497-9D7E-AC26AEF33878}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{946C78F0-5ED6-4C82-B486-0A2D01401586}" name="final_evaluation_seed" dataDxfId="199"/>
+    <tableColumn id="2" xr3:uid="{F6F73ED1-AC25-4A5B-AA43-B4420270A65B}" name="best_pearson_r" dataDxfId="198"/>
+    <tableColumn id="3" xr3:uid="{9D33DA5E-9FA5-4B81-8347-66FB3F9D278F}" name="I_background_e" dataDxfId="197"/>
+    <tableColumn id="4" xr3:uid="{045CBE2B-CC02-4815-AFDF-FD55F14A5948}" name="I_background_i" dataDxfId="196"/>
+    <tableColumn id="5" xr3:uid="{DD07A8E1-0F8D-4F93-9FFC-80537E7DA893}" name="I_background_dend" dataDxfId="195"/>
+    <tableColumn id="6" xr3:uid="{F002D97C-F001-4AAB-86C7-02AFD658391E}" name="mu_ee" dataDxfId="194"/>
+    <tableColumn id="7" xr3:uid="{6A9A90F5-365B-424C-8DFB-AC07BB4F58AB}" name="mu_ie" dataDxfId="193"/>
+    <tableColumn id="8" xr3:uid="{3C77AB83-9D42-417E-973A-786B92AD8D39}" name="e_grad_min" dataDxfId="192"/>
+    <tableColumn id="9" xr3:uid="{202C73E4-ED7F-44C3-8FE0-67B8DEC3AF51}" name="balloon_kappa" dataDxfId="191"/>
+    <tableColumn id="10" xr3:uid="{39BA6440-2759-406C-962E-1F482C31D9D8}" name="balloon_gamma" dataDxfId="190"/>
+    <tableColumn id="11" xr3:uid="{71495690-5E12-40F8-8FB8-D35062B95476}" name="balloon_tau" dataDxfId="189"/>
+    <tableColumn id="12" xr3:uid="{8A36076C-771F-4AEE-9D70-4AD96422152A}" name="best_difference_vector_cosine" dataDxfId="188"/>
+    <tableColumn id="13" xr3:uid="{BFB3270A-0A01-4F9E-A631-862F3E8D9B12}" name="best_pearson_r2" dataDxfId="187"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0AA8468E-35CF-47CB-BBB1-E82D79B508B4}" name="Table112" displayName="Table112" ref="A1:O11" totalsRowShown="0" headerRowDxfId="188" dataDxfId="186" headerRowBorderDxfId="187" tableBorderDxfId="185">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0AA8468E-35CF-47CB-BBB1-E82D79B508B4}" name="Table112" displayName="Table112" ref="A1:O11" totalsRowShown="0" headerRowDxfId="186" dataDxfId="184" headerRowBorderDxfId="185" tableBorderDxfId="183">
   <autoFilter ref="A1:O11" xr:uid="{0AA8468E-35CF-47CB-BBB1-E82D79B508B4}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5A2518A5-0C39-4BE0-8539-9F65123ED022}" name="seed" dataDxfId="184"/>
-    <tableColumn id="2" xr3:uid="{DECF84D9-CAF5-47BD-A6E4-D268671B8AF0}" name="r" dataDxfId="183"/>
-    <tableColumn id="3" xr3:uid="{DFB8AAA2-2333-48A2-BBEC-5BC4763C536A}" name="I_background_e" dataDxfId="182"/>
-    <tableColumn id="4" xr3:uid="{A0403004-5B3F-4971-82E7-C3DD9CC768BC}" name="I_background_i" dataDxfId="181"/>
-    <tableColumn id="5" xr3:uid="{55645ADB-2DE6-4470-8D97-7BD3E8A2072B}" name="I_background_dend" dataDxfId="180"/>
-    <tableColumn id="6" xr3:uid="{DE4F9698-73B0-45AE-98CB-18EC17C1E5C7}" name="mu_ee" dataDxfId="179"/>
-    <tableColumn id="7" xr3:uid="{2D122CFB-25EF-479D-9614-B53C87A158B9}" name="mu_ie" dataDxfId="178"/>
-    <tableColumn id="8" xr3:uid="{57738AAA-F1FC-4531-8EF7-1E8364CA800A}" name="e_grad_min" dataDxfId="177"/>
-    <tableColumn id="9" xr3:uid="{6825AB37-C2BD-44BF-B0E4-270EE0FB0A7E}" name="balloon_kappa" dataDxfId="176"/>
-    <tableColumn id="10" xr3:uid="{C1515A5A-0566-48B8-B6A6-70B8E1EAD853}" name="balloon_gamma" dataDxfId="175"/>
-    <tableColumn id="11" xr3:uid="{B90DC991-DB68-4B30-A5C5-B61FEB53097C}" name="balloon_tau" dataDxfId="174"/>
-    <tableColumn id="12" xr3:uid="{0D0F6034-D566-4618-AEC8-3275BFF2F760}" name="Stim" dataDxfId="173"/>
-    <tableColumn id="13" xr3:uid="{C91D58C0-382F-4FF3-8460-220BACFC2671}" name="Auto" dataDxfId="172"/>
-    <tableColumn id="14" xr3:uid="{E8779799-2FBC-4C3A-A217-D9C280212DC4}" name="BOLD" dataDxfId="171"/>
-    <tableColumn id="15" xr3:uid="{7671ADD5-87B4-43C4-A4D2-AEFEA0DFC960}" name="cosine" dataDxfId="170"/>
+    <tableColumn id="1" xr3:uid="{5A2518A5-0C39-4BE0-8539-9F65123ED022}" name="seed" dataDxfId="182"/>
+    <tableColumn id="2" xr3:uid="{DECF84D9-CAF5-47BD-A6E4-D268671B8AF0}" name="r" dataDxfId="181"/>
+    <tableColumn id="3" xr3:uid="{DFB8AAA2-2333-48A2-BBEC-5BC4763C536A}" name="I_background_e" dataDxfId="180"/>
+    <tableColumn id="4" xr3:uid="{A0403004-5B3F-4971-82E7-C3DD9CC768BC}" name="I_background_i" dataDxfId="179"/>
+    <tableColumn id="5" xr3:uid="{55645ADB-2DE6-4470-8D97-7BD3E8A2072B}" name="I_background_dend" dataDxfId="178"/>
+    <tableColumn id="6" xr3:uid="{DE4F9698-73B0-45AE-98CB-18EC17C1E5C7}" name="mu_ee" dataDxfId="177"/>
+    <tableColumn id="7" xr3:uid="{2D122CFB-25EF-479D-9614-B53C87A158B9}" name="mu_ie" dataDxfId="176"/>
+    <tableColumn id="8" xr3:uid="{57738AAA-F1FC-4531-8EF7-1E8364CA800A}" name="e_grad_min" dataDxfId="175"/>
+    <tableColumn id="9" xr3:uid="{6825AB37-C2BD-44BF-B0E4-270EE0FB0A7E}" name="balloon_kappa" dataDxfId="174"/>
+    <tableColumn id="10" xr3:uid="{C1515A5A-0566-48B8-B6A6-70B8E1EAD853}" name="balloon_gamma" dataDxfId="173"/>
+    <tableColumn id="11" xr3:uid="{B90DC991-DB68-4B30-A5C5-B61FEB53097C}" name="balloon_tau" dataDxfId="172"/>
+    <tableColumn id="12" xr3:uid="{0D0F6034-D566-4618-AEC8-3275BFF2F760}" name="Stim" dataDxfId="171"/>
+    <tableColumn id="13" xr3:uid="{C91D58C0-382F-4FF3-8460-220BACFC2671}" name="Auto" dataDxfId="170"/>
+    <tableColumn id="14" xr3:uid="{E8779799-2FBC-4C3A-A217-D9C280212DC4}" name="BOLD" dataDxfId="169"/>
+    <tableColumn id="15" xr3:uid="{7671ADD5-87B4-43C4-A4D2-AEFEA0DFC960}" name="cosine" dataDxfId="168"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6975,20 +7746,20 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}" name="Table1" displayName="Table1" ref="C4:M14" totalsRowShown="0" headerRowDxfId="169" dataDxfId="167" headerRowBorderDxfId="168" tableBorderDxfId="166">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}" name="Table1" displayName="Table1" ref="C4:M14" totalsRowShown="0" headerRowDxfId="167" dataDxfId="165" headerRowBorderDxfId="166" tableBorderDxfId="164">
   <autoFilter ref="C4:M14" xr:uid="{93BC65FE-52EE-498D-924D-E681633D1E4B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{87805D45-55EC-4CC4-8B30-E06DA4E7E751}" name="final_evaluation_seed" dataDxfId="165"/>
-    <tableColumn id="2" xr3:uid="{79824F93-C2A5-45B6-9B69-441998802D80}" name="best_pearson_r" dataDxfId="164"/>
-    <tableColumn id="3" xr3:uid="{7EAF5609-B791-402E-8A39-55B740926D2B}" name="I_background_e" dataDxfId="163"/>
-    <tableColumn id="4" xr3:uid="{5EE101D7-0D41-494A-805A-94CFC73331CF}" name="I_background_i" dataDxfId="162"/>
-    <tableColumn id="5" xr3:uid="{2CCF00EF-4BDB-4EB6-A318-9502957678DF}" name="I_background_dend" dataDxfId="161"/>
-    <tableColumn id="6" xr3:uid="{F5AB52A3-CD6E-43D7-A21D-129262695C38}" name="mu_ee" dataDxfId="160"/>
-    <tableColumn id="7" xr3:uid="{778CC36A-8D50-4F01-8B3E-FCAED3521F9B}" name="mu_ie" dataDxfId="159"/>
-    <tableColumn id="8" xr3:uid="{A7B4CCC7-3054-4367-9B57-4F9D70B71AE8}" name="e_grad_min" dataDxfId="158"/>
-    <tableColumn id="9" xr3:uid="{6C33EE26-7CA7-4527-87D8-E28DD20FFD4E}" name="balloon_kappa" dataDxfId="157"/>
-    <tableColumn id="10" xr3:uid="{DBBC495E-05F7-4608-AD56-F33F1FD9FB2E}" name="balloon_gamma" dataDxfId="156"/>
-    <tableColumn id="11" xr3:uid="{D7DB4319-ACF4-4A69-B4F4-EBD25833DB72}" name="balloon_tau" dataDxfId="155"/>
+    <tableColumn id="1" xr3:uid="{87805D45-55EC-4CC4-8B30-E06DA4E7E751}" name="final_evaluation_seed" dataDxfId="163"/>
+    <tableColumn id="2" xr3:uid="{79824F93-C2A5-45B6-9B69-441998802D80}" name="best_pearson_r" dataDxfId="162"/>
+    <tableColumn id="3" xr3:uid="{7EAF5609-B791-402E-8A39-55B740926D2B}" name="I_background_e" dataDxfId="161"/>
+    <tableColumn id="4" xr3:uid="{5EE101D7-0D41-494A-805A-94CFC73331CF}" name="I_background_i" dataDxfId="160"/>
+    <tableColumn id="5" xr3:uid="{2CCF00EF-4BDB-4EB6-A318-9502957678DF}" name="I_background_dend" dataDxfId="159"/>
+    <tableColumn id="6" xr3:uid="{F5AB52A3-CD6E-43D7-A21D-129262695C38}" name="mu_ee" dataDxfId="158"/>
+    <tableColumn id="7" xr3:uid="{778CC36A-8D50-4F01-8B3E-FCAED3521F9B}" name="mu_ie" dataDxfId="157"/>
+    <tableColumn id="8" xr3:uid="{A7B4CCC7-3054-4367-9B57-4F9D70B71AE8}" name="e_grad_min" dataDxfId="156"/>
+    <tableColumn id="9" xr3:uid="{6C33EE26-7CA7-4527-87D8-E28DD20FFD4E}" name="balloon_kappa" dataDxfId="155"/>
+    <tableColumn id="10" xr3:uid="{DBBC495E-05F7-4608-AD56-F33F1FD9FB2E}" name="balloon_gamma" dataDxfId="154"/>
+    <tableColumn id="11" xr3:uid="{D7DB4319-ACF4-4A69-B4F4-EBD25833DB72}" name="balloon_tau" dataDxfId="153"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6998,9 +7769,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}" name="Table1411" displayName="Table1411" ref="T21:V31" totalsRowShown="0">
   <autoFilter ref="T21:V31" xr:uid="{F317B012-7B9A-4E8A-93F6-841923811227}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2EE0C1C9-847E-49D1-B328-3A3EED7F56C1}" name="Stim" dataDxfId="154"/>
-    <tableColumn id="2" xr3:uid="{865FC042-E96D-4C4D-B1EA-4B7C3183DA79}" name="Auto" dataDxfId="153"/>
-    <tableColumn id="3" xr3:uid="{D9EC8ABD-24A2-4068-9CAB-09D34D97FE88}" name="BOLD" dataDxfId="152"/>
+    <tableColumn id="1" xr3:uid="{2EE0C1C9-847E-49D1-B328-3A3EED7F56C1}" name="Stim" dataDxfId="152"/>
+    <tableColumn id="2" xr3:uid="{865FC042-E96D-4C4D-B1EA-4B7C3183DA79}" name="Auto" dataDxfId="151"/>
+    <tableColumn id="3" xr3:uid="{D9EC8ABD-24A2-4068-9CAB-09D34D97FE88}" name="BOLD" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7011,94 +7782,94 @@
   <autoFilter ref="A1:U11" xr:uid="{2B1EA398-6077-43CD-8151-400DF211F33C}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{DFDC78A7-E47E-494D-9C61-107C2DD6F0AD}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="151"/>
-    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="150"/>
-    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="149"/>
-    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="148"/>
-    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="147"/>
-    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="146"/>
-    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="145"/>
-    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="144"/>
-    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="143"/>
-    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="142"/>
-    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="141"/>
-    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="140"/>
-    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="139"/>
-    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="138"/>
-    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="137"/>
-    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="136"/>
-    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="135"/>
-    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="134"/>
-    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="133"/>
-    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{E6238561-586D-4726-BEAC-8D7C182F1ECE}" name="best_pearson_r" dataDxfId="149"/>
+    <tableColumn id="3" xr3:uid="{00BD204A-1182-4612-A32A-03FAAAD1C5B3}" name="best_difference_vector_r" dataDxfId="148"/>
+    <tableColumn id="4" xr3:uid="{EA4F656D-3132-4F0F-90EB-703FEFD588E3}" name="seed_a_e" dataDxfId="147"/>
+    <tableColumn id="5" xr3:uid="{2119A095-4FE6-40A2-BB73-772A4DBC0853}" name="seed_b_e" dataDxfId="146"/>
+    <tableColumn id="6" xr3:uid="{43B41629-39C8-4499-96ED-D757A61D611E}" name="seed_d_e" dataDxfId="145"/>
+    <tableColumn id="7" xr3:uid="{38B71045-B36F-4D69-907D-F3535FE6FAC7}" name="seed_c_I_sst" dataDxfId="144"/>
+    <tableColumn id="8" xr3:uid="{3B6EBF4F-F34C-44BC-A921-2C293371AFF9}" name="seed_c_I_vip" dataDxfId="143"/>
+    <tableColumn id="9" xr3:uid="{CE4D64C6-BC0F-45E5-BCA1-0F3DD9D0F6BB}" name="seed_c_I_pv" dataDxfId="142"/>
+    <tableColumn id="10" xr3:uid="{A85130F6-49C1-4A18-82C6-0F9062ADA2E3}" name="seed_r_0_sst" dataDxfId="141"/>
+    <tableColumn id="11" xr3:uid="{9A75ADE8-D030-4790-AEA1-1C6238B966A2}" name="seed_r_0_vip" dataDxfId="140"/>
+    <tableColumn id="12" xr3:uid="{FFF57A59-AE10-4D44-81FB-52C5CBCFEC25}" name="seed_r_0_pv" dataDxfId="139"/>
+    <tableColumn id="13" xr3:uid="{6D48A2DF-2920-4376-A540-3067A2DBBF7B}" name="I_background_e" dataDxfId="138"/>
+    <tableColumn id="14" xr3:uid="{C0D2BFAA-4FDB-49F3-A3D6-4B86953BBAF1}" name="I_background_i" dataDxfId="137"/>
+    <tableColumn id="15" xr3:uid="{B4080DB5-B404-4E2F-AA52-5F60D4B8F71E}" name="I_background_dend" dataDxfId="136"/>
+    <tableColumn id="16" xr3:uid="{78855599-A588-4661-8E05-CC2213BB031B}" name="mu_ee" dataDxfId="135"/>
+    <tableColumn id="17" xr3:uid="{2B08E395-BD03-4337-B69F-505205876C59}" name="mu_ie" dataDxfId="134"/>
+    <tableColumn id="18" xr3:uid="{17EE54A1-EF0E-4B12-B040-DE29E5B25B0E}" name="e_grad_min" dataDxfId="133"/>
+    <tableColumn id="19" xr3:uid="{1291F550-B65C-4783-B993-83CF16A2575B}" name="balloon_kappa" dataDxfId="132"/>
+    <tableColumn id="20" xr3:uid="{9534CA96-35D8-4100-8608-98B62DE50899}" name="balloon_gamma" dataDxfId="131"/>
+    <tableColumn id="21" xr3:uid="{E372A247-0964-467C-9715-0710A4B32F4D}" name="balloon_tau" dataDxfId="130"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="131" headerRowBorderDxfId="130" tableBorderDxfId="129">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}" name="Table20" displayName="Table20" ref="A22:U32" headerRowDxfId="129" headerRowBorderDxfId="128" tableBorderDxfId="127">
   <autoFilter ref="A22:U32" xr:uid="{C5F27522-66E5-4CAD-A776-48231BCC5378}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="128" totalsRowDxfId="127"/>
-    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="126">
+    <tableColumn id="1" xr3:uid="{C0E199AB-EA77-41D7-B34F-40752CC13826}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="126" totalsRowDxfId="125"/>
+    <tableColumn id="2" xr3:uid="{20EC2763-260E-4D89-9E2E-C3FA0D892A31}" name="best_pearson_r" dataDxfId="124">
       <calculatedColumnFormula>(B2-B$17)/B$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="125">
+    <tableColumn id="3" xr3:uid="{0D799710-AB04-42CE-B929-4C269ACD8A9D}" name="best_difference_vector_r" dataDxfId="123">
       <calculatedColumnFormula>(C2-C$17)/C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="124">
+    <tableColumn id="4" xr3:uid="{F05464EF-6EB0-4999-B612-060599124E20}" name="seed_a_e" dataDxfId="122">
       <calculatedColumnFormula>(D2-D$17)/D$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="123">
+    <tableColumn id="5" xr3:uid="{6A36B8C8-D20E-400B-B1AB-3BE5CFE22404}" name="seed_b_e" dataDxfId="121">
       <calculatedColumnFormula>(E2-E$17)/E$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="122">
+    <tableColumn id="6" xr3:uid="{356296AE-61EA-4910-8552-372F0CBA58E9}" name="seed_d_e" dataDxfId="120">
       <calculatedColumnFormula>(F2-F$17)/F$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="121">
+    <tableColumn id="7" xr3:uid="{D0072FDE-5ED8-442B-933C-60DA405E2140}" name="seed_c_I_sst" dataDxfId="119">
       <calculatedColumnFormula>(G2-G$17)/G$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="120">
+    <tableColumn id="8" xr3:uid="{475FCB14-17C7-4600-B64D-5305708129D1}" name="seed_c_I_vip" dataDxfId="118">
       <calculatedColumnFormula>(H2-H$17)/H$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="119">
+    <tableColumn id="9" xr3:uid="{8DA305B1-1787-401A-B635-8F01C968940C}" name="seed_c_I_pv" dataDxfId="117">
       <calculatedColumnFormula>(I2-I$17)/I$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{99EA0776-03DD-4283-B952-50843E63108A}" name="seed_r_0_sst" dataDxfId="116">
       <calculatedColumnFormula>(J2-J$17)/J$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="117">
+    <tableColumn id="11" xr3:uid="{596CBE18-5967-4CFC-AA04-B3256D9A29AE}" name="seed_r_0_vip" dataDxfId="115">
       <calculatedColumnFormula>(K2-K$17)/K$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="116">
+    <tableColumn id="12" xr3:uid="{15973661-29DE-45D9-A75F-FBC44DAB6149}" name="seed_r_0_pv" dataDxfId="114">
       <calculatedColumnFormula>(L2-L$17)/L$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="115">
+    <tableColumn id="13" xr3:uid="{BDACEA53-7DD5-4051-832A-6BC449BBA433}" name="I_background_e" dataDxfId="113">
       <calculatedColumnFormula>(M2-M$17)/M$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="114">
+    <tableColumn id="14" xr3:uid="{A6D1142E-BEFE-4668-AD5D-57A8C34BD2E2}" name="I_background_i" dataDxfId="112">
       <calculatedColumnFormula>(N2-N$17)/N$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="113">
+    <tableColumn id="15" xr3:uid="{76F216FA-5560-4A83-BC12-2190B72144A4}" name="I_background_dend" dataDxfId="111">
       <calculatedColumnFormula>(O2-O$17)/O$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{923534A9-34A7-400B-A7BA-C6B6D7656ABA}" name="mu_ee" dataDxfId="110">
       <calculatedColumnFormula>(P2-P$17)/P$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="111">
+    <tableColumn id="17" xr3:uid="{14F13ADA-964F-486F-B481-4F4D9AC0ACA5}" name="mu_ie" dataDxfId="109">
       <calculatedColumnFormula>(Q2-Q$17)/Q$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="110">
+    <tableColumn id="18" xr3:uid="{D985AF65-3489-4235-9BDC-572AAD6BF24C}" name="e_grad_min" dataDxfId="108">
       <calculatedColumnFormula>(R2-R$17)/R$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="109">
+    <tableColumn id="19" xr3:uid="{DAED7033-C306-4AC0-B10A-9492EB5E8A31}" name="balloon_kappa" dataDxfId="107">
       <calculatedColumnFormula>(S2-S$17)/S$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="108">
+    <tableColumn id="20" xr3:uid="{613B4BFB-F236-443F-9EA3-703B180B954F}" name="balloon_gamma" dataDxfId="106">
       <calculatedColumnFormula>(T2-T$17)/T$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="107" totalsRowDxfId="106">
+    <tableColumn id="21" xr3:uid="{CF78233D-9905-4DA4-AFAF-D8810740788C}" name="balloon_tau" totalsRowFunction="sum" dataDxfId="105" totalsRowDxfId="104">
       <calculatedColumnFormula>(U2-U$17)/U$19</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7107,29 +7878,29 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="105" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102" totalsRowBorderDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}" name="Table32" displayName="Table32" ref="A77:C87" headerRowDxfId="103" dataDxfId="101" headerRowBorderDxfId="102" tableBorderDxfId="100" totalsRowBorderDxfId="99">
   <autoFilter ref="A77:C87" xr:uid="{130CC90B-5DA4-47B5-B97F-6E46FE6E2C86}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="100" totalsRowDxfId="99"/>
-    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="98" totalsRowDxfId="97"/>
-    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="1" xr3:uid="{BEB68755-0D3D-4EA9-B92D-8D870499889A}" name="final_evaluation_seed" totalsRowLabel="Total" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="2" xr3:uid="{B0E0C2F8-C260-45D8-B0C8-12C373D2ED7F}" name="best_pearson_r" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{D45076E7-DC49-4261-BA00-8A6F2AA8ED28}" name="best_difference_vector_r" totalsRowFunction="sum" dataDxfId="94" totalsRowDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="94" headerRowBorderDxfId="93" tableBorderDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}" name="Table33" displayName="Table33" ref="F77:I87" totalsRowShown="0" headerRowDxfId="92" headerRowBorderDxfId="91" tableBorderDxfId="90">
   <autoFilter ref="F77:I87" xr:uid="{B7EBF3CF-8121-445C-934B-7BA8EAFCB35B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="91"/>
-    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="90">
+    <tableColumn id="1" xr3:uid="{F3D81A77-240B-4341-A370-982BCE706467}" name="final_evaluation_seed" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{E1544024-0896-43F4-A452-7D342C70FD6A}" name="best_pearson_r" dataDxfId="88">
       <calculatedColumnFormula>Table32[[#This Row],[best_pearson_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="89">
+    <tableColumn id="3" xr3:uid="{484759CA-AF62-4630-AB69-8BE04FFD0378}" name="best_difference_vector_r" dataDxfId="87">
       <calculatedColumnFormula>Table32[[#This Row],[best_difference_vector_r]]^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="88">
+    <tableColumn id="4" xr3:uid="{71A368F7-FF59-4C82-BF74-F9DB068563C0}" name="sum of R^2" dataDxfId="86">
       <calculatedColumnFormula>Table33[[#This Row],[best_pearson_r]]+Table33[[#This Row],[best_difference_vector_r]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7138,11 +7909,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="87" headerRowBorderDxfId="86" tableBorderDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}" name="Table23" displayName="Table23" ref="A50:L60" totalsRowShown="0" headerRowDxfId="85" headerRowBorderDxfId="84" tableBorderDxfId="83">
   <autoFilter ref="A50:L60" xr:uid="{55512B5A-5AD6-42A4-A605-60934FF0F564}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="83">
+    <tableColumn id="1" xr3:uid="{0EF454CB-83C9-4D43-892C-22B0D4354130}" name="Column1" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{278B6A16-7B9A-44D4-9B79-3E3C3C9AADB3}" name="seed_a_e" dataDxfId="81">
       <calculatedColumnFormula>D2/B$46</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{19814F94-E875-4959-AFE5-7848DB2FC6EC}" name="seed_b_e">
@@ -7169,76 +7940,76 @@
     <tableColumn id="10" xr3:uid="{40D401B7-4651-43DA-A526-6D0D5CEB229D}" name="seed_r_0_pv">
       <calculatedColumnFormula>L2/J$46</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="82"/>
-    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="81"/>
+    <tableColumn id="11" xr3:uid="{E64D061D-0CFC-4D4D-BEB3-3CFA3EC77FEC}" name="best_pearson_r" dataDxfId="80"/>
+    <tableColumn id="12" xr3:uid="{B7C266CC-9B34-4746-886C-22843A98BDBD}" name="best_difference_vector_r" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DFD61772-D69C-4F23-9385-16963B13A2DF}" name="Table4" displayName="Table4" ref="A22:U32" totalsRowShown="0" headerRowDxfId="299" headerRowBorderDxfId="298" tableBorderDxfId="297">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DFD61772-D69C-4F23-9385-16963B13A2DF}" name="Table4" displayName="Table4" ref="A22:U32" totalsRowShown="0" headerRowDxfId="296" headerRowBorderDxfId="295" tableBorderDxfId="294">
   <autoFilter ref="A22:U32" xr:uid="{DFD61772-D69C-4F23-9385-16963B13A2DF}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{1AEB5A3A-F66E-487F-8B57-78476E3E17F7}" name="final_evaluation_seed" dataDxfId="296"/>
-    <tableColumn id="2" xr3:uid="{87B559BD-A209-4B7E-8D6E-BB923AB7A8E8}" name="best_difference_vector_cosine" dataDxfId="295">
+    <tableColumn id="1" xr3:uid="{1AEB5A3A-F66E-487F-8B57-78476E3E17F7}" name="final_evaluation_seed" dataDxfId="293"/>
+    <tableColumn id="2" xr3:uid="{87B559BD-A209-4B7E-8D6E-BB923AB7A8E8}" name="best_difference_vector_cosine" dataDxfId="292">
       <calculatedColumnFormula>(B2-B$17)/B$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{385CEE55-6660-4848-AF20-71847F4B542D}" name="best_pearson_r" dataDxfId="294">
+    <tableColumn id="3" xr3:uid="{385CEE55-6660-4848-AF20-71847F4B542D}" name="best_pearson_r" dataDxfId="291">
       <calculatedColumnFormula>(C2-C$17)/C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9FD6AB42-5FFB-4D20-B3F4-CE63A83B6D12}" name="seed_a_e" dataDxfId="293">
+    <tableColumn id="4" xr3:uid="{9FD6AB42-5FFB-4D20-B3F4-CE63A83B6D12}" name="seed_a_e" dataDxfId="290">
       <calculatedColumnFormula>(D2-D$17)/D$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{12425BD5-667B-4BD9-A2D5-E3413A89F26B}" name="seed_b_e" dataDxfId="292">
+    <tableColumn id="5" xr3:uid="{12425BD5-667B-4BD9-A2D5-E3413A89F26B}" name="seed_b_e" dataDxfId="289">
       <calculatedColumnFormula>(E2-E$17)/E$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{48A1E88D-847D-44D6-8AA1-FDFD1F597332}" name="seed_d_e" dataDxfId="291">
+    <tableColumn id="6" xr3:uid="{48A1E88D-847D-44D6-8AA1-FDFD1F597332}" name="seed_d_e" dataDxfId="288">
       <calculatedColumnFormula>(F2-F$17)/F$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8BADB531-31CB-4F1E-A33D-A4903B0CCA47}" name="seed_c_I_sst" dataDxfId="290">
+    <tableColumn id="7" xr3:uid="{8BADB531-31CB-4F1E-A33D-A4903B0CCA47}" name="seed_c_I_sst" dataDxfId="287">
       <calculatedColumnFormula>(G2-G$17)/G$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F7C9E813-1F15-4645-A977-D3F082CB992C}" name="seed_c_I_vip" dataDxfId="289">
+    <tableColumn id="8" xr3:uid="{F7C9E813-1F15-4645-A977-D3F082CB992C}" name="seed_c_I_vip" dataDxfId="286">
       <calculatedColumnFormula>(H2-H$17)/H$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5D08ABDD-556E-4A7C-A59D-5F82AF9D6DCC}" name="seed_c_I_pv" dataDxfId="288">
+    <tableColumn id="9" xr3:uid="{5D08ABDD-556E-4A7C-A59D-5F82AF9D6DCC}" name="seed_c_I_pv" dataDxfId="285">
       <calculatedColumnFormula>(I2-I$17)/I$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E98DCCCB-DE18-497E-B8B5-617FC5273627}" name="seed_r_0_sst" dataDxfId="287">
+    <tableColumn id="10" xr3:uid="{E98DCCCB-DE18-497E-B8B5-617FC5273627}" name="seed_r_0_sst" dataDxfId="284">
       <calculatedColumnFormula>(J2-J$17)/J$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4A41846B-5748-4141-B926-2D1720DDC295}" name="seed_r_0_vip" dataDxfId="286">
+    <tableColumn id="11" xr3:uid="{4A41846B-5748-4141-B926-2D1720DDC295}" name="seed_r_0_vip" dataDxfId="283">
       <calculatedColumnFormula>(K2-K$17)/K$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00345844-80B6-4710-BBB6-182F979E75C0}" name="seed_r_0_pv" dataDxfId="285">
+    <tableColumn id="12" xr3:uid="{00345844-80B6-4710-BBB6-182F979E75C0}" name="seed_r_0_pv" dataDxfId="282">
       <calculatedColumnFormula>(L2-L$17)/L$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{8C4D71B1-F32C-4B68-8E32-C87B2962B441}" name="I_background_e" dataDxfId="284">
+    <tableColumn id="13" xr3:uid="{8C4D71B1-F32C-4B68-8E32-C87B2962B441}" name="I_background_e" dataDxfId="281">
       <calculatedColumnFormula>(M2-M$17)/M$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6C6EEF91-A2EB-4237-810F-E03C26A20E2E}" name="I_background_i" dataDxfId="283">
+    <tableColumn id="14" xr3:uid="{6C6EEF91-A2EB-4237-810F-E03C26A20E2E}" name="I_background_i" dataDxfId="280">
       <calculatedColumnFormula>(N2-N$17)/N$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F6C5A251-ECD9-431A-B5BC-50BF7B66898F}" name="I_background_dend" dataDxfId="282">
+    <tableColumn id="15" xr3:uid="{F6C5A251-ECD9-431A-B5BC-50BF7B66898F}" name="I_background_dend" dataDxfId="279">
       <calculatedColumnFormula>(O2-O$17)/O$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{290A288B-4107-4FA2-8DAA-9AC2562ABE78}" name="mu_ee" dataDxfId="281">
+    <tableColumn id="16" xr3:uid="{290A288B-4107-4FA2-8DAA-9AC2562ABE78}" name="mu_ee" dataDxfId="278">
       <calculatedColumnFormula>(P2-P$17)/P$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C8FEE778-D4A0-49C9-812A-38E859DD0CF6}" name="mu_ie" dataDxfId="280">
+    <tableColumn id="17" xr3:uid="{C8FEE778-D4A0-49C9-812A-38E859DD0CF6}" name="mu_ie" dataDxfId="277">
       <calculatedColumnFormula>(Q2-Q$17)/Q$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00DD43C9-F907-4912-A951-59897BDE04D8}" name="e_grad_min" dataDxfId="279">
+    <tableColumn id="18" xr3:uid="{00DD43C9-F907-4912-A951-59897BDE04D8}" name="e_grad_min" dataDxfId="276">
       <calculatedColumnFormula>(R2-R$17)/R$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{3172B8BE-C05C-4B6C-B46C-82BFCBC9F5B6}" name="balloon_kappa" dataDxfId="278">
+    <tableColumn id="19" xr3:uid="{3172B8BE-C05C-4B6C-B46C-82BFCBC9F5B6}" name="balloon_kappa" dataDxfId="275">
       <calculatedColumnFormula>(S2-S$17)/S$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F109293C-9D49-45E3-8FB2-18F0FB9F9C49}" name="balloon_gamma" dataDxfId="277">
+    <tableColumn id="20" xr3:uid="{F109293C-9D49-45E3-8FB2-18F0FB9F9C49}" name="balloon_gamma" dataDxfId="274">
       <calculatedColumnFormula>(T2-T$17)/T$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{9DB8825C-87FA-4083-9DE6-33B59F795E4F}" name="balloon_tau" dataDxfId="276">
+    <tableColumn id="21" xr3:uid="{9DB8825C-87FA-4083-9DE6-33B59F795E4F}" name="balloon_tau" dataDxfId="273">
       <calculatedColumnFormula>(U2-U$17)/U$19</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7251,74 +8022,74 @@
   <autoFilter ref="N50:Y60" xr:uid="{7D09C930-E854-4E6C-82B9-35C9655B8B61}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{016F4276-D961-4FD1-B77D-67CC688C159B}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="80">
+    <tableColumn id="2" xr3:uid="{4C873845-2678-47CC-A73A-84DFB574AD5C}" name="seed_a_e" dataDxfId="78">
       <calculatedColumnFormula>Table23[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="79">
+    <tableColumn id="3" xr3:uid="{9FB2A1BD-0F7E-41E8-AC5A-2FAE7768370C}" name="seed_b_e" dataDxfId="77">
       <calculatedColumnFormula>Table23[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="78">
+    <tableColumn id="4" xr3:uid="{9ED76BBE-98BF-4E28-B5A7-4A6BEF2388C4}" name="seed_d_e" dataDxfId="76">
       <calculatedColumnFormula>Table23[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="77">
+    <tableColumn id="5" xr3:uid="{C94EA546-E3E3-4B2B-90CB-D159F27375DF}" name="seed_c_I_sst" dataDxfId="75">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="76">
+    <tableColumn id="6" xr3:uid="{0568E36A-ED4B-42AA-AA46-663A3BBEC902}" name="seed_c_I_vip" dataDxfId="74">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="75">
+    <tableColumn id="7" xr3:uid="{2D78BB87-D5C8-41D2-B184-ED1CD1165E46}" name="seed_c_I_pv" dataDxfId="73">
       <calculatedColumnFormula>Table23[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="74">
+    <tableColumn id="8" xr3:uid="{1D853EFF-C894-4D9C-97F1-C40D40F08585}" name="seed_r_0_sst" dataDxfId="72">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="73">
+    <tableColumn id="9" xr3:uid="{87A5087C-01D3-45B6-A5DF-EE0E483DA5C6}" name="seed_r_0_vip" dataDxfId="71">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="72">
+    <tableColumn id="10" xr3:uid="{1D9B3506-F84A-43D4-BD42-C8C62A953A9B}" name="seed_r_0_pv" dataDxfId="70">
       <calculatedColumnFormula>Table23[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="70"/>
+    <tableColumn id="11" xr3:uid="{0B6CF83F-A1CF-4E3C-82E2-3C7108926CB7}" name="best_pearson_r" dataDxfId="69"/>
+    <tableColumn id="12" xr3:uid="{8116CD38-BCD5-42BB-8A36-2012EB4FD001}" name="best_difference_vector_r" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="69" headerRowBorderDxfId="68" tableBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}" name="Table28" displayName="Table28" ref="A63:L73" totalsRowShown="0" headerRowDxfId="67" headerRowBorderDxfId="66" tableBorderDxfId="65">
   <autoFilter ref="A63:L73" xr:uid="{2FBD4250-BAE0-41BC-97CC-9BDD36A09171}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="65">
+    <tableColumn id="1" xr3:uid="{B4490C8F-A623-46A3-BD03-9EF1B06FC551}" name="final_evaluation_seed" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{5F8175F6-987F-4B2D-829A-9B6C84ECECB1}" name="seed_a_e" dataDxfId="63">
       <calculatedColumnFormula>LOG(B51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="64">
+    <tableColumn id="3" xr3:uid="{A194688A-F8A3-4E25-8AA8-3F0D332E48AC}" name="seed_b_e" dataDxfId="62">
       <calculatedColumnFormula>LOG(C51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="63">
+    <tableColumn id="4" xr3:uid="{28D14303-AF43-49B3-9D20-9892F101B73C}" name="seed_d_e" dataDxfId="61">
       <calculatedColumnFormula>LOG(D51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="62">
+    <tableColumn id="5" xr3:uid="{C781CCD2-FFA6-4237-98D5-FFA2409809E2}" name="seed_c_I_sst" dataDxfId="60">
       <calculatedColumnFormula>LOG(E51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="61">
+    <tableColumn id="6" xr3:uid="{3CA982C7-8F81-4C35-AAE4-D65611E41123}" name="seed_c_I_vip" dataDxfId="59">
       <calculatedColumnFormula>LOG(F51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="60">
+    <tableColumn id="7" xr3:uid="{0E6094B7-3705-4FE9-99F4-A307F289DD8A}" name="seed_c_I_pv" dataDxfId="58">
       <calculatedColumnFormula>LOG(G51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="59">
+    <tableColumn id="8" xr3:uid="{B886920C-27CD-4855-A527-9226DF1C1987}" name="seed_r_0_sst" dataDxfId="57">
       <calculatedColumnFormula>LOG(H51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="58">
+    <tableColumn id="9" xr3:uid="{008023C7-5B0F-4F74-B0B6-9E4FE2C9AF92}" name="seed_r_0_vip" dataDxfId="56">
       <calculatedColumnFormula>LOG(I51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="57">
+    <tableColumn id="10" xr3:uid="{6594ECF7-B8B8-451D-8861-41ED5893CD85}" name="seed_r_0_pv" dataDxfId="55">
       <calculatedColumnFormula>LOG(J51,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="56"/>
-    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{01D48AB5-4BFC-4F00-BDF7-E5FE3A16755E}" name="best_pearson_r" dataDxfId="54"/>
+    <tableColumn id="12" xr3:uid="{B95368D8-FDC0-4D9D-9B12-3540C021B1C6}" name="best_difference_vector_r" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7329,35 +8100,35 @@
   <autoFilter ref="N63:Y73" xr:uid="{2806A620-3E6B-4861-AE70-E4C12B09B013}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00CF6880-3883-432C-B0EF-EBC8FF079300}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="54">
+    <tableColumn id="2" xr3:uid="{A0747E35-5BF2-4693-B7BD-C2D9E37B4979}" name="seed_a_e" dataDxfId="52">
       <calculatedColumnFormula>Table28[[#This Row],[seed_a_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="53">
+    <tableColumn id="3" xr3:uid="{128F7D4C-0DE3-413F-B1BE-08D0594F124E}" name="seed_b_e" dataDxfId="51">
       <calculatedColumnFormula>Table28[[#This Row],[seed_b_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="52">
+    <tableColumn id="4" xr3:uid="{6EECB48C-B6DC-4F34-97D7-C5B88F438774}" name="seed_d_e" dataDxfId="50">
       <calculatedColumnFormula>Table28[[#This Row],[seed_d_e]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="51">
+    <tableColumn id="5" xr3:uid="{722296E4-DE1C-4E97-8A2C-C282870189B4}" name="seed_c_I_sst" dataDxfId="49">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="50">
+    <tableColumn id="6" xr3:uid="{9850F111-136F-4503-9F3D-64618026D1B3}" name="seed_c_I_vip" dataDxfId="48">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="49">
+    <tableColumn id="7" xr3:uid="{D8B2F850-139F-4CCC-A97D-EB67049313FD}" name="seed_c_I_pv" dataDxfId="47">
       <calculatedColumnFormula>Table28[[#This Row],[seed_c_I_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="48">
+    <tableColumn id="8" xr3:uid="{E82809A0-55FA-415B-BCEA-A2A85402A4DD}" name="seed_r_0_sst" dataDxfId="46">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_sst]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="47">
+    <tableColumn id="9" xr3:uid="{058856AF-3C19-450F-A349-EA74AEE2DFBF}" name="seed_r_0_vip" dataDxfId="45">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_vip]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="46">
+    <tableColumn id="10" xr3:uid="{6B0B7E7F-2BC9-454F-B571-33AAB628926A}" name="seed_r_0_pv" dataDxfId="44">
       <calculatedColumnFormula>Table28[[#This Row],[seed_r_0_pv]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{685C0F06-FC6C-4110-8528-A6A019C29B89}" name="best_pearson_r" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{225E3DAB-1D3B-4C2C-88C0-11CD52BBB66B}" name="best_difference_vector_r" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7368,31 +8139,31 @@
   <autoFilter ref="A48:J58" xr:uid="{97EFFDD9-6247-402C-AB46-14867C9F85D4}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F4FBFAE2-9088-497A-9057-916DC5DB15D4}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{C4B1F04F-8E5A-439A-932B-B7B90B770F92}" name="seed_a_e" dataDxfId="275">
+    <tableColumn id="2" xr3:uid="{C4B1F04F-8E5A-439A-932B-B7B90B770F92}" name="seed_a_e" dataDxfId="272">
       <calculatedColumnFormula>D2/B$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB9D53EB-8B03-4520-98A3-50420B8DDFEA}" name="seed_b_e" dataDxfId="274">
+    <tableColumn id="3" xr3:uid="{DB9D53EB-8B03-4520-98A3-50420B8DDFEA}" name="seed_b_e" dataDxfId="271">
       <calculatedColumnFormula>E2/C$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{635855CC-4D50-4F2E-AD09-A74DD01A1ADD}" name="seed_d_e" dataDxfId="273">
+    <tableColumn id="4" xr3:uid="{635855CC-4D50-4F2E-AD09-A74DD01A1ADD}" name="seed_d_e" dataDxfId="270">
       <calculatedColumnFormula>F2/D$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F3709610-A526-40FE-B7D2-70F6B421C5CC}" name="seed_c_I_sst" dataDxfId="272">
+    <tableColumn id="5" xr3:uid="{F3709610-A526-40FE-B7D2-70F6B421C5CC}" name="seed_c_I_sst" dataDxfId="269">
       <calculatedColumnFormula>G2/E$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F5B39384-6EB0-4288-80D9-908F2B12B79D}" name="seed_c_I_vip" dataDxfId="271">
+    <tableColumn id="6" xr3:uid="{F5B39384-6EB0-4288-80D9-908F2B12B79D}" name="seed_c_I_vip" dataDxfId="268">
       <calculatedColumnFormula>H2/F$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{66CDCA44-9C31-41A1-8C31-0B27E71C85A1}" name="seed_c_I_pv" dataDxfId="270">
+    <tableColumn id="7" xr3:uid="{66CDCA44-9C31-41A1-8C31-0B27E71C85A1}" name="seed_c_I_pv" dataDxfId="267">
       <calculatedColumnFormula>I2/G$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{23822275-B279-4D54-B818-6046B8F37F2F}" name="seed_r_0_sst" dataDxfId="269">
+    <tableColumn id="8" xr3:uid="{23822275-B279-4D54-B818-6046B8F37F2F}" name="seed_r_0_sst" dataDxfId="266">
       <calculatedColumnFormula>J2/H$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{9BA3CF7B-6BE4-4514-9ED5-A9F04AE8D4D2}" name="seed_r_0_vip" dataDxfId="268">
+    <tableColumn id="9" xr3:uid="{9BA3CF7B-6BE4-4514-9ED5-A9F04AE8D4D2}" name="seed_r_0_vip" dataDxfId="265">
       <calculatedColumnFormula>K2/I$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{9684379E-C620-49D0-9297-A073F778E9B6}" name="seed_r_0_pv" dataDxfId="267">
+    <tableColumn id="10" xr3:uid="{9684379E-C620-49D0-9297-A073F778E9B6}" name="seed_r_0_pv" dataDxfId="264">
       <calculatedColumnFormula>L2/J$44</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7401,35 +8172,35 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4DD75104-6774-4C8F-8B0B-A5E15769D0D0}" name="Table8" displayName="Table8" ref="A66:J76" totalsRowShown="0" headerRowDxfId="266" headerRowBorderDxfId="265" tableBorderDxfId="264">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4DD75104-6774-4C8F-8B0B-A5E15769D0D0}" name="Table8" displayName="Table8" ref="A66:J76" totalsRowShown="0" headerRowDxfId="263" headerRowBorderDxfId="262" tableBorderDxfId="261">
   <autoFilter ref="A66:J76" xr:uid="{4DD75104-6774-4C8F-8B0B-A5E15769D0D0}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{22FE01C1-7C04-4B98-B6C0-92DBAFAFCA56}" name="final_evaluation_seed" dataDxfId="263"/>
-    <tableColumn id="2" xr3:uid="{1F95DED3-D749-4644-83B5-6B330DC0DC38}" name="seed_a_e" dataDxfId="262">
+    <tableColumn id="1" xr3:uid="{22FE01C1-7C04-4B98-B6C0-92DBAFAFCA56}" name="final_evaluation_seed" dataDxfId="260"/>
+    <tableColumn id="2" xr3:uid="{1F95DED3-D749-4644-83B5-6B330DC0DC38}" name="seed_a_e" dataDxfId="259">
       <calculatedColumnFormula>LOG(B49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{02366814-CBD1-45A2-A259-363B4B6E520F}" name="seed_b_e" dataDxfId="261">
+    <tableColumn id="3" xr3:uid="{02366814-CBD1-45A2-A259-363B4B6E520F}" name="seed_b_e" dataDxfId="258">
       <calculatedColumnFormula>LOG(C49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E4CDF7FB-1C5B-46B8-9DD8-2D3797D90AC7}" name="seed_d_e" dataDxfId="260">
+    <tableColumn id="4" xr3:uid="{E4CDF7FB-1C5B-46B8-9DD8-2D3797D90AC7}" name="seed_d_e" dataDxfId="257">
       <calculatedColumnFormula>LOG(D49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{453B0FFC-FD7C-44AA-9A50-64AD33D3319E}" name="seed_c_I_sst" dataDxfId="259">
+    <tableColumn id="5" xr3:uid="{453B0FFC-FD7C-44AA-9A50-64AD33D3319E}" name="seed_c_I_sst" dataDxfId="256">
       <calculatedColumnFormula>LOG(E49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2263A195-7621-4E69-A20A-AD1DCB8039BA}" name="seed_c_I_vip" dataDxfId="258">
+    <tableColumn id="6" xr3:uid="{2263A195-7621-4E69-A20A-AD1DCB8039BA}" name="seed_c_I_vip" dataDxfId="255">
       <calculatedColumnFormula>LOG(F49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5DD607AE-E111-47EF-827E-9F92EE37D88A}" name="seed_c_I_pv" dataDxfId="257">
+    <tableColumn id="7" xr3:uid="{5DD607AE-E111-47EF-827E-9F92EE37D88A}" name="seed_c_I_pv" dataDxfId="254">
       <calculatedColumnFormula>LOG(G49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A1C02190-5F07-4816-9DB5-5A2CB3631EBA}" name="seed_r_0_sst" dataDxfId="256">
+    <tableColumn id="8" xr3:uid="{A1C02190-5F07-4816-9DB5-5A2CB3631EBA}" name="seed_r_0_sst" dataDxfId="253">
       <calculatedColumnFormula>LOG(H49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{81E30CEB-7912-4939-A4D4-2DF9452B08E1}" name="seed_r_0_vip" dataDxfId="255">
+    <tableColumn id="9" xr3:uid="{81E30CEB-7912-4939-A4D4-2DF9452B08E1}" name="seed_r_0_vip" dataDxfId="252">
       <calculatedColumnFormula>LOG(I49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{CEDE804F-029D-4EC6-AF1F-7014BC8A9A11}" name="seed_r_0_pv" dataDxfId="254">
+    <tableColumn id="10" xr3:uid="{CEDE804F-029D-4EC6-AF1F-7014BC8A9A11}" name="seed_r_0_pv" dataDxfId="251">
       <calculatedColumnFormula>LOG(J49,2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7442,54 +8213,54 @@
   <autoFilter ref="L48:V58" xr:uid="{6F7FBBF5-4735-475C-ACA0-5A23C14BF699}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{3F02BD34-270A-4822-956C-2DDCC5712605}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{09E7F0DA-CA50-436D-BDB6-D809D0C3F061}" name="seed_a_e" dataDxfId="253"/>
-    <tableColumn id="3" xr3:uid="{9BDD528B-BC4E-40FD-826B-CDC2F2A66851}" name="seed_b_e" dataDxfId="252"/>
-    <tableColumn id="4" xr3:uid="{CFB644C0-8E98-46D0-A16E-A3B30D7558B4}" name="seed_d_e" dataDxfId="251"/>
-    <tableColumn id="5" xr3:uid="{27BE3A49-7EE0-4BF5-A5EB-DAE368609638}" name="seed_c_I_sst" dataDxfId="250"/>
-    <tableColumn id="6" xr3:uid="{C8DB1166-7992-4A7A-B711-AE1433816777}" name="seed_c_I_vip" dataDxfId="249"/>
-    <tableColumn id="7" xr3:uid="{05B823EE-3D09-41A6-B630-4DA1158655E9}" name="seed_c_I_pv" dataDxfId="248"/>
-    <tableColumn id="8" xr3:uid="{4442F8FB-038E-4A4D-A10D-AEBF4520DEAD}" name="seed_r_0_sst" dataDxfId="247"/>
-    <tableColumn id="9" xr3:uid="{74B2E56A-A200-4799-BC74-E266EEFF9D93}" name="seed_r_0_vip" dataDxfId="246"/>
-    <tableColumn id="10" xr3:uid="{6B158E59-D908-4B50-AB3A-F978257DD29D}" name="seed_r_0_pv" dataDxfId="245"/>
-    <tableColumn id="11" xr3:uid="{DB51154D-A98B-4303-AAD5-5ACAD0949DF1}" name="best_difference_vector_cosine" dataDxfId="244"/>
+    <tableColumn id="2" xr3:uid="{09E7F0DA-CA50-436D-BDB6-D809D0C3F061}" name="seed_a_e" dataDxfId="250"/>
+    <tableColumn id="3" xr3:uid="{9BDD528B-BC4E-40FD-826B-CDC2F2A66851}" name="seed_b_e" dataDxfId="249"/>
+    <tableColumn id="4" xr3:uid="{CFB644C0-8E98-46D0-A16E-A3B30D7558B4}" name="seed_d_e" dataDxfId="248"/>
+    <tableColumn id="5" xr3:uid="{27BE3A49-7EE0-4BF5-A5EB-DAE368609638}" name="seed_c_I_sst" dataDxfId="247"/>
+    <tableColumn id="6" xr3:uid="{C8DB1166-7992-4A7A-B711-AE1433816777}" name="seed_c_I_vip" dataDxfId="246"/>
+    <tableColumn id="7" xr3:uid="{05B823EE-3D09-41A6-B630-4DA1158655E9}" name="seed_c_I_pv" dataDxfId="245"/>
+    <tableColumn id="8" xr3:uid="{4442F8FB-038E-4A4D-A10D-AEBF4520DEAD}" name="seed_r_0_sst" dataDxfId="244"/>
+    <tableColumn id="9" xr3:uid="{74B2E56A-A200-4799-BC74-E266EEFF9D93}" name="seed_r_0_vip" dataDxfId="243"/>
+    <tableColumn id="10" xr3:uid="{6B158E59-D908-4B50-AB3A-F978257DD29D}" name="seed_r_0_pv" dataDxfId="242"/>
+    <tableColumn id="11" xr3:uid="{DB51154D-A98B-4303-AAD5-5ACAD0949DF1}" name="best_difference_vector_cosine" dataDxfId="241"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E28C8B6A-1FB1-4F51-B313-972AE5E332CA}" name="Table814" displayName="Table814" ref="L66:V76" totalsRowShown="0" headerRowDxfId="243" headerRowBorderDxfId="242" tableBorderDxfId="241">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E28C8B6A-1FB1-4F51-B313-972AE5E332CA}" name="Table814" displayName="Table814" ref="L66:V76" totalsRowShown="0" headerRowDxfId="240" headerRowBorderDxfId="239" tableBorderDxfId="238">
   <autoFilter ref="L66:V76" xr:uid="{E28C8B6A-1FB1-4F51-B313-972AE5E332CA}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{015AC9AA-0FB9-4151-943F-AE82B49C07F8}" name="final_evaluation_seed" dataDxfId="240"/>
-    <tableColumn id="2" xr3:uid="{4D0C05EB-6A2A-402F-B9D2-AE471D304861}" name="seed_a_e" dataDxfId="239">
+    <tableColumn id="1" xr3:uid="{015AC9AA-0FB9-4151-943F-AE82B49C07F8}" name="final_evaluation_seed" dataDxfId="237"/>
+    <tableColumn id="2" xr3:uid="{4D0C05EB-6A2A-402F-B9D2-AE471D304861}" name="seed_a_e" dataDxfId="236">
       <calculatedColumnFormula>LOG(M49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F818FC1A-0CB6-49D2-8323-1F1D5C351685}" name="seed_b_e" dataDxfId="238">
+    <tableColumn id="3" xr3:uid="{F818FC1A-0CB6-49D2-8323-1F1D5C351685}" name="seed_b_e" dataDxfId="235">
       <calculatedColumnFormula>LOG(N49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B0B1392D-8E4E-4B92-ADDA-58CB1F8768B7}" name="seed_d_e" dataDxfId="237">
+    <tableColumn id="4" xr3:uid="{B0B1392D-8E4E-4B92-ADDA-58CB1F8768B7}" name="seed_d_e" dataDxfId="234">
       <calculatedColumnFormula>LOG(O49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{18A2346B-DA04-4C32-96E8-691120F0AEE1}" name="seed_c_I_sst" dataDxfId="236">
+    <tableColumn id="5" xr3:uid="{18A2346B-DA04-4C32-96E8-691120F0AEE1}" name="seed_c_I_sst" dataDxfId="233">
       <calculatedColumnFormula>LOG(P49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{827A23AF-D7EF-418C-AE96-E3529E1D74E4}" name="seed_c_I_vip" dataDxfId="235">
+    <tableColumn id="6" xr3:uid="{827A23AF-D7EF-418C-AE96-E3529E1D74E4}" name="seed_c_I_vip" dataDxfId="232">
       <calculatedColumnFormula>LOG(Q49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BB03EA5B-E58C-4978-B947-C4DA9B31F4E8}" name="seed_c_I_pv" dataDxfId="234">
+    <tableColumn id="7" xr3:uid="{BB03EA5B-E58C-4978-B947-C4DA9B31F4E8}" name="seed_c_I_pv" dataDxfId="231">
       <calculatedColumnFormula>LOG(R49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{325C3F8D-426F-49E2-B239-2A986C13BAB3}" name="seed_r_0_sst" dataDxfId="233">
+    <tableColumn id="8" xr3:uid="{325C3F8D-426F-49E2-B239-2A986C13BAB3}" name="seed_r_0_sst" dataDxfId="230">
       <calculatedColumnFormula>LOG(S49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1C9D470D-52B6-46AE-908F-9C78B731AE73}" name="seed_r_0_vip" dataDxfId="232">
+    <tableColumn id="9" xr3:uid="{1C9D470D-52B6-46AE-908F-9C78B731AE73}" name="seed_r_0_vip" dataDxfId="229">
       <calculatedColumnFormula>LOG(T49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{DE930B3E-6CEC-41DC-B7DA-9D377C1E0493}" name="seed_r_0_pv" dataDxfId="231">
+    <tableColumn id="10" xr3:uid="{DE930B3E-6CEC-41DC-B7DA-9D377C1E0493}" name="seed_r_0_pv" dataDxfId="228">
       <calculatedColumnFormula>LOG(U49,2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D022E080-9A73-4747-BE95-197C6EEE0D66}" name="best_difference_vector_cosine" dataDxfId="230"/>
+    <tableColumn id="11" xr3:uid="{D022E080-9A73-4747-BE95-197C6EEE0D66}" name="best_difference_vector_cosine" dataDxfId="227"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7499,9 +8270,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{FCD4B681-E473-42B6-B040-F1403AF7C04D}" name="Table14" displayName="Table14" ref="Y48:AA58" totalsRowShown="0">
   <autoFilter ref="Y48:AA58" xr:uid="{FCD4B681-E473-42B6-B040-F1403AF7C04D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B6D16439-85A8-46E4-881D-A7A8D9208144}" name="Stim" dataDxfId="229"/>
-    <tableColumn id="2" xr3:uid="{83CB5D98-7946-4391-84D7-7BB717F5267A}" name="Auto" dataDxfId="228"/>
-    <tableColumn id="3" xr3:uid="{500C6F3D-55AA-463E-B538-D91D98F88DB6}" name="BOLD" dataDxfId="227"/>
+    <tableColumn id="1" xr3:uid="{B6D16439-85A8-46E4-881D-A7A8D9208144}" name="Stim" dataDxfId="226"/>
+    <tableColumn id="2" xr3:uid="{83CB5D98-7946-4391-84D7-7BB717F5267A}" name="Auto" dataDxfId="225"/>
+    <tableColumn id="3" xr3:uid="{500C6F3D-55AA-463E-B538-D91D98F88DB6}" name="BOLD" dataDxfId="224"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7515,34 +8286,34 @@
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{45778312-C73E-4142-8D98-09B51AD29C97}" name="final_evaluation_seed"/>
-    <tableColumn id="2" xr3:uid="{8543C9FA-310D-4D2C-86DA-D352F099E3F2}" name="seed_a_e" dataDxfId="226"/>
-    <tableColumn id="3" xr3:uid="{A7FD3580-474A-4405-9EAD-B93EA4A32AE6}" name="seed_b_e" dataDxfId="225"/>
-    <tableColumn id="4" xr3:uid="{EA684B5D-99C1-4A32-A3EC-30564128701B}" name="seed_d_e" dataDxfId="224"/>
-    <tableColumn id="5" xr3:uid="{32AD5A85-3748-4639-BC0B-99FFC16F408E}" name="seed_c_I_sst" dataDxfId="223"/>
-    <tableColumn id="6" xr3:uid="{19BA603B-63D9-46B3-90DF-7402BEFDD3A8}" name="seed_c_I_vip" dataDxfId="222"/>
-    <tableColumn id="7" xr3:uid="{33433CFB-03AD-4FC5-88CB-005F669B11B5}" name="seed_c_I_pv" dataDxfId="221"/>
-    <tableColumn id="8" xr3:uid="{862DAC63-1554-4142-A5BA-F391ED3DF0AE}" name="seed_r_0_sst" dataDxfId="220"/>
-    <tableColumn id="9" xr3:uid="{832CB555-1A44-4984-BE42-8B801C12E557}" name="seed_r_0_vip" dataDxfId="219"/>
-    <tableColumn id="10" xr3:uid="{2CBB8CD2-430A-496B-BE9B-986ADFAF0244}" name="seed_r_0_pv" dataDxfId="218"/>
-    <tableColumn id="11" xr3:uid="{E6F34906-FD08-40A7-A514-2C610EBB0315}" name="best_difference_vector_cosine" dataDxfId="217"/>
+    <tableColumn id="2" xr3:uid="{8543C9FA-310D-4D2C-86DA-D352F099E3F2}" name="seed_a_e" dataDxfId="223"/>
+    <tableColumn id="3" xr3:uid="{A7FD3580-474A-4405-9EAD-B93EA4A32AE6}" name="seed_b_e" dataDxfId="222"/>
+    <tableColumn id="4" xr3:uid="{EA684B5D-99C1-4A32-A3EC-30564128701B}" name="seed_d_e" dataDxfId="221"/>
+    <tableColumn id="5" xr3:uid="{32AD5A85-3748-4639-BC0B-99FFC16F408E}" name="seed_c_I_sst" dataDxfId="220"/>
+    <tableColumn id="6" xr3:uid="{19BA603B-63D9-46B3-90DF-7402BEFDD3A8}" name="seed_c_I_vip" dataDxfId="219"/>
+    <tableColumn id="7" xr3:uid="{33433CFB-03AD-4FC5-88CB-005F669B11B5}" name="seed_c_I_pv" dataDxfId="218"/>
+    <tableColumn id="8" xr3:uid="{862DAC63-1554-4142-A5BA-F391ED3DF0AE}" name="seed_r_0_sst" dataDxfId="217"/>
+    <tableColumn id="9" xr3:uid="{832CB555-1A44-4984-BE42-8B801C12E557}" name="seed_r_0_vip" dataDxfId="216"/>
+    <tableColumn id="10" xr3:uid="{2CBB8CD2-430A-496B-BE9B-986ADFAF0244}" name="seed_r_0_pv" dataDxfId="215"/>
+    <tableColumn id="11" xr3:uid="{E6F34906-FD08-40A7-A514-2C610EBB0315}" name="best_difference_vector_cosine" dataDxfId="214"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{47408CFF-1559-4407-86A0-0A65C58408F0}" name="Table6" displayName="Table6" ref="A92:F102" totalsRowShown="0" headerRowDxfId="216" dataDxfId="214" headerRowBorderDxfId="215" tableBorderDxfId="213">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{47408CFF-1559-4407-86A0-0A65C58408F0}" name="Table6" displayName="Table6" ref="A92:F102" totalsRowShown="0" headerRowDxfId="213" dataDxfId="211" headerRowBorderDxfId="212" tableBorderDxfId="210">
   <autoFilter ref="A92:F102" xr:uid="{47408CFF-1559-4407-86A0-0A65C58408F0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A93:F102">
     <sortCondition descending="1" ref="B92:B102"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2A379670-8DD1-40F7-88F4-838C6A0F14A8}" name="final_evaluation_seed" dataDxfId="212"/>
-    <tableColumn id="2" xr3:uid="{94C026B0-B434-4C68-B386-9A2D7873AFB7}" name="best_pearson_r" dataDxfId="211"/>
-    <tableColumn id="3" xr3:uid="{47BF99FD-8002-4CE1-AF82-352FCFBC3B21}" name="best_difference_vector_cosine" dataDxfId="210"/>
-    <tableColumn id="4" xr3:uid="{8584DC60-8470-4406-BC16-AFFFE16FF642}" name="stimulus" dataDxfId="209"/>
-    <tableColumn id="5" xr3:uid="{3F2FA6AF-7F1A-4150-B794-704F2B1ED811}" name="Auto" dataDxfId="208"/>
-    <tableColumn id="6" xr3:uid="{A60217A7-8F2D-4DD0-96DC-08129C1F48E5}" name="BOLD" dataDxfId="207"/>
+    <tableColumn id="1" xr3:uid="{2A379670-8DD1-40F7-88F4-838C6A0F14A8}" name="final_evaluation_seed" dataDxfId="209"/>
+    <tableColumn id="2" xr3:uid="{94C026B0-B434-4C68-B386-9A2D7873AFB7}" name="best_pearson_r" dataDxfId="208"/>
+    <tableColumn id="3" xr3:uid="{47BF99FD-8002-4CE1-AF82-352FCFBC3B21}" name="best_difference_vector_cosine" dataDxfId="207"/>
+    <tableColumn id="4" xr3:uid="{8584DC60-8470-4406-BC16-AFFFE16FF642}" name="stimulus" dataDxfId="206"/>
+    <tableColumn id="5" xr3:uid="{3F2FA6AF-7F1A-4150-B794-704F2B1ED811}" name="Auto" dataDxfId="205"/>
+    <tableColumn id="6" xr3:uid="{A60217A7-8F2D-4DD0-96DC-08129C1F48E5}" name="BOLD" dataDxfId="204"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7867,42 +8638,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237B445F-8D43-4D1E-9470-CD21867C00BD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AI155"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="41.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="23" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="20" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" customWidth="1"/>
-    <col min="24" max="24" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.7109375" customWidth="1"/>
+    <col min="24" max="24" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="18" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -8003,7 +8774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="35">
         <v>12345</v>
       </c>
@@ -8067,7 +8838,7 @@
       <c r="U2" s="46">
         <v>1.5778363102433</v>
       </c>
-      <c r="X2" s="118">
+      <c r="X2" s="116">
         <v>12345</v>
       </c>
       <c r="Y2" s="23">
@@ -8104,7 +8875,7 @@
         <v>1.5778363102433</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>24690</v>
       </c>
@@ -8168,7 +8939,7 @@
       <c r="U3" s="48">
         <v>2.4971317426222299</v>
       </c>
-      <c r="X3" s="119">
+      <c r="X3" s="117">
         <v>24690</v>
       </c>
       <c r="Y3" s="24">
@@ -8205,7 +8976,7 @@
         <v>2.4971317426222299</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>37035</v>
       </c>
@@ -8269,7 +9040,7 @@
       <c r="U4" s="48">
         <v>0.39592331101205303</v>
       </c>
-      <c r="X4" s="118">
+      <c r="X4" s="116">
         <v>37035</v>
       </c>
       <c r="Y4" s="23">
@@ -8306,7 +9077,7 @@
         <v>0.39592331101205303</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>49380</v>
       </c>
@@ -8370,7 +9141,7 @@
       <c r="U5" s="48">
         <v>1.6140854471050099</v>
       </c>
-      <c r="X5" s="119">
+      <c r="X5" s="117">
         <v>49380</v>
       </c>
       <c r="Y5" s="24">
@@ -8407,7 +9178,7 @@
         <v>1.6140854471050099</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>61725</v>
       </c>
@@ -8471,7 +9242,7 @@
       <c r="U6" s="48">
         <v>1.5598435050494699</v>
       </c>
-      <c r="X6" s="118">
+      <c r="X6" s="116">
         <v>61725</v>
       </c>
       <c r="Y6" s="23">
@@ -8508,7 +9279,7 @@
         <v>1.5598435050494699</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>74070</v>
       </c>
@@ -8572,7 +9343,7 @@
       <c r="U7" s="48">
         <v>1.4268128233335999</v>
       </c>
-      <c r="X7" s="119">
+      <c r="X7" s="117">
         <v>74070</v>
       </c>
       <c r="Y7" s="24">
@@ -8609,7 +9380,7 @@
         <v>1.4268128233335999</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>86415</v>
       </c>
@@ -8673,7 +9444,7 @@
       <c r="U8" s="48">
         <v>0.39658030424374302</v>
       </c>
-      <c r="X8" s="118">
+      <c r="X8" s="116">
         <v>86415</v>
       </c>
       <c r="Y8" s="23">
@@ -8710,7 +9481,7 @@
         <v>0.39658030424374302</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>98760</v>
       </c>
@@ -8774,7 +9545,7 @@
       <c r="U9" s="48">
         <v>0.80814293920319002</v>
       </c>
-      <c r="X9" s="119">
+      <c r="X9" s="117">
         <v>98760</v>
       </c>
       <c r="Y9" s="24">
@@ -8811,7 +9582,7 @@
         <v>0.80814293920319002</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>111105</v>
       </c>
@@ -8875,7 +9646,7 @@
       <c r="U10" s="48">
         <v>1.2350472397530501</v>
       </c>
-      <c r="X10" s="118">
+      <c r="X10" s="116">
         <v>111105</v>
       </c>
       <c r="Y10" s="23">
@@ -8912,7 +9683,7 @@
         <v>1.2350472397530501</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>123450</v>
       </c>
@@ -8976,7 +9747,7 @@
       <c r="U11" s="51">
         <v>1.7917193119714701</v>
       </c>
-      <c r="X11" s="119">
+      <c r="X11" s="117">
         <v>123450</v>
       </c>
       <c r="Y11" s="24">
@@ -9013,8 +9784,8 @@
         <v>1.7917193119714701</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -9129,7 +9900,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -9244,7 +10015,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>60</v>
       </c>
@@ -9359,8 +10130,8 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
         <v>32</v>
       </c>
@@ -9484,7 +10255,7 @@
         <v>0.39592331101205303</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
         <v>33</v>
       </c>
@@ -9608,7 +10379,7 @@
         <v>2.4971317426222299</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="40" t="s">
         <v>34</v>
       </c>
@@ -9693,7 +10464,7 @@
         <v>2.1012084316101767</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Y20" t="s">
         <v>133</v>
       </c>
@@ -9737,7 +10508,7 @@
         <v>2.1012084316101767</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30" t="s">
         <v>61</v>
       </c>
@@ -9781,7 +10552,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>18</v>
       </c>
@@ -9885,7 +10656,7 @@
         <v>95.509474164098933</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="52">
         <v>12345</v>
       </c>
@@ -9970,7 +10741,7 @@
         <v>0.56249203146664295</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>24690</v>
       </c>
@@ -10097,7 +10868,7 @@
         <v>1.5171317426222299</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="52">
         <v>37035</v>
       </c>
@@ -10221,7 +10992,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="53">
         <v>49380</v>
       </c>
@@ -10344,7 +11115,7 @@
         <v>99.811298856725656</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="52">
         <v>61725</v>
       </c>
@@ -10429,7 +11200,7 @@
         <v>0.55392895656024632</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="53">
         <v>74070</v>
       </c>
@@ -10556,7 +11327,7 @@
         <v>0.58407668898794696</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="52">
         <v>86415</v>
       </c>
@@ -10680,7 +11451,7 @@
         <v>0.67999999999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="53">
         <v>98760</v>
       </c>
@@ -10804,7 +11575,7 @@
         <v>85.893630733521618</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="52">
         <v>111105</v>
       </c>
@@ -10889,7 +11660,7 @@
         <v>0.39935301806207207</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>123450</v>
       </c>
@@ -11021,8 +11792,8 @@
         <v>-0.25894728122590877</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="55" t="s">
         <v>36</v>
       </c>
@@ -11107,7 +11878,7 @@
         <v>0.44469123975750807</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="56" t="s">
         <v>37</v>
       </c>
@@ -11192,7 +11963,7 @@
         <v>0.29356112226284808</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="57" t="s">
         <v>60</v>
       </c>
@@ -11277,13 +12048,13 @@
         <v>0.66014595300534396</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="30" t="s">
         <v>50</v>
       </c>
@@ -11315,7 +12086,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31" t="s">
         <v>51</v>
       </c>
@@ -11347,8 +12118,8 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:27" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:27" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="30" t="s">
         <v>62</v>
       </c>
@@ -11359,7 +12130,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -11436,7 +12207,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12345</v>
       </c>
@@ -11522,7 +12293,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>24690</v>
       </c>
@@ -11608,7 +12379,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>37035</v>
       </c>
@@ -11694,7 +12465,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>49380</v>
       </c>
@@ -11780,7 +12551,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>61725</v>
       </c>
@@ -11866,7 +12637,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>74070</v>
       </c>
@@ -11952,7 +12723,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>86415</v>
       </c>
@@ -12038,7 +12809,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>98760</v>
       </c>
@@ -12124,7 +12895,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>111105</v>
       </c>
@@ -12210,7 +12981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>123450</v>
       </c>
@@ -12296,8 +13067,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="55" t="s">
         <v>36</v>
       </c>
@@ -12338,7 +13109,7 @@
         <v>1.5488461195205676</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" s="56" t="s">
         <v>37</v>
       </c>
@@ -12379,7 +13150,7 @@
         <v>1.1420367587685476</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="57" t="s">
         <v>60</v>
       </c>
@@ -12420,8 +13191,8 @@
         <v>0.73734681862524576</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="1:22" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:22" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="30" t="s">
         <v>63</v>
       </c>
@@ -12429,7 +13200,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>18</v>
       </c>
@@ -12494,7 +13265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="32">
         <v>12345</v>
       </c>
@@ -12577,7 +13348,7 @@
         <v>0.60391527521822497</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="33">
         <v>24690</v>
       </c>
@@ -12660,7 +13431,7 @@
         <v>0.48624727790761502</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="32">
         <v>37035</v>
       </c>
@@ -12743,7 +13514,7 @@
         <v>0.66176179774459298</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="33">
         <v>49380</v>
       </c>
@@ -12826,7 +13597,7 @@
         <v>0.52520044160502999</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="32">
         <v>61725</v>
       </c>
@@ -12909,7 +13680,7 @@
         <v>0.65013584412540804</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="33">
         <v>74070</v>
       </c>
@@ -12992,7 +13763,7 @@
         <v>0.54313186736951702</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="32">
         <v>86415</v>
       </c>
@@ -13075,7 +13846,7 @@
         <v>0.689942458078181</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="33">
         <v>98760</v>
       </c>
@@ -13158,7 +13929,7 @@
         <v>0.59117161347732095</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="32">
         <v>111105</v>
       </c>
@@ -13241,7 +14012,7 @@
         <v>0.50762810253022606</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="33">
         <v>123450</v>
       </c>
@@ -13324,8 +14095,8 @@
         <v>0.53793669261472898</v>
       </c>
     </row>
-    <row r="77" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="55" t="s">
         <v>36</v>
       </c>
@@ -13366,7 +14137,7 @@
         <v>0.23061347902091037</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="56" t="s">
         <v>37</v>
       </c>
@@ -13407,7 +14178,7 @@
         <v>1.0979835831797293</v>
       </c>
     </row>
-    <row r="80" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="57" t="s">
         <v>60</v>
       </c>
@@ -13448,13 +14219,13 @@
         <v>4.7611422707870954</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="115" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8" t="s">
         <v>18</v>
       </c>
@@ -13474,7 +14245,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="52">
         <v>12345</v>
       </c>
@@ -13500,7 +14271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="53">
         <v>49380</v>
       </c>
@@ -13526,7 +14297,7 @@
         <v>4.2323150644463636</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="53">
         <v>98760</v>
       </c>
@@ -13552,7 +14323,7 @@
         <v>3.3284810109961214</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="53">
         <v>74070</v>
       </c>
@@ -13578,7 +14349,7 @@
         <v>1.0401550241609454</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="52">
         <v>111105</v>
       </c>
@@ -13604,7 +14375,7 @@
         <v>0.98923642634283937</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="52">
         <v>37035</v>
       </c>
@@ -13630,7 +14401,7 @@
         <v>1.2108064443826665</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="52">
         <v>86415</v>
       </c>
@@ -13656,7 +14427,7 @@
         <v>2.3896762324972909</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="53">
         <v>123450</v>
       </c>
@@ -13682,7 +14453,7 @@
         <v>0.92912236506217571</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="52">
         <v>61725</v>
       </c>
@@ -13708,7 +14479,7 @@
         <v>4.1588265843502423</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="53">
         <v>24690</v>
       </c>
@@ -13734,7 +14505,7 @@
         <v>0.57485219838322121</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T103" s="63">
         <v>2.6667941689618107</v>
       </c>
@@ -13742,7 +14513,7 @@
         <v>3.5235494014104844</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T105" s="94" t="s">
         <v>4</v>
       </c>
@@ -13750,7 +14521,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T106" s="97">
         <v>0.56653283755186434</v>
       </c>
@@ -13758,7 +14529,7 @@
         <v>3.9022623769436366</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T107" s="62">
         <v>0.99752166924869701</v>
       </c>
@@ -13766,7 +14537,7 @@
         <v>0.80802691626256673</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E108" s="113"/>
       <c r="F108" s="105"/>
       <c r="G108" s="114"/>
@@ -13780,7 +14551,7 @@
         <v>1.1188254856170972</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -13821,7 +14592,7 @@
         <v>0.95785527468573939</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>86415</v>
       </c>
@@ -13862,7 +14633,7 @@
         <v>3.4442998367507274</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>37035</v>
       </c>
@@ -13903,7 +14674,7 @@
         <v>0.63335878413151825</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>61725</v>
       </c>
@@ -13944,7 +14715,7 @@
         <v>0.82868180848462425</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>12345</v>
       </c>
@@ -13985,7 +14756,7 @@
         <v>2.4041401174379877</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>98760</v>
       </c>
@@ -14026,7 +14797,7 @@
         <v>2.5390543601866122</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>74070</v>
       </c>
@@ -14067,7 +14838,7 @@
         <v>2.314705358795603</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>123450</v>
       </c>
@@ -14102,7 +14873,7 @@
         <v>0.53793669261472898</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>49380</v>
       </c>
@@ -14143,7 +14914,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>111105</v>
       </c>
@@ -14184,7 +14955,7 @@
         <v>4.0071833665052106</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>24690</v>
       </c>
@@ -14225,7 +14996,7 @@
         <v>2.272358817360137</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T120" s="97">
         <v>1.0297531392620909</v>
       </c>
@@ -14233,7 +15004,7 @@
         <v>1.0101821342935104</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T121" s="62">
         <v>0.99776518683000603</v>
       </c>
@@ -14241,7 +15012,7 @@
         <v>1.0072851214242537</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T122" s="97">
         <v>2.2958241789090819</v>
       </c>
@@ -14249,7 +15020,7 @@
         <v>0.52356982480844416</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T123" s="62">
         <v>2.1782135934575275</v>
       </c>
@@ -14257,7 +15028,7 @@
         <v>0.38310460441034316</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T124" s="97">
         <v>0.85293908330560908</v>
       </c>
@@ -14265,7 +15036,7 @@
         <v>1.4229035070601472</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T125" s="62">
         <v>0.59189197949472416</v>
       </c>
@@ -14273,7 +15044,7 @@
         <v>0.44761912533182319</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T126" s="97">
         <v>1.9021837738526788</v>
       </c>
@@ -14281,7 +15052,7 @@
         <v>3.0398230274516944</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="T127" s="62">
         <v>2.4200260825085391</v>
       </c>
@@ -14289,8 +15060,8 @@
         <v>1.3744316665601157</v>
       </c>
     </row>
-    <row r="129" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="130" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="130" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K130" s="108" t="s">
         <v>117</v>
       </c>
@@ -14304,7 +15075,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="131" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I131" s="95" t="s">
         <v>59</v>
       </c>
@@ -14339,7 +15110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="132" spans="8:22" x14ac:dyDescent="0.25">
       <c r="H132" s="113"/>
       <c r="I132" s="111">
         <v>0.60391527521822497</v>
@@ -14387,7 +15158,7 @@
         <v>1.660234270533365</v>
       </c>
     </row>
-    <row r="133" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="133" spans="8:22" x14ac:dyDescent="0.25">
       <c r="I133" s="112">
         <v>0.48624727790761502</v>
       </c>
@@ -14434,7 +15205,7 @@
         <v>4.0044140963703505</v>
       </c>
     </row>
-    <row r="134" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="134" spans="8:22" x14ac:dyDescent="0.25">
       <c r="I134" s="111">
         <v>0.66176179774459298</v>
       </c>
@@ -14481,7 +15252,7 @@
         <v>0.98099446923501998</v>
       </c>
     </row>
-    <row r="135" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="135" spans="8:22" x14ac:dyDescent="0.25">
       <c r="I135" s="112">
         <v>0.52520044160502999</v>
       </c>
@@ -14528,7 +15299,7 @@
         <v>1.0095412575222167</v>
       </c>
     </row>
-    <row r="136" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="136" spans="8:22" x14ac:dyDescent="0.25">
       <c r="I136" s="111">
         <v>0.65013584412540804</v>
       </c>
@@ -14575,7 +15346,7 @@
         <v>0.22805310163482617</v>
       </c>
     </row>
-    <row r="137" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="137" spans="8:22" x14ac:dyDescent="0.25">
       <c r="I137" s="112">
         <v>0.54313186736951702</v>
       </c>
@@ -14622,7 +15393,7 @@
         <v>0.1758801825317014</v>
       </c>
     </row>
-    <row r="138" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="138" spans="8:22" x14ac:dyDescent="0.25">
       <c r="I138" s="111">
         <v>0.689942458078181</v>
       </c>
@@ -14669,7 +15440,7 @@
         <v>1.6682357918757948</v>
       </c>
     </row>
-    <row r="139" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="139" spans="8:22" x14ac:dyDescent="0.25">
       <c r="I139" s="112">
         <v>0.59117161347732095</v>
       </c>
@@ -14716,7 +15487,7 @@
         <v>0.75625137835781919</v>
       </c>
     </row>
-    <row r="140" spans="8:22" x14ac:dyDescent="0.3">
+    <row r="140" spans="8:22" x14ac:dyDescent="0.25">
       <c r="H140" s="113"/>
       <c r="I140" s="111">
         <v>0.50762810253022606</v>
@@ -14764,7 +15535,7 @@
         <v>1.5980701072298833</v>
       </c>
     </row>
-    <row r="141" spans="8:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="8:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I141" s="112">
         <v>0.53793669261472898</v>
       </c>
@@ -14811,8 +15582,8 @@
         <v>0.56794084844549031</v>
       </c>
     </row>
-    <row r="145" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="146" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L146" s="106" t="s">
         <v>108</v>
       </c>
@@ -14829,7 +15600,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L147" s="108" t="s">
         <v>109</v>
       </c>
@@ -14846,7 +15617,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="148" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L148" s="107" t="s">
         <v>110</v>
       </c>
@@ -14854,8 +15625,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="153" spans="11:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="154" spans="11:19" x14ac:dyDescent="0.3">
+    <row r="153" spans="11:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="154" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K154" s="102">
         <v>3.7015741310872814</v>
       </c>
@@ -14884,7 +15655,7 @@
         <v>4.0071833665052106</v>
       </c>
     </row>
-    <row r="155" spans="11:19" x14ac:dyDescent="0.3">
+    <row r="155" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K155" s="100">
         <v>0.8150807597453037</v>
       </c>
@@ -14916,134 +15687,134 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B110:J119">
-    <cfRule type="cellIs" dxfId="43" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D93:F102">
-    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K132:O141">
-    <cfRule type="cellIs" dxfId="38" priority="52" operator="between">
+    <cfRule type="cellIs" dxfId="36" priority="52" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="53" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="53" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="54" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K154:S155">
-    <cfRule type="cellIs" dxfId="35" priority="10" operator="between">
+    <cfRule type="cellIs" dxfId="33" priority="10" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="11" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="12" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49:U58">
-    <cfRule type="cellIs" dxfId="32" priority="93" operator="between">
+    <cfRule type="cellIs" dxfId="30" priority="93" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="96" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="96" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="97" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="97" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67:U76">
-    <cfRule type="cellIs" dxfId="29" priority="94" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="94" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="95" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="95" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q132:R141">
-    <cfRule type="cellIs" dxfId="27" priority="61" operator="between">
+    <cfRule type="cellIs" dxfId="25" priority="61" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="62" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T94:U103">
-    <cfRule type="cellIs" dxfId="24" priority="79" operator="between">
+    <cfRule type="cellIs" dxfId="22" priority="79" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="80" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="80" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="81" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="81" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T106:U115">
-    <cfRule type="cellIs" dxfId="21" priority="76" operator="between">
+    <cfRule type="cellIs" dxfId="19" priority="76" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="77" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="77" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="78" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="78" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T118:U127">
-    <cfRule type="cellIs" dxfId="18" priority="73" operator="between">
+    <cfRule type="cellIs" dxfId="16" priority="73" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="74" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="74" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="75" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="75" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T132:U141">
-    <cfRule type="cellIs" dxfId="15" priority="55" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="55" operator="between">
       <formula>0.975</formula>
       <formula>1.025</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="56" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="56" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="57" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="57" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y49:AA58">
-    <cfRule type="cellIs" dxfId="12" priority="91" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="91" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="92" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15065,22 +15836,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B9B394B-2F94-478A-9EA6-A5E96B91D71F}">
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="17.109375" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -15114,17 +15892,20 @@
       <c r="K1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="117" t="s">
-        <v>67</v>
+      <c r="L1" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="N1" s="114" t="s">
+        <v>150</v>
+      </c>
+      <c r="S1" s="105" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>12345</v>
       </c>
@@ -15158,15 +15939,35 @@
       <c r="K2" s="85">
         <v>1.5778363102433</v>
       </c>
-      <c r="L2" s="116" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="116" t="s">
-        <v>70</v>
-      </c>
-      <c r="N2" s="116"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L2" s="93">
+        <v>0.60391527521822497</v>
+      </c>
+      <c r="M2" s="118">
+        <v>0.712406808509643</v>
+      </c>
+      <c r="N2" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="O2" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="P2" s="114" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2" s="114" t="s">
+        <v>163</v>
+      </c>
+      <c r="S2" s="105" t="s">
+        <v>151</v>
+      </c>
+      <c r="T2" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>24690</v>
       </c>
@@ -15200,13 +16001,35 @@
       <c r="K3" s="87">
         <v>2.4971317426222299</v>
       </c>
-      <c r="L3" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L3" s="24">
+        <v>0.48624727790761502</v>
+      </c>
+      <c r="M3" s="24">
+        <v>0.48840316014479601</v>
+      </c>
+      <c r="N3" s="114" t="s">
+        <v>139</v>
+      </c>
+      <c r="O3" s="114" t="s">
+        <v>143</v>
+      </c>
+      <c r="P3" s="114" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3" s="114" t="s">
+        <v>164</v>
+      </c>
+      <c r="S3" s="105" t="s">
+        <v>151</v>
+      </c>
+      <c r="T3" s="105" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>37035</v>
       </c>
@@ -15240,13 +16063,35 @@
       <c r="K4" s="89">
         <v>0.39592331101205303</v>
       </c>
-      <c r="L4" s="116" t="s">
-        <v>70</v>
-      </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L4" s="24">
+        <v>0.66176179774459298</v>
+      </c>
+      <c r="M4" s="23">
+        <v>0.59089730657681105</v>
+      </c>
+      <c r="N4" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="O4" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="P4" s="114" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4" s="114" t="s">
+        <v>165</v>
+      </c>
+      <c r="S4" s="105" t="s">
+        <v>154</v>
+      </c>
+      <c r="T4" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>49380</v>
       </c>
@@ -15280,11 +16125,35 @@
       <c r="K5" s="87">
         <v>1.6140854471050099</v>
       </c>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L5" s="24">
+        <v>0.52520044160502999</v>
+      </c>
+      <c r="M5" s="24">
+        <v>0.67887988874580396</v>
+      </c>
+      <c r="N5" s="114" t="s">
+        <v>145</v>
+      </c>
+      <c r="O5" s="114" t="s">
+        <v>143</v>
+      </c>
+      <c r="P5" s="114" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5" s="114" t="s">
+        <v>166</v>
+      </c>
+      <c r="S5" s="105" t="s">
+        <v>155</v>
+      </c>
+      <c r="T5" s="105" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>61725</v>
       </c>
@@ -15318,11 +16187,35 @@
       <c r="K6" s="89">
         <v>1.5598435050494699</v>
       </c>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="116"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L6" s="24">
+        <v>0.65013584412540804</v>
+      </c>
+      <c r="M6" s="23">
+        <v>0.51157923348573597</v>
+      </c>
+      <c r="N6" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="O6" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="P6" s="114" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q6">
+        <v>5</v>
+      </c>
+      <c r="R6" s="114" t="s">
+        <v>117</v>
+      </c>
+      <c r="S6" s="105" t="s">
+        <v>157</v>
+      </c>
+      <c r="T6" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>74070</v>
       </c>
@@ -15356,11 +16249,35 @@
       <c r="K7" s="87">
         <v>1.4268128233335999</v>
       </c>
-      <c r="L7" s="54"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="54"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L7" s="24">
+        <v>0.54313186736951702</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0.61136346201208103</v>
+      </c>
+      <c r="N7" s="114" t="s">
+        <v>146</v>
+      </c>
+      <c r="O7" s="114" t="s">
+        <v>146</v>
+      </c>
+      <c r="P7" s="114" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q7">
+        <v>6</v>
+      </c>
+      <c r="R7" s="114" t="s">
+        <v>167</v>
+      </c>
+      <c r="S7" s="105" t="s">
+        <v>158</v>
+      </c>
+      <c r="T7" s="105" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>86415</v>
       </c>
@@ -15394,11 +16311,35 @@
       <c r="K8" s="89">
         <v>0.39658030424374302</v>
       </c>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L8" s="24">
+        <v>0.689942458078181</v>
+      </c>
+      <c r="M8" s="23">
+        <v>0.55681124125554704</v>
+      </c>
+      <c r="N8" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="O8" s="114" t="s">
+        <v>147</v>
+      </c>
+      <c r="P8" s="114" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q8">
+        <v>7</v>
+      </c>
+      <c r="R8" s="114" t="s">
+        <v>168</v>
+      </c>
+      <c r="S8" s="105" t="s">
+        <v>157</v>
+      </c>
+      <c r="T8" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>98760</v>
       </c>
@@ -15432,11 +16373,35 @@
       <c r="K9" s="87">
         <v>0.80814293920319002</v>
       </c>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L9" s="24">
+        <v>0.59117161347732095</v>
+      </c>
+      <c r="M9" s="24">
+        <v>0.65351070789674404</v>
+      </c>
+      <c r="N9" s="114" t="s">
+        <v>148</v>
+      </c>
+      <c r="O9" s="114" t="s">
+        <v>149</v>
+      </c>
+      <c r="P9" s="114" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q9">
+        <v>8</v>
+      </c>
+      <c r="R9" s="114" t="s">
+        <v>169</v>
+      </c>
+      <c r="S9" s="105" t="s">
+        <v>157</v>
+      </c>
+      <c r="T9" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>111105</v>
       </c>
@@ -15470,11 +16435,35 @@
       <c r="K10" s="89">
         <v>1.2350472397530501</v>
       </c>
-      <c r="L10" s="116"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="116"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="24">
+        <v>0.50762810253022606</v>
+      </c>
+      <c r="M10" s="23">
+        <v>0.60026349158933801</v>
+      </c>
+      <c r="N10" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="114" t="s">
+        <v>147</v>
+      </c>
+      <c r="P10" s="114" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q10">
+        <v>9</v>
+      </c>
+      <c r="R10" s="114" t="s">
+        <v>170</v>
+      </c>
+      <c r="S10" s="105" t="s">
+        <v>160</v>
+      </c>
+      <c r="T10" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>123450</v>
       </c>
@@ -15508,22 +16497,39 @@
       <c r="K11" s="92">
         <v>1.7917193119714701</v>
       </c>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
+      <c r="L11" s="26">
+        <v>0.53793669261472898</v>
+      </c>
+      <c r="M11" s="26">
+        <v>0.52796028692755004</v>
+      </c>
+      <c r="N11" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" s="114" t="s">
+        <v>147</v>
+      </c>
+      <c r="P11" s="114" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="114" t="s">
+        <v>171</v>
+      </c>
+      <c r="S11" s="105" t="s">
+        <v>161</v>
+      </c>
+      <c r="T11" s="105" t="s">
+        <v>152</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:N11">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
-      <formula>"Pass"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15531,20 +16537,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FCF11C-DDE7-4784-B0AC-FF45FB494109}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.109375" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>107</v>
       </c>
@@ -15591,7 +16597,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="52">
         <v>12345</v>
       </c>
@@ -15638,7 +16644,7 @@
         <v>0.60391527521822497</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="53">
         <v>24690</v>
       </c>
@@ -15685,7 +16691,7 @@
         <v>0.48624727790761502</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="52">
         <v>37035</v>
       </c>
@@ -15732,7 +16738,7 @@
         <v>0.66176179774459298</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="53">
         <v>49380</v>
       </c>
@@ -15779,7 +16785,7 @@
         <v>0.52520044160502999</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="52">
         <v>61725</v>
       </c>
@@ -15826,7 +16832,7 @@
         <v>0.65013584412540804</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="53">
         <v>74070</v>
       </c>
@@ -15873,7 +16879,7 @@
         <v>0.54313186736951702</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="52">
         <v>86415</v>
       </c>
@@ -15920,7 +16926,7 @@
         <v>0.689942458078181</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="53">
         <v>98760</v>
       </c>
@@ -15967,7 +16973,7 @@
         <v>0.59117161347732095</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="52">
         <v>111105</v>
       </c>
@@ -16014,7 +17020,7 @@
         <v>0.50762810253022606</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53">
         <v>123450</v>
       </c>
@@ -16073,15 +17079,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74838A9-EA36-440F-BC03-31688569CF0D}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>72</v>
       </c>
@@ -16095,7 +17101,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -16109,7 +17115,7 @@
         <v>-0.45965949888373803</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -16123,7 +17129,7 @@
         <v>0.19376473419892001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -16137,7 +17143,7 @@
         <v>-0.28405184904618402</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -16151,7 +17157,7 @@
         <v>7.2200220231434506E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -16165,7 +17171,7 @@
         <v>-9.6022789968516306E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -16179,7 +17185,7 @@
         <v>-0.47201309660431301</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -16193,7 +17199,7 @@
         <v>-0.13640339554943001</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -16207,7 +17213,7 @@
         <v>6.3205573209875798E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -16221,7 +17227,7 @@
         <v>5.8121653149551603E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -16235,7 +17241,7 @@
         <v>0.44130801936368202</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -16249,7 +17255,7 @@
         <v>0.23885655891296401</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5</v>
       </c>
@@ -16263,7 +17269,7 @@
         <v>-2.2231198244722101E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2</v>
       </c>
@@ -16277,7 +17283,7 @@
         <v>1.49421743525793E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -16291,7 +17297,7 @@
         <v>-2.5767946213576299E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -16305,7 +17311,7 @@
         <v>-0.208721184212809</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -16319,7 +17325,7 @@
         <v>0.14536670100049301</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -16333,7 +17339,7 @@
         <v>-2.0865512606801799E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>10</v>
       </c>
@@ -16347,7 +17353,7 @@
         <v>0.96646564267355795</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>88</v>
       </c>
@@ -16361,7 +17367,7 @@
         <v>-5.090744290343E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -16375,7 +17381,7 @@
         <v>-3.3134686314884303E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -16389,7 +17395,7 @@
         <v>0.77286824351740502</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>91</v>
       </c>
@@ -16403,7 +17409,7 @@
         <v>0.11083096187591999</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -16417,7 +17423,7 @@
         <v>-0.35513067931786702</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -16431,7 +17437,7 @@
         <v>0.41934943267650499</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -16445,7 +17451,7 @@
         <v>0.27430664460676102</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>95</v>
       </c>
@@ -16459,7 +17465,7 @@
         <v>-0.232398016499614</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -16473,7 +17479,7 @@
         <v>0.46601541381699302</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>96</v>
       </c>
@@ -16487,7 +17493,7 @@
         <v>0.121100210187723</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>32</v>
       </c>
@@ -16501,7 +17507,7 @@
         <v>1.1877979999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -16515,7 +17521,7 @@
         <v>-0.24863147470347399</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9</v>
       </c>
@@ -16529,7 +17535,7 @@
         <v>0.76242033842198298</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>98</v>
       </c>
@@ -16543,7 +17549,7 @@
         <v>0.276280659692554</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -16557,7 +17563,7 @@
         <v>0.80364542202849298</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>100</v>
       </c>
@@ -16571,7 +17577,7 @@
         <v>-0.53736354954134202</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -16585,7 +17591,7 @@
         <v>-0.29963637906952301</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>102</v>
       </c>
@@ -16599,7 +17605,7 @@
         <v>0.94816817278999399</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>103</v>
       </c>
@@ -16613,7 +17619,7 @@
         <v>8.5007066231793701E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>104</v>
       </c>
@@ -16627,7 +17633,7 @@
         <v>0.17337086753551201</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>105</v>
       </c>
@@ -16641,7 +17647,7 @@
         <v>0.91885899999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>106</v>
       </c>
@@ -16666,20 +17672,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D838E4-5041-4172-BF4F-6C64A37B593C}">
   <dimension ref="C4:V31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.109375" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="8" t="s">
         <v>18</v>
       </c>
@@ -16732,7 +17738,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C5" s="52">
         <v>12345</v>
       </c>
@@ -16788,7 +17794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C6" s="53">
         <v>24690</v>
       </c>
@@ -16844,7 +17850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C7" s="52">
         <v>37035</v>
       </c>
@@ -16900,7 +17906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C8" s="53">
         <v>49380</v>
       </c>
@@ -16956,7 +17962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C9" s="52">
         <v>61725</v>
       </c>
@@ -17012,7 +18018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C10" s="53">
         <v>74070</v>
       </c>
@@ -17068,7 +18074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C11" s="52">
         <v>86415</v>
       </c>
@@ -17124,7 +18130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C12" s="53">
         <v>98760</v>
       </c>
@@ -17180,7 +18186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C13" s="52">
         <v>111105</v>
       </c>
@@ -17236,7 +18242,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="53">
         <v>123450</v>
       </c>
@@ -17292,8 +18298,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
         <v>36</v>
       </c>
@@ -17362,7 +18368,7 @@
         <v>8.69439801662652E-2</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
@@ -17407,7 +18413,7 @@
         <v>0.61683310529164304</v>
       </c>
     </row>
-    <row r="19" spans="3:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="4" t="s">
         <v>60</v>
       </c>
@@ -17452,7 +18458,7 @@
         <v>0.46367541540959673</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
       <c r="P21">
         <f>Q17^2</f>
         <v>0.20416068933626805</v>
@@ -17467,7 +18473,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T22" s="54" t="s">
         <v>70</v>
       </c>
@@ -17478,7 +18484,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T23" s="54" t="s">
         <v>71</v>
       </c>
@@ -17489,7 +18495,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T24" s="54" t="s">
         <v>70</v>
       </c>
@@ -17500,7 +18506,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T25" s="54" t="s">
         <v>71</v>
       </c>
@@ -17511,7 +18517,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T26" s="54" t="s">
         <v>70</v>
       </c>
@@ -17522,7 +18528,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T27" s="54" t="s">
         <v>71</v>
       </c>
@@ -17533,7 +18539,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T28" s="54" t="s">
         <v>70</v>
       </c>
@@ -17544,7 +18550,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T29" s="54" t="s">
         <v>70</v>
       </c>
@@ -17555,7 +18561,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T30" s="54" t="s">
         <v>70</v>
       </c>
@@ -17566,7 +18572,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:22" x14ac:dyDescent="0.25">
       <c r="T31" s="54" t="s">
         <v>70</v>
       </c>
@@ -17598,34 +18604,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E8849C-2D02-46F4-ACC4-400EB6662519}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Y87"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="8" width="25.5546875" customWidth="1"/>
-    <col min="9" max="10" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" customWidth="1"/>
-    <col min="13" max="13" width="21.109375" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
-    <col min="15" max="15" width="20.44140625" customWidth="1"/>
-    <col min="16" max="16" width="10.88671875" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" customWidth="1"/>
     <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="17.109375" customWidth="1"/>
-    <col min="21" max="21" width="13.6640625" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" customWidth="1"/>
+    <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" customWidth="1"/>
     <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="25" max="25" width="27.88671875" customWidth="1"/>
+    <col min="25" max="25" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -17690,7 +18696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -17755,7 +18761,7 @@
         <v>1.5778363102433</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -17823,7 +18829,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -17892,7 +18898,7 @@
         <v>0.15529912764928527</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -17957,7 +18963,7 @@
         <v>1.6140854471050099</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -18022,7 +19028,7 @@
         <v>1.5598435050494699</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -18087,7 +19093,7 @@
         <v>1.4268128233335999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -18152,7 +19158,7 @@
         <v>0.39658030424374302</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -18217,7 +19223,7 @@
         <v>0.80814293920319002</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -18282,7 +19288,7 @@
         <v>1.2350472397530501</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -18347,8 +19353,8 @@
         <v>1.7917193119714701</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -18433,7 +19439,7 @@
         <v>1.3303122934537115</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
@@ -18518,7 +19524,7 @@
         <v>0.61683310529164304</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
@@ -18603,8 +19609,8 @@
         <v>0.4227589775374791</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>32</v>
       </c>
@@ -18689,7 +19695,7 @@
         <v>0.39592331101205303</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>33</v>
       </c>
@@ -18774,7 +19780,7 @@
         <v>2.4971317426222299</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>34</v>
       </c>
@@ -18859,13 +19865,13 @@
         <v>2.1012084316101767</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>18</v>
       </c>
@@ -18930,7 +19936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -19015,7 +20021,7 @@
         <v>0.56249203146664295</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
@@ -19100,7 +20106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -19185,7 +20191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
@@ -19270,7 +20276,7 @@
         <v>0.5797435979064044</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -19355,7 +20361,7 @@
         <v>0.55392895656024632</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
@@ -19440,7 +20446,7 @@
         <v>0.49061744509161626</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -19525,7 +20531,7 @@
         <v>3.1267399359640623E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
@@ -19610,7 +20616,7 @@
         <v>0.19618216926497342</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -19695,7 +20701,7 @@
         <v>0.39935301806207207</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
@@ -19780,8 +20786,8 @@
         <v>0.6642825052295287</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>36</v>
       </c>
@@ -19866,7 +20872,7 @@
         <v>0.44469123975750807</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
@@ -19951,7 +20957,7 @@
         <v>0.29356112226284808</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>38</v>
       </c>
@@ -20036,13 +21042,13 @@
         <v>9.57534805602476E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="30" t="s">
         <v>50</v>
       </c>
@@ -20074,7 +21080,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="31" t="s">
         <v>51</v>
       </c>
@@ -20106,8 +21112,8 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="49" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>57</v>
       </c>
@@ -20115,7 +21121,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>31</v>
       </c>
@@ -20189,7 +21195,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>21</v>
       </c>
@@ -20281,7 +21287,7 @@
         <v>0.52304667728695398</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>22</v>
       </c>
@@ -20373,7 +21379,7 @@
         <v>0.495336580378823</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>23</v>
       </c>
@@ -20465,7 +21471,7 @@
         <v>0.58339645238371796</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>24</v>
       </c>
@@ -20557,7 +21563,7 @@
         <v>0.39443555162616101</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>25</v>
       </c>
@@ -20649,7 +21655,7 @@
         <v>0.59310751110297899</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>26</v>
       </c>
@@ -20741,7 +21747,7 @@
         <v>0.46257299662969398</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>27</v>
       </c>
@@ -20833,7 +21839,7 @@
         <v>0.35074167737220402</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>28</v>
       </c>
@@ -20925,7 +21931,7 @@
         <v>0.67467449249167699</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>29</v>
       </c>
@@ -21017,7 +22023,7 @@
         <v>0.52135653128783699</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>30</v>
       </c>
@@ -21109,8 +22115,8 @@
         <v>0.36092217938737903</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
         <v>57</v>
       </c>
@@ -21118,7 +22124,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>18</v>
       </c>
@@ -21192,7 +22198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>21</v>
       </c>
@@ -21284,7 +22290,7 @@
         <v>0.52304667728695398</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>22</v>
       </c>
@@ -21376,7 +22382,7 @@
         <v>0.495336580378823</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>23</v>
       </c>
@@ -21468,7 +22474,7 @@
         <v>0.58339645238371796</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>24</v>
       </c>
@@ -21560,7 +22566,7 @@
         <v>0.39443555162616101</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>25</v>
       </c>
@@ -21652,7 +22658,7 @@
         <v>0.59310751110297899</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>26</v>
       </c>
@@ -21744,7 +22750,7 @@
         <v>0.46257299662969398</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>27</v>
       </c>
@@ -21836,7 +22842,7 @@
         <v>0.35074167737220402</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>28</v>
       </c>
@@ -21928,7 +22934,7 @@
         <v>0.67467449249167699</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>29</v>
       </c>
@@ -22020,7 +23026,7 @@
         <v>0.52135653128783699</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>30</v>
       </c>
@@ -22112,8 +23118,8 @@
         <v>0.36092217938737903</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
         <v>53</v>
       </c>
@@ -22121,7 +23127,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>18</v>
       </c>
@@ -22147,7 +23153,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>21</v>
       </c>
@@ -22173,7 +23179,7 @@
         <v>0.78110128743181817</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>22</v>
       </c>
@@ -22199,7 +23205,7 @@
         <v>0.48389597470080942</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>23</v>
       </c>
@@ -22225,7 +23231,7 @@
         <v>0.68951104757363746</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>24</v>
       </c>
@@ -22251,7 +23257,7 @@
         <v>0.61645730773014906</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>25</v>
       </c>
@@ -22277,7 +23283,7 @@
         <v>0.61348983186062345</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>26</v>
       </c>
@@ -22303,7 +23309,7 @@
         <v>0.58773905989437214</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>27</v>
       </c>
@@ -22329,7 +23335,7 @@
         <v>0.43305848263441027</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>28</v>
       </c>
@@ -22355,7 +23361,7 @@
         <v>0.88226191615460547</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>29</v>
       </c>
@@ -22381,7 +23387,7 @@
         <v>0.63212889205150868</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="25" t="s">
         <v>30</v>
       </c>
